--- a/data/ENI.MI.xlsx
+++ b/data/ENI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2257" uniqueCount="2257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2258" uniqueCount="2258">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,37 +38,37 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26820516586304</t>
+    <t xml:space="preserve">7.26820802688599</t>
   </si>
   <si>
     <t xml:space="preserve">ENI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3331503868103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12749528884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07337760925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87313556671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84607696533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86231422424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94349098205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04090785980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79195833206177</t>
+    <t xml:space="preserve">7.33314943313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12749814987183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07337856292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87313652038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84607839584351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86231374740601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94349241256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04090642929077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79195785522461</t>
   </si>
   <si>
     <t xml:space="preserve">6.71619129180908</t>
@@ -77,328 +77,328 @@
     <t xml:space="preserve">6.80819416046143</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58089351654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01925897598267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93266820907593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07879066467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11126232147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18702840805054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77031087875366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74325180053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89478445053101</t>
+    <t xml:space="preserve">6.58089303970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01926040649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9326696395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07879114151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11126279830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1870288848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77031135559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74325227737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89478588104248</t>
   </si>
   <si>
     <t xml:space="preserve">6.78113508224487</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53759717941284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27782583236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29406309127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91522693634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31029748916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46183347702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41312551498413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61877679824829</t>
+    <t xml:space="preserve">6.53759813308716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27782726287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29406070709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91522836685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31029653549194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46183061599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41312265396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61877727508545</t>
   </si>
   <si>
     <t xml:space="preserve">6.47806692123413</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45100784301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68371915817261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37524271011353</t>
+    <t xml:space="preserve">6.45100831985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68372106552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37523937225342</t>
   </si>
   <si>
     <t xml:space="preserve">6.54301023483276</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87854814529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00843334197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22491359710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27903175354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37644577026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3277382850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35479640960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17079401016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25197076797485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00302314758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20867538452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24656105041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14373254776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23573684692383</t>
+    <t xml:space="preserve">6.87854957580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00843477249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22491312026978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27903079986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37644624710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32773876190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35479688644409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17079210281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25197315216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00302171707153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2086763381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24655961990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14373445510864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23573589324951</t>
   </si>
   <si>
     <t xml:space="preserve">7.36562156677246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43056535720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46844911575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28985452651978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11667346954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31691551208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19785308837891</t>
+    <t xml:space="preserve">7.43056440353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46845006942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28985595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1166729927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31691455841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19785213470459</t>
   </si>
   <si>
     <t xml:space="preserve">6.92184400558472</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90560817718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73242664337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8027811050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66748571395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95431613922119</t>
+    <t xml:space="preserve">6.90560674667358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7324275970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80278205871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66748332977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95431661605835</t>
   </si>
   <si>
     <t xml:space="preserve">6.97596311569214</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01384878158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2952675819397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42515277862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30609226226807</t>
+    <t xml:space="preserve">7.01384687423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29526805877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42515182495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30609083175659</t>
   </si>
   <si>
     <t xml:space="preserve">7.39809274673462</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51715612411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61456918716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65786552429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61998176574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65245342254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72280788421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79316234588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68492603302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54962730407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39268112182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24114799499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34397554397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4089150428772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13832092285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22407817840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44721603393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7038254737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74287509918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71498203277588</t>
+    <t xml:space="preserve">7.51715517044067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61457109451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65786504745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6199803352356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65245389938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72280883789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79316282272339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68492555618286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54962825775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39268398284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24114608764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34397459030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40891695022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1383204460144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22407674789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44721698760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70382595062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74287462234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71498346328735</t>
   </si>
   <si>
     <t xml:space="preserve">7.77634382247925</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65919780731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55320692062378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54763031005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48626613616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68151044845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86002206802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8823356628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84328746795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50300121307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36353874206543</t>
+    <t xml:space="preserve">7.65919876098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55320739746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54762935638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48626708984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68151187896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86002254486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88233518600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84328651428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50299978256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36354064941406</t>
   </si>
   <si>
     <t xml:space="preserve">7.45837259292603</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38027620315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67035627365112</t>
+    <t xml:space="preserve">7.38027477264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67035675048828</t>
   </si>
   <si>
     <t xml:space="preserve">7.89907026290894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99948167800903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8767557144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13336563110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38585329055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62014865875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97716903686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09989356994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26724910736084</t>
+    <t xml:space="preserve">7.99948263168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87675523757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1333646774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38585376739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62015008926392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97716951370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09989452362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26724720001221</t>
   </si>
   <si>
     <t xml:space="preserve">8.03853130340576</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88791275024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93253993988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08873748779297</t>
+    <t xml:space="preserve">7.8879132270813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93254041671753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08873653411865</t>
   </si>
   <si>
     <t xml:space="preserve">8.18356990814209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26166820526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16125679016113</t>
+    <t xml:space="preserve">8.26166915893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16125869750977</t>
   </si>
   <si>
     <t xml:space="preserve">8.31187534332275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21146392822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12220859527588</t>
+    <t xml:space="preserve">8.21146297454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1222095489502</t>
   </si>
   <si>
     <t xml:space="preserve">8.09431457519531</t>
@@ -407,13 +407,13 @@
     <t xml:space="preserve">8.01621723175049</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97158908843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93811798095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82655000686646</t>
+    <t xml:space="preserve">7.9715895652771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93811845779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82655143737793</t>
   </si>
   <si>
     <t xml:space="preserve">7.83212900161743</t>
@@ -422,283 +422,283 @@
     <t xml:space="preserve">7.6257266998291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63130569458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48068952560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32449054718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37469863891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39143323898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56994247436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55878639221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53647089004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64246129989624</t>
+    <t xml:space="preserve">7.63130521774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48068618774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32449150085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37469673156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39143228530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56994342803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55878496170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53647136688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64246082305908</t>
   </si>
   <si>
     <t xml:space="preserve">7.66477632522583</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51415777206421</t>
+    <t xml:space="preserve">7.51415920257568</t>
   </si>
   <si>
     <t xml:space="preserve">7.4974217414856</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59783267974854</t>
+    <t xml:space="preserve">7.59783506393433</t>
   </si>
   <si>
     <t xml:space="preserve">7.59225511550903</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65362024307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56436443328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31333351135254</t>
+    <t xml:space="preserve">7.65361881256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56436347961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31333446502686</t>
   </si>
   <si>
     <t xml:space="preserve">7.33564710617065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36911916732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20176410675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31114387512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17873764038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20176553726196</t>
+    <t xml:space="preserve">7.36911630630493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20176362991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31114482879639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17873811721802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20176649093628</t>
   </si>
   <si>
     <t xml:space="preserve">7.2823600769043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25357627868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12117052078247</t>
+    <t xml:space="preserve">7.25357580184937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12117147445679</t>
   </si>
   <si>
     <t xml:space="preserve">7.08662986755371</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10965585708618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43779373168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38022613525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42052412033081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4665789604187</t>
+    <t xml:space="preserve">7.10965728759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43779468536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38022756576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42052316665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46658039093018</t>
   </si>
   <si>
     <t xml:space="preserve">7.63928174972534</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65079641342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82925796508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6795825958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62777042388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57595682144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72563505172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66230964660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80047416687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82349967956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90409564971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92712259292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87531185150146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79471683502197</t>
+    <t xml:space="preserve">7.65079784393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82925891876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6795802116394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62776899337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57595729827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72563743591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66231060028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80047225952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8235011100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90409708023071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92712306976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87531232833862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79471635818481</t>
   </si>
   <si>
     <t xml:space="preserve">7.91561031341553</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7774453163147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60474300384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48385047912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37447071075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31690120697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24782085418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35144281387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39749765396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36871242523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.339928150177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22479248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0578465461731</t>
+    <t xml:space="preserve">7.77744770050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60474109649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4838490486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37446975708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31689977645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2478199005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35143995285034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39749670028687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36871337890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33992671966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22479152679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05784559249878</t>
   </si>
   <si>
     <t xml:space="preserve">7.19600772857666</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14995574951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12692737579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23630475997925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24206113815308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28811693191528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56444406509399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8350133895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8810658454895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03650283813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11709690093994</t>
+    <t xml:space="preserve">7.14995336532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1269268989563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23630666732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24206161499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28811740875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56444358825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83501529693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88106966018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03650188446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11709880828857</t>
   </si>
   <si>
     <t xml:space="preserve">8.19193649291992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20345115661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50855922698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59491443634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56612968444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61793899536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6639928817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61218357086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72156143188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73307609558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83094215393066</t>
+    <t xml:space="preserve">8.20345020294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50856113433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5949125289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56612777709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61794090270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66399383544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61218452453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72156238555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73307514190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83094120025635</t>
   </si>
   <si>
     <t xml:space="preserve">8.81367206573486</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88850975036621</t>
+    <t xml:space="preserve">8.88850879669189</t>
   </si>
   <si>
     <t xml:space="preserve">8.90578079223633</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00364780426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99789142608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03243064880371</t>
+    <t xml:space="preserve">9.00364589691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99788856506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03243160247803</t>
   </si>
   <si>
     <t xml:space="preserve">9.0496997833252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85972690582275</t>
+    <t xml:space="preserve">8.85972595214844</t>
   </si>
   <si>
     <t xml:space="preserve">8.9518346786499</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94607543945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90002250671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02091503143311</t>
+    <t xml:space="preserve">8.94607830047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90002536773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02091789245605</t>
   </si>
   <si>
     <t xml:space="preserve">8.86548328399658</t>
@@ -707,73 +707,73 @@
     <t xml:space="preserve">8.96334743499756</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92880916595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83670043945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60642719268799</t>
+    <t xml:space="preserve">8.92880725860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83669853210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60642528533936</t>
   </si>
   <si>
     <t xml:space="preserve">8.50280380249023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28404426574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18042182922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13436698913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15163803100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36463928222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17466640472412</t>
+    <t xml:space="preserve">8.2840461730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18042278289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13436889648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15163993835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36464023590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17466831207275</t>
   </si>
   <si>
     <t xml:space="preserve">8.14012432098389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26677513122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2898006439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37039756774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27828788757324</t>
+    <t xml:space="preserve">8.26677417755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28980159759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37039661407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27828979492188</t>
   </si>
   <si>
     <t xml:space="preserve">8.12861156463623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39342594146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29555702209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2322359085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35888195037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63521003723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64096927642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79064464569092</t>
+    <t xml:space="preserve">8.39342308044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29555892944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23223495483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35888290405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63521289825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64096832275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7906436920166</t>
   </si>
   <si>
     <t xml:space="preserve">8.68702220916748</t>
@@ -782,13 +782,13 @@
     <t xml:space="preserve">8.52007484436035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46250820159912</t>
+    <t xml:space="preserve">8.46250534057617</t>
   </si>
   <si>
     <t xml:space="preserve">8.42220878601074</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4337215423584</t>
+    <t xml:space="preserve">8.43372058868408</t>
   </si>
   <si>
     <t xml:space="preserve">8.33010005950928</t>
@@ -797,70 +797,70 @@
     <t xml:space="preserve">8.44523525238037</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58915615081787</t>
+    <t xml:space="preserve">8.58915519714355</t>
   </si>
   <si>
     <t xml:space="preserve">8.54885864257812</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57188510894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65247917175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62945556640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70429229736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81942749023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76761627197266</t>
+    <t xml:space="preserve">8.57188606262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65248203277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62945365905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70429134368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81942844390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76761722564697</t>
   </si>
   <si>
     <t xml:space="preserve">8.76186180114746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7733736038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45099449157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45675086975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60751914978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57199859619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47728157043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44768238067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46544361114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42992210388184</t>
+    <t xml:space="preserve">8.77337265014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4509916305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45674800872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60751628875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57199954986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47728061676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44768047332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46544170379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42992115020752</t>
   </si>
   <si>
     <t xml:space="preserve">8.4240026473999</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63711738586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72591495513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77327728271484</t>
+    <t xml:space="preserve">8.63711833953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72591781616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77327442169189</t>
   </si>
   <si>
     <t xml:space="preserve">8.82063484191895</t>
@@ -869,106 +869,106 @@
     <t xml:space="preserve">8.81471538543701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87983322143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90943241119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79695415496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90351390838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89167308807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87391567230225</t>
+    <t xml:space="preserve">8.8798360824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90943145751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79695510864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90351295471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89167213439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8739128112793</t>
   </si>
   <si>
     <t xml:space="preserve">8.83839511871338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67263698577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47136306762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45360279083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34112453460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4417610168457</t>
+    <t xml:space="preserve">8.67263889312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47136116027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45360088348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34112548828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44176292419434</t>
   </si>
   <si>
     <t xml:space="preserve">8.31744480133057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26416492462158</t>
+    <t xml:space="preserve">8.2641658782959</t>
   </si>
   <si>
     <t xml:space="preserve">8.32928371429443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16352558135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22272491455078</t>
+    <t xml:space="preserve">8.1635274887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22272777557373</t>
   </si>
   <si>
     <t xml:space="preserve">8.22864532470703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28784275054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1990442276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15168762207031</t>
+    <t xml:space="preserve">8.28784465789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19904518127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.151686668396</t>
   </si>
   <si>
     <t xml:space="preserve">8.23456573486328</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06880950927734</t>
+    <t xml:space="preserve">8.06880855560303</t>
   </si>
   <si>
     <t xml:space="preserve">8.11024761199951</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08656692504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03920841217041</t>
+    <t xml:space="preserve">8.08656978607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03921031951904</t>
   </si>
   <si>
     <t xml:space="preserve">8.05104923248291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00369071960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02737140655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87345361709595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79057312011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88529300689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90897035598755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79649305343628</t>
+    <t xml:space="preserve">8.00368881225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02737045288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87345170974731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79057359695435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88529109954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90897226333618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79649543762207</t>
   </si>
   <si>
     <t xml:space="preserve">7.74913358688354</t>
@@ -977,28 +977,28 @@
     <t xml:space="preserve">7.67217779159546</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69585752487183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67809629440308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80833339691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82017421722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83793306350708</t>
+    <t xml:space="preserve">7.69585418701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67809772491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80833387374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82017278671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83793258666992</t>
   </si>
   <si>
     <t xml:space="preserve">7.77873468399048</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77281618118286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78465461730957</t>
+    <t xml:space="preserve">7.7728157043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78465270996094</t>
   </si>
   <si>
     <t xml:space="preserve">7.71953582763672</t>
@@ -1007,118 +1007,118 @@
     <t xml:space="preserve">7.73137617111206</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84977388381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82609462738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91489171981812</t>
+    <t xml:space="preserve">7.84977531433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82609367370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91489267349243</t>
   </si>
   <si>
     <t xml:space="preserve">7.97409152984619</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00961112976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99185037612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02145099639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03328990936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01552963256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98593187332153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90305233001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93857383728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8438549041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76097249984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87937164306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89121294021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9267315864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98001194000244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96816968917847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99776935577393</t>
+    <t xml:space="preserve">8.00961017608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99185085296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02145004272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03328895568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01553058624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98593091964722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90305137634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93857192993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84385347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76097869873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87937259674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89121389389038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92673063278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98001098632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96817064285278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99777126312256</t>
   </si>
   <si>
     <t xml:space="preserve">8.07472991943359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17536735534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20584964752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24852180480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31558704376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37655067443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4009370803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49847984313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52896213531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49238395690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50457859039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53505802154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.516770362854</t>
+    <t xml:space="preserve">8.17536544799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20584869384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24852466583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31558609008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37654876708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40093803405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49848079681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52896118164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49238300323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50457572937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53505897521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51676940917969</t>
   </si>
   <si>
     <t xml:space="preserve">8.57773494720459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47409152984619</t>
+    <t xml:space="preserve">8.47409439086914</t>
   </si>
   <si>
     <t xml:space="preserve">8.55334854125977</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44361019134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48628616333008</t>
+    <t xml:space="preserve">8.44361114501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48628520965576</t>
   </si>
   <si>
     <t xml:space="preserve">8.44970798492432</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">8.46190166473389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3948392868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43141841888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41312885284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43751335144043</t>
+    <t xml:space="preserve">8.39484024047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43141937255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41313076019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43751525878906</t>
   </si>
   <si>
     <t xml:space="preserve">8.55944538116455</t>
@@ -1148,73 +1148,73 @@
     <t xml:space="preserve">8.66917991638184</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71795463562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76672554016113</t>
+    <t xml:space="preserve">8.71795272827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7667236328125</t>
   </si>
   <si>
     <t xml:space="preserve">8.83988189697266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97400665283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9130392074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84597778320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78501319885254</t>
+    <t xml:space="preserve">8.97400569915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91303825378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84598064422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78501415252686</t>
   </si>
   <si>
     <t xml:space="preserve">8.72405052185059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62040996551514</t>
+    <t xml:space="preserve">8.62041091918945</t>
   </si>
   <si>
     <t xml:space="preserve">8.37045383453369</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38874435424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45580387115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48018932342529</t>
+    <t xml:space="preserve">8.38874244689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4558048248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48019027709961</t>
   </si>
   <si>
     <t xml:space="preserve">8.42532348632812</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34607028961182</t>
+    <t xml:space="preserve">8.3460693359375</t>
   </si>
   <si>
     <t xml:space="preserve">8.41922760009766</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54725074768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57163906097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52286434173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5106725692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68747043609619</t>
+    <t xml:space="preserve">8.5472526550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57163715362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52286529541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51067352294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68746948242188</t>
   </si>
   <si>
     <t xml:space="preserve">8.79720878601074</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85207557678223</t>
+    <t xml:space="preserve">8.85207748413086</t>
   </si>
   <si>
     <t xml:space="preserve">8.96181201934814</t>
@@ -1223,67 +1223,67 @@
     <t xml:space="preserve">9.09593391418457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08983898162842</t>
+    <t xml:space="preserve">9.0898380279541</t>
   </si>
   <si>
     <t xml:space="preserve">9.05935573577881</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11422348022461</t>
+    <t xml:space="preserve">9.11422443389893</t>
   </si>
   <si>
     <t xml:space="preserve">9.04106521606445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10812377929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12032032012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10202884674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01668071746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8667049407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83134651184082</t>
+    <t xml:space="preserve">9.10812759399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12031936645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10202980041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01668167114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86670684814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83134746551514</t>
   </si>
   <si>
     <t xml:space="preserve">8.89475154876709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74721622467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62894344329834</t>
+    <t xml:space="preserve">8.74721431732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62894439697266</t>
   </si>
   <si>
     <t xml:space="preserve">8.38508605957031</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33509254455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16804981231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21926116943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14000797271729</t>
+    <t xml:space="preserve">8.33509635925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16805076599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21926307678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14000701904297</t>
   </si>
   <si>
     <t xml:space="preserve">8.19243621826172</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23267269134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31070709228516</t>
+    <t xml:space="preserve">8.23267364501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31070804595947</t>
   </si>
   <si>
     <t xml:space="preserve">8.35704040527344</t>
@@ -1292,22 +1292,22 @@
     <t xml:space="preserve">8.3594799041748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33997249603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40703105926514</t>
+    <t xml:space="preserve">8.33997058868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40703392028809</t>
   </si>
   <si>
     <t xml:space="preserve">8.450927734375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36069774627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27412796020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15585803985596</t>
+    <t xml:space="preserve">8.36069869995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27412891387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15585899353027</t>
   </si>
   <si>
     <t xml:space="preserve">8.12659549713135</t>
@@ -1319,73 +1319,73 @@
     <t xml:space="preserve">8.28022575378418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28632259368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36313724517822</t>
+    <t xml:space="preserve">8.28632068634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36313819885254</t>
   </si>
   <si>
     <t xml:space="preserve">8.42776107788086</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59602355957031</t>
+    <t xml:space="preserve">8.59602451324463</t>
   </si>
   <si>
     <t xml:space="preserve">8.49726104736328</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61431407928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68137264251709</t>
+    <t xml:space="preserve">8.61431217193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68137359619141</t>
   </si>
   <si>
     <t xml:space="preserve">8.63869953155518</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6008996963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57041549682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65698719024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63382053375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71063804626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79842662811279</t>
+    <t xml:space="preserve">8.60090160369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57041835784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6569881439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63382148742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71063709259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79842567443848</t>
   </si>
   <si>
     <t xml:space="preserve">8.87402248382568</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06057643890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07642459869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13738918304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22639751434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28370475769043</t>
+    <t xml:space="preserve">9.06057453155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07642364501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13739204406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22639942169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28370571136475</t>
   </si>
   <si>
     <t xml:space="preserve">9.3458890914917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40807247161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41782665252686</t>
+    <t xml:space="preserve">9.4080753326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41782855987549</t>
   </si>
   <si>
     <t xml:space="preserve">9.55926513671875</t>
@@ -1394,55 +1394,55 @@
     <t xml:space="preserve">9.62998390197754</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75435161590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72509002685547</t>
+    <t xml:space="preserve">9.75435352325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72508907318115</t>
   </si>
   <si>
     <t xml:space="preserve">9.80800151824951</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77142429351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66290664672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85799598693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85067939758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87628364562988</t>
+    <t xml:space="preserve">9.7714204788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6629056930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85799121856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85067844390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87628269195557</t>
   </si>
   <si>
     <t xml:space="preserve">9.95065975189209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83238792419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96772766113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1591577529907</t>
+    <t xml:space="preserve">9.83238697052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96772956848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.159158706665</t>
   </si>
   <si>
     <t xml:space="preserve">9.89822959899902</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1725730895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0030889511108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0225982666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1664752960205</t>
+    <t xml:space="preserve">10.1725692749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0030870437622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0225973129272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1664733886719</t>
   </si>
   <si>
     <t xml:space="preserve">10.2201242446899</t>
@@ -1451,121 +1451,121 @@
     <t xml:space="preserve">10.0823440551758</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1213617324829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.090877532959</t>
+    <t xml:space="preserve">10.1213607788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0908784866333</t>
   </si>
   <si>
     <t xml:space="preserve">10.010910987854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0596399307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94843673706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85722637176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61232566833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41740417480469</t>
+    <t xml:space="preserve">10.0596418380737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94843578338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8572244644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61232280731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41740322113037</t>
   </si>
   <si>
     <t xml:space="preserve">9.42989826202393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67729568481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82848358154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73727321624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65355682373047</t>
+    <t xml:space="preserve">9.67729759216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8284854888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73727416992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6535587310791</t>
   </si>
   <si>
     <t xml:space="preserve">9.65230751037598</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76476192474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51111507415771</t>
+    <t xml:space="preserve">9.7647590637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51111602783203</t>
   </si>
   <si>
     <t xml:space="preserve">9.78850269317627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69104290008545</t>
+    <t xml:space="preserve">9.69104099273682</t>
   </si>
   <si>
     <t xml:space="preserve">9.879714012146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70353507995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70853424072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64231204986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47238159179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76850891113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54734897613525</t>
+    <t xml:space="preserve">9.70353698730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70853519439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64231109619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47238063812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76850986480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5473518371582</t>
   </si>
   <si>
     <t xml:space="preserve">9.64106273651123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90720462799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9396915435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93719291687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85472583770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0933780670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0871324539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1308622360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1083707809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1933355331421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3270330429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1533546447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.158350944519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1708469390869</t>
+    <t xml:space="preserve">9.90720081329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93969058990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93719100952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85472679138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0933752059937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0871295928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1308631896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1083698272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1933374404907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3270311355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1533527374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1583499908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1708459854126</t>
   </si>
   <si>
     <t xml:space="preserve">10.0296535491943</t>
@@ -1574,58 +1574,58 @@
     <t xml:space="preserve">10.0821313858032</t>
   </si>
   <si>
-    <t xml:space="preserve">10.080883026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0458965301514</t>
+    <t xml:space="preserve">10.0808839797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0458955764771</t>
   </si>
   <si>
     <t xml:space="preserve">10.0496473312378</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0771331787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1446075439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1383600234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1895875930786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.120867729187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.174596786499</t>
+    <t xml:space="preserve">10.0771322250366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.144606590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1383571624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1895866394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1208658218384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1745920181274</t>
   </si>
   <si>
     <t xml:space="preserve">10.2857990264893</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2095804214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.123366355896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1783428192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3770132064819</t>
+    <t xml:space="preserve">10.2095794677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1233644485474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1783418655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3770122528076</t>
   </si>
   <si>
     <t xml:space="preserve">10.3082895278931</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2370691299438</t>
+    <t xml:space="preserve">10.2370681762695</t>
   </si>
   <si>
     <t xml:space="preserve">9.96842765808105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96967601776123</t>
+    <t xml:space="preserve">9.96967887878418</t>
   </si>
   <si>
     <t xml:space="preserve">10.067138671875</t>
@@ -1634,52 +1634,52 @@
     <t xml:space="preserve">9.94093894958496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88596439361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0034112930298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1046237945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1958351135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1421051025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2458152770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2658042907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2483139038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98342227935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.048394203186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0733833312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97092723846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88721179962158</t>
+    <t xml:space="preserve">9.88596153259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0034122467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.104621887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1958360671997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.142107963562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2458143234253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2658081054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.24831199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98342132568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0483951568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0733871459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97092819213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88721084594727</t>
   </si>
   <si>
     <t xml:space="preserve">9.82473754882812</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9022045135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92094898223877</t>
+    <t xml:space="preserve">9.90220546722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92094802856445</t>
   </si>
   <si>
     <t xml:space="preserve">10.0071630477905</t>
@@ -1688,22 +1688,22 @@
     <t xml:space="preserve">9.9884204864502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98716926574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0783853530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2070827484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3601627349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6115350723267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6423177719116</t>
+    <t xml:space="preserve">9.9871711730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0783834457397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2070817947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3601608276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6115341186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6423149108887</t>
   </si>
   <si>
     <t xml:space="preserve">10.6012754440308</t>
@@ -1715,94 +1715,94 @@
     <t xml:space="preserve">10.4653291702271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4794368743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5012378692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4383955001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4319820404053</t>
+    <t xml:space="preserve">10.479434967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.501238822937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4383964538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4319849014282</t>
   </si>
   <si>
     <t xml:space="preserve">10.1613731384277</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4281368255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3588800430298</t>
+    <t xml:space="preserve">10.4281358718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3588819503784</t>
   </si>
   <si>
     <t xml:space="preserve">10.0741605758667</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0164499282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1075067520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1523952484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9933614730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80611705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86895942687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73044586181641</t>
+    <t xml:space="preserve">10.0164489746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1075086593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1523933410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99336242675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80611515045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86895847320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73044681549072</t>
   </si>
   <si>
     <t xml:space="preserve">9.58680629730225</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44059944152832</t>
+    <t xml:space="preserve">9.440598487854</t>
   </si>
   <si>
     <t xml:space="preserve">9.60219669342041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70479679107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85100269317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86639308929443</t>
+    <t xml:space="preserve">9.70479583740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85100364685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86639213562012</t>
   </si>
   <si>
     <t xml:space="preserve">10.0715961456299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8920431137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84972190856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90871620178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83561420440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0254278182983</t>
+    <t xml:space="preserve">9.89204502105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8497200012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90871906280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83561325073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0254249572754</t>
   </si>
   <si>
     <t xml:space="preserve">9.9869499206543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91128253936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93180179595947</t>
+    <t xml:space="preserve">9.91128349304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93180084228516</t>
   </si>
   <si>
     <t xml:space="preserve">9.71377468109131</t>
@@ -1811,7 +1811,7 @@
     <t xml:space="preserve">9.57141494750977</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60347747802734</t>
+    <t xml:space="preserve">9.60347652435303</t>
   </si>
   <si>
     <t xml:space="preserve">9.55474281311035</t>
@@ -1823,46 +1823,46 @@
     <t xml:space="preserve">9.26745796203613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38032054901123</t>
+    <t xml:space="preserve">9.38032150268555</t>
   </si>
   <si>
     <t xml:space="preserve">9.18024826049805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01608467102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1674222946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10201358795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0763635635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11612129211426</t>
+    <t xml:space="preserve">9.01608753204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16742324829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10201454162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07636260986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11612319946289</t>
   </si>
   <si>
     <t xml:space="preserve">9.13536071777344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30593776702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24308967590332</t>
+    <t xml:space="preserve">9.30593490600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24309253692627</t>
   </si>
   <si>
     <t xml:space="preserve">9.16357517242432</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87116146087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05071353912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93913459777832</t>
+    <t xml:space="preserve">8.87116050720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05071449279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93913555145264</t>
   </si>
   <si>
     <t xml:space="preserve">9.01993274688721</t>
@@ -1874,130 +1874,130 @@
     <t xml:space="preserve">9.14562034606934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07251739501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95195865631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85833835601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94554805755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86603260040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83268642425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66980648040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81601333618164</t>
+    <t xml:space="preserve">9.07251834869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95196151733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85833549499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94554996490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86603164672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83268737792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66980838775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81601524353027</t>
   </si>
   <si>
     <t xml:space="preserve">8.83653259277344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87501049041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19563961029053</t>
+    <t xml:space="preserve">8.87500858306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19563865661621</t>
   </si>
   <si>
     <t xml:space="preserve">9.11483860015869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0584077835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14177131652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13279247283936</t>
+    <t xml:space="preserve">9.05840873718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14177322387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13279342651367</t>
   </si>
   <si>
     <t xml:space="preserve">9.08662509918213</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05456161499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13792705535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1571626663208</t>
+    <t xml:space="preserve">9.05456352233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13792514801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15716075897217</t>
   </si>
   <si>
     <t xml:space="preserve">9.11740398406982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36749458312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32773590087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28284931182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2443733215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34441089630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25463581085205</t>
+    <t xml:space="preserve">9.3674955368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32773685455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28284740447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24437427520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34440994262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25463485717773</t>
   </si>
   <si>
     <t xml:space="preserve">9.31234645843506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39058303833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49446201324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47266006469727</t>
+    <t xml:space="preserve">9.3905782699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49446296691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4726619720459</t>
   </si>
   <si>
     <t xml:space="preserve">9.48163890838623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5803918838501</t>
+    <t xml:space="preserve">9.58039283752441</t>
   </si>
   <si>
     <t xml:space="preserve">9.52909183502197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32004261016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30849933624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39442729949951</t>
+    <t xml:space="preserve">9.32004165649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30850124359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39442825317383</t>
   </si>
   <si>
     <t xml:space="preserve">9.46240139007568</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52652931213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47779083251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69581985473633</t>
+    <t xml:space="preserve">9.52652645111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47779273986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69581890106201</t>
   </si>
   <si>
     <t xml:space="preserve">9.73172855377197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74583911895752</t>
+    <t xml:space="preserve">9.74583721160889</t>
   </si>
   <si>
     <t xml:space="preserve">9.78046607971191</t>
@@ -2009,7 +2009,7 @@
     <t xml:space="preserve">9.80354976654053</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75481700897217</t>
+    <t xml:space="preserve">9.7548131942749</t>
   </si>
   <si>
     <t xml:space="preserve">9.75353240966797</t>
@@ -2018,16 +2018,16 @@
     <t xml:space="preserve">9.76122856140137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72531700134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64323806762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6894063949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73686027526855</t>
+    <t xml:space="preserve">9.72531986236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.643235206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68940734863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73686218261719</t>
   </si>
   <si>
     <t xml:space="preserve">9.79841995239258</t>
@@ -2036,40 +2036,40 @@
     <t xml:space="preserve">9.59834861755371</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69709968566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72403430938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96771335601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96386528015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99592876434326</t>
+    <t xml:space="preserve">9.69710063934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72403526306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96771144866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9638671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99592685699463</t>
   </si>
   <si>
     <t xml:space="preserve">10.0959634780884</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1164855957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1511135101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0677480697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0190134048462</t>
+    <t xml:space="preserve">10.1164846420288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1511125564575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0677490234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0190143585205</t>
   </si>
   <si>
     <t xml:space="preserve">10.0138835906982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99721050262451</t>
+    <t xml:space="preserve">9.99721145629883</t>
   </si>
   <si>
     <t xml:space="preserve">9.92667198181152</t>
@@ -2078,7 +2078,7 @@
     <t xml:space="preserve">10.1023769378662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1254606246948</t>
+    <t xml:space="preserve">10.1254625320435</t>
   </si>
   <si>
     <t xml:space="preserve">10.1985654830933</t>
@@ -2090,10 +2090,10 @@
     <t xml:space="preserve">10.1626539230347</t>
   </si>
   <si>
-    <t xml:space="preserve">10.140851020813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.188304901123</t>
+    <t xml:space="preserve">10.1408519744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1883058547974</t>
   </si>
   <si>
     <t xml:space="preserve">10.2216510772705</t>
@@ -2102,277 +2102,277 @@
     <t xml:space="preserve">10.2113904953003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1421327590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0485124588013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89460945129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89589214324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1305913925171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97156047821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94334506988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83817768096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6817102432251</t>
+    <t xml:space="preserve">10.1421356201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0485105514526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89461135864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8958911895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1305923461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97156143188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94334411621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83818054199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68171310424805</t>
   </si>
   <si>
     <t xml:space="preserve">9.75866317749023</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64066982269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67529964447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53678798675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29182529449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28541278839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.185378074646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14818572998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2482213973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36493110656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30978107452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45855331420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51626873016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50703430175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58881092071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50835227966309</t>
+    <t xml:space="preserve">9.64067268371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6752986907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53678703308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29182720184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28541374206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18537902832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14818477630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24822044372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36492919921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30978202819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4585542678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51626586914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50703620910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5888090133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50835418701172</t>
   </si>
   <si>
     <t xml:space="preserve">9.17993259429932</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26830196380615</t>
+    <t xml:space="preserve">9.26830387115479</t>
   </si>
   <si>
     <t xml:space="preserve">9.2788553237915</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24983692169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05727005004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02957153320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95571041107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11398506164551</t>
+    <t xml:space="preserve">9.24983787536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05727100372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02957344055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95570945739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11398696899414</t>
   </si>
   <si>
     <t xml:space="preserve">9.24456214904785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1456413269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16674137115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20631217956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23269081115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26302719116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1693811416626</t>
+    <t xml:space="preserve">9.14563941955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16674327850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20631313323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23269271850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26302814483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16938304901123</t>
   </si>
   <si>
     <t xml:space="preserve">9.19576072692871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14695644378662</t>
+    <t xml:space="preserve">9.14695930480957</t>
   </si>
   <si>
     <t xml:space="preserve">9.33556938171387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37909698486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46878242492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63233375549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57693767547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52286052703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56770610809326</t>
+    <t xml:space="preserve">9.37909603118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46878528594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63233280181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57694053649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52286243438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56770515441895</t>
   </si>
   <si>
     <t xml:space="preserve">9.54000759124756</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65475845336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.561110496521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60727310180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65871429443359</t>
+    <t xml:space="preserve">9.65475654602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56111145019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60727405548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65871334075928</t>
   </si>
   <si>
     <t xml:space="preserve">9.59540367126465</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66399002075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69828319549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76027297973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77742195129395</t>
+    <t xml:space="preserve">9.66398906707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69828224182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76027488708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77742099761963</t>
   </si>
   <si>
     <t xml:space="preserve">9.70223999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67190265655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50571346282959</t>
+    <t xml:space="preserve">9.67190456390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50571537017822</t>
   </si>
   <si>
     <t xml:space="preserve">9.43053436279297</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37777519226074</t>
+    <t xml:space="preserve">9.37777709960938</t>
   </si>
   <si>
     <t xml:space="preserve">9.44108581542969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48988914489746</t>
+    <t xml:space="preserve">9.48988819122314</t>
   </si>
   <si>
     <t xml:space="preserve">9.46350860595703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45559406280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39624214172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29468154907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36722469329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29599952697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0216588973999</t>
+    <t xml:space="preserve">9.45559501647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39624118804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2946834564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36722660064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29600143432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02165985107422</t>
   </si>
   <si>
     <t xml:space="preserve">8.88976192474365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82645034790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70115089416504</t>
+    <t xml:space="preserve">8.82645320892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70115184783936</t>
   </si>
   <si>
     <t xml:space="preserve">8.8594274520874</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69983386993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68532371520996</t>
+    <t xml:space="preserve">8.69983291625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68532562255859</t>
   </si>
   <si>
     <t xml:space="preserve">8.85019397735596</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64048004150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59959316253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75391006469727</t>
+    <t xml:space="preserve">8.64047908782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5995922088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75391101837158</t>
   </si>
   <si>
     <t xml:space="preserve">8.66817951202393</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80403327941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77897071838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6668586730957</t>
+    <t xml:space="preserve">8.80403232574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77897262573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66686058044434</t>
   </si>
   <si>
     <t xml:space="preserve">8.71697902679443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77237606048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83700275421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9807710647583</t>
+    <t xml:space="preserve">8.77237510681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83700466156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98077011108398</t>
   </si>
   <si>
     <t xml:space="preserve">9.04276180267334</t>
@@ -2384,25 +2384,25 @@
     <t xml:space="preserve">9.01506328582764</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08101081848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18125152587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29995822906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28149223327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26170825958252</t>
+    <t xml:space="preserve">9.08101177215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18125247955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29995918273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28149127960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26170921325684</t>
   </si>
   <si>
     <t xml:space="preserve">9.4397668838501</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33293056488037</t>
+    <t xml:space="preserve">9.332932472229</t>
   </si>
   <si>
     <t xml:space="preserve">9.44636344909668</t>
@@ -2411,97 +2411,97 @@
     <t xml:space="preserve">9.59672355651855</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60895538330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51109981536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42003726959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46896457672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55051136016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53692245483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50022411346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21209335327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11151790618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20393657684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27733135223389</t>
+    <t xml:space="preserve">9.60895729064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51110076904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4200382232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46896553039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55051326751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53692150115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50022506713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21209144592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11151885986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20393943786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27733039855957</t>
   </si>
   <si>
     <t xml:space="preserve">9.1971435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24199390411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29771709442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40236949920654</t>
+    <t xml:space="preserve">9.24199485778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2977180480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40236854553223</t>
   </si>
   <si>
     <t xml:space="preserve">9.33985137939453</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40373039245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38877773284912</t>
+    <t xml:space="preserve">9.40372848510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38877868652344</t>
   </si>
   <si>
     <t xml:space="preserve">9.36431312561035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48255634307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56274318695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6075963973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54099941253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47168350219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39693260192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30859088897705</t>
+    <t xml:space="preserve">9.48255729675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56274509429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60759544372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5409984588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47168254852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39693450927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30858993530273</t>
   </si>
   <si>
     <t xml:space="preserve">9.22160720825195</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31266689300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49614715576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6483678817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62526321411133</t>
+    <t xml:space="preserve">9.31266784667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49614810943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64836883544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62526416778564</t>
   </si>
   <si>
     <t xml:space="preserve">9.63341808319092</t>
@@ -2510,40 +2510,40 @@
     <t xml:space="preserve">9.6429328918457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60623741149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68642520904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63749599456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6633186340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58856773376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49343299865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52197265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54235744476318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54643440246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46760845184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43906593322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37790679931641</t>
+    <t xml:space="preserve">9.60623550415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68642330169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63749694824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66332054138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58856964111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49343204498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52197170257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54235649108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54643726348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46760749816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43906402587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37790584564209</t>
   </si>
   <si>
     <t xml:space="preserve">9.31946277618408</t>
@@ -2552,196 +2552,196 @@
     <t xml:space="preserve">9.22296524047852</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16044425964355</t>
+    <t xml:space="preserve">9.16044616699219</t>
   </si>
   <si>
     <t xml:space="preserve">9.27189445495605</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35751819610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25966358184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28684520721436</t>
+    <t xml:space="preserve">9.35751914978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25966262817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28684329986572</t>
   </si>
   <si>
     <t xml:space="preserve">9.23655605316162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27596950531006</t>
+    <t xml:space="preserve">9.27597045898438</t>
   </si>
   <si>
     <t xml:space="preserve">9.24471187591553</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31130695343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39013481140137</t>
+    <t xml:space="preserve">9.25830268859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31130886077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39013671875</t>
   </si>
   <si>
     <t xml:space="preserve">9.40916442871094</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52468776702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51381587982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51925563812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58584880828857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72855758666992</t>
+    <t xml:space="preserve">9.52469062805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51381874084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51925277709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58584976196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72855663299561</t>
   </si>
   <si>
     <t xml:space="preserve">9.73127460479736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65380859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58177280426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42819213867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37654685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43770503997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4567346572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43362903594971</t>
+    <t xml:space="preserve">9.65380573272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58177375793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42819118499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37654590606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43770599365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45673370361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43362998962402</t>
   </si>
   <si>
     <t xml:space="preserve">9.21345138549805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14549541473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15364933013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96745109558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10472202301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02997207641602</t>
+    <t xml:space="preserve">9.1454963684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15365028381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96745014190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10472393035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0299711227417</t>
   </si>
   <si>
     <t xml:space="preserve">8.78397083282471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60184860229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5692310333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69019031524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85328483581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81387138366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77037906646729</t>
+    <t xml:space="preserve">8.60184955596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56923294067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6901912689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85328674316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81387042999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77037811279297</t>
   </si>
   <si>
     <t xml:space="preserve">8.6847562789917</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90221500396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82610416412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76086521148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77309799194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7921257019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76630306243896</t>
+    <t xml:space="preserve">8.90221405029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82610321044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76086711883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77309894561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79212474822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76630210876465</t>
   </si>
   <si>
     <t xml:space="preserve">8.67388248443604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26886653900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13839244842529</t>
+    <t xml:space="preserve">8.26886463165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13839054107666</t>
   </si>
   <si>
     <t xml:space="preserve">8.19819164276123</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99024677276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58251428604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55533075332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55668783187866</t>
+    <t xml:space="preserve">7.99024820327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58251047134399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55532932281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55668830871582</t>
   </si>
   <si>
     <t xml:space="preserve">7.57843399047852</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45339632034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95460081100464</t>
+    <t xml:space="preserve">7.4533953666687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95460176467896</t>
   </si>
   <si>
     <t xml:space="preserve">5.50442361831665</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54859352111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47044563293457</t>
+    <t xml:space="preserve">5.54859304428101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47044515609741</t>
   </si>
   <si>
     <t xml:space="preserve">4.47964811325073</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6964282989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41169214248657</t>
+    <t xml:space="preserve">4.69642686843872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41169309616089</t>
   </si>
   <si>
     <t xml:space="preserve">4.66584825515747</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54896402359009</t>
+    <t xml:space="preserve">4.54896259307861</t>
   </si>
   <si>
     <t xml:space="preserve">4.73312425613403</t>
@@ -2750,70 +2750,70 @@
     <t xml:space="preserve">4.95601892471313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95194053649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69130182266235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92778730392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91963243484497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58393049240112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8394455909729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26552724838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25193500518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68549585342407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3368821144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33008575439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40687561035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31649351119995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32532978057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22951173782349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83196926116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74498701095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83536720275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73139524459839</t>
+    <t xml:space="preserve">4.95194149017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6913013458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92778825759888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91963291168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58393144607544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83944463729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26552820205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25193738937378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6854944229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33688116073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33008670806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40687608718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31649446487427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32532835006714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22951030731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83197021484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74498558044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83536863327026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73139429092407</t>
   </si>
   <si>
     <t xml:space="preserve">5.40928411483765</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67295360565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75721836090088</t>
+    <t xml:space="preserve">5.67295265197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75721883773804</t>
   </si>
   <si>
     <t xml:space="preserve">5.60635566711426</t>
@@ -2822,28 +2822,28 @@
     <t xml:space="preserve">5.71100854873657</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90128469467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0868034362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92167186737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57985353469849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90332365036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7239203453064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81430196762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86526775360107</t>
+    <t xml:space="preserve">5.90128517150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08680486679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92167139053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5798544883728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90332317352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72391986846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81430101394653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86526727676392</t>
   </si>
   <si>
     <t xml:space="preserve">5.79323482513428</t>
@@ -2852,49 +2852,49 @@
     <t xml:space="preserve">5.78575944900513</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78983783721924</t>
+    <t xml:space="preserve">5.78983640670776</t>
   </si>
   <si>
     <t xml:space="preserve">6.19562673568726</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00024604797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03245210647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88430690765381</t>
+    <t xml:space="preserve">6.00024652481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03245162963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88430595397949</t>
   </si>
   <si>
     <t xml:space="preserve">5.84995365142822</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91150188446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92152166366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04748153686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07753896713257</t>
+    <t xml:space="preserve">5.91150236129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92152118682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04748058319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07753944396973</t>
   </si>
   <si>
     <t xml:space="preserve">5.81345462799072</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9687557220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27721452713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44038915634155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41533899307251</t>
+    <t xml:space="preserve">5.96875667572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27721261978149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44038820266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41534042358398</t>
   </si>
   <si>
     <t xml:space="preserve">6.80323696136475</t>
@@ -2903,46 +2903,46 @@
     <t xml:space="preserve">6.91631412506104</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71020030975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60571098327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14123582839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1455283164978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14051914215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39458465576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36667251586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32301616668701</t>
+    <t xml:space="preserve">6.71019792556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60571002960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1412353515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14553022384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14051961898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39458417892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36667346954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32301664352417</t>
   </si>
   <si>
     <t xml:space="preserve">6.35092830657959</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30011653900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06322622299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06966686248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00955057144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17272424697876</t>
+    <t xml:space="preserve">6.30011558532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0632266998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06966638565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00954961776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17272567749023</t>
   </si>
   <si>
     <t xml:space="preserve">6.0761079788208</t>
@@ -2951,76 +2951,76 @@
     <t xml:space="preserve">6.06537389755249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24071502685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20779323577881</t>
+    <t xml:space="preserve">6.24071359634399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20779228210449</t>
   </si>
   <si>
     <t xml:space="preserve">6.26791000366211</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3122820854187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22496891021729</t>
+    <t xml:space="preserve">6.31228160858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22497081756592</t>
   </si>
   <si>
     <t xml:space="preserve">6.03602981567383</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19777393341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28580093383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32373237609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36595916748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3072714805603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28437042236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39029169082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23141050338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15554809570312</t>
+    <t xml:space="preserve">6.19777250289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28580188751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32373380661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36595869064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30727291107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28437185287476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39029026031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23140907287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15554714202881</t>
   </si>
   <si>
     <t xml:space="preserve">6.09757852554321</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05678558349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06680488586426</t>
+    <t xml:space="preserve">6.05678510665894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0668044090271</t>
   </si>
   <si>
     <t xml:space="preserve">6.01885318756104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59517192840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39692974090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39192008972168</t>
+    <t xml:space="preserve">5.59517288208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39693021774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39191961288452</t>
   </si>
   <si>
     <t xml:space="preserve">5.62451553344727</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79413032531738</t>
+    <t xml:space="preserve">5.79413080215454</t>
   </si>
   <si>
     <t xml:space="preserve">5.68391609191895</t>
@@ -3032,10 +3032,10 @@
     <t xml:space="preserve">5.71540689468384</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90005159378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9923734664917</t>
+    <t xml:space="preserve">5.90005111694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99237394332886</t>
   </si>
   <si>
     <t xml:space="preserve">5.90076684951782</t>
@@ -3047,28 +3047,28 @@
     <t xml:space="preserve">5.79699420928955</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76407194137573</t>
+    <t xml:space="preserve">5.76407241821289</t>
   </si>
   <si>
     <t xml:space="preserve">5.81703281402588</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67890596389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63453578948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86211967468262</t>
+    <t xml:space="preserve">5.67890739440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63453483581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86212110519409</t>
   </si>
   <si>
     <t xml:space="preserve">5.78124904632568</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69822978973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58228969573975</t>
+    <t xml:space="preserve">5.69822931289673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5822901725769</t>
   </si>
   <si>
     <t xml:space="preserve">5.56511402130127</t>
@@ -3077,40 +3077,40 @@
     <t xml:space="preserve">5.49354648590088</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5078592300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47135972976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56296682357788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38118505477905</t>
+    <t xml:space="preserve">5.50785970687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.471360206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56296730041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38118362426758</t>
   </si>
   <si>
     <t xml:space="preserve">5.45919418334961</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45776176452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43843936920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35041046142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44774198532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47565460205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43486070632935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28743028640747</t>
+    <t xml:space="preserve">5.45776271820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4384388923645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35041093826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44774293899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47565364837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43485975265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28743076324463</t>
   </si>
   <si>
     <t xml:space="preserve">5.05608701705933</t>
@@ -3119,25 +3119,25 @@
     <t xml:space="preserve">5.13320255279541</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0400824546814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95569229125977</t>
+    <t xml:space="preserve">5.04008293151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95569324493408</t>
   </si>
   <si>
     <t xml:space="preserve">4.86621189117432</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99061298370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84875202178955</t>
+    <t xml:space="preserve">4.99061346054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84875154495239</t>
   </si>
   <si>
     <t xml:space="preserve">4.8654842376709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7010703086853</t>
+    <t xml:space="preserve">4.70107078552246</t>
   </si>
   <si>
     <t xml:space="preserve">4.72653245925903</t>
@@ -3146,103 +3146,103 @@
     <t xml:space="preserve">4.86693954467773</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03280878067017</t>
+    <t xml:space="preserve">5.03280735015869</t>
   </si>
   <si>
     <t xml:space="preserve">4.89603900909424</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00880098342896</t>
+    <t xml:space="preserve">5.0088005065918</t>
   </si>
   <si>
     <t xml:space="preserve">4.99206829071045</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96078538894653</t>
+    <t xml:space="preserve">4.96078586578369</t>
   </si>
   <si>
     <t xml:space="preserve">4.8640284538269</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87275886535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66906023025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77454662322998</t>
+    <t xml:space="preserve">4.87275838851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66906070709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77454853057861</t>
   </si>
   <si>
     <t xml:space="preserve">4.79127931594849</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77381944656372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61231565475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61304378509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68797540664673</t>
+    <t xml:space="preserve">4.77381992340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61231517791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61304235458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68797492980957</t>
   </si>
   <si>
     <t xml:space="preserve">4.54320383071899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43771743774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28130531311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30531311035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37297058105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62832117080688</t>
+    <t xml:space="preserve">4.43771648406982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28130626678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30531358718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37297105789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62832021713257</t>
   </si>
   <si>
     <t xml:space="preserve">4.73889970779419</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79928159713745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79855442047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75926923751831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36745595932007</t>
+    <t xml:space="preserve">4.79928207397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79855394363403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75927019119263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36745548248291</t>
   </si>
   <si>
     <t xml:space="preserve">5.58570384979248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52313899993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54205417633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57260847091675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79667711257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88252210617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9610915184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87597465515137</t>
+    <t xml:space="preserve">5.52313947677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54205369949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57260799407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79667615890503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8825216293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96109104156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87597417831421</t>
   </si>
   <si>
     <t xml:space="preserve">5.9108943939209</t>
@@ -3251,133 +3251,133 @@
     <t xml:space="preserve">6.06002998352051</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27100229263306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30883359909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22589874267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24335861206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0403881072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12186717987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18297719955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14878368377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36121273040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37794542312622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39467859268188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43323659896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50089168548584</t>
+    <t xml:space="preserve">6.27100276947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30883407592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22589826583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24335908889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04038715362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12186765670776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18297624588013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1487832069397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36121368408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37794494628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39467811584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43323516845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50089120864868</t>
   </si>
   <si>
     <t xml:space="preserve">6.40777254104614</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31319808959961</t>
+    <t xml:space="preserve">6.31319856643677</t>
   </si>
   <si>
     <t xml:space="preserve">6.3670334815979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36994314193726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3372049331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27173089981079</t>
+    <t xml:space="preserve">6.36994361877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33720588684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27173042297363</t>
   </si>
   <si>
     <t xml:space="preserve">5.99746608734131</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08185482025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24481344223022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25354337692261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22880935668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21862459182739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14587497711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37357950210571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58236980438232</t>
+    <t xml:space="preserve">6.08185434341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24481391906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25354433059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22880840301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21862411499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14587450027466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37357997894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5823712348938</t>
   </si>
   <si>
     <t xml:space="preserve">6.59692192077637</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56927633285522</t>
+    <t xml:space="preserve">6.56927728652954</t>
   </si>
   <si>
     <t xml:space="preserve">6.53144645690918</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58673620223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5911021232605</t>
+    <t xml:space="preserve">6.58673572540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59110164642334</t>
   </si>
   <si>
     <t xml:space="preserve">6.5510892868042</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42450571060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44269180297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42159461975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47542953491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30592393875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21425819396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0767617225647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20407342910767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21789693832397</t>
+    <t xml:space="preserve">6.42450523376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44269275665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42159414291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47542905807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30592441558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21425867080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07676267623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20407438278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21789598464966</t>
   </si>
   <si>
     <t xml:space="preserve">6.07603597640991</t>
@@ -3386,196 +3386,196 @@
     <t xml:space="preserve">5.96545600891113</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04620790481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17570209503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23462915420532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26445722579956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31538009643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38376426696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43396139144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38522005081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45942497253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63693475723267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60492277145386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66603374481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61801910400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69149541854858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80643892288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85590839385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96721458435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04214811325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89810419082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95557546615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90537929534912</t>
+    <t xml:space="preserve">6.0462064743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1757025718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23462963104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2644567489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31538152694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38376522064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43396186828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38522052764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45942401885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63693332672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60492420196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6660327911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61801815032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69149684906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80644035339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85590887069702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9672155380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04214906692505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89810466766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95557594299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90537786483765</t>
   </si>
   <si>
     <t xml:space="preserve">7.02759790420532</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18473720550537</t>
+    <t xml:space="preserve">7.18473768234253</t>
   </si>
   <si>
     <t xml:space="preserve">7.3200511932373</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40589618682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37679576873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4349946975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49319362640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57903909683228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5179295539856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44954347610474</t>
+    <t xml:space="preserve">7.4058952331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37679529190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43499517440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49319267272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57903814315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51792860031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44954633712769</t>
   </si>
   <si>
     <t xml:space="preserve">7.52084064483643</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40152978897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38115930557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26039695739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4539098739624</t>
+    <t xml:space="preserve">7.40152883529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38116073608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2603964805603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45390892028809</t>
   </si>
   <si>
     <t xml:space="preserve">7.35642528533936</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44372606277466</t>
+    <t xml:space="preserve">7.44372463226318</t>
   </si>
   <si>
     <t xml:space="preserve">7.52811241149902</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5746750831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63433027267456</t>
+    <t xml:space="preserve">7.57467269897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63432931900024</t>
   </si>
   <si>
     <t xml:space="preserve">7.68961763381958</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6197772026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60668325424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46409559249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42044639587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39280033111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43935871124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62996292114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53975343704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52956867218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51065492630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32878255844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38406896591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39716577529907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34914922714233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3826150894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35497045516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42335510253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4219012260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22402191162109</t>
+    <t xml:space="preserve">7.61977958679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6066837310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4640941619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42044591903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39279985427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43936014175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62996530532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53975439071655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52956914901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51065397262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32877969741821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38407182693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39716529846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34915113449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38261556625366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35496950149536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42335557937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42190027236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22402143478394</t>
   </si>
   <si>
     <t xml:space="preserve">7.34769678115845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4990119934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51211166381836</t>
+    <t xml:space="preserve">7.49901294708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51210832595825</t>
   </si>
   <si>
     <t xml:space="preserve">7.50774431228638</t>
@@ -3584,241 +3584,241 @@
     <t xml:space="preserve">7.57176494598389</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60813856124878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4961051940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58776807785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61250400543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59067916870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41753578186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48155546188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53071737289429</t>
+    <t xml:space="preserve">7.60813903808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49610280990601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58776903152466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61250305175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59068059921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41753625869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48155498504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53071546554565</t>
   </si>
   <si>
     <t xml:space="preserve">7.43760633468628</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47112512588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.523268699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51879835128784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49049282073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66777276992798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72438621520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.776526927948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73183298110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78695583343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81823921203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77950811386108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8316478729248</t>
+    <t xml:space="preserve">7.47112655639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52326965332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51879739761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49049377441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66777372360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72438430786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77652645111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73183393478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78695631027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81824016571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77950716018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83164596557617</t>
   </si>
   <si>
     <t xml:space="preserve">7.88229751586914</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99105167388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.995521068573</t>
+    <t xml:space="preserve">7.99104976654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99552011489868</t>
   </si>
   <si>
     <t xml:space="preserve">8.00147914886475</t>
   </si>
   <si>
-    <t xml:space="preserve">7.918053150177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68267202377319</t>
+    <t xml:space="preserve">7.91805362701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68267154693604</t>
   </si>
   <si>
     <t xml:space="preserve">7.76013851165771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75715923309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76311826705933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85101509094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8629322052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.703528881073</t>
+    <t xml:space="preserve">7.75715732574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76312017440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85101461410522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8629298210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70352792739868</t>
   </si>
   <si>
     <t xml:space="preserve">7.7005500793457</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64989757537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79142236709595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74524259567261</t>
+    <t xml:space="preserve">7.64989900588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79142570495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74524021148682</t>
   </si>
   <si>
     <t xml:space="preserve">7.78844451904297</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57540941238403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42121887207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50836944580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45176076889038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46665716171265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38174057006836</t>
+    <t xml:space="preserve">7.57540893554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42122030258179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50836896896362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45176029205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46665668487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3817400932312</t>
   </si>
   <si>
     <t xml:space="preserve">7.32363986968994</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04207706451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07857608795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26255989074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18360328674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20222663879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34896612167358</t>
+    <t xml:space="preserve">7.04207849502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07857656478882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26256084442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18360280990601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20222520828247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3489670753479</t>
   </si>
   <si>
     <t xml:space="preserve">7.30576324462891</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38695526123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4592080116272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42792320251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55008411407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53816509246826</t>
+    <t xml:space="preserve">7.38695621490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45920896530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42792272567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55008220672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53816604614258</t>
   </si>
   <si>
     <t xml:space="preserve">7.59775686264038</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67373466491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66032648086548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70948696136475</t>
+    <t xml:space="preserve">7.67373418807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66032552719116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7094874382019</t>
   </si>
   <si>
     <t xml:space="preserve">7.7586498260498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80483150482178</t>
+    <t xml:space="preserve">7.80483293533325</t>
   </si>
   <si>
     <t xml:space="preserve">7.83462619781494</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72587394714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7288556098938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72140455245972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5053915977478</t>
+    <t xml:space="preserve">7.72587490081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72885417938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72140502929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50539064407349</t>
   </si>
   <si>
     <t xml:space="preserve">7.49496269226074</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62308263778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6856517791748</t>
+    <t xml:space="preserve">7.62308359146118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68565082550049</t>
   </si>
   <si>
     <t xml:space="preserve">7.69458866119385</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67671203613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76758813858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7705659866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91954183578491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84356546401978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88527917861938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88825941085815</t>
+    <t xml:space="preserve">7.67671346664429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76758766174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77056550979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91954326629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84356594085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88527822494507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88825654983521</t>
   </si>
   <si>
     <t xml:space="preserve">7.85399389266968</t>
@@ -3827,43 +3827,43 @@
     <t xml:space="preserve">8.04915237426758</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12214946746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18621063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21153259277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1504545211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07447147369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22333812713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4404354095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45283985137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47610187530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67304039001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73351669311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8296594619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95216464996338</t>
+    <t xml:space="preserve">8.12215232849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1862096786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21153545379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15045738220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07446956634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22333908081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44043636322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45284080505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47610092163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67303943634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73351764678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82966232299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95216369628906</t>
   </si>
   <si>
     <t xml:space="preserve">8.9025411605835</t>
@@ -3875,61 +3875,61 @@
     <t xml:space="preserve">9.18631935119629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04520797729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9847297668457</t>
+    <t xml:space="preserve">9.04520606994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98473072052002</t>
   </si>
   <si>
     <t xml:space="preserve">9.19407367706299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30882549285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28401279449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16615867614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28866481781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46544361114502</t>
+    <t xml:space="preserve">9.30882453918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28401470184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16615962982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28866577148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46544456481934</t>
   </si>
   <si>
     <t xml:space="preserve">9.48715496063232</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43753147125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55073165893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4080696105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36464977264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51972007751465</t>
+    <t xml:space="preserve">9.43753337860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55073261260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40806865692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36464881896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51971912384033</t>
   </si>
   <si>
     <t xml:space="preserve">9.58174610137939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51196479797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43133068084717</t>
+    <t xml:space="preserve">9.51196384429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43132972717285</t>
   </si>
   <si>
     <t xml:space="preserve">9.61741256713867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88258361816406</t>
+    <t xml:space="preserve">9.88258266448975</t>
   </si>
   <si>
     <t xml:space="preserve">9.72286033630371</t>
@@ -3938,13 +3938,13 @@
     <t xml:space="preserve">9.59880447387695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73836803436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8252067565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8329610824585</t>
+    <t xml:space="preserve">9.73836898803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82520580291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83295822143555</t>
   </si>
   <si>
     <t xml:space="preserve">9.78488826751709</t>
@@ -3953,22 +3953,22 @@
     <t xml:space="preserve">9.81900215148926</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8050479888916</t>
+    <t xml:space="preserve">9.80504608154297</t>
   </si>
   <si>
     <t xml:space="preserve">9.70115184783936</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72751235961914</t>
+    <t xml:space="preserve">9.72751045227051</t>
   </si>
   <si>
     <t xml:space="preserve">9.76782989501953</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7631778717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6375732421875</t>
+    <t xml:space="preserve">9.76317977905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63757228851318</t>
   </si>
   <si>
     <t xml:space="preserve">9.43443012237549</t>
@@ -3977,55 +3977,55 @@
     <t xml:space="preserve">9.55848789215088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59105205535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53367519378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93976020812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14910316467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22973918914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25765037536621</t>
+    <t xml:space="preserve">9.59104824066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53367805480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93975925445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14910411834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22974014282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25765132904053</t>
   </si>
   <si>
     <t xml:space="preserve">9.31192588806152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53057479858398</t>
+    <t xml:space="preserve">9.53057289123535</t>
   </si>
   <si>
     <t xml:space="preserve">9.74456977844238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60655784606934</t>
+    <t xml:space="preserve">9.60655975341797</t>
   </si>
   <si>
     <t xml:space="preserve">9.51041412353516</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46389389038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31968116760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41892528533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30417442321777</t>
+    <t xml:space="preserve">9.46389484405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31968021392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41892433166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30417346954346</t>
   </si>
   <si>
     <t xml:space="preserve">9.45769119262695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34448909759521</t>
+    <t xml:space="preserve">9.34449195861816</t>
   </si>
   <si>
     <t xml:space="preserve">9.17546367645264</t>
@@ -4034,25 +4034,25 @@
     <t xml:space="preserve">9.44373607635498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43908214569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49025630950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53212642669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52126979827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47475051879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62051391601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77713394165039</t>
+    <t xml:space="preserve">9.43908405303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49025726318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53212451934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52127075195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47474956512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62051486968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77713489532471</t>
   </si>
   <si>
     <t xml:space="preserve">9.89033508300781</t>
@@ -4061,163 +4061,163 @@
     <t xml:space="preserve">9.80814838409424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91669940948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83450889587402</t>
+    <t xml:space="preserve">9.91669750213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83451080322266</t>
   </si>
   <si>
     <t xml:space="preserve">9.93220520019531</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1198396682739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0981283187866</t>
+    <t xml:space="preserve">10.1198387145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0981292724609</t>
   </si>
   <si>
     <t xml:space="preserve">10.2035760879517</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2438936233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2888650894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4051666259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.304370880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1617059707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83605861663818</t>
+    <t xml:space="preserve">10.2438955307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2888641357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4051656723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3043699264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1617050170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83606052398682</t>
   </si>
   <si>
     <t xml:space="preserve">10.1524019241333</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4547891616821</t>
+    <t xml:space="preserve">10.4547872543335</t>
   </si>
   <si>
     <t xml:space="preserve">10.7091035842896</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5245714187622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3183259963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4330797195435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3555431365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3028202056885</t>
+    <t xml:space="preserve">10.5245704650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3183269500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4330787658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.355544090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3028192520142</t>
   </si>
   <si>
     <t xml:space="preserve">10.4516878128052</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2237358093262</t>
+    <t xml:space="preserve">10.2237348556519</t>
   </si>
   <si>
     <t xml:space="preserve">10.1074333190918</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2749080657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3105745315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.48890209198</t>
+    <t xml:space="preserve">10.2749061584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3105735778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4889030456543</t>
   </si>
   <si>
     <t xml:space="preserve">10.3307323455811</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2128810882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3384866714478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4439353942871</t>
+    <t xml:space="preserve">10.2128801345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3384857177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4439334869385</t>
   </si>
   <si>
     <t xml:space="preserve">10.322979927063</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4609909057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.409818649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3601980209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6842918395996</t>
+    <t xml:space="preserve">10.460991859436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4098176956177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3601970672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.684289932251</t>
   </si>
   <si>
     <t xml:space="preserve">10.7246084213257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0502548217773</t>
+    <t xml:space="preserve">11.050253868103</t>
   </si>
   <si>
     <t xml:space="preserve">11.2658023834229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7509708404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96631908416748</t>
+    <t xml:space="preserve">10.7509717941284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96631813049316</t>
   </si>
   <si>
     <t xml:space="preserve">10.3943109512329</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5990037918091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5462789535522</t>
+    <t xml:space="preserve">10.5990028381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5462799072266</t>
   </si>
   <si>
     <t xml:space="preserve">10.1601552963257</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0624618530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0205926895142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9011926651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1648082733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86862659454346</t>
+    <t xml:space="preserve">10.0624628067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0205936431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90118789672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1648073196411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86862564086914</t>
   </si>
   <si>
     <t xml:space="preserve">10.2516479492188</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4392805099487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2904167175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1539535522461</t>
+    <t xml:space="preserve">10.439281463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2904148101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1539516448975</t>
   </si>
   <si>
     <t xml:space="preserve">10.3757028579712</t>
@@ -4226,7 +4226,7 @@
     <t xml:space="preserve">10.3074722290039</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4005136489868</t>
+    <t xml:space="preserve">10.4005126953125</t>
   </si>
   <si>
     <t xml:space="preserve">10.4222259521484</t>
@@ -4238,133 +4238,133 @@
     <t xml:space="preserve">10.3803539276123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.282660484314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.713755607605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6966972351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9897775650024</t>
+    <t xml:space="preserve">10.2826633453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7137537002563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6966981887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9897794723511</t>
   </si>
   <si>
     <t xml:space="preserve">11.0099382400513</t>
   </si>
   <si>
-    <t xml:space="preserve">10.971170425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0316467285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8548698425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5292234420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0252456665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0469560623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2020273208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3819046020508</t>
+    <t xml:space="preserve">10.9711694717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0316476821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.854868888855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5292224884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0252475738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0469551086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2020244598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3819055557251</t>
   </si>
   <si>
     <t xml:space="preserve">10.2345886230469</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5447282791138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.474946975708</t>
+    <t xml:space="preserve">10.5447292327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4749479293823</t>
   </si>
   <si>
     <t xml:space="preserve">10.547830581665</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1399974822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2795600891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5602359771729</t>
+    <t xml:space="preserve">10.1399955749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2795610427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5602350234985</t>
   </si>
   <si>
     <t xml:space="preserve">10.5757436752319</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7199573516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8021459579468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6889429092407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7695808410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9728088378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8895978927612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2976551055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3984718322754</t>
+    <t xml:space="preserve">10.7199583053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8021440505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.688943862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7695789337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9728107452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8895969390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2976570129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3984746932983</t>
   </si>
   <si>
     <t xml:space="preserve">11.3552665710449</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3616676330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3600664138794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2800531387329</t>
+    <t xml:space="preserve">11.361665725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3600654602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2800550460815</t>
   </si>
   <si>
     <t xml:space="preserve">11.2592515945435</t>
   </si>
   <si>
-    <t xml:space="preserve">11.408073425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5472955703735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.544093132019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5152893066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2224454879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5935525894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3839225769043</t>
+    <t xml:space="preserve">11.4080753326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5472946166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5440940856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5152883529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2224464416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5935535430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3839235305786</t>
   </si>
   <si>
     <t xml:space="preserve">10.5375461578369</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6047534942627</t>
+    <t xml:space="preserve">10.6047554016113</t>
   </si>
   <si>
     <t xml:space="preserve">10.0862798690796</t>
@@ -4373,100 +4373,100 @@
     <t xml:space="preserve">9.60940933227539</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63661289215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6654167175293</t>
+    <t xml:space="preserve">9.63661193847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66541767120361</t>
   </si>
   <si>
     <t xml:space="preserve">9.32936859130859</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14534282684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3341703414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20134925842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28296089172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06372833251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98371696472168</t>
+    <t xml:space="preserve">9.14534187316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33416843414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20135116577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28296184539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06373119354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98371887207031</t>
   </si>
   <si>
     <t xml:space="preserve">9.19974899291992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6668701171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60606288909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83809566497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98211765289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96131420135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91170597076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89410495758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51644897460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67167186737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81249237060547</t>
+    <t xml:space="preserve">8.66687107086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6060619354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83809471130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98211669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96131324768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91170692443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89410305023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51644992828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67167091369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81249141693115</t>
   </si>
   <si>
     <t xml:space="preserve">9.04452705383301</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94050979614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80129146575928</t>
+    <t xml:space="preserve">8.94051170349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80129051208496</t>
   </si>
   <si>
     <t xml:space="preserve">8.77728748321533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85089778900146</t>
+    <t xml:space="preserve">8.85089874267578</t>
   </si>
   <si>
     <t xml:space="preserve">8.81729412078857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87490177154541</t>
+    <t xml:space="preserve">8.87490272521973</t>
   </si>
   <si>
     <t xml:space="preserve">9.37417602539062</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3629732131958</t>
+    <t xml:space="preserve">9.36297130584717</t>
   </si>
   <si>
     <t xml:space="preserve">9.15654373168945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12133693695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11333751678467</t>
+    <t xml:space="preserve">9.12133884429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11333560943604</t>
   </si>
   <si>
     <t xml:space="preserve">9.16614532470703</t>
@@ -4475,7 +4475,7 @@
     <t xml:space="preserve">9.15814304351807</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1949462890625</t>
+    <t xml:space="preserve">9.19495010375977</t>
   </si>
   <si>
     <t xml:space="preserve">9.14054203033447</t>
@@ -4484,22 +4484,22 @@
     <t xml:space="preserve">9.27336025238037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30536460876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26375770568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35497093200684</t>
+    <t xml:space="preserve">9.30536556243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26375675201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35497379302979</t>
   </si>
   <si>
     <t xml:space="preserve">9.54860019683838</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41738033294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56940269470215</t>
+    <t xml:space="preserve">9.41738128662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56940460205078</t>
   </si>
   <si>
     <t xml:space="preserve">9.92785549163818</t>
@@ -4511,19 +4511,19 @@
     <t xml:space="preserve">10.0062665939331</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85424327850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0014657974243</t>
+    <t xml:space="preserve">9.85424709320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0014667510986</t>
   </si>
   <si>
     <t xml:space="preserve">9.7902364730835</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44778442382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38217639923096</t>
+    <t xml:space="preserve">9.44778728485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38217735290527</t>
   </si>
   <si>
     <t xml:space="preserve">9.6702184677124</t>
@@ -4532,112 +4532,112 @@
     <t xml:space="preserve">9.83344268798828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56300067901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29576396942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26695823669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34697151184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55660343170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47019004821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.449387550354</t>
+    <t xml:space="preserve">9.56300354003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29576301574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26695919036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34697246551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55660247802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47019100189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44938659667969</t>
   </si>
   <si>
     <t xml:space="preserve">9.23335456848145</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08801651000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25117683410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81227588653564</t>
+    <t xml:space="preserve">9.08801555633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25117492675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81227684020996</t>
   </si>
   <si>
     <t xml:space="preserve">8.75680160522461</t>
   </si>
   <si>
-    <t xml:space="preserve">8.771484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79922199249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90038204193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17122554779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41433525085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56444358825684</t>
+    <t xml:space="preserve">8.77148628234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79922294616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90038108825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17122650146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41433620452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56444454193115</t>
   </si>
   <si>
     <t xml:space="preserve">9.56933784484863</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65907573699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61175918579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43881034851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29686069488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53507423400879</t>
+    <t xml:space="preserve">9.65907669067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61176013946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43880939483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29685974121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53507518768311</t>
   </si>
   <si>
     <t xml:space="preserve">9.67865562438965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6802864074707</t>
+    <t xml:space="preserve">9.68028831481934</t>
   </si>
   <si>
     <t xml:space="preserve">9.86628913879395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83692073822021</t>
+    <t xml:space="preserve">9.83692169189453</t>
   </si>
   <si>
     <t xml:space="preserve">10.0783967971802</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0522899627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1844520568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5385103225708</t>
+    <t xml:space="preserve">10.0522909164429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1844530105591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5385093688965</t>
   </si>
   <si>
     <t xml:space="preserve">10.7163534164429</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8126173019409</t>
+    <t xml:space="preserve">10.8126182556152</t>
   </si>
   <si>
     <t xml:space="preserve">10.9839353561401</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0377779006958</t>
+    <t xml:space="preserve">11.0377788543701</t>
   </si>
   <si>
     <t xml:space="preserve">11.1927814483643</t>
@@ -4646,82 +4646,82 @@
     <t xml:space="preserve">11.4293632507324</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6398391723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5957860946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.439151763916</t>
+    <t xml:space="preserve">11.639838218689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5957851409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4391527175903</t>
   </si>
   <si>
     <t xml:space="preserve">11.478310585022</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6479978561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8078947067261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8095264434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7132596969604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4913654327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5745754241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1403636932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6441812515259</t>
+    <t xml:space="preserve">11.6479988098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8078937530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8095245361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7132616043091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4913635253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.57457447052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1403617858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6441841125488</t>
   </si>
   <si>
     <t xml:space="preserve">11.7005310058594</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7535648345947</t>
+    <t xml:space="preserve">11.7535629272461</t>
   </si>
   <si>
     <t xml:space="preserve">11.848030090332</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6160068511963</t>
+    <t xml:space="preserve">11.6160078048706</t>
   </si>
   <si>
     <t xml:space="preserve">11.7635078430176</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8695764541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6756715774536</t>
+    <t xml:space="preserve">11.869574546814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.675669670105</t>
   </si>
   <si>
     <t xml:space="preserve">11.5115995407104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4635362625122</t>
+    <t xml:space="preserve">11.4635372161865</t>
   </si>
   <si>
     <t xml:space="preserve">11.3044357299805</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1337356567383</t>
+    <t xml:space="preserve">11.1337337493896</t>
   </si>
   <si>
     <t xml:space="preserve">11.206654548645</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2083120346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2762603759766</t>
+    <t xml:space="preserve">11.2083129882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2762613296509</t>
   </si>
   <si>
     <t xml:space="preserve">11.446964263916</t>
@@ -4730,40 +4730,40 @@
     <t xml:space="preserve">11.2779178619385</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8138751983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6895790100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7641553878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7724418640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1552782058716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0840167999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.166880607605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2248868942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1933975219727</t>
+    <t xml:space="preserve">10.8138761520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6895771026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7641563415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.772442817688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1552791595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0840158462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1668796539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2248849868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1933965682983</t>
   </si>
   <si>
     <t xml:space="preserve">11.2630033493042</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0094356536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3591270446777</t>
+    <t xml:space="preserve">11.0094366073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3591279983521</t>
   </si>
   <si>
     <t xml:space="preserve">11.4237613677979</t>
@@ -4772,34 +4772,34 @@
     <t xml:space="preserve">11.2497444152832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.466851234436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5546894073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5795469284058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7999668121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9458112716675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9507827758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8728895187378</t>
+    <t xml:space="preserve">11.4668521881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5795478820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7999687194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9458103179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9507818222046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8728904724121</t>
   </si>
   <si>
     <t xml:space="preserve">11.9093494415283</t>
   </si>
   <si>
-    <t xml:space="preserve">11.982271194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8115701675415</t>
+    <t xml:space="preserve">11.9822721481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8115692138672</t>
   </si>
   <si>
     <t xml:space="preserve">11.9789571762085</t>
@@ -4808,28 +4808,28 @@
     <t xml:space="preserve">11.9325513839722</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7502498626709</t>
+    <t xml:space="preserve">11.7502479553223</t>
   </si>
   <si>
     <t xml:space="preserve">11.6640691757202</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7651643753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8430585861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7419624328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7137889862061</t>
+    <t xml:space="preserve">11.7651634216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8430576324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7419633865356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7137899398804</t>
   </si>
   <si>
     <t xml:space="preserve">11.4734811782837</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3939304351807</t>
+    <t xml:space="preserve">11.393928527832</t>
   </si>
   <si>
     <t xml:space="preserve">11.4718236923218</t>
@@ -4838,7 +4838,7 @@
     <t xml:space="preserve">11.3491830825806</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5231990814209</t>
+    <t xml:space="preserve">11.5232000350952</t>
   </si>
   <si>
     <t xml:space="preserve">11.7336769104004</t>
@@ -4847,109 +4847,109 @@
     <t xml:space="preserve">11.8861474990845</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2225799560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2374963760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2855567932129</t>
+    <t xml:space="preserve">12.222580909729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2374954223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2855577468872</t>
   </si>
   <si>
     <t xml:space="preserve">12.1728610992432</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1927490234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8496885299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8911190032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8231706619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6955595016479</t>
+    <t xml:space="preserve">12.1927480697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8496875762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8911209106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8231716156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6955575942993</t>
   </si>
   <si>
     <t xml:space="preserve">11.0690984725952</t>
   </si>
   <si>
-    <t xml:space="preserve">10.931544303894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1039018630981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0757293701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9133129119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0574989318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1320762634277</t>
+    <t xml:space="preserve">10.9315452575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1039037704468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0757284164429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9133138656616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0574998855591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1320781707764</t>
   </si>
   <si>
     <t xml:space="preserve">11.2166013717651</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1221332550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1188182830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0972747802734</t>
+    <t xml:space="preserve">11.1221313476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1188201904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0972738265991</t>
   </si>
   <si>
     <t xml:space="preserve">11.1287622451782</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7094650268555</t>
+    <t xml:space="preserve">10.7094659805298</t>
   </si>
   <si>
     <t xml:space="preserve">10.805588722229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2006750106812</t>
+    <t xml:space="preserve">10.2006759643555</t>
   </si>
   <si>
     <t xml:space="preserve">10.0780344009399</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3008270263672</t>
+    <t xml:space="preserve">10.3008289337158</t>
   </si>
   <si>
     <t xml:space="preserve">10.5185585021973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5303726196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5101194381714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2721338272095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3869066238403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5877590179443</t>
+    <t xml:space="preserve">10.5303716659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.51012134552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2721357345581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3869075775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5877599716187</t>
   </si>
   <si>
     <t xml:space="preserve">10.6957807540894</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8746900558472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8915672302246</t>
+    <t xml:space="preserve">10.8746891021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8915681838989</t>
   </si>
   <si>
     <t xml:space="preserve">11.3354682922363</t>
@@ -4958,91 +4958,91 @@
     <t xml:space="preserve">11.2325115203857</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3371543884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4266090393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6325263977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5329456329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7000408172607</t>
+    <t xml:space="preserve">11.3371572494507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4266109466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6325273513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5329446792603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7000398635864</t>
   </si>
   <si>
     <t xml:space="preserve">11.6477174758911</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7135419845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.721981048584</t>
+    <t xml:space="preserve">11.7135429382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7219800949097</t>
   </si>
   <si>
     <t xml:space="preserve">11.6072082519531</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4637422561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6173362731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6612195968628</t>
+    <t xml:space="preserve">11.4637432098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.617335319519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6612186431885</t>
   </si>
   <si>
     <t xml:space="preserve">11.4890604019165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6004571914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.37766456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1143617630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0029640197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9489555358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4519281387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5143785476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4097328186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1346158981323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.296648979187</t>
+    <t xml:space="preserve">11.6004581451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3776655197144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1143627166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0029668807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9489545822144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4519290924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5143756866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4097347259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1346168518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2966470718384</t>
   </si>
   <si>
     <t xml:space="preserve">11.2628917694092</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1649971008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3050880432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2578268051147</t>
+    <t xml:space="preserve">11.1649961471558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3050870895386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2578277587891</t>
   </si>
   <si>
     <t xml:space="preserve">11.350658416748</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3849763870239</t>
+    <t xml:space="preserve">11.3849773406982</t>
   </si>
   <si>
     <t xml:space="preserve">11.4656238555908</t>
@@ -5051,34 +5051,34 @@
     <t xml:space="preserve">11.4690561294556</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1927967071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3180570602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3386468887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.072681427002</t>
+    <t xml:space="preserve">11.192795753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3180561065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3386459350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0726842880249</t>
   </si>
   <si>
     <t xml:space="preserve">10.6814594268799</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9714469909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2751598358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2408418655396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1396017074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2219667434692</t>
+    <t xml:space="preserve">10.9714460372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2751588821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2408409118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1396036148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2219657897949</t>
   </si>
   <si>
     <t xml:space="preserve">11.2528524398804</t>
@@ -5096,34 +5096,34 @@
     <t xml:space="preserve">11.1962280273438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1344547271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1447505950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9954671859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2099561691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0555238723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9783086776733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1001377105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9354104995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9834575653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0572414398193</t>
+    <t xml:space="preserve">11.1344566345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1447496414185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9954681396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2099552154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0555257797241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.978307723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.100136756897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9354124069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9834566116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0572395324707</t>
   </si>
   <si>
     <t xml:space="preserve">11.3094778060913</t>
@@ -5132,49 +5132,49 @@
     <t xml:space="preserve">11.5068054199219</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5514183044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4707708358765</t>
+    <t xml:space="preserve">11.5514192581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4707717895508</t>
   </si>
   <si>
     <t xml:space="preserve">11.1825008392334</t>
   </si>
   <si>
-    <t xml:space="preserve">11.197943687439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2562847137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3540906906128</t>
+    <t xml:space="preserve">11.1979446411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2562828063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3540916442871</t>
   </si>
   <si>
     <t xml:space="preserve">11.611475944519</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6852588653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.518816947937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4055681228638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5222492218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6166219711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7024202346802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8465518951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7624759674072</t>
+    <t xml:space="preserve">11.6852598190308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5188150405884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4055662155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5222482681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6166229248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7024183273315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8465509414673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7624750137329</t>
   </si>
   <si>
     <t xml:space="preserve">11.6595211029053</t>
@@ -5183,7 +5183,7 @@
     <t xml:space="preserve">11.7796325683594</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7178602218628</t>
+    <t xml:space="preserve">11.7178611755371</t>
   </si>
   <si>
     <t xml:space="preserve">11.9117574691772</t>
@@ -5192,10 +5192,10 @@
     <t xml:space="preserve">11.8190984725952</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7247257232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7744836807251</t>
+    <t xml:space="preserve">11.7247247695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7744846343994</t>
   </si>
   <si>
     <t xml:space="preserve">11.7350196838379</t>
@@ -5204,97 +5204,97 @@
     <t xml:space="preserve">11.6904058456421</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0696201324463</t>
+    <t xml:space="preserve">12.0696182250977</t>
   </si>
   <si>
     <t xml:space="preserve">12.1193809509277</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0524597167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.023289680481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9512243270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9889717102051</t>
+    <t xml:space="preserve">12.0524606704712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0232915878296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9512233734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9889726638794</t>
   </si>
   <si>
     <t xml:space="preserve">12.0404510498047</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0884952545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1090860366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0747671127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1210966110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1434020996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2669486999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3167085647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3270053863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.254937171936</t>
+    <t xml:space="preserve">12.0884943008423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1090850830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0747680664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1210956573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1434030532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2669477462769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3167095184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3270034790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2549362182617</t>
   </si>
   <si>
     <t xml:space="preserve">12.4728555679321</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5277633666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.726806640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6907739639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6461601257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6959209442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.91383934021</t>
+    <t xml:space="preserve">12.5277652740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7268095016479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6907749176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6461620330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6959228515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9138422012329</t>
   </si>
   <si>
     <t xml:space="preserve">12.9567394256592</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9738960266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1866674423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1574983596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0511655807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3353023529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2795209884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0877714157104</t>
+    <t xml:space="preserve">12.9738969802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1866693496704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1574993133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0511636734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.335301399231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2795190811157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0877704620361</t>
   </si>
   <si>
     <t xml:space="preserve">13.2812633514404</t>
@@ -5303,25 +5303,25 @@
     <t xml:space="preserve">13.2638330459595</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2289695739746</t>
+    <t xml:space="preserve">13.2289686203003</t>
   </si>
   <si>
     <t xml:space="preserve">13.3980560302734</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4398918151855</t>
+    <t xml:space="preserve">13.4398927688599</t>
   </si>
   <si>
     <t xml:space="preserve">13.2969522476196</t>
   </si>
   <si>
-    <t xml:space="preserve">12.986665725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8367519378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6362895965576</t>
+    <t xml:space="preserve">12.9866647720337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8367528915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6362886428833</t>
   </si>
   <si>
     <t xml:space="preserve">12.5857362747192</t>
@@ -5336,61 +5336,61 @@
     <t xml:space="preserve">13.2045631408691</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1487846374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3318157196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5078763961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4921865463257</t>
+    <t xml:space="preserve">13.1487827301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3318147659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5078754425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4921884536743</t>
   </si>
   <si>
     <t xml:space="preserve">13.5375099182129</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6316423416138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4677829742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4207181930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.453839302063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4276914596558</t>
+    <t xml:space="preserve">13.6316432952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4677839279175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4207191467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4538383483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4276905059814</t>
   </si>
   <si>
     <t xml:space="preserve">13.4939317703247</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5183372497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3910837173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4468650817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.687424659729</t>
+    <t xml:space="preserve">13.5183353424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3910856246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4468660354614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6874256134033</t>
   </si>
   <si>
     <t xml:space="preserve">13.3928279876709</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4259490966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0842838287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9221687316895</t>
+    <t xml:space="preserve">13.4259481430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0842847824097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9221706390381</t>
   </si>
   <si>
     <t xml:space="preserve">13.0180435180664</t>
@@ -5399,13 +5399,13 @@
     <t xml:space="preserve">13.0720825195312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2760343551636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2917213439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.239426612854</t>
+    <t xml:space="preserve">13.2760334014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2917222976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2394275665283</t>
   </si>
   <si>
     <t xml:space="preserve">12.9518032073975</t>
@@ -5414,7 +5414,7 @@
     <t xml:space="preserve">13.2843294143677</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2188282012939</t>
+    <t xml:space="preserve">13.2188272476196</t>
   </si>
   <si>
     <t xml:space="preserve">13.0329465866089</t>
@@ -5423,7 +5423,7 @@
     <t xml:space="preserve">13.2205972671509</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3374376296997</t>
+    <t xml:space="preserve">13.3374366760254</t>
   </si>
   <si>
     <t xml:space="preserve">13.3038024902344</t>
@@ -5435,16 +5435,16 @@
     <t xml:space="preserve">13.3728437423706</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4259519577026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.49853515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2418422698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3569107055664</t>
+    <t xml:space="preserve">13.425952911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4985342025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2418403625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3569116592407</t>
   </si>
   <si>
     <t xml:space="preserve">13.1993541717529</t>
@@ -5453,85 +5453,85 @@
     <t xml:space="preserve">13.0736637115479</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2860994338989</t>
+    <t xml:space="preserve">13.2860975265503</t>
   </si>
   <si>
     <t xml:space="preserve">13.2630853652954</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1037588119507</t>
+    <t xml:space="preserve">13.1037578582764</t>
   </si>
   <si>
     <t xml:space="preserve">13.0559606552124</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1427049636841</t>
+    <t xml:space="preserve">13.1427040100098</t>
   </si>
   <si>
     <t xml:space="preserve">13.1126098632812</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2701644897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3002605438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4578170776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4542760848999</t>
+    <t xml:space="preserve">13.2701663970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3002614974976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.457818031311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4542779922485</t>
   </si>
   <si>
     <t xml:space="preserve">13.5321702957153</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6631727218628</t>
+    <t xml:space="preserve">13.6631717681885</t>
   </si>
   <si>
     <t xml:space="preserve">13.5941305160522</t>
   </si>
   <si>
-    <t xml:space="preserve">13.585277557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7693910598755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6649436950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7375249862671</t>
+    <t xml:space="preserve">13.5852794647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7693891525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.664942741394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7375268936157</t>
   </si>
   <si>
     <t xml:space="preserve">13.7552270889282</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3480606079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2099771499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1745710372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.11083984375</t>
+    <t xml:space="preserve">13.3480587005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2099761962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1745700836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1108388900757</t>
   </si>
   <si>
     <t xml:space="preserve">13.3144235610962</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2737073898315</t>
+    <t xml:space="preserve">13.2737064361572</t>
   </si>
   <si>
     <t xml:space="preserve">13.2170572280884</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9692153930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9302673339844</t>
+    <t xml:space="preserve">12.9692163467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9302682876587</t>
   </si>
   <si>
     <t xml:space="preserve">12.7904148101807</t>
@@ -5546,43 +5546,43 @@
     <t xml:space="preserve">12.8258209228516</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8930921554565</t>
+    <t xml:space="preserve">12.8930931091309</t>
   </si>
   <si>
     <t xml:space="preserve">13.0612716674805</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2064361572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0984468460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.910795211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7231435775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9249572753906</t>
+    <t xml:space="preserve">13.2064371109009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0984477996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9107971191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7231426239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9249591827393</t>
   </si>
   <si>
     <t xml:space="preserve">12.7196035385132</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7160634994507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6523323059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7797918319702</t>
+    <t xml:space="preserve">12.7160625457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6523313522339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7797927856445</t>
   </si>
   <si>
     <t xml:space="preserve">12.8081178665161</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8364429473877</t>
+    <t xml:space="preserve">12.836443901062</t>
   </si>
   <si>
     <t xml:space="preserve">12.9267282485962</t>
@@ -5591,10 +5591,10 @@
     <t xml:space="preserve">12.5284109115601</t>
   </si>
   <si>
-    <t xml:space="preserve">12.542573928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5089359283447</t>
+    <t xml:space="preserve">12.5425729751587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5089378356934</t>
   </si>
   <si>
     <t xml:space="preserve">12.6594123840332</t>
@@ -5606,22 +5606,22 @@
     <t xml:space="preserve">12.6186962127686</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6151542663574</t>
+    <t xml:space="preserve">12.6151533126831</t>
   </si>
   <si>
     <t xml:space="preserve">12.7284545898438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7072105407715</t>
+    <t xml:space="preserve">12.7072114944458</t>
   </si>
   <si>
     <t xml:space="preserve">12.6116151809692</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6824264526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7355346679688</t>
+    <t xml:space="preserve">12.682427406311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7355356216431</t>
   </si>
   <si>
     <t xml:space="preserve">12.8417539596558</t>
@@ -5630,43 +5630,43 @@
     <t xml:space="preserve">12.9479713439941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.951512336731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0134716033936</t>
+    <t xml:space="preserve">12.9515132904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0134725570679</t>
   </si>
   <si>
     <t xml:space="preserve">12.8860111236572</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0046224594116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.257773399353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8541450500488</t>
+    <t xml:space="preserve">13.0046215057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2577753067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8541460037231</t>
   </si>
   <si>
     <t xml:space="preserve">12.8399839401245</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7949810028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1009950637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.893985748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9245862960815</t>
+    <t xml:space="preserve">12.7949819564819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1009960174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8939867019653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9245872497559</t>
   </si>
   <si>
     <t xml:space="preserve">12.9191865921021</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0991945266724</t>
+    <t xml:space="preserve">13.0991954803467</t>
   </si>
   <si>
     <t xml:space="preserve">13.0955944061279</t>
@@ -5675,19 +5675,19 @@
     <t xml:space="preserve">13.1135950088501</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1837997436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5276136398315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6590213775635</t>
+    <t xml:space="preserve">13.1837978363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5276155471802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6590194702148</t>
   </si>
   <si>
     <t xml:space="preserve">13.8138275146484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9578351974487</t>
+    <t xml:space="preserve">13.9578342437744</t>
   </si>
   <si>
     <t xml:space="preserve">13.9632339477539</t>
@@ -5702,7 +5702,7 @@
     <t xml:space="preserve">13.786826133728</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1576414108276</t>
+    <t xml:space="preserve">14.1576433181763</t>
   </si>
   <si>
     <t xml:space="preserve">13.9812355041504</t>
@@ -5714,10 +5714,10 @@
     <t xml:space="preserve">13.7976264953613</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7076225280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7328233718872</t>
+    <t xml:space="preserve">13.7076234817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7328252792358</t>
   </si>
   <si>
     <t xml:space="preserve">13.8066272735596</t>
@@ -5726,10 +5726,10 @@
     <t xml:space="preserve">13.968635559082</t>
   </si>
   <si>
-    <t xml:space="preserve">13.71302318573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7292232513428</t>
+    <t xml:space="preserve">13.7130212783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7292242050171</t>
   </si>
   <si>
     <t xml:space="preserve">13.7346239089966</t>
@@ -5738,10 +5738,10 @@
     <t xml:space="preserve">13.7472248077393</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6230192184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3422069549561</t>
+    <t xml:space="preserve">13.6230182647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3422060012817</t>
   </si>
   <si>
     <t xml:space="preserve">13.2378015518188</t>
@@ -5753,13 +5753,13 @@
     <t xml:space="preserve">13.47181224823</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4430103302002</t>
+    <t xml:space="preserve">13.4430112838745</t>
   </si>
   <si>
     <t xml:space="preserve">13.5294141769409</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6626205444336</t>
+    <t xml:space="preserve">13.6626214981079</t>
   </si>
   <si>
     <t xml:space="preserve">13.714822769165</t>
@@ -5777,19 +5777,19 @@
     <t xml:space="preserve">13.4024887084961</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3366651535034</t>
+    <t xml:space="preserve">13.3366641998291</t>
   </si>
   <si>
     <t xml:space="preserve">13.2105016708374</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2452430725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1501636505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3311786651611</t>
+    <t xml:space="preserve">13.2452421188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1501626968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3311796188354</t>
   </si>
   <si>
     <t xml:space="preserve">13.3092374801636</t>
@@ -5798,10 +5798,10 @@
     <t xml:space="preserve">13.1519918441772</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1355361938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2525568008423</t>
+    <t xml:space="preserve">13.1355352401733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.252555847168</t>
   </si>
   <si>
     <t xml:space="preserve">13.1812467575073</t>
@@ -5810,7 +5810,7 @@
     <t xml:space="preserve">12.8119010925293</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7497339248657</t>
+    <t xml:space="preserve">12.7497329711914</t>
   </si>
   <si>
     <t xml:space="preserve">12.8630971908569</t>
@@ -5828,28 +5828,28 @@
     <t xml:space="preserve">12.7460775375366</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5412912368774</t>
+    <t xml:space="preserve">12.5412921905518</t>
   </si>
   <si>
     <t xml:space="preserve">12.3493051528931</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3730754852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6016292572021</t>
+    <t xml:space="preserve">12.3730745315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6016302108765</t>
   </si>
   <si>
     <t xml:space="preserve">12.7058515548706</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9197788238525</t>
+    <t xml:space="preserve">12.9197797775269</t>
   </si>
   <si>
     <t xml:space="preserve">12.7405920028687</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9124641418457</t>
+    <t xml:space="preserve">12.9124660491943</t>
   </si>
   <si>
     <t xml:space="preserve">13.0148582458496</t>
@@ -5858,13 +5858,13 @@
     <t xml:space="preserve">13.0185146331787</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0861682891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1227369308472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2854681015015</t>
+    <t xml:space="preserve">13.0861673355103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1227359771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2854671478271</t>
   </si>
   <si>
     <t xml:space="preserve">13.2818117141724</t>
@@ -5879,25 +5879,25 @@
     <t xml:space="preserve">13.2141580581665</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0751981735229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9014959335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9636611938477</t>
+    <t xml:space="preserve">13.0751972198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9014949798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.963662147522</t>
   </si>
   <si>
     <t xml:space="preserve">12.9819469451904</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0678825378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0166873931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8100719451904</t>
+    <t xml:space="preserve">13.0678834915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0166864395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8100728988647</t>
   </si>
   <si>
     <t xml:space="preserve">12.9216079711914</t>
@@ -5906,25 +5906,25 @@
     <t xml:space="preserve">13.064227104187</t>
   </si>
   <si>
-    <t xml:space="preserve">12.872239112854</t>
+    <t xml:space="preserve">12.8722410202026</t>
   </si>
   <si>
     <t xml:space="preserve">12.8649253845215</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8228712081909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8521270751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8173866271973</t>
+    <t xml:space="preserve">12.8228731155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.852126121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8173875808716</t>
   </si>
   <si>
     <t xml:space="preserve">13.3750619888306</t>
   </si>
   <si>
-    <t xml:space="preserve">13.384204864502</t>
+    <t xml:space="preserve">13.3842039108276</t>
   </si>
   <si>
     <t xml:space="preserve">13.5286512374878</t>
@@ -5933,10 +5933,10 @@
     <t xml:space="preserve">13.3019237518311</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9965734481812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7387628555298</t>
+    <t xml:space="preserve">12.9965744018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7387638092041</t>
   </si>
   <si>
     <t xml:space="preserve">12.7277927398682</t>
@@ -5945,31 +5945,31 @@
     <t xml:space="preserve">13.0441131591797</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2159872055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0971384048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2543840408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3640899658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2507266998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2708406448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1666202545166</t>
+    <t xml:space="preserve">13.2159881591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0971393585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2543849945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3640918731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2507286071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2708396911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1666193008423</t>
   </si>
   <si>
     <t xml:space="preserve">13.3458061218262</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4719686508179</t>
+    <t xml:space="preserve">13.4719696044922</t>
   </si>
   <si>
     <t xml:space="preserve">13.4408855438232</t>
@@ -5981,25 +5981,25 @@
     <t xml:space="preserve">13.5359649658203</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4152870178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4390573501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1007947921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9490356445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5815162658691</t>
+    <t xml:space="preserve">13.4152860641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4390554428101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1007957458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9490337371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5815172195435</t>
   </si>
   <si>
     <t xml:space="preserve">12.5540904998779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6619691848755</t>
+    <t xml:space="preserve">12.6619701385498</t>
   </si>
   <si>
     <t xml:space="preserve">12.8064155578613</t>
@@ -6008,7 +6008,7 @@
     <t xml:space="preserve">12.9033231735229</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0002307891846</t>
+    <t xml:space="preserve">13.0002317428589</t>
   </si>
   <si>
     <t xml:space="preserve">13.0276584625244</t>
@@ -6017,13 +6017,13 @@
     <t xml:space="preserve">13.0569114685059</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1220483779907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1778783798218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0234146118164</t>
+    <t xml:space="preserve">13.122049331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1778793334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0234155654907</t>
   </si>
   <si>
     <t xml:space="preserve">12.6270170211792</t>
@@ -6032,25 +6032,25 @@
     <t xml:space="preserve">12.7200689315796</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7312345504761</t>
+    <t xml:space="preserve">12.7312335968018</t>
   </si>
   <si>
     <t xml:space="preserve">12.9247808456421</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1369371414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1257696151733</t>
+    <t xml:space="preserve">13.1369361877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1257705688477</t>
   </si>
   <si>
     <t xml:space="preserve">13.3286228179932</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4961137771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2076559066772</t>
+    <t xml:space="preserve">13.4961128234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2076549530029</t>
   </si>
   <si>
     <t xml:space="preserve">13.181601524353</t>
@@ -6059,10 +6059,10 @@
     <t xml:space="preserve">13.2709302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3267593383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3565378189087</t>
+    <t xml:space="preserve">13.3267602920532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3565368652344</t>
   </si>
   <si>
     <t xml:space="preserve">12.9936370849609</t>
@@ -6071,16 +6071,16 @@
     <t xml:space="preserve">13.0606355667114</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2653465270996</t>
+    <t xml:space="preserve">13.2653474807739</t>
   </si>
   <si>
     <t xml:space="preserve">13.2858180999756</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1946277618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2374315261841</t>
+    <t xml:space="preserve">13.1946287155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2374324798584</t>
   </si>
   <si>
     <t xml:space="preserve">13.4253950119019</t>
@@ -6089,34 +6089,34 @@
     <t xml:space="preserve">13.0196924209595</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0383014678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0587739944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0476083755493</t>
+    <t xml:space="preserve">13.0383024215698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0587749481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.047607421875</t>
   </si>
   <si>
     <t xml:space="preserve">13.1350755691528</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0308570861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1108827590942</t>
+    <t xml:space="preserve">13.0308589935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1108818054199</t>
   </si>
   <si>
     <t xml:space="preserve">12.9620008468628</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0364427566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8522005081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7647323608398</t>
+    <t xml:space="preserve">13.0364418029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.852201461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7647333145142</t>
   </si>
   <si>
     <t xml:space="preserve">13.1164646148682</t>
@@ -6125,16 +6125,16 @@
     <t xml:space="preserve">13.1638307571411</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0103673934937</t>
+    <t xml:space="preserve">13.0103664398193</t>
   </si>
   <si>
     <t xml:space="preserve">13.0046825408936</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0861511230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1827783584595</t>
+    <t xml:space="preserve">13.0861520767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1827774047852</t>
   </si>
   <si>
     <t xml:space="preserve">13.0160503387451</t>
@@ -6146,19 +6146,19 @@
     <t xml:space="preserve">12.7091226577759</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7166996002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.699649810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6390218734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7602777481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7754344940186</t>
+    <t xml:space="preserve">12.716700553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6996488571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6390209197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7602767944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7754335403442</t>
   </si>
   <si>
     <t xml:space="preserve">12.7451200485229</t>
@@ -6176,22 +6176,22 @@
     <t xml:space="preserve">12.6693344116211</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6181802749634</t>
+    <t xml:space="preserve">12.6181793212891</t>
   </si>
   <si>
     <t xml:space="preserve">12.5954446792603</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4097719192505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1104211807251</t>
+    <t xml:space="preserve">12.4097728729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1104221343994</t>
   </si>
   <si>
     <t xml:space="preserve">12.2127313613892</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1085262298584</t>
+    <t xml:space="preserve">12.1085271835327</t>
   </si>
   <si>
     <t xml:space="preserve">12.0535831451416</t>
@@ -6203,7 +6203,7 @@
     <t xml:space="preserve">12.2714643478394</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4002981185913</t>
+    <t xml:space="preserve">12.4002990722656</t>
   </si>
   <si>
     <t xml:space="preserve">12.7526979446411</t>
@@ -6212,13 +6212,13 @@
     <t xml:space="preserve">12.9213199615479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.94215965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9516344070435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0141553878784</t>
+    <t xml:space="preserve">12.9421606063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9516334533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0141563415527</t>
   </si>
   <si>
     <t xml:space="preserve">13.0198402404785</t>
@@ -6227,10 +6227,10 @@
     <t xml:space="preserve">13.1410961151123</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2471952438354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2093029022217</t>
+    <t xml:space="preserve">13.2471942901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2093019485474</t>
   </si>
   <si>
     <t xml:space="preserve">13.3495044708252</t>
@@ -6239,7 +6239,7 @@
     <t xml:space="preserve">13.160041809082</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0027875900269</t>
+    <t xml:space="preserve">13.0027885437012</t>
   </si>
   <si>
     <t xml:space="preserve">12.9554224014282</t>
@@ -6257,46 +6257,46 @@
     <t xml:space="preserve">12.7242794036865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7413291931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9175310134888</t>
+    <t xml:space="preserve">12.7413311004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9175300598145</t>
   </si>
   <si>
     <t xml:space="preserve">12.9781579971313</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9118461608887</t>
+    <t xml:space="preserve">12.911847114563</t>
   </si>
   <si>
     <t xml:space="preserve">13.0577325820923</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0842571258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1316242218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1543579101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3210859298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2869806289673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2547721862793</t>
+    <t xml:space="preserve">13.0842580795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1316232681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1543569564819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3210849761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2869825363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2547731399536</t>
   </si>
   <si>
     <t xml:space="preserve">13.2983493804932</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3343467712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3513984680176</t>
+    <t xml:space="preserve">13.3343477249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3513994216919</t>
   </si>
   <si>
     <t xml:space="preserve">13.3135061264038</t>
@@ -6311,16 +6311,16 @@
     <t xml:space="preserve">13.2964553833008</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3930807113647</t>
+    <t xml:space="preserve">13.3930797576904</t>
   </si>
   <si>
     <t xml:space="preserve">13.521915435791</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3324537277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1240434646606</t>
+    <t xml:space="preserve">13.3324527740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.124044418335</t>
   </si>
   <si>
     <t xml:space="preserve">13.1202554702759</t>
@@ -6329,10 +6329,10 @@
     <t xml:space="preserve">12.5651302337646</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4514532089233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5196590423584</t>
+    <t xml:space="preserve">12.4514541625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5196599960327</t>
   </si>
   <si>
     <t xml:space="preserve">12.8227996826172</t>
@@ -6344,22 +6344,22 @@
     <t xml:space="preserve">12.9307928085327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9364767074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9952096939087</t>
+    <t xml:space="preserve">12.9364757537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.995210647583</t>
   </si>
   <si>
     <t xml:space="preserve">13.2850875854492</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4044485092163</t>
+    <t xml:space="preserve">13.404447555542</t>
   </si>
   <si>
     <t xml:space="preserve">13.5806484222412</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6848526000977</t>
+    <t xml:space="preserve">13.6848516464233</t>
   </si>
   <si>
     <t xml:space="preserve">13.618540763855</t>
@@ -6398,28 +6398,28 @@
     <t xml:space="preserve">11.6113328933716</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4628658294678</t>
+    <t xml:space="preserve">11.4628667831421</t>
   </si>
   <si>
     <t xml:space="preserve">10.8304319381714</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1427927017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0849475860596</t>
+    <t xml:space="preserve">11.1427917480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0849485397339</t>
   </si>
   <si>
     <t xml:space="preserve">11.3548889160156</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5303516387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7366638183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8311424255371</t>
+    <t xml:space="preserve">11.5303506851196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7366628646851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8311433792114</t>
   </si>
   <si>
     <t xml:space="preserve">11.952615737915</t>
@@ -6434,13 +6434,13 @@
     <t xml:space="preserve">12.2996845245361</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2611207962036</t>
+    <t xml:space="preserve">12.2611217498779</t>
   </si>
   <si>
     <t xml:space="preserve">12.2302703857422</t>
   </si>
   <si>
-    <t xml:space="preserve">12.243766784668</t>
+    <t xml:space="preserve">12.2437677383423</t>
   </si>
   <si>
     <t xml:space="preserve">12.2013483047485</t>
@@ -6455,7 +6455,7 @@
     <t xml:space="preserve">12.1955633163452</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2881155014038</t>
+    <t xml:space="preserve">12.2881145477295</t>
   </si>
   <si>
     <t xml:space="preserve">12.5329904556274</t>
@@ -6464,7 +6464,7 @@
     <t xml:space="preserve">12.7913627624512</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9899625778198</t>
+    <t xml:space="preserve">12.9899616241455</t>
   </si>
   <si>
     <t xml:space="preserve">12.9629688262939</t>
@@ -6473,7 +6473,7 @@
     <t xml:space="preserve">12.8453512191772</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9109086990356</t>
+    <t xml:space="preserve">12.9109077453613</t>
   </si>
   <si>
     <t xml:space="preserve">12.8480339050293</t>
@@ -6783,6 +6783,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.8439998626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8999996185303</t>
   </si>
 </sst>
 </file>
@@ -71913,7 +71916,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6493287037</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>8408418</v>
@@ -71934,6 +71937,32 @@
         <v>2245</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6511921296</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>7832427</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>15.0080003738403</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>14.8819999694824</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>14.9139995574951</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>14.8999996185303</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>2257</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ENI.MI.xlsx
+++ b/data/ENI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2260" uniqueCount="2260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2261" uniqueCount="2261">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26820611953735</t>
+    <t xml:space="preserve">7.26820802688599</t>
   </si>
   <si>
     <t xml:space="preserve">ENI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3331503868103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12749671936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07337856292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87313747406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84607791900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8623161315918</t>
+    <t xml:space="preserve">7.33314943313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12749767303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07337760925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87313795089722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84607839584351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86231327056885</t>
   </si>
   <si>
     <t xml:space="preserve">6.94349145889282</t>
@@ -71,283 +71,283 @@
     <t xml:space="preserve">6.79195833206177</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7161922454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8081955909729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58089256286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0192608833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93266820907593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07879161834717</t>
+    <t xml:space="preserve">6.71619081497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80819368362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58089399337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01925945281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93266868591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07879114151001</t>
   </si>
   <si>
     <t xml:space="preserve">7.11126375198364</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18702745437622</t>
+    <t xml:space="preserve">7.18702793121338</t>
   </si>
   <si>
     <t xml:space="preserve">6.77031087875366</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74325180053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89478254318237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78113555908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53759860992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27782678604126</t>
+    <t xml:space="preserve">6.74325084686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89478492736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78113460540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53759813308716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27782535552979</t>
   </si>
   <si>
     <t xml:space="preserve">6.29406213760376</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91522645950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31029653549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46183156967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41312456130981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61877679824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47806739807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45100784301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6837215423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37524032592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54300880432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87854909896851</t>
+    <t xml:space="preserve">5.91522789001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3102970123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46183013916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41312265396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61877727508545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47806644439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4510064125061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68372106552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37524223327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54301071166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87854862213135</t>
   </si>
   <si>
     <t xml:space="preserve">7.00843477249146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22491264343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27902984619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37644529342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32773733139038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35479927062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1707935333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25197172164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00302267074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20867681503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24656105041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14373397827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23573589324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36562299728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43056583404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46845149993896</t>
+    <t xml:space="preserve">7.2249116897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27903079986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37644624710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32773780822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35479688644409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17079544067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25197219848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00302410125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20867443084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24656057357788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14373445510864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23573637008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3656210899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43056392669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46844911575317</t>
   </si>
   <si>
     <t xml:space="preserve">7.28985452651978</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11667490005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31691551208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19785165786743</t>
+    <t xml:space="preserve">7.1166729927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3169150352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19785213470459</t>
   </si>
   <si>
     <t xml:space="preserve">6.92184448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90560865402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73242664337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80278253555298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66748523712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95431613922119</t>
+    <t xml:space="preserve">6.90561008453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73242855072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80278062820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66748428344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95431804656982</t>
   </si>
   <si>
     <t xml:space="preserve">6.97596311569214</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01384592056274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2952675819397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4251537322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30609083175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39809322357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51715469360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61457061767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65786552429199</t>
+    <t xml:space="preserve">7.01384782791138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29526662826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42515325546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30609226226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39809274673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51715707778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61456966400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65786695480347</t>
   </si>
   <si>
     <t xml:space="preserve">7.61998224258423</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6524543762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7228102684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79316329956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68492603302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54962682723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39268064498901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24114894866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34397411346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4089183807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13832092285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22407865524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44721603393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70382642745972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74287462234497</t>
+    <t xml:space="preserve">7.65245294570923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72280693054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79316473007202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6849250793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54962778091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39267921447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24114751815796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34397554397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40891790390015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13832139968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22407817840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44721794128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70382690429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74287366867065</t>
   </si>
   <si>
     <t xml:space="preserve">7.71498155593872</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77634286880493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65919780731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55320596694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54762983322144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48626470565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68151044845581</t>
+    <t xml:space="preserve">7.77634334564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65919637680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5532054901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54762744903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48626756668091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68151330947876</t>
   </si>
   <si>
     <t xml:space="preserve">7.86002206802368</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88233470916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84328556060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50299978256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36353921890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45837593078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38027429580688</t>
+    <t xml:space="preserve">7.88233327865601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84328460693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50299882888794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36354112625122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4583740234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38027667999268</t>
   </si>
   <si>
     <t xml:space="preserve">7.67035388946533</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89907026290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99948167800903</t>
+    <t xml:space="preserve">7.89906978607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99948215484619</t>
   </si>
   <si>
     <t xml:space="preserve">7.8767557144165</t>
@@ -356,76 +356,76 @@
     <t xml:space="preserve">8.1333646774292</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3858528137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62014770507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97717094421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09989547729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26724624633789</t>
+    <t xml:space="preserve">7.38585472106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6201491355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97716760635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09989643096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26724720001221</t>
   </si>
   <si>
     <t xml:space="preserve">8.03853130340576</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88791465759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93253993988037</t>
+    <t xml:space="preserve">7.88791513442993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93254327774048</t>
   </si>
   <si>
     <t xml:space="preserve">8.08873653411865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18356990814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26166915893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16125583648682</t>
+    <t xml:space="preserve">8.18357086181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26166820526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16125965118408</t>
   </si>
   <si>
     <t xml:space="preserve">8.31187534332275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21146202087402</t>
+    <t xml:space="preserve">8.21146297454834</t>
   </si>
   <si>
     <t xml:space="preserve">8.12220764160156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09431648254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01621723175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97158908843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93812084197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82654905319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83212995529175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62572622299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63130569458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48068618774414</t>
+    <t xml:space="preserve">8.094313621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01622009277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97159194946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93811845779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82655143737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83212900161743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62572717666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6313042640686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4806866645813</t>
   </si>
   <si>
     <t xml:space="preserve">7.32449150085449</t>
@@ -437,214 +437,214 @@
     <t xml:space="preserve">7.39143323898315</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56994199752808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55878686904907</t>
+    <t xml:space="preserve">7.56994247436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55878400802612</t>
   </si>
   <si>
     <t xml:space="preserve">7.53647184371948</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64246129989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66477584838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51415777206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49742221832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59783554077148</t>
+    <t xml:space="preserve">7.64245986938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6647777557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51415729522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49742269515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59783363342285</t>
   </si>
   <si>
     <t xml:space="preserve">7.59225606918335</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65361976623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56436491012573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31333446502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33564901351929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36912059783936</t>
+    <t xml:space="preserve">7.65362024307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56436586380005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3133339881897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33564758300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36911725997925</t>
   </si>
   <si>
     <t xml:space="preserve">7.2017674446106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31114625930786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1787371635437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28236198425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25357627868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12116956710815</t>
+    <t xml:space="preserve">7.31114721298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17873907089233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28236150741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25357675552368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12117147445679</t>
   </si>
   <si>
     <t xml:space="preserve">7.08662891387939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10965824127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43779706954956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38022613525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42052507400513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46657943725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63928365707397</t>
+    <t xml:space="preserve">7.1096568107605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43779420852661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38022804260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42052412033081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4665789604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6392822265625</t>
   </si>
   <si>
     <t xml:space="preserve">7.65079784393311</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82925891876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67958211898804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62776899337769</t>
+    <t xml:space="preserve">7.82925701141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6795802116394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.627769947052</t>
   </si>
   <si>
     <t xml:space="preserve">7.57595729827881</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72563505172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66231155395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80047416687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8235011100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90409564971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92712354660034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87531185150146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79471683502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91561031341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77744817733765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60474395751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48384809494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37446975708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31690216064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2478199005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35144281387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39749717712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36871242523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33992910385132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22479343414307</t>
+    <t xml:space="preserve">7.72563600540161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66230916976929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80047178268433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82350015640259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90409374237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92712593078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87531232833862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79471731185913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91560888290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77744579315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60474061965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48384761810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37447071075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31690120697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24781894683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35144329071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39749670028687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36871290206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33993005752563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22479248046875</t>
   </si>
   <si>
     <t xml:space="preserve">7.05784511566162</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1960072517395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14995527267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12692832946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23630666732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24206209182739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2881178855896</t>
+    <t xml:space="preserve">7.19600820541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14995431900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12692737579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23630619049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24206447601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28811740875244</t>
   </si>
   <si>
     <t xml:space="preserve">7.56444358825684</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83501243591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88106870651245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03650093078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11709976196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19193649291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20344924926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50856018066406</t>
+    <t xml:space="preserve">7.8350133895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88106632232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03650283813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11709785461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19193553924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20345115661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50856113433838</t>
   </si>
   <si>
     <t xml:space="preserve">8.59491348266602</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56612968444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61794090270996</t>
+    <t xml:space="preserve">8.56612777709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61793899536133</t>
   </si>
   <si>
     <t xml:space="preserve">8.6639928817749</t>
@@ -659,112 +659,112 @@
     <t xml:space="preserve">8.73307609558105</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83094024658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81367015838623</t>
+    <t xml:space="preserve">8.83094310760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81367301940918</t>
   </si>
   <si>
     <t xml:space="preserve">8.88851070404053</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90577983856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00364685058594</t>
+    <t xml:space="preserve">8.90578079223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00364780426025</t>
   </si>
   <si>
     <t xml:space="preserve">8.99788951873779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03243160247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04970073699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85972690582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95183563232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94607639312744</t>
+    <t xml:space="preserve">9.03242969512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0496997833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85972499847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95183181762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94607925415039</t>
   </si>
   <si>
     <t xml:space="preserve">8.90002346038818</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02091503143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86548328399658</t>
+    <t xml:space="preserve">9.02091693878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86548233032227</t>
   </si>
   <si>
     <t xml:space="preserve">8.96334838867188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92880821228027</t>
+    <t xml:space="preserve">8.92880535125732</t>
   </si>
   <si>
     <t xml:space="preserve">8.83669853210449</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60642433166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50280475616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2840461730957</t>
+    <t xml:space="preserve">8.60642623901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50280380249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28404426574707</t>
   </si>
   <si>
     <t xml:space="preserve">8.18042278289795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13436698913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15163707733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36464214324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17466640472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14012336730957</t>
+    <t xml:space="preserve">8.13436889648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15163803100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36464023590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17466735839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14012241363525</t>
   </si>
   <si>
     <t xml:space="preserve">8.26677417755127</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28980159759521</t>
+    <t xml:space="preserve">8.28979969024658</t>
   </si>
   <si>
     <t xml:space="preserve">8.37039661407471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27828693389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12861251831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39342594146729</t>
+    <t xml:space="preserve">8.27828979492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12861156463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39342403411865</t>
   </si>
   <si>
     <t xml:space="preserve">8.29555797576904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2322359085083</t>
+    <t xml:space="preserve">8.23223304748535</t>
   </si>
   <si>
     <t xml:space="preserve">8.35888481140137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63521289825439</t>
+    <t xml:space="preserve">8.63521003723145</t>
   </si>
   <si>
     <t xml:space="preserve">8.64096736907959</t>
@@ -776,10 +776,10 @@
     <t xml:space="preserve">8.68702030181885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52007579803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46250534057617</t>
+    <t xml:space="preserve">8.52007484436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46250629425049</t>
   </si>
   <si>
     <t xml:space="preserve">8.42220878601074</t>
@@ -788,49 +788,49 @@
     <t xml:space="preserve">8.43372058868408</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33010005950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44523811340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58915615081787</t>
+    <t xml:space="preserve">8.33009910583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44523620605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58915519714355</t>
   </si>
   <si>
     <t xml:space="preserve">8.54885768890381</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5718879699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65248107910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62945556640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70429229736328</t>
+    <t xml:space="preserve">8.57188415527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65248012542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6294527053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70429039001465</t>
   </si>
   <si>
     <t xml:space="preserve">8.81942749023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76761627197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76186180114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77337265014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45099353790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45674896240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60751819610596</t>
+    <t xml:space="preserve">8.76761531829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76185989379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7733736038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4509916305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45674991607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60751724243164</t>
   </si>
   <si>
     <t xml:space="preserve">8.57199954986572</t>
@@ -839,40 +839,40 @@
     <t xml:space="preserve">8.47728061676025</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44768142700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46544361114502</t>
+    <t xml:space="preserve">8.44768238067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46543979644775</t>
   </si>
   <si>
     <t xml:space="preserve">8.42992305755615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42400169372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63711738586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72591495513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77327537536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82063484191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81471729278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87983226776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90943241119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79695510864258</t>
+    <t xml:space="preserve">8.4240026473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63712024688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72591590881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77327442169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82063579559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8147144317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87983131408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90943431854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79695415496826</t>
   </si>
   <si>
     <t xml:space="preserve">8.90351390838623</t>
@@ -881,31 +881,31 @@
     <t xml:space="preserve">8.89167499542236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87391567230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83839416503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67263698577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47136116027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45360088348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34112358093262</t>
+    <t xml:space="preserve">8.87391376495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8383960723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67263793945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47136402130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45360469818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34112453460693</t>
   </si>
   <si>
     <t xml:space="preserve">8.44176292419434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31744575500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26416397094727</t>
+    <t xml:space="preserve">8.31744384765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2641658782959</t>
   </si>
   <si>
     <t xml:space="preserve">8.32928466796875</t>
@@ -914,79 +914,79 @@
     <t xml:space="preserve">8.16352844238281</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22272682189941</t>
+    <t xml:space="preserve">8.2227258682251</t>
   </si>
   <si>
     <t xml:space="preserve">8.22864437103271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28784370422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19904708862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15168762207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23456764221191</t>
+    <t xml:space="preserve">8.28784561157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19904804229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15168857574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23456573486328</t>
   </si>
   <si>
     <t xml:space="preserve">8.06880950927734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11024570465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08656787872314</t>
+    <t xml:space="preserve">8.11024761199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08656692504883</t>
   </si>
   <si>
     <t xml:space="preserve">8.03921127319336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05105018615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00368881225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02736949920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87345170974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79057455062866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88529205322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9089732170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7964940071106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74913501739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6721773147583</t>
+    <t xml:space="preserve">8.05104923248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00369071960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02736854553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87345409393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7905740737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88529062271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90897274017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79649353027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74913454055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67217445373535</t>
   </si>
   <si>
     <t xml:space="preserve">7.69585514068604</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67809677124023</t>
+    <t xml:space="preserve">7.67809581756592</t>
   </si>
   <si>
     <t xml:space="preserve">7.80833435058594</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8201732635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83793306350708</t>
+    <t xml:space="preserve">7.82017421722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83793354034424</t>
   </si>
   <si>
     <t xml:space="preserve">7.77873373031616</t>
@@ -995,67 +995,67 @@
     <t xml:space="preserve">7.77281427383423</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78465557098389</t>
+    <t xml:space="preserve">7.78465461730957</t>
   </si>
   <si>
     <t xml:space="preserve">7.71953392028809</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73137521743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84977197647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82609272003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91489171981812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97409057617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00960922241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99185132980347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02145099639893</t>
+    <t xml:space="preserve">7.73137426376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84977340698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82609510421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91488981246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97409009933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00961017608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99185037612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02144908905029</t>
   </si>
   <si>
     <t xml:space="preserve">8.03328895568848</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01553058624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98593091964722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90305233001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93857002258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84385299682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7609748840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87937450408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89121103286743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92673254013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98001003265381</t>
+    <t xml:space="preserve">8.01552963256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9859299659729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90305185317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93857049942017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84385538101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76097440719604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87937211990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89121341705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92673206329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98001289367676</t>
   </si>
   <si>
     <t xml:space="preserve">7.96817064285278</t>
@@ -1064,61 +1064,61 @@
     <t xml:space="preserve">7.99777221679688</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07472801208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.175368309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20585060119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2485237121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31558513641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37654972076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40093803405762</t>
+    <t xml:space="preserve">8.07472896575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17536735534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20584869384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24852466583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31558418273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37655067443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40093612670898</t>
   </si>
   <si>
     <t xml:space="preserve">8.49847984313965</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52896404266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49238300323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50457572937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53506183624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.516770362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57773494720459</t>
+    <t xml:space="preserve">8.52896308898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49238204956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50457763671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53505897521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51676750183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57773399353027</t>
   </si>
   <si>
     <t xml:space="preserve">8.47409248352051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55334758758545</t>
+    <t xml:space="preserve">8.55334854125977</t>
   </si>
   <si>
     <t xml:space="preserve">8.44361209869385</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48628711700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44970893859863</t>
+    <t xml:space="preserve">8.48628807067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44970798492432</t>
   </si>
   <si>
     <t xml:space="preserve">8.46799755096436</t>
@@ -1136,25 +1136,25 @@
     <t xml:space="preserve">8.41312980651855</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43751430511475</t>
+    <t xml:space="preserve">8.43751525878906</t>
   </si>
   <si>
     <t xml:space="preserve">8.55944442749023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66917991638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7179536819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76672458648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83988189697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97400379180908</t>
+    <t xml:space="preserve">8.66918182373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71795272827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76672649383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83988285064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97400283813477</t>
   </si>
   <si>
     <t xml:space="preserve">8.9130392074585</t>
@@ -1163,79 +1163,79 @@
     <t xml:space="preserve">8.84597778320312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78501319885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72404861450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62040901184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37045383453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38874340057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45580387115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48019123077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42532062530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3460693359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41922760009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54725360870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57163619995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52286434173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51067352294922</t>
+    <t xml:space="preserve">8.78501415252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7240514755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62040710449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37045288085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38874244689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4558048248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48019027709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42532253265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34606742858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41922664642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54725170135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57163906097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52286529541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51067447662354</t>
   </si>
   <si>
     <t xml:space="preserve">8.68746948242188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79720592498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85207653045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96181106567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09593200683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08983612060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05935573577881</t>
+    <t xml:space="preserve">8.79720878601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85207557678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96181011199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09593486785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0898380279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05935382843018</t>
   </si>
   <si>
     <t xml:space="preserve">9.11422348022461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04106426239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10812473297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12031936645508</t>
+    <t xml:space="preserve">9.04106712341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10812664031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12032127380371</t>
   </si>
   <si>
     <t xml:space="preserve">9.10203075408936</t>
@@ -1247,37 +1247,37 @@
     <t xml:space="preserve">8.86670589447021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83134937286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89475154876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74721622467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62894439697266</t>
+    <t xml:space="preserve">8.83134651184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89475059509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74721431732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62894725799561</t>
   </si>
   <si>
     <t xml:space="preserve">8.38508605957031</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33509540557861</t>
+    <t xml:space="preserve">8.3350944519043</t>
   </si>
   <si>
     <t xml:space="preserve">8.16805171966553</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21926116943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1400089263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19243812561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23267459869385</t>
+    <t xml:space="preserve">8.21926021575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14000701904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19243717193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23267364501953</t>
   </si>
   <si>
     <t xml:space="preserve">8.31070804595947</t>
@@ -1286,25 +1286,25 @@
     <t xml:space="preserve">8.35704231262207</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35948085784912</t>
+    <t xml:space="preserve">8.35947895050049</t>
   </si>
   <si>
     <t xml:space="preserve">8.33997249603271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40703296661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45092678070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36069965362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27412891387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15585613250732</t>
+    <t xml:space="preserve">8.40703392028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.450927734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3607006072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27413082122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15585803985596</t>
   </si>
   <si>
     <t xml:space="preserve">8.12659645080566</t>
@@ -1313,10 +1313,10 @@
     <t xml:space="preserve">8.23877048492432</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28022480010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28632259368896</t>
+    <t xml:space="preserve">8.2802267074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28632354736328</t>
   </si>
   <si>
     <t xml:space="preserve">8.36313915252686</t>
@@ -1325,202 +1325,202 @@
     <t xml:space="preserve">8.42776107788086</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59602546691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4972620010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61431312561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68137264251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63869667053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60090065002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57041835784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6569881439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63382244110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71063709259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79842662811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8740234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06057453155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07642650604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13739109039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22639942169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28370666503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34588718414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40807247161865</t>
+    <t xml:space="preserve">8.59602451324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49726009368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61431407928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68137454986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63869857788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60089874267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57041645050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65698909759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63382148742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71063899993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79842758178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87402153015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06057548522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07642459869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13739013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22640132904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28370571136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34589099884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40807437896729</t>
   </si>
   <si>
     <t xml:space="preserve">9.41782665252686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55926609039307</t>
+    <t xml:space="preserve">9.55926513671875</t>
   </si>
   <si>
     <t xml:space="preserve">9.62998485565186</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75435161590576</t>
+    <t xml:space="preserve">9.75435352325439</t>
   </si>
   <si>
     <t xml:space="preserve">9.72509098052979</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8080005645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77142333984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6629056930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85799407958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85067844390869</t>
+    <t xml:space="preserve">9.80799961090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77142143249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66290664672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85799217224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85067558288574</t>
   </si>
   <si>
     <t xml:space="preserve">9.87628269195557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95066070556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83239078521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96772861480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1591558456421</t>
+    <t xml:space="preserve">9.95065784454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83238697052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96773147583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.159158706665</t>
   </si>
   <si>
     <t xml:space="preserve">9.89822959899902</t>
   </si>
   <si>
-    <t xml:space="preserve">10.172571182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0030899047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0225992202759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1664752960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2201223373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0823431015015</t>
+    <t xml:space="preserve">10.1725721359253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0030889511108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0225963592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1664743423462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2201251983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0823450088501</t>
   </si>
   <si>
     <t xml:space="preserve">10.1213607788086</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0908784866333</t>
+    <t xml:space="preserve">10.090877532959</t>
   </si>
   <si>
     <t xml:space="preserve">10.010910987854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0596399307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94843578338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85722160339355</t>
+    <t xml:space="preserve">10.0596408843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94843673706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85722541809082</t>
   </si>
   <si>
     <t xml:space="preserve">9.61232376098633</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41740322113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42989635467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67729949951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8284854888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73727416992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65355587005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65230846405029</t>
+    <t xml:space="preserve">9.41740226745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42989730834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67729663848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82848358154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73727226257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65355682373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65230941772461</t>
   </si>
   <si>
     <t xml:space="preserve">9.76476287841797</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51111507415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78850078582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69104099273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.879714012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70353698730469</t>
+    <t xml:space="preserve">9.5111141204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78850269317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69104194641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87971305847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70353603363037</t>
   </si>
   <si>
     <t xml:space="preserve">9.70853424072266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64231395721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47237968444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76850891113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54735088348389</t>
+    <t xml:space="preserve">9.64231300354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47238063812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76851081848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54734897613525</t>
   </si>
   <si>
     <t xml:space="preserve">9.64106178283691</t>
@@ -1529,13 +1529,13 @@
     <t xml:space="preserve">9.90720272064209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93968963623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9371919631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8547248840332</t>
+    <t xml:space="preserve">9.9396915435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93719100952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85472774505615</t>
   </si>
   <si>
     <t xml:space="preserve">10.0933771133423</t>
@@ -1544,13 +1544,13 @@
     <t xml:space="preserve">10.0871295928955</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1308603286743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1083707809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1933345794678</t>
+    <t xml:space="preserve">10.1308612823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1083717346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1933374404907</t>
   </si>
   <si>
     <t xml:space="preserve">10.3270320892334</t>
@@ -1562,31 +1562,31 @@
     <t xml:space="preserve">10.158350944519</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1708478927612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0296535491943</t>
+    <t xml:space="preserve">10.1708450317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0296516418457</t>
   </si>
   <si>
     <t xml:space="preserve">10.0821313858032</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0808820724487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0458955764771</t>
+    <t xml:space="preserve">10.0808811187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0458974838257</t>
   </si>
   <si>
     <t xml:space="preserve">10.0496454238892</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0771331787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1446075439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1383600234985</t>
+    <t xml:space="preserve">10.0771350860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.144606590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1383581161499</t>
   </si>
   <si>
     <t xml:space="preserve">10.1895866394043</t>
@@ -1595,16 +1595,16 @@
     <t xml:space="preserve">10.1208667755127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1745948791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2857980728149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2095804214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1233644485474</t>
+    <t xml:space="preserve">10.1745939254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2857971191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2095785140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1233682632446</t>
   </si>
   <si>
     <t xml:space="preserve">10.1783418655396</t>
@@ -1619,52 +1619,52 @@
     <t xml:space="preserve">10.2370681762695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96842765808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96967697143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0671367645264</t>
+    <t xml:space="preserve">9.96842956542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96967792510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0671396255493</t>
   </si>
   <si>
     <t xml:space="preserve">9.94093990325928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88596153259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0034132003784</t>
+    <t xml:space="preserve">9.88596057891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0034141540527</t>
   </si>
   <si>
     <t xml:space="preserve">10.104621887207</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1958341598511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.142107963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2458143234253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2658071517944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2483139038086</t>
+    <t xml:space="preserve">10.1958351135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1421060562134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2458152770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2658061981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2483129501343</t>
   </si>
   <si>
     <t xml:space="preserve">9.98342132568359</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0483951568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0733852386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97092723846436</t>
+    <t xml:space="preserve">10.0483961105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0733861923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97092819213867</t>
   </si>
   <si>
     <t xml:space="preserve">9.88721084594727</t>
@@ -1673,28 +1673,28 @@
     <t xml:space="preserve">9.82473754882812</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9022045135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92094898223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0071640014648</t>
+    <t xml:space="preserve">9.90220546722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92094802856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0071620941162</t>
   </si>
   <si>
     <t xml:space="preserve">9.98841953277588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98717212677002</t>
+    <t xml:space="preserve">9.98717021942139</t>
   </si>
   <si>
     <t xml:space="preserve">10.0783843994141</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2070817947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.360164642334</t>
+    <t xml:space="preserve">10.2070789337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3601636886597</t>
   </si>
   <si>
     <t xml:space="preserve">10.6115369796753</t>
@@ -1703,34 +1703,34 @@
     <t xml:space="preserve">10.6423149108887</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6012735366821</t>
+    <t xml:space="preserve">10.6012754440308</t>
   </si>
   <si>
     <t xml:space="preserve">10.4409608840942</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4653291702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.479434967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5012378692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4383964538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4319829940796</t>
+    <t xml:space="preserve">10.4653272628784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4794359207153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5012369155884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4383935928345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4319820404053</t>
   </si>
   <si>
     <t xml:space="preserve">10.1613721847534</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4281339645386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3588790893555</t>
+    <t xml:space="preserve">10.4281349182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3588800430298</t>
   </si>
   <si>
     <t xml:space="preserve">10.074161529541</t>
@@ -1739,28 +1739,28 @@
     <t xml:space="preserve">10.0164489746094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1075067520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1523942947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99336242675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80611610412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86895942687988</t>
+    <t xml:space="preserve">10.1075077056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1523952484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9933614730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80611515045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8689603805542</t>
   </si>
   <si>
     <t xml:space="preserve">9.73044776916504</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58680629730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.440598487854</t>
+    <t xml:space="preserve">9.58680534362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44059944152832</t>
   </si>
   <si>
     <t xml:space="preserve">9.60219478607178</t>
@@ -1769,22 +1769,22 @@
     <t xml:space="preserve">9.70479679107666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8510046005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86639308929443</t>
+    <t xml:space="preserve">9.85100555419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86639499664307</t>
   </si>
   <si>
     <t xml:space="preserve">10.0715951919556</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89204502105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84972190856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90871620178223</t>
+    <t xml:space="preserve">9.89204406738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84972095489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90871715545654</t>
   </si>
   <si>
     <t xml:space="preserve">9.83561325073242</t>
@@ -1799,25 +1799,25 @@
     <t xml:space="preserve">9.91128349304199</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93180084228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71377658843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57141494750977</t>
+    <t xml:space="preserve">9.93180179595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71377468109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57141399383545</t>
   </si>
   <si>
     <t xml:space="preserve">9.60347652435303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55474090576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43931770324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26745891571045</t>
+    <t xml:space="preserve">9.55474281311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43931579589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26745986938477</t>
   </si>
   <si>
     <t xml:space="preserve">9.38031959533691</t>
@@ -1832,49 +1832,49 @@
     <t xml:space="preserve">9.16742324829102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10201358795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07636451721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11612319946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1353588104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30593395233154</t>
+    <t xml:space="preserve">9.10201454162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0763635635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11612224578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13536167144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30593299865723</t>
   </si>
   <si>
     <t xml:space="preserve">9.24309158325195</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16357517242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87116050720215</t>
+    <t xml:space="preserve">9.16357612609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87116241455078</t>
   </si>
   <si>
     <t xml:space="preserve">9.05071449279785</t>
   </si>
   <si>
-    <t xml:space="preserve">8.939133644104</t>
+    <t xml:space="preserve">8.93913459777832</t>
   </si>
   <si>
     <t xml:space="preserve">9.01993370056152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12894725799561</t>
+    <t xml:space="preserve">9.12894630432129</t>
   </si>
   <si>
     <t xml:space="preserve">9.14561939239502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07251644134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95196056365967</t>
+    <t xml:space="preserve">9.07251739501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95195960998535</t>
   </si>
   <si>
     <t xml:space="preserve">8.85833644866943</t>
@@ -1883,10 +1883,10 @@
     <t xml:space="preserve">8.94554805755615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8660306930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83268547058105</t>
+    <t xml:space="preserve">8.86603164672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83268642425537</t>
   </si>
   <si>
     <t xml:space="preserve">8.66980743408203</t>
@@ -1895,7 +1895,7 @@
     <t xml:space="preserve">8.81601428985596</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83653354644775</t>
+    <t xml:space="preserve">8.83653163909912</t>
   </si>
   <si>
     <t xml:space="preserve">8.87500858306885</t>
@@ -1907,61 +1907,61 @@
     <t xml:space="preserve">9.11483955383301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05841159820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14177131652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13279438018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0866231918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05456066131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13792514801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1571626663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11740589141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36749458312988</t>
+    <t xml:space="preserve">9.05841064453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14177227020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13279247283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08662414550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05456161499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13792419433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15716361999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11740207672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3674955368042</t>
   </si>
   <si>
     <t xml:space="preserve">9.32773685455322</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2828483581543</t>
+    <t xml:space="preserve">9.28284931182861</t>
   </si>
   <si>
     <t xml:space="preserve">9.24437427520752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34441089630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25463390350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31234741210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39058017730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49446487426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47266101837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48164081573486</t>
+    <t xml:space="preserve">9.34440803527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25463199615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31234645843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39058303833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49446392059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4726619720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48163986206055</t>
   </si>
   <si>
     <t xml:space="preserve">9.5803918838501</t>
@@ -1979,130 +1979,130 @@
     <t xml:space="preserve">9.39442920684814</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46239948272705</t>
+    <t xml:space="preserve">9.46240043640137</t>
   </si>
   <si>
     <t xml:space="preserve">9.52652740478516</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47779178619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69581890106201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73172855377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74583625793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7804651260376</t>
+    <t xml:space="preserve">9.47778987884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69581985473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73173046112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7458381652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78046607971191</t>
   </si>
   <si>
     <t xml:space="preserve">9.79200744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80354976654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75481510162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75353145599365</t>
+    <t xml:space="preserve">9.80355072021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75481414794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75353336334229</t>
   </si>
   <si>
     <t xml:space="preserve">9.76122856140137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72531700134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64323711395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68940544128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73685836791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79841995239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59834861755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69710254669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72403621673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96771335601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96386623382568</t>
+    <t xml:space="preserve">9.72531604766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64323616027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6894063949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73686122894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79842090606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59834671020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69710063934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72403335571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96771240234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96386337280273</t>
   </si>
   <si>
     <t xml:space="preserve">9.99592876434326</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0959644317627</t>
+    <t xml:space="preserve">10.095965385437</t>
   </si>
   <si>
     <t xml:space="preserve">10.1895875930786</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1164846420288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1511135101318</t>
+    <t xml:space="preserve">10.1164836883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1511116027832</t>
   </si>
   <si>
     <t xml:space="preserve">10.0677480697632</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0190134048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0138835906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99721145629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92667293548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1023778915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1254615783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1985654830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1036596298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.162654876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1408529281616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.188304901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2216529846191</t>
+    <t xml:space="preserve">10.0190143585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0138816833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99721240997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92667198181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1023769378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1254625320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1985645294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1036586761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1626558303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.140851020813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1883058547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2216510772705</t>
   </si>
   <si>
     <t xml:space="preserve">10.211389541626</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1421337127686</t>
+    <t xml:space="preserve">10.1421346664429</t>
   </si>
   <si>
     <t xml:space="preserve">10.048511505127</t>
@@ -2111,103 +2111,103 @@
     <t xml:space="preserve">9.89460849761963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8958911895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.13059425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97155857086182</t>
+    <t xml:space="preserve">9.89589214324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1305932998657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97156047821045</t>
   </si>
   <si>
     <t xml:space="preserve">9.94334411621094</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83817863464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68171119689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75866317749023</t>
+    <t xml:space="preserve">9.83817768096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68171215057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75866413116455</t>
   </si>
   <si>
     <t xml:space="preserve">9.64067268371582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6752986907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53678607940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29182529449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28541564941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.185378074646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14818477630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24822330474854</t>
+    <t xml:space="preserve">9.67530059814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53678894042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29182815551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28541278839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18537902832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14818572998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2482213973999</t>
   </si>
   <si>
     <t xml:space="preserve">9.36493015289307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30978202819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45855617523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51626586914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50703525543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58881092071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5083532333374</t>
+    <t xml:space="preserve">9.30978107452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4585542678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51626682281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50703430175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58880996704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50835227966309</t>
   </si>
   <si>
     <t xml:space="preserve">9.17993259429932</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2683048248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2788553237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24983692169189</t>
+    <t xml:space="preserve">9.26830387115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27885437011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24983882904053</t>
   </si>
   <si>
     <t xml:space="preserve">9.05727005004883</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02957057952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95571041107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11398410797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24456310272217</t>
+    <t xml:space="preserve">9.02957248687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95571231842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11398315429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24456214904785</t>
   </si>
   <si>
     <t xml:space="preserve">9.14564037322998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16674327850342</t>
+    <t xml:space="preserve">9.1667423248291</t>
   </si>
   <si>
     <t xml:space="preserve">9.20631217956543</t>
@@ -2216,127 +2216,127 @@
     <t xml:space="preserve">9.23269176483154</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26302719116211</t>
+    <t xml:space="preserve">9.26302623748779</t>
   </si>
   <si>
     <t xml:space="preserve">9.16938304901123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19576072692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14695835113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3355712890625</t>
+    <t xml:space="preserve">9.19576168060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14695739746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33556938171387</t>
   </si>
   <si>
     <t xml:space="preserve">9.37909507751465</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46878528594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63233375549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57693767547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52286434173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56770801544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54000759124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65475845336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56111240386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60727596282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65871524810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59540462493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66398906707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69828414916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76027297973633</t>
+    <t xml:space="preserve">9.46878433227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63233470916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57694053649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52286148071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56770610809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54000854492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65475654602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.561110496521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60727691650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65871238708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59540367126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66399192810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69828224182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76027488708496</t>
   </si>
   <si>
     <t xml:space="preserve">9.77742004394531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70223999023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67190361022949</t>
+    <t xml:space="preserve">9.70223903656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67190456390381</t>
   </si>
   <si>
     <t xml:space="preserve">9.50571441650391</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4305362701416</t>
+    <t xml:space="preserve">9.43053531646729</t>
   </si>
   <si>
     <t xml:space="preserve">9.37777709960938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44108581542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48988914489746</t>
+    <t xml:space="preserve">9.441086769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48988723754883</t>
   </si>
   <si>
     <t xml:space="preserve">9.46350860595703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45559406280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39624214172363</t>
+    <t xml:space="preserve">9.45559501647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39624118804932</t>
   </si>
   <si>
     <t xml:space="preserve">9.29468154907227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36722373962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29599952697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02165794372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88976097106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82645320892334</t>
+    <t xml:space="preserve">9.36722564697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29600143432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0216588973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88976287841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82645416259766</t>
   </si>
   <si>
     <t xml:space="preserve">8.70115280151367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85942554473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6998348236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68532466888428</t>
+    <t xml:space="preserve">8.8594274520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69983196258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68532562255859</t>
   </si>
   <si>
     <t xml:space="preserve">8.85019493103027</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">8.64048099517822</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59959316253662</t>
+    <t xml:space="preserve">8.59959125518799</t>
   </si>
   <si>
     <t xml:space="preserve">8.75391006469727</t>
@@ -2354,139 +2354,139 @@
     <t xml:space="preserve">8.66817951202393</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80402946472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77896976470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66685962677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71697998046875</t>
+    <t xml:space="preserve">8.804030418396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77897071838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66685771942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71697902679443</t>
   </si>
   <si>
     <t xml:space="preserve">8.77237510681152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83700561523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98077297210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04276084899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9702205657959</t>
+    <t xml:space="preserve">8.83700370788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98076915740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04276275634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97021865844727</t>
   </si>
   <si>
     <t xml:space="preserve">9.01506423950195</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08101177215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18124961853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29995918273926</t>
+    <t xml:space="preserve">9.08101272583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18125247955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29995727539062</t>
   </si>
   <si>
     <t xml:space="preserve">9.28149318695068</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2617073059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4397668838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33293151855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.446364402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59672355651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60895442962646</t>
+    <t xml:space="preserve">9.26170825958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43976783752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.332932472229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44636344909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59672546386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60895347595215</t>
   </si>
   <si>
     <t xml:space="preserve">9.51109886169434</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42003726959229</t>
+    <t xml:space="preserve">9.4200382232666</t>
   </si>
   <si>
     <t xml:space="preserve">9.46896553039551</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55051517486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53692054748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50022602081299</t>
+    <t xml:space="preserve">9.55051136016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5369234085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50022411346436</t>
   </si>
   <si>
     <t xml:space="preserve">9.21209239959717</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11151885986328</t>
+    <t xml:space="preserve">9.11151695251465</t>
   </si>
   <si>
     <t xml:space="preserve">9.20393753051758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27733135223389</t>
+    <t xml:space="preserve">9.27733039855957</t>
   </si>
   <si>
     <t xml:space="preserve">9.19714260101318</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24199295043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29771518707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40236759185791</t>
+    <t xml:space="preserve">9.24199390411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29771614074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40236854553223</t>
   </si>
   <si>
     <t xml:space="preserve">9.3398494720459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40373039245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38877964019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36431407928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48255920410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.562744140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6075963973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5409984588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47168445587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39693260192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30859088897705</t>
+    <t xml:space="preserve">9.40372943878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38877773284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36431312561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48255825042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56274700164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60759449005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54099941253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47168350219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39693355560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30858898162842</t>
   </si>
   <si>
     <t xml:space="preserve">9.22160720825195</t>
@@ -2495,16 +2495,16 @@
     <t xml:space="preserve">9.312668800354</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49614810943604</t>
+    <t xml:space="preserve">9.49614715576172</t>
   </si>
   <si>
     <t xml:space="preserve">9.64836883544922</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62526321411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63341808319092</t>
+    <t xml:space="preserve">9.62526416778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63341903686523</t>
   </si>
   <si>
     <t xml:space="preserve">9.6429328918457</t>
@@ -2513,34 +2513,34 @@
     <t xml:space="preserve">9.60623645782471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68642520904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6374979019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66332149505615</t>
+    <t xml:space="preserve">9.68642425537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63749694824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66332244873047</t>
   </si>
   <si>
     <t xml:space="preserve">9.58856773376465</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49342823028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52197265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5423583984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54643726348877</t>
+    <t xml:space="preserve">9.49343013763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52197074890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54235744476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54643535614014</t>
   </si>
   <si>
     <t xml:space="preserve">9.46760749816895</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43906402587891</t>
+    <t xml:space="preserve">9.43906497955322</t>
   </si>
   <si>
     <t xml:space="preserve">9.37790584564209</t>
@@ -2549,16 +2549,16 @@
     <t xml:space="preserve">9.31946277618408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22296524047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16044425964355</t>
+    <t xml:space="preserve">9.22296619415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16044616699219</t>
   </si>
   <si>
     <t xml:space="preserve">9.27189350128174</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35752010345459</t>
+    <t xml:space="preserve">9.35751914978027</t>
   </si>
   <si>
     <t xml:space="preserve">9.25966358184814</t>
@@ -2567,28 +2567,28 @@
     <t xml:space="preserve">9.28684425354004</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23655891418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27597141265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24471187591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25830173492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31130790710449</t>
+    <t xml:space="preserve">9.23655700683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27597332000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24471092224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25830268859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31130886077881</t>
   </si>
   <si>
     <t xml:space="preserve">9.39013767242432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40916538238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52469062805176</t>
+    <t xml:space="preserve">9.40916347503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52468967437744</t>
   </si>
   <si>
     <t xml:space="preserve">9.51381683349609</t>
@@ -2597,127 +2597,127 @@
     <t xml:space="preserve">9.51925373077393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58584976196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72855758666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73127555847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65380573272705</t>
+    <t xml:space="preserve">9.58584880828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72855472564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73127365112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65380668640137</t>
   </si>
   <si>
     <t xml:space="preserve">9.58177375793457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42819213867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37654590606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43770599365234</t>
+    <t xml:space="preserve">9.42819404602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37654685974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43770694732666</t>
   </si>
   <si>
     <t xml:space="preserve">9.4567346572876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43362712860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21345233917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14549446105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15365219116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96745109558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10472393035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0299711227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78397178649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60185050964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5692310333252</t>
+    <t xml:space="preserve">9.43362903594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21345043182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14549732208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15365028381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96745204925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10472202301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02997016906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78397083282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60184955596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56922912597656</t>
   </si>
   <si>
     <t xml:space="preserve">8.69019317626953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85328483581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81387233734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77038097381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68475341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90221500396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82610416412354</t>
+    <t xml:space="preserve">8.85328674316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81387138366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77037906646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68475532531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90221405029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82610511779785</t>
   </si>
   <si>
     <t xml:space="preserve">8.76086521148682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77309703826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7921257019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76630401611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67388153076172</t>
+    <t xml:space="preserve">8.77309894561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79212665557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76630210876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67388248443604</t>
   </si>
   <si>
     <t xml:space="preserve">8.26886653900146</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13838863372803</t>
+    <t xml:space="preserve">8.13839149475098</t>
   </si>
   <si>
     <t xml:space="preserve">8.19819164276123</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99024868011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58251142501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55532884597778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5566873550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57843446731567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45339632034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9546012878418</t>
+    <t xml:space="preserve">7.99024724960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58251237869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55533027648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55669069290161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57843351364136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45339727401733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95460081100464</t>
   </si>
   <si>
     <t xml:space="preserve">5.50442314147949</t>
@@ -2738,46 +2738,46 @@
     <t xml:space="preserve">4.41169309616089</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66584730148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54896402359009</t>
+    <t xml:space="preserve">4.66584777832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54896354675293</t>
   </si>
   <si>
     <t xml:space="preserve">4.73312377929688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95601940155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95194101333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69129991531372</t>
+    <t xml:space="preserve">4.95601892471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95194149017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69130039215088</t>
   </si>
   <si>
     <t xml:space="preserve">5.92778635025024</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91963338851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58393001556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8394455909729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26552772521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25193500518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68549394607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33688163757324</t>
+    <t xml:space="preserve">5.91963291168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58393049240112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83944606781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26552820205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2519359588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68549537658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3368821144104</t>
   </si>
   <si>
     <t xml:space="preserve">6.33008623123169</t>
@@ -2786,166 +2786,166 @@
     <t xml:space="preserve">6.40687608718872</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31649446487427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32532787322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22951126098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83196926116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74498701095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83536720275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73139524459839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4092845916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67295217514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75721836090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60635757446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71100854873657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90128517150879</t>
+    <t xml:space="preserve">6.31649541854858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3253288269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22951173782349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83196878433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74498653411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83536767959595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73139572143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40928411483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6729531288147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7572193145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60635662078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71100807189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90128421783447</t>
   </si>
   <si>
     <t xml:space="preserve">6.0868034362793</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92167043685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5798544883728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90332269668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72392082214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81430149078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86526727676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79323387145996</t>
+    <t xml:space="preserve">5.92167091369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57985401153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90332317352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72391986846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81430053710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86526679992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79323434829712</t>
   </si>
   <si>
     <t xml:space="preserve">5.78576040267944</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78983736038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19562721252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00024652481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03245162963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88430643081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84995317459106</t>
+    <t xml:space="preserve">5.78983688354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19562673568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00024557113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03245115280151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88430595397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84995412826538</t>
   </si>
   <si>
     <t xml:space="preserve">5.91150188446045</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92152118682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04748010635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07753992080688</t>
+    <t xml:space="preserve">5.92152214050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04748106002808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07753849029541</t>
   </si>
   <si>
     <t xml:space="preserve">5.81345415115356</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96875667572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27721452713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44038820266724</t>
+    <t xml:space="preserve">5.96875715255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27721405029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44038867950439</t>
   </si>
   <si>
     <t xml:space="preserve">6.41533994674683</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8032374382019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91631317138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7101993560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60570859909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14123582839966</t>
+    <t xml:space="preserve">6.80323648452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91631364822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71019983291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60571050643921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1412353515625</t>
   </si>
   <si>
     <t xml:space="preserve">6.14552879333496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14051818847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39458608627319</t>
+    <t xml:space="preserve">6.14051961898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39458513259888</t>
   </si>
   <si>
     <t xml:space="preserve">6.36667394638062</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3230185508728</t>
+    <t xml:space="preserve">6.32301712036133</t>
   </si>
   <si>
     <t xml:space="preserve">6.35092830657959</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30011415481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06322622299194</t>
+    <t xml:space="preserve">6.30011606216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06322717666626</t>
   </si>
   <si>
     <t xml:space="preserve">6.06966733932495</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00955152511597</t>
+    <t xml:space="preserve">6.00955057144165</t>
   </si>
   <si>
     <t xml:space="preserve">6.17272472381592</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07610750198364</t>
+    <t xml:space="preserve">6.07610702514648</t>
   </si>
   <si>
     <t xml:space="preserve">6.06537294387817</t>
@@ -2954,40 +2954,40 @@
     <t xml:space="preserve">6.24071407318115</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20779323577881</t>
+    <t xml:space="preserve">6.20779275894165</t>
   </si>
   <si>
     <t xml:space="preserve">6.26790952682495</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3122820854187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22496938705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03603029251099</t>
+    <t xml:space="preserve">6.31228113174438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22496843338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03602981567383</t>
   </si>
   <si>
     <t xml:space="preserve">6.19777297973633</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28580141067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32373428344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36595630645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30727243423462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2843713760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39029169082642</t>
+    <t xml:space="preserve">6.28580093383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32373380661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36595773696899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30727100372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28437042236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39029121398926</t>
   </si>
   <si>
     <t xml:space="preserve">6.23141050338745</t>
@@ -2996,7 +2996,7 @@
     <t xml:space="preserve">6.15554857254028</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09757852554321</t>
+    <t xml:space="preserve">6.09757900238037</t>
   </si>
   <si>
     <t xml:space="preserve">6.05678510665894</t>
@@ -3005,82 +3005,82 @@
     <t xml:space="preserve">6.0668044090271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01885366439819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59517192840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3969292640686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39192008972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62451410293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79413080215454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68391609191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58658504486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71540641784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90005111694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99237442016602</t>
+    <t xml:space="preserve">6.01885461807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5951714515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39692878723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39191961288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62451505661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79413032531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6839165687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58658456802368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71540689468384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90005207061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9923734664917</t>
   </si>
   <si>
     <t xml:space="preserve">5.90076684951782</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85353183746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79699420928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76407241821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81703186035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67890691757202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63453435897827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86212015151978</t>
+    <t xml:space="preserve">5.85353231430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79699468612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76407289505005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81703281402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67890644073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63453483581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86211967468262</t>
   </si>
   <si>
     <t xml:space="preserve">5.78124904632568</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69823026657104</t>
+    <t xml:space="preserve">5.69822978973389</t>
   </si>
   <si>
     <t xml:space="preserve">5.5822901725769</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56511402130127</t>
+    <t xml:space="preserve">5.56511354446411</t>
   </si>
   <si>
     <t xml:space="preserve">5.49354648590088</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50786018371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47135972976685</t>
+    <t xml:space="preserve">5.50785970687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.471360206604</t>
   </si>
   <si>
     <t xml:space="preserve">5.56296682357788</t>
@@ -3095,13 +3095,13 @@
     <t xml:space="preserve">5.45776224136353</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43844032287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35041046142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44774198532104</t>
+    <t xml:space="preserve">5.43843936920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35040998458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44774293899536</t>
   </si>
   <si>
     <t xml:space="preserve">5.47565412521362</t>
@@ -3110,19 +3110,19 @@
     <t xml:space="preserve">5.43486070632935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28742980957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05608797073364</t>
+    <t xml:space="preserve">5.28743028640747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05608701705933</t>
   </si>
   <si>
     <t xml:space="preserve">5.13320207595825</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0400824546814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95569276809692</t>
+    <t xml:space="preserve">5.04008197784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95569324493408</t>
   </si>
   <si>
     <t xml:space="preserve">4.86621141433716</t>
@@ -3131,67 +3131,67 @@
     <t xml:space="preserve">4.99061298370361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84875202178955</t>
+    <t xml:space="preserve">4.84875059127808</t>
   </si>
   <si>
     <t xml:space="preserve">4.8654842376709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70106935501099</t>
+    <t xml:space="preserve">4.7010703086853</t>
   </si>
   <si>
     <t xml:space="preserve">4.72653293609619</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86693954467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03280830383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8960394859314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00880146026611</t>
+    <t xml:space="preserve">4.86693906784058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03280782699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89603900909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00880193710327</t>
   </si>
   <si>
     <t xml:space="preserve">4.99206781387329</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96078586578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8640284538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87275838851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66906023025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77454614639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79127883911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77381944656372</t>
+    <t xml:space="preserve">4.96078538894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86403036117554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87275791168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66906118392944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7745475769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79127979278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77382040023804</t>
   </si>
   <si>
     <t xml:space="preserve">4.61231660842896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6130428314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68797540664673</t>
+    <t xml:space="preserve">4.61304330825806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68797492980957</t>
   </si>
   <si>
     <t xml:space="preserve">4.54320383071899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43771600723267</t>
+    <t xml:space="preserve">4.43771696090698</t>
   </si>
   <si>
     <t xml:space="preserve">4.28130626678467</t>
@@ -3200,91 +3200,91 @@
     <t xml:space="preserve">4.30531311035156</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37297058105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62832069396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73890018463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79928159713745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79855537414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75926923751831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36745548248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58570337295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52313995361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54205465316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57260894775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79667663574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88252210617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96109104156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87597274780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91089344024658</t>
+    <t xml:space="preserve">4.37297105789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62832021713257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73889875411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79928255081177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79855442047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75926971435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36745500564575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5857048034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52313899993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54205417633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57260799407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7966775894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88252115249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96109056472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87597465515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91089296340942</t>
   </si>
   <si>
     <t xml:space="preserve">6.06002998352051</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27100467681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30883312225342</t>
+    <t xml:space="preserve">6.27100324630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30883455276489</t>
   </si>
   <si>
     <t xml:space="preserve">6.22589826583862</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24335908889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04038763046265</t>
+    <t xml:space="preserve">6.24335861206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0403881072998</t>
   </si>
   <si>
     <t xml:space="preserve">6.12186765670776</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18297576904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1487832069397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36121368408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37794637680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39467763900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43323516845703</t>
+    <t xml:space="preserve">6.18297624588013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14878463745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36121416091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37794542312622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39467716217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43323469161987</t>
   </si>
   <si>
     <t xml:space="preserve">6.50089120864868</t>
@@ -3293,16 +3293,16 @@
     <t xml:space="preserve">6.40777254104614</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31319999694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36703252792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36994123458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33720541000366</t>
+    <t xml:space="preserve">6.31319856643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36703205108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36994218826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33720588684082</t>
   </si>
   <si>
     <t xml:space="preserve">6.27173089981079</t>
@@ -3311,40 +3311,40 @@
     <t xml:space="preserve">5.99746656417847</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08185434341431</t>
+    <t xml:space="preserve">6.08185482025146</t>
   </si>
   <si>
     <t xml:space="preserve">6.24481344223022</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25354337692261</t>
+    <t xml:space="preserve">6.25354433059692</t>
   </si>
   <si>
     <t xml:space="preserve">6.22880935668945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21862363815308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1458740234375</t>
+    <t xml:space="preserve">6.21862411499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14587354660034</t>
   </si>
   <si>
     <t xml:space="preserve">6.37357997894287</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5823712348938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59692287445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56927585601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53144598007202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58673620223999</t>
+    <t xml:space="preserve">6.58237218856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59692049026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56927537918091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53144693374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58673667907715</t>
   </si>
   <si>
     <t xml:space="preserve">6.5911021232605</t>
@@ -3353,7 +3353,7 @@
     <t xml:space="preserve">6.55108880996704</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42450618743896</t>
+    <t xml:space="preserve">6.42450428009033</t>
   </si>
   <si>
     <t xml:space="preserve">6.44269227981567</t>
@@ -3362,298 +3362,298 @@
     <t xml:space="preserve">6.42159509658813</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47542858123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3059229850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21425867080688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07676267623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20407485961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21789693832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07603549957275</t>
+    <t xml:space="preserve">6.47542905807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30592393875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2142596244812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07676219940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20407342910767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21789646148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07603597640991</t>
   </si>
   <si>
     <t xml:space="preserve">5.96545600891113</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04620790481567</t>
+    <t xml:space="preserve">6.04620742797852</t>
   </si>
   <si>
     <t xml:space="preserve">6.17570209503174</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23462915420532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26445579528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31538009643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38376426696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43396282196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38521957397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45942544937134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63693332672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60492515563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66603326797485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61801862716675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6914963722229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80643939971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85590839385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9672155380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04214906692505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8981032371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95557546615601</t>
+    <t xml:space="preserve">6.23462772369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2644567489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31537961959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38376474380493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43396186828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38522052764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45942401885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63693284988403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60492420196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66603469848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61801815032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69149398803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80643844604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85590934753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96721601486206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04214954376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89810371398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95557641983032</t>
   </si>
   <si>
     <t xml:space="preserve">6.90537929534912</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02759838104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18473720550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32004976272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4058952331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37679576873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43499660491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49319458007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57903814315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51792860031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44954395294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52083969116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40153074264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38116025924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26039600372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45391035079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35642671585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4437255859375</t>
+    <t xml:space="preserve">7.02759742736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18473672866821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32005023956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40589380264282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37679481506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43499517440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49319505691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57904052734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51792812347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44954347610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52083921432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40152931213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38115882873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26039457321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45391082763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35642623901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44372606277466</t>
   </si>
   <si>
     <t xml:space="preserve">7.52811431884766</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57467269897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63432884216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68961763381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61977910995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60668325424194</t>
+    <t xml:space="preserve">7.57467460632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6343297958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68961906433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61977767944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6066837310791</t>
   </si>
   <si>
     <t xml:space="preserve">7.46409463882446</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42044448852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39279985427856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43936014175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62996435165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53975391387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52956771850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51065492630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32878160476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3840708732605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39716482162476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34914922714233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38261556625366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35496950149536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4233570098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42189884185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22402095794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34769582748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49901390075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51210975646973</t>
+    <t xml:space="preserve">7.42044591903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39280128479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43936109542847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62996339797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53975439071655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52956867218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51065444946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.328782081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38406991958618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39716577529907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34915065765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3826150894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35497045516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42335557937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42190074920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22402191162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34769630432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49901151657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51211023330688</t>
   </si>
   <si>
     <t xml:space="preserve">7.50774431228638</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57176303863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60813999176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49610424041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58776950836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61250257492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59067821502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41753530502319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4815559387207</t>
+    <t xml:space="preserve">7.57176351547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60813760757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49610280990601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58776807785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61250352859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59067869186401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41753482818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48155546188354</t>
   </si>
   <si>
     <t xml:space="preserve">7.53071641921997</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43760585784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47112607955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52326917648315</t>
+    <t xml:space="preserve">7.43760681152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47112655639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.523268699646</t>
   </si>
   <si>
     <t xml:space="preserve">7.518798828125</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49049186706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66777563095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72438335418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.776526927948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73183393478394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78695392608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81823921203613</t>
+    <t xml:space="preserve">7.49049139022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66777467727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7243857383728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77652740478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73183441162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78695487976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81824111938477</t>
   </si>
   <si>
     <t xml:space="preserve">7.77950716018677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83164596557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88229846954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99105262756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99552011489868</t>
+    <t xml:space="preserve">7.83164691925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88229751586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99105167388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99552059173584</t>
   </si>
   <si>
     <t xml:space="preserve">8.00148010253906</t>
@@ -3662,118 +3662,118 @@
     <t xml:space="preserve">7.91805410385132</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68267202377319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76013803482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75716018676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76311922073364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85101509094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8629322052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70352745056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70054912567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6498966217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79142379760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74524116516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7884464263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57541131973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42122030258179</t>
+    <t xml:space="preserve">7.68267011642456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76014089584351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75715923309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76311874389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85101413726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86293172836304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70352935791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70054864883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64989805221558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79142427444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74523973464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78844451904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57540893554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42121982574463</t>
   </si>
   <si>
     <t xml:space="preserve">7.50837135314941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45175838470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4666576385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38174057006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32363986968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04207563400269</t>
+    <t xml:space="preserve">7.45175981521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46665811538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38174104690552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32364225387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04207849502563</t>
   </si>
   <si>
     <t xml:space="preserve">7.0785756111145</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26255989074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18360376358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20222473144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34896612167358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30576372146606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38695573806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4592080116272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42792320251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55008268356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53816652297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59775495529175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67373466491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66032600402832</t>
+    <t xml:space="preserve">7.26256036758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18360280990601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20222425460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34896755218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30576276779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38695478439331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45920848846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42792224884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55008411407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53816366195679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59775638580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67373418807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66032648086548</t>
   </si>
   <si>
     <t xml:space="preserve">7.70948696136475</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75865077972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80483150482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83462619781494</t>
+    <t xml:space="preserve">7.75865125656128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80483102798462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83462715148926</t>
   </si>
   <si>
     <t xml:space="preserve">7.72587442398071</t>
@@ -3782,37 +3782,37 @@
     <t xml:space="preserve">7.72885608673096</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72140550613403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50539207458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49496078491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62308263778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6856517791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69458961486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67671394348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76758813858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77056980133057</t>
+    <t xml:space="preserve">7.72140455245972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50539302825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49496221542358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62308120727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68565225601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69458913803101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67671203613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76758766174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7705659866333</t>
   </si>
   <si>
     <t xml:space="preserve">7.91954278945923</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84356451034546</t>
+    <t xml:space="preserve">7.84356546401978</t>
   </si>
   <si>
     <t xml:space="preserve">7.88527965545654</t>
@@ -3821,22 +3821,22 @@
     <t xml:space="preserve">7.88825941085815</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85399436950684</t>
+    <t xml:space="preserve">7.85399341583252</t>
   </si>
   <si>
     <t xml:space="preserve">8.04915237426758</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12214946746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18621063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21153354644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15045547485352</t>
+    <t xml:space="preserve">8.12215137481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1862096786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21153545379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1504545211792</t>
   </si>
   <si>
     <t xml:space="preserve">8.07447147369385</t>
@@ -3848,37 +3848,37 @@
     <t xml:space="preserve">8.44043445587158</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45284080505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47610092163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67304039001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73351573944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82965850830078</t>
+    <t xml:space="preserve">8.45284175872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47610282897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67303943634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73351764678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82966041564941</t>
   </si>
   <si>
     <t xml:space="preserve">8.95216464996338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90254402160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02659797668457</t>
+    <t xml:space="preserve">8.90254211425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02659893035889</t>
   </si>
   <si>
     <t xml:space="preserve">9.18632030487061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04520702362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9847297668457</t>
+    <t xml:space="preserve">9.04520606994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98472690582275</t>
   </si>
   <si>
     <t xml:space="preserve">9.19407367706299</t>
@@ -3887,31 +3887,31 @@
     <t xml:space="preserve">9.30882453918457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28401279449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16616153717041</t>
+    <t xml:space="preserve">9.28401470184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16616058349609</t>
   </si>
   <si>
     <t xml:space="preserve">9.28866577148438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46544361114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48715496063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43753242492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55073261260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4080696105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36465072631836</t>
+    <t xml:space="preserve">9.46544551849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48715400695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43753147125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55073165893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40806865692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36464881896973</t>
   </si>
   <si>
     <t xml:space="preserve">9.51971817016602</t>
@@ -3920,115 +3920,115 @@
     <t xml:space="preserve">9.58174610137939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51196479797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43132877349854</t>
+    <t xml:space="preserve">9.51196575164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43132972717285</t>
   </si>
   <si>
     <t xml:space="preserve">9.61741256713867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88258361816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72285938262939</t>
+    <t xml:space="preserve">9.8825798034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72286033630371</t>
   </si>
   <si>
     <t xml:space="preserve">9.59880447387695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73836803436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82520771026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83295822143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78488826751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81900215148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80504608154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70115184783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72751331329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76782894134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76317977905273</t>
+    <t xml:space="preserve">9.73836708068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8252067565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83295917510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78488636016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81900310516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80504703521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70114994049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72751235961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76782989501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76317882537842</t>
   </si>
   <si>
     <t xml:space="preserve">9.6375732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43443202972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55848693847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59105205535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53367710113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93975830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1491003036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22974109649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25765228271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31192493438721</t>
+    <t xml:space="preserve">9.43443012237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55848598480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59105014801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53367519378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93975734710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14910221099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2297420501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25765132904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31192588806152</t>
   </si>
   <si>
     <t xml:space="preserve">9.53057479858398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7445707321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60655784606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51041412353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46389389038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31968021392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41892433166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30417537689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45769119262695</t>
+    <t xml:space="preserve">9.74456977844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60655975341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51041603088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46389484405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31968116760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41892528533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30417060852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45769023895264</t>
   </si>
   <si>
     <t xml:space="preserve">9.34449100494385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17546272277832</t>
+    <t xml:space="preserve">9.17546367645264</t>
   </si>
   <si>
     <t xml:space="preserve">9.44373607635498</t>
@@ -4040,7 +4040,7 @@
     <t xml:space="preserve">9.49025630950928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53212547302246</t>
+    <t xml:space="preserve">9.53212356567383</t>
   </si>
   <si>
     <t xml:space="preserve">9.52126979827881</t>
@@ -4049,7 +4049,7 @@
     <t xml:space="preserve">9.47474956512451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62051391601562</t>
+    <t xml:space="preserve">9.62051486968994</t>
   </si>
   <si>
     <t xml:space="preserve">9.77713489532471</t>
@@ -4058,73 +4058,73 @@
     <t xml:space="preserve">9.89033508300781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80814933776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91669750213623</t>
+    <t xml:space="preserve">9.80814838409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91669845581055</t>
   </si>
   <si>
     <t xml:space="preserve">9.83450984954834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.932204246521</t>
+    <t xml:space="preserve">9.93220520019531</t>
   </si>
   <si>
     <t xml:space="preserve">10.1198387145996</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0981283187866</t>
+    <t xml:space="preserve">10.0981273651123</t>
   </si>
   <si>
     <t xml:space="preserve">10.2035751342773</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2438936233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2888650894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4051656723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3043727874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1617059707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83606147766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1524028778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4547872543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7091026306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5245695114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3183259963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4330797195435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.355544090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3028202056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4516859054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2237339019775</t>
+    <t xml:space="preserve">10.2438926696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2888631820679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4051675796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.304370880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1617069244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8360595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1524057388306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4547882080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7091016769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5245704650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3183288574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4330787658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3555450439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3028211593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4516878128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2237358093262</t>
   </si>
   <si>
     <t xml:space="preserve">10.1074342727661</t>
@@ -4133,64 +4133,64 @@
     <t xml:space="preserve">10.2749080657959</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3105745315552</t>
+    <t xml:space="preserve">10.3105726242065</t>
   </si>
   <si>
     <t xml:space="preserve">10.4889030456543</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3307342529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2128791809082</t>
+    <t xml:space="preserve">10.3307332992554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2128810882568</t>
   </si>
   <si>
     <t xml:space="preserve">10.3384866714478</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4439334869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3229789733887</t>
+    <t xml:space="preserve">10.4439325332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.322979927063</t>
   </si>
   <si>
     <t xml:space="preserve">10.4609899520874</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4098167419434</t>
+    <t xml:space="preserve">10.4098176956177</t>
   </si>
   <si>
     <t xml:space="preserve">10.3601961135864</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6842918395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7246084213257</t>
+    <t xml:space="preserve">10.6842908859253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7246103286743</t>
   </si>
   <si>
     <t xml:space="preserve">11.0502548217773</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2658004760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7509737014771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9663200378418</t>
+    <t xml:space="preserve">11.2658033370972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7509708404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96631813049316</t>
   </si>
   <si>
     <t xml:space="preserve">10.3943119049072</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5990028381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5462808609009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1601572036743</t>
+    <t xml:space="preserve">10.5990018844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5462789535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1601552963257</t>
   </si>
   <si>
     <t xml:space="preserve">10.0624628067017</t>
@@ -4199,91 +4199,91 @@
     <t xml:space="preserve">10.0205945968628</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90119171142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1648073196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86862468719482</t>
+    <t xml:space="preserve">9.90118885040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1648092269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86862754821777</t>
   </si>
   <si>
     <t xml:space="preserve">10.2516469955444</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4392824172974</t>
+    <t xml:space="preserve">10.4392805099487</t>
   </si>
   <si>
     <t xml:space="preserve">10.2904138565063</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1539535522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3757019042969</t>
+    <t xml:space="preserve">10.1539545059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3757038116455</t>
   </si>
   <si>
     <t xml:space="preserve">10.3074731826782</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4005146026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4222230911255</t>
+    <t xml:space="preserve">10.4005136489868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4222240447998</t>
   </si>
   <si>
     <t xml:space="preserve">10.4733972549438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3803548812866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.282660484314</t>
+    <t xml:space="preserve">10.3803558349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2826623916626</t>
   </si>
   <si>
     <t xml:space="preserve">10.7137546539307</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6966953277588</t>
+    <t xml:space="preserve">10.6966972351074</t>
   </si>
   <si>
     <t xml:space="preserve">10.9897794723511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.009937286377</t>
+    <t xml:space="preserve">11.0099391937256</t>
   </si>
   <si>
     <t xml:space="preserve">10.9711694717407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0316476821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.854868888855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5292205810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0252456665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0469560623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2020254135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3819046020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2345886230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5447282791138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4749479293823</t>
+    <t xml:space="preserve">11.0316467285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8548679351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.529221534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0252466201782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0469551086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2020244598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3819065093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2345905303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5447301864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.474949836731</t>
   </si>
   <si>
     <t xml:space="preserve">10.5478296279907</t>
@@ -4292,97 +4292,97 @@
     <t xml:space="preserve">10.1399974822998</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2795610427856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5602340698242</t>
+    <t xml:space="preserve">10.27956199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5602378845215</t>
   </si>
   <si>
     <t xml:space="preserve">10.5757427215576</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7199573516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8021440505981</t>
+    <t xml:space="preserve">10.7199583053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8021450042725</t>
   </si>
   <si>
     <t xml:space="preserve">10.688943862915</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7695789337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9728088378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8895978927612</t>
+    <t xml:space="preserve">10.7695798873901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9728097915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8895959854126</t>
   </si>
   <si>
     <t xml:space="preserve">11.2976570129395</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3984708786011</t>
+    <t xml:space="preserve">11.3984718322754</t>
   </si>
   <si>
     <t xml:space="preserve">11.3552656173706</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3616666793823</t>
+    <t xml:space="preserve">11.3616676330566</t>
   </si>
   <si>
     <t xml:space="preserve">11.3600664138794</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2800531387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2592515945435</t>
+    <t xml:space="preserve">11.2800521850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2592506408691</t>
   </si>
   <si>
     <t xml:space="preserve">11.4080743789673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5472946166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.544095993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5152902603149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2224464416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5935535430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3839235305786</t>
+    <t xml:space="preserve">11.5472936630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5440921783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.515287399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2224454879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5935544967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3839225769043</t>
   </si>
   <si>
     <t xml:space="preserve">10.5375461578369</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6047554016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.086277961731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60940837860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6366138458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66541767120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32936859130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14534187316895</t>
+    <t xml:space="preserve">10.6047563552856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0862798690796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60941123962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63661289215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66541862487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32936668395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14534282684326</t>
   </si>
   <si>
     <t xml:space="preserve">9.33416938781738</t>
@@ -4391,127 +4391,127 @@
     <t xml:space="preserve">9.20134925842285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28296184539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06373119354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.983717918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19974899291992</t>
+    <t xml:space="preserve">9.28296089172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06373023986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98371887207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19974994659424</t>
   </si>
   <si>
     <t xml:space="preserve">8.6668701171875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6060619354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83809471130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98211669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9613151550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91170597076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89410495758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51644802093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67167282104492</t>
+    <t xml:space="preserve">8.60606098175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83809661865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9821195602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96131324768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91170692443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89410591125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51644992828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67167186737061</t>
   </si>
   <si>
     <t xml:space="preserve">8.81249237060547</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04452705383301</t>
+    <t xml:space="preserve">9.04452800750732</t>
   </si>
   <si>
     <t xml:space="preserve">8.94051170349121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80128955841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77728748321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85089874267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81729507446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87490081787109</t>
+    <t xml:space="preserve">8.80129146575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77728843688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8508996963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81729125976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87490177154541</t>
   </si>
   <si>
     <t xml:space="preserve">9.37417507171631</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3629732131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15654182434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.121337890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11333751678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16614532470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1581449508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19494819641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14054203033447</t>
+    <t xml:space="preserve">9.36297416687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15654563903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12133598327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11333847045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16614437103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15814304351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19494915008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14054107666016</t>
   </si>
   <si>
     <t xml:space="preserve">9.27336025238037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30536556243896</t>
+    <t xml:space="preserve">9.30536460876465</t>
   </si>
   <si>
     <t xml:space="preserve">9.26375961303711</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35497283935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54860019683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41738128662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56940460205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92785549163818</t>
+    <t xml:space="preserve">9.35497188568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5486011505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41738224029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56940364837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92785453796387</t>
   </si>
   <si>
     <t xml:space="preserve">9.80463695526123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0062665939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85424709320068</t>
+    <t xml:space="preserve">10.0062675476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85424518585205</t>
   </si>
   <si>
     <t xml:space="preserve">10.0014667510986</t>
@@ -4520,31 +4520,31 @@
     <t xml:space="preserve">9.7902364730835</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44778537750244</t>
+    <t xml:space="preserve">9.44778633117676</t>
   </si>
   <si>
     <t xml:space="preserve">9.38217639923096</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6702184677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83344078063965</t>
+    <t xml:space="preserve">9.67021942138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83344173431396</t>
   </si>
   <si>
     <t xml:space="preserve">9.56300258636475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29576301574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26695919036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34697151184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55660343170166</t>
+    <t xml:space="preserve">9.29576396942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26696014404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34697246551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55660152435303</t>
   </si>
   <si>
     <t xml:space="preserve">9.47018909454346</t>
@@ -4553,55 +4553,55 @@
     <t xml:space="preserve">9.44938659667969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23335552215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1565408706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08801555633545</t>
+    <t xml:space="preserve">9.23335361480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15654373168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08801651000977</t>
   </si>
   <si>
     <t xml:space="preserve">9.25117588043213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81227588653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75680065155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77148532867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79922389984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90038108825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17122840881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41433715820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56444358825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56933689117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65907573699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61176109313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43881034851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29686260223389</t>
+    <t xml:space="preserve">8.81227493286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75680255889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.771484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79922485351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90038013458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17122936248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41433525085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56444263458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56933784484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65907669067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61175918579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43880939483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29686069488525</t>
   </si>
   <si>
     <t xml:space="preserve">9.53507423400879</t>
@@ -4610,58 +4610,58 @@
     <t xml:space="preserve">9.67865562438965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68028736114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86628913879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83692169189453</t>
+    <t xml:space="preserve">9.68028831481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86629009246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83692073822021</t>
   </si>
   <si>
     <t xml:space="preserve">10.0783967971802</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0522928237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1844520568848</t>
+    <t xml:space="preserve">10.0522909164429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1844511032104</t>
   </si>
   <si>
     <t xml:space="preserve">10.5385103225708</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7163534164429</t>
+    <t xml:space="preserve">10.7163524627686</t>
   </si>
   <si>
     <t xml:space="preserve">10.8126182556152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9839372634888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0377788543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1927824020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4293622970581</t>
+    <t xml:space="preserve">10.9839363098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0377769470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1927814483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4293642044067</t>
   </si>
   <si>
     <t xml:space="preserve">11.6398391723633</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5957870483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4391527175903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.478307723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6479969024658</t>
+    <t xml:space="preserve">11.5957851409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.439151763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.478310585022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6479949951172</t>
   </si>
   <si>
     <t xml:space="preserve">11.8078947067261</t>
@@ -4670,49 +4670,49 @@
     <t xml:space="preserve">11.8095264434814</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7132625579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4913644790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.57457447052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1403636932373</t>
+    <t xml:space="preserve">11.7132616043091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4913635253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5745735168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.140362739563</t>
   </si>
   <si>
     <t xml:space="preserve">11.6441812515259</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7005310058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.753565788269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.848030090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6160078048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7635078430176</t>
+    <t xml:space="preserve">11.7005300521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7535638809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8480291366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6160087585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7635068893433</t>
   </si>
   <si>
     <t xml:space="preserve">11.8695755004883</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6756706237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5115976333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4635362625122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3044366836548</t>
+    <t xml:space="preserve">11.6756715774536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5115985870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4635372161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3044376373291</t>
   </si>
   <si>
     <t xml:space="preserve">11.1337337493896</t>
@@ -4721,10 +4721,10 @@
     <t xml:space="preserve">11.2066555023193</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2083120346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2762622833252</t>
+    <t xml:space="preserve">11.2083129882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2762613296509</t>
   </si>
   <si>
     <t xml:space="preserve">11.4469633102417</t>
@@ -4733,7 +4733,7 @@
     <t xml:space="preserve">11.2779188156128</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8138751983643</t>
+    <t xml:space="preserve">10.8138780593872</t>
   </si>
   <si>
     <t xml:space="preserve">10.6895780563354</t>
@@ -4742,7 +4742,7 @@
     <t xml:space="preserve">10.7641563415527</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7724409103394</t>
+    <t xml:space="preserve">10.7724456787109</t>
   </si>
   <si>
     <t xml:space="preserve">11.1552782058716</t>
@@ -4751,64 +4751,64 @@
     <t xml:space="preserve">11.0840158462524</t>
   </si>
   <si>
-    <t xml:space="preserve">11.166880607605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2248859405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1933975219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2630043029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0094375610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3591251373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4237632751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2497463226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4668531417847</t>
+    <t xml:space="preserve">11.1668796539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2248849868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1933965682983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2630033493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0094347000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3591270446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4237613677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2497434616089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4668521881104</t>
   </si>
   <si>
     <t xml:space="preserve">11.5546884536743</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5795478820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7999668121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9458112716675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9507827758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8728885650635</t>
+    <t xml:space="preserve">11.5795469284058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7999677658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9458103179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9507846832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8728895187378</t>
   </si>
   <si>
     <t xml:space="preserve">11.9093503952026</t>
   </si>
   <si>
-    <t xml:space="preserve">11.982271194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8115692138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9789562225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9325532913208</t>
+    <t xml:space="preserve">11.9822721481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8115682601929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9789571762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9325523376465</t>
   </si>
   <si>
     <t xml:space="preserve">11.7502498626709</t>
@@ -4823,46 +4823,46 @@
     <t xml:space="preserve">11.8430585861206</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7419624328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7137870788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4734792709351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3939294815063</t>
+    <t xml:space="preserve">11.7419633865356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7137899398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4734783172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3939304351807</t>
   </si>
   <si>
     <t xml:space="preserve">11.4718236923218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3491840362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5231990814209</t>
+    <t xml:space="preserve">11.3491830825806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5232000350952</t>
   </si>
   <si>
     <t xml:space="preserve">11.7336778640747</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8861484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2225799560547</t>
+    <t xml:space="preserve">11.8861474990845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2225790023804</t>
   </si>
   <si>
     <t xml:space="preserve">12.237494468689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2855558395386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1728610992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1927490234375</t>
+    <t xml:space="preserve">12.2855567932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1728601455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1927480697632</t>
   </si>
   <si>
     <t xml:space="preserve">11.8496866226196</t>
@@ -4880,193 +4880,193 @@
     <t xml:space="preserve">11.0690984725952</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9315452575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1039009094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0757293701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9133138656616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0574989318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1320762634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2166004180908</t>
+    <t xml:space="preserve">10.9315433502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1039028167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0757284164429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9133129119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0574970245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1320772171021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2165994644165</t>
   </si>
   <si>
     <t xml:space="preserve">11.1221323013306</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1188182830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0972747802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1287612915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7094650268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8055877685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2006750106812</t>
+    <t xml:space="preserve">11.1188192367554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0972738265991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1287641525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7094659805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8055868148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2006740570068</t>
   </si>
   <si>
     <t xml:space="preserve">10.0780344009399</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3008289337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5185575485229</t>
+    <t xml:space="preserve">10.3008270263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5185585021973</t>
   </si>
   <si>
     <t xml:space="preserve">10.5303735733032</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5101194381714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2721357345581</t>
+    <t xml:space="preserve">10.5101203918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2721338272095</t>
   </si>
   <si>
     <t xml:space="preserve">10.3869066238403</t>
   </si>
   <si>
-    <t xml:space="preserve">10.58775806427</t>
+    <t xml:space="preserve">10.5877599716187</t>
   </si>
   <si>
     <t xml:space="preserve">10.6957807540894</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8746900558472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8915681838989</t>
+    <t xml:space="preserve">10.8746891021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8915691375732</t>
   </si>
   <si>
     <t xml:space="preserve">11.3354682922363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2325096130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3371553421021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4266119003296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6325283050537</t>
+    <t xml:space="preserve">11.2325124740601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3371562957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4266109466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6325263977051</t>
   </si>
   <si>
     <t xml:space="preserve">11.5329456329346</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7000379562378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6477174758911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7135438919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7219820022583</t>
+    <t xml:space="preserve">11.7000398635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6477184295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7135429382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7219829559326</t>
   </si>
   <si>
     <t xml:space="preserve">11.6072092056274</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4637432098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6173372268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6612205505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4890632629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6004581451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3776626586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1143636703491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0029649734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9489555358887</t>
+    <t xml:space="preserve">11.4637441635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.617335319519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6612195968628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4890604019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.600456237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3776636123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1143627166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.002965927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9489545822144</t>
   </si>
   <si>
     <t xml:space="preserve">11.4519281387329</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5143804550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4097337722778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1346168518066</t>
+    <t xml:space="preserve">11.5143785476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4097318649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1346158981323</t>
   </si>
   <si>
     <t xml:space="preserve">11.296648979187</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2628908157349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1649990081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3050870895386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2578296661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.350658416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3849782943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4656248092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4690561294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.192795753479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.318058013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3386468887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0726823806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6814594268799</t>
+    <t xml:space="preserve">11.2628917694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1649980545044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3050861358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2578287124634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3506593704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3849763870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4656238555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4690551757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1927967071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3180570602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3386478424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0726833343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6814584732056</t>
   </si>
   <si>
     <t xml:space="preserve">10.9714450836182</t>
@@ -5087,13 +5087,13 @@
     <t xml:space="preserve">11.2528524398804</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0074796676636</t>
+    <t xml:space="preserve">11.0074777603149</t>
   </si>
   <si>
     <t xml:space="preserve">11.1190118789673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1413202285767</t>
+    <t xml:space="preserve">11.1413192749023</t>
   </si>
   <si>
     <t xml:space="preserve">11.1962289810181</t>
@@ -5105,10 +5105,10 @@
     <t xml:space="preserve">11.1447515487671</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9954681396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2099552154541</t>
+    <t xml:space="preserve">10.9954671859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2099571228027</t>
   </si>
   <si>
     <t xml:space="preserve">11.0555229187012</t>
@@ -5126,7 +5126,7 @@
     <t xml:space="preserve">10.9834566116333</t>
   </si>
   <si>
-    <t xml:space="preserve">11.057240486145</t>
+    <t xml:space="preserve">11.0572395324707</t>
   </si>
   <si>
     <t xml:space="preserve">11.3094778060913</t>
@@ -5135,28 +5135,28 @@
     <t xml:space="preserve">11.5068044662476</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5514183044434</t>
+    <t xml:space="preserve">11.5514192581177</t>
   </si>
   <si>
     <t xml:space="preserve">11.4707717895508</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1825017929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1979427337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2562847137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3540906906128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6114749908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6852569580078</t>
+    <t xml:space="preserve">11.1825008392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1979446411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2562837600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3540916442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.611475944519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6852588653564</t>
   </si>
   <si>
     <t xml:space="preserve">11.5188159942627</t>
@@ -5165,7 +5165,7 @@
     <t xml:space="preserve">11.4055671691895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5222501754761</t>
+    <t xml:space="preserve">11.5222492218018</t>
   </si>
   <si>
     <t xml:space="preserve">11.6166229248047</t>
@@ -5174,46 +5174,46 @@
     <t xml:space="preserve">11.7024173736572</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8465538024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7624750137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6595211029053</t>
+    <t xml:space="preserve">11.8465518951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7624759674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6595191955566</t>
   </si>
   <si>
     <t xml:space="preserve">11.7796325683594</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7178602218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9117565155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8190975189209</t>
+    <t xml:space="preserve">11.7178611755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9117574691772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8190984725952</t>
   </si>
   <si>
     <t xml:space="preserve">11.7247247695923</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7744855880737</t>
+    <t xml:space="preserve">11.7744846343994</t>
   </si>
   <si>
     <t xml:space="preserve">11.7350206375122</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6904058456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0696182250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1193819046021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0524625778198</t>
+    <t xml:space="preserve">11.6904067993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.069619178772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1193809509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0524616241455</t>
   </si>
   <si>
     <t xml:space="preserve">12.0232906341553</t>
@@ -5228,31 +5228,31 @@
     <t xml:space="preserve">12.0404500961304</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0884952545166</t>
+    <t xml:space="preserve">12.0884943008423</t>
   </si>
   <si>
     <t xml:space="preserve">12.1090850830078</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0747680664062</t>
+    <t xml:space="preserve">12.0747671127319</t>
   </si>
   <si>
     <t xml:space="preserve">12.1210966110229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1434030532837</t>
+    <t xml:space="preserve">12.143404006958</t>
   </si>
   <si>
     <t xml:space="preserve">12.2669477462769</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3167095184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3270044326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2549381256104</t>
+    <t xml:space="preserve">12.3167085647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3270053863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2549362182617</t>
   </si>
   <si>
     <t xml:space="preserve">12.4728546142578</t>
@@ -5261,16 +5261,16 @@
     <t xml:space="preserve">12.5277643203735</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7268095016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6907739639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6461601257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6959228515625</t>
+    <t xml:space="preserve">12.7268075942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6907749176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6461610794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6959238052368</t>
   </si>
   <si>
     <t xml:space="preserve">12.9138402938843</t>
@@ -5282,73 +5282,73 @@
     <t xml:space="preserve">12.9738960266113</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1866683959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1574983596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0511646270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.335301399231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.27952003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0877714157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2812643051147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2638320922852</t>
+    <t xml:space="preserve">13.1866693496704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1574993133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0511636734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3353023529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2795209884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0877704620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2812652587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2638311386108</t>
   </si>
   <si>
     <t xml:space="preserve">13.2289695739746</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3980550765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4398927688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2969512939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9866676330566</t>
+    <t xml:space="preserve">13.3980569839478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4398937225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2969522476196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.986665725708</t>
   </si>
   <si>
     <t xml:space="preserve">12.8367538452148</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6362895965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5857353210449</t>
+    <t xml:space="preserve">12.6362886428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5857343673706</t>
   </si>
   <si>
     <t xml:space="preserve">12.7600536346436</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0494213104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2045640945435</t>
+    <t xml:space="preserve">13.0494203567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2045650482178</t>
   </si>
   <si>
     <t xml:space="preserve">13.1487827301025</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3318157196045</t>
+    <t xml:space="preserve">13.3318147659302</t>
   </si>
   <si>
     <t xml:space="preserve">13.5078763961792</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4921865463257</t>
+    <t xml:space="preserve">13.4921875</t>
   </si>
   <si>
     <t xml:space="preserve">13.5375108718872</t>
@@ -5357,10 +5357,10 @@
     <t xml:space="preserve">13.6316423416138</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4677829742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4207172393799</t>
+    <t xml:space="preserve">13.4677839279175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4207181930542</t>
   </si>
   <si>
     <t xml:space="preserve">13.4538383483887</t>
@@ -5369,37 +5369,37 @@
     <t xml:space="preserve">13.4276914596558</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4939308166504</t>
+    <t xml:space="preserve">13.4939317703247</t>
   </si>
   <si>
     <t xml:space="preserve">13.5183362960815</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3910837173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4468650817871</t>
+    <t xml:space="preserve">13.3910846710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4468660354614</t>
   </si>
   <si>
     <t xml:space="preserve">13.687424659729</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3928279876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4259471893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.084285736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9221687316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.018045425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0720834732056</t>
+    <t xml:space="preserve">13.3928270339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4259481430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0842847824097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9221706390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0180425643921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0720815658569</t>
   </si>
   <si>
     <t xml:space="preserve">13.2760343551636</t>
@@ -5408,40 +5408,40 @@
     <t xml:space="preserve">13.2917232513428</t>
   </si>
   <si>
-    <t xml:space="preserve">13.239426612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9518022537231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2843284606934</t>
+    <t xml:space="preserve">13.2394275665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9518032073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.284330368042</t>
   </si>
   <si>
     <t xml:space="preserve">13.2188272476196</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0329456329346</t>
+    <t xml:space="preserve">13.0329465866089</t>
   </si>
   <si>
     <t xml:space="preserve">13.2205972671509</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3374366760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3038024902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.452507019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3728446960449</t>
+    <t xml:space="preserve">13.3374376296997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3038015365601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4525060653687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3728437423706</t>
   </si>
   <si>
     <t xml:space="preserve">13.425952911377</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4985342025757</t>
+    <t xml:space="preserve">13.49853515625</t>
   </si>
   <si>
     <t xml:space="preserve">13.2418413162231</t>
@@ -5450,28 +5450,28 @@
     <t xml:space="preserve">13.3569107055664</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1993532180786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0736637115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2860994338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2630844116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1037578582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0559587478638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1427040100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1126079559326</t>
+    <t xml:space="preserve">13.1993541717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0736627578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2860984802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2630853652954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1037588119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0559606552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1427030563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1126108169556</t>
   </si>
   <si>
     <t xml:space="preserve">13.2701654434204</t>
@@ -5480,16 +5480,16 @@
     <t xml:space="preserve">13.3002614974976</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4578189849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4542779922485</t>
+    <t xml:space="preserve">13.457818031311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4542770385742</t>
   </si>
   <si>
     <t xml:space="preserve">13.5321702957153</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6631727218628</t>
+    <t xml:space="preserve">13.6631717681885</t>
   </si>
   <si>
     <t xml:space="preserve">13.5941305160522</t>
@@ -5501,31 +5501,31 @@
     <t xml:space="preserve">13.7693901062012</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6649436950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7375259399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7552289962769</t>
+    <t xml:space="preserve">13.664942741394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7375249862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7552280426025</t>
   </si>
   <si>
     <t xml:space="preserve">13.3480587005615</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2099752426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1745691299438</t>
+    <t xml:space="preserve">13.2099771499634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1745700836182</t>
   </si>
   <si>
     <t xml:space="preserve">13.1108388900757</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3144226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2737064361572</t>
+    <t xml:space="preserve">13.3144235610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2737073898315</t>
   </si>
   <si>
     <t xml:space="preserve">13.2170581817627</t>
@@ -5534,34 +5534,34 @@
     <t xml:space="preserve">12.9692153930664</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9302682876587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7904138565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6930484771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7089824676514</t>
+    <t xml:space="preserve">12.9302673339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7904148101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6930475234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7089815139771</t>
   </si>
   <si>
     <t xml:space="preserve">12.8258209228516</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8930921554565</t>
+    <t xml:space="preserve">12.8930931091309</t>
   </si>
   <si>
     <t xml:space="preserve">13.0612697601318</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2064352035522</t>
+    <t xml:space="preserve">13.2064361572266</t>
   </si>
   <si>
     <t xml:space="preserve">13.0984477996826</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9107961654663</t>
+    <t xml:space="preserve">12.910795211792</t>
   </si>
   <si>
     <t xml:space="preserve">12.7231435775757</t>
@@ -5570,16 +5570,16 @@
     <t xml:space="preserve">12.9249582290649</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7196016311646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7160634994507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6523323059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7797927856445</t>
+    <t xml:space="preserve">12.7196025848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7160625457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6523313522339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7797918319702</t>
   </si>
   <si>
     <t xml:space="preserve">12.8081188201904</t>
@@ -5591,124 +5591,124 @@
     <t xml:space="preserve">12.9267282485962</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5284109115601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5425729751587</t>
+    <t xml:space="preserve">12.5284118652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5425720214844</t>
   </si>
   <si>
     <t xml:space="preserve">12.508936882019</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6594133377075</t>
+    <t xml:space="preserve">12.6594123840332</t>
   </si>
   <si>
     <t xml:space="preserve">12.595682144165</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6186952590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6151552200317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7284536361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7072114944458</t>
+    <t xml:space="preserve">12.6186962127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6151561737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7284545898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7072105407715</t>
   </si>
   <si>
     <t xml:space="preserve">12.6116151809692</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6824254989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7355346679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8417530059814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9479703903198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9515132904053</t>
+    <t xml:space="preserve">12.682427406311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7355356216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8417539596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9479722976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.951512336731</t>
   </si>
   <si>
     <t xml:space="preserve">13.0134725570679</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8860120773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.004620552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.257773399353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8541460037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8399820327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7949810028076</t>
+    <t xml:space="preserve">12.8860101699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0046215057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2577753067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8541450500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8399829864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7949819564819</t>
   </si>
   <si>
     <t xml:space="preserve">13.1009941101074</t>
   </si>
   <si>
-    <t xml:space="preserve">12.893985748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9245872497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9191875457764</t>
+    <t xml:space="preserve">12.8939867019653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9245882034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9191865921021</t>
   </si>
   <si>
     <t xml:space="preserve">13.0991954803467</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0955953598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1135950088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1837978363037</t>
+    <t xml:space="preserve">13.0955944061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1135959625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1837997436523</t>
   </si>
   <si>
     <t xml:space="preserve">13.5276145935059</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6590204238892</t>
+    <t xml:space="preserve">13.6590194702148</t>
   </si>
   <si>
     <t xml:space="preserve">13.8138275146484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9578342437744</t>
+    <t xml:space="preserve">13.9578332901001</t>
   </si>
   <si>
     <t xml:space="preserve">13.9632339477539</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9020309448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8390293121338</t>
+    <t xml:space="preserve">13.9020318984985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8390302658081</t>
   </si>
   <si>
     <t xml:space="preserve">13.786826133728</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1576414108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9812355041504</t>
+    <t xml:space="preserve">14.1576433181763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9812345504761</t>
   </si>
   <si>
     <t xml:space="preserve">13.6806221008301</t>
@@ -5720,10 +5720,10 @@
     <t xml:space="preserve">13.7076225280762</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7328243255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8066272735596</t>
+    <t xml:space="preserve">13.7328252792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8066282272339</t>
   </si>
   <si>
     <t xml:space="preserve">13.9686346054077</t>
@@ -5732,22 +5732,22 @@
     <t xml:space="preserve">13.7130222320557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7292222976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7346248626709</t>
+    <t xml:space="preserve">13.7292232513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7346239089966</t>
   </si>
   <si>
     <t xml:space="preserve">13.7472248077393</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6230192184448</t>
+    <t xml:space="preserve">13.6230182647705</t>
   </si>
   <si>
     <t xml:space="preserve">13.3422069549561</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2378005981445</t>
+    <t xml:space="preserve">13.2378015518188</t>
   </si>
   <si>
     <t xml:space="preserve">13.3692073822021</t>
@@ -5759,43 +5759,43 @@
     <t xml:space="preserve">13.4430112838745</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5294141769409</t>
+    <t xml:space="preserve">13.5294132232666</t>
   </si>
   <si>
     <t xml:space="preserve">13.6626214981079</t>
   </si>
   <si>
-    <t xml:space="preserve">13.714822769165</t>
+    <t xml:space="preserve">13.7148237228394</t>
   </si>
   <si>
     <t xml:space="preserve">13.6014184951782</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3026037216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3458070755005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4024887084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3366651535034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2105016708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2452421188354</t>
+    <t xml:space="preserve">13.302604675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3458061218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4024877548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3366641998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2105026245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2452430725098</t>
   </si>
   <si>
     <t xml:space="preserve">13.1501626968384</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3311786651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3092384338379</t>
+    <t xml:space="preserve">13.3311796188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3092374801636</t>
   </si>
   <si>
     <t xml:space="preserve">13.1519918441772</t>
@@ -5804,25 +5804,25 @@
     <t xml:space="preserve">13.1355352401733</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2525568008423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1812467575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8119010925293</t>
+    <t xml:space="preserve">13.252555847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.181245803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.811900138855</t>
   </si>
   <si>
     <t xml:space="preserve">12.7497339248657</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8630962371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7917881011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.897837638855</t>
+    <t xml:space="preserve">12.8630971908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.791787147522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8978366851807</t>
   </si>
   <si>
     <t xml:space="preserve">12.7881307601929</t>
@@ -5831,58 +5831,58 @@
     <t xml:space="preserve">12.7460775375366</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5412912368774</t>
+    <t xml:space="preserve">12.5412921905518</t>
   </si>
   <si>
     <t xml:space="preserve">12.3493051528931</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3730745315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6016311645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7058506011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9197778701782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7405910491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9124660491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0148572921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0185146331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0861682891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1227369308472</t>
+    <t xml:space="preserve">12.3730754852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6016302108765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7058515548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9197797775269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7405920028687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.91246509552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0148591995239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0185136795044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0861673355103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1227359771729</t>
   </si>
   <si>
     <t xml:space="preserve">13.2854681015015</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2818117141724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.221471786499</t>
+    <t xml:space="preserve">13.281810760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2214727401733</t>
   </si>
   <si>
     <t xml:space="preserve">13.3531198501587</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2141590118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0751972198486</t>
+    <t xml:space="preserve">13.2141580581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0751962661743</t>
   </si>
   <si>
     <t xml:space="preserve">12.9014959335327</t>
@@ -5894,13 +5894,13 @@
     <t xml:space="preserve">12.9819469451904</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0678844451904</t>
+    <t xml:space="preserve">13.0678825378418</t>
   </si>
   <si>
     <t xml:space="preserve">13.0166873931885</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8100728988647</t>
+    <t xml:space="preserve">12.8100738525391</t>
   </si>
   <si>
     <t xml:space="preserve">12.9216070175171</t>
@@ -5912,16 +5912,16 @@
     <t xml:space="preserve">12.872239112854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8649263381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8228721618652</t>
+    <t xml:space="preserve">12.8649253845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8228712081909</t>
   </si>
   <si>
     <t xml:space="preserve">12.8521270751953</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8173875808716</t>
+    <t xml:space="preserve">12.8173866271973</t>
   </si>
   <si>
     <t xml:space="preserve">13.3750610351562</t>
@@ -5930,61 +5930,61 @@
     <t xml:space="preserve">13.3842039108276</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5286521911621</t>
+    <t xml:space="preserve">13.5286512374878</t>
   </si>
   <si>
     <t xml:space="preserve">13.3019247055054</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9965734481812</t>
+    <t xml:space="preserve">12.9965724945068</t>
   </si>
   <si>
     <t xml:space="preserve">12.7387638092041</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7277936935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0441131591797</t>
+    <t xml:space="preserve">12.7277927398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0441122055054</t>
   </si>
   <si>
     <t xml:space="preserve">13.2159872055054</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0971384048462</t>
+    <t xml:space="preserve">13.0971393585205</t>
   </si>
   <si>
     <t xml:space="preserve">13.2543849945068</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3640899658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2507286071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2708406448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1666202545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4719705581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4408855438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.413459777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5359659194946</t>
+    <t xml:space="preserve">13.3640909194946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2507276535034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2708396911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.166618347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4719686508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4408864974976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4134588241577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5359649658203</t>
   </si>
   <si>
     <t xml:space="preserve">13.4152870178223</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4390563964844</t>
+    <t xml:space="preserve">13.4390573501587</t>
   </si>
   <si>
     <t xml:space="preserve">13.1007957458496</t>
@@ -6011,13 +6011,13 @@
     <t xml:space="preserve">13.0002317428589</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0276584625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0569124221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.122049331665</t>
+    <t xml:space="preserve">13.0276575088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0569114685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1220483779907</t>
   </si>
   <si>
     <t xml:space="preserve">13.1778783798218</t>
@@ -6026,7 +6026,7 @@
     <t xml:space="preserve">13.0234155654907</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6270179748535</t>
+    <t xml:space="preserve">12.6270170211792</t>
   </si>
   <si>
     <t xml:space="preserve">12.7200689315796</t>
@@ -6035,7 +6035,7 @@
     <t xml:space="preserve">12.7312345504761</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9247817993164</t>
+    <t xml:space="preserve">12.9247808456421</t>
   </si>
   <si>
     <t xml:space="preserve">13.1369371414185</t>
@@ -6047,7 +6047,7 @@
     <t xml:space="preserve">13.3286218643188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4961137771606</t>
+    <t xml:space="preserve">13.4961128234863</t>
   </si>
   <si>
     <t xml:space="preserve">13.2076549530029</t>
@@ -6056,61 +6056,61 @@
     <t xml:space="preserve">13.181601524353</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2709302902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3267602920532</t>
+    <t xml:space="preserve">13.2709312438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3267593383789</t>
   </si>
   <si>
     <t xml:space="preserve">13.3565368652344</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9936380386353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0606365203857</t>
+    <t xml:space="preserve">12.9936370849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0606355667114</t>
   </si>
   <si>
     <t xml:space="preserve">13.2653465270996</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2858171463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1946296691895</t>
+    <t xml:space="preserve">13.2858180999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1946287155151</t>
   </si>
   <si>
     <t xml:space="preserve">13.2374315261841</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4253950119019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0196924209595</t>
+    <t xml:space="preserve">13.4253940582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0196914672852</t>
   </si>
   <si>
     <t xml:space="preserve">13.0383033752441</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0587749481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0476083755493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1350755691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0308589935303</t>
+    <t xml:space="preserve">13.0587739944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0476093292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1350765228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.030858039856</t>
   </si>
   <si>
     <t xml:space="preserve">13.1108827590942</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9620018005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0364418029785</t>
+    <t xml:space="preserve">12.9620008468628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0364427566528</t>
   </si>
   <si>
     <t xml:space="preserve">12.8522005081177</t>
@@ -6125,19 +6125,19 @@
     <t xml:space="preserve">13.1638307571411</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0103664398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0046834945679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0861520767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1827774047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0160512924194</t>
+    <t xml:space="preserve">13.0103673934937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0046825408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0861511230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1827783584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0160503387451</t>
   </si>
   <si>
     <t xml:space="preserve">12.7470149993896</t>
@@ -6155,7 +6155,7 @@
     <t xml:space="preserve">12.6390218734741</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7602767944336</t>
+    <t xml:space="preserve">12.7602777481079</t>
   </si>
   <si>
     <t xml:space="preserve">12.7754344940186</t>
@@ -6170,7 +6170,7 @@
     <t xml:space="preserve">12.7830123901367</t>
   </si>
   <si>
-    <t xml:space="preserve">12.69775390625</t>
+    <t xml:space="preserve">12.6977548599243</t>
   </si>
   <si>
     <t xml:space="preserve">12.6693344116211</t>
@@ -6185,7 +6185,7 @@
     <t xml:space="preserve">12.4097719192505</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1104221343994</t>
+    <t xml:space="preserve">12.1104211807251</t>
   </si>
   <si>
     <t xml:space="preserve">12.2127313613892</t>
@@ -6209,19 +6209,19 @@
     <t xml:space="preserve">12.7526979446411</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9213190078735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9421606063843</t>
+    <t xml:space="preserve">12.9213199615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.94215965271</t>
   </si>
   <si>
     <t xml:space="preserve">12.9516344070435</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0141563415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0198392868042</t>
+    <t xml:space="preserve">13.0141553878784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0198402404785</t>
   </si>
   <si>
     <t xml:space="preserve">13.1410961151123</t>
@@ -6230,7 +6230,7 @@
     <t xml:space="preserve">13.2471952438354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2093019485474</t>
+    <t xml:space="preserve">13.2093029022217</t>
   </si>
   <si>
     <t xml:space="preserve">13.3495044708252</t>
@@ -6245,7 +6245,7 @@
     <t xml:space="preserve">12.9554224014282</t>
   </si>
   <si>
-    <t xml:space="preserve">12.877742767334</t>
+    <t xml:space="preserve">12.8777437210083</t>
   </si>
   <si>
     <t xml:space="preserve">12.7015438079834</t>
@@ -6257,25 +6257,25 @@
     <t xml:space="preserve">12.7242794036865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7413301467896</t>
+    <t xml:space="preserve">12.7413291931152</t>
   </si>
   <si>
     <t xml:space="preserve">12.9175310134888</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9781589508057</t>
+    <t xml:space="preserve">12.9781579971313</t>
   </si>
   <si>
     <t xml:space="preserve">12.9118461608887</t>
   </si>
   <si>
-    <t xml:space="preserve">13.057731628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0842561721802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1316232681274</t>
+    <t xml:space="preserve">13.0577325820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0842571258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1316242218018</t>
   </si>
   <si>
     <t xml:space="preserve">13.1543579101562</t>
@@ -6284,7 +6284,7 @@
     <t xml:space="preserve">13.3210859298706</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2869815826416</t>
+    <t xml:space="preserve">13.2869806289673</t>
   </si>
   <si>
     <t xml:space="preserve">13.2547721862793</t>
@@ -6293,7 +6293,7 @@
     <t xml:space="preserve">13.2983493804932</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3343477249146</t>
+    <t xml:space="preserve">13.3343467712402</t>
   </si>
   <si>
     <t xml:space="preserve">13.3513984680176</t>
@@ -6305,34 +6305,34 @@
     <t xml:space="preserve">13.3154001235962</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2263526916504</t>
+    <t xml:space="preserve">13.2263536453247</t>
   </si>
   <si>
     <t xml:space="preserve">13.2964553833008</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3930797576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5219144821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3324527740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.124044418335</t>
+    <t xml:space="preserve">13.3930807113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.521915435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3324537277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1240434646606</t>
   </si>
   <si>
     <t xml:space="preserve">13.1202554702759</t>
   </si>
   <si>
-    <t xml:space="preserve">12.565131187439</t>
+    <t xml:space="preserve">12.5651302337646</t>
   </si>
   <si>
     <t xml:space="preserve">12.4514532089233</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5196599960327</t>
+    <t xml:space="preserve">12.5196590423584</t>
   </si>
   <si>
     <t xml:space="preserve">12.8227996826172</t>
@@ -6347,19 +6347,19 @@
     <t xml:space="preserve">12.9364767074585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.995210647583</t>
+    <t xml:space="preserve">12.9952096939087</t>
   </si>
   <si>
     <t xml:space="preserve">13.2850875854492</t>
   </si>
   <si>
-    <t xml:space="preserve">13.404447555542</t>
+    <t xml:space="preserve">13.4044485092163</t>
   </si>
   <si>
     <t xml:space="preserve">13.5806484222412</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6848516464233</t>
+    <t xml:space="preserve">13.6848526000977</t>
   </si>
   <si>
     <t xml:space="preserve">13.618540763855</t>
@@ -6792,6 +6792,9 @@
   </si>
   <si>
     <t xml:space="preserve">15.5860004425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8360004425049</t>
   </si>
 </sst>
 </file>
@@ -72000,7 +72003,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45953.6522106481</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>30583218</v>
@@ -72021,6 +72024,32 @@
         <v>2259</v>
       </c>
       <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.6494444444</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>21544743</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>16.0319995880127</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>15.6379995346069</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>15.8299999237061</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>15.8360004425049</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>2260</v>
+      </c>
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ENI.MI.xlsx
+++ b/data/ENI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2280" uniqueCount="2280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2281" uniqueCount="2281">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,118 +38,118 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26820802688599</t>
+    <t xml:space="preserve">7.26820659637451</t>
   </si>
   <si>
     <t xml:space="preserve">ENI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33315086364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12749814987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07337999343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8731369972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84608030319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86231279373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94349241256714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04090595245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79195928573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71619081497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8081955909729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58089351654053</t>
+    <t xml:space="preserve">7.3331503868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12749767303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07337856292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87313795089722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84607744216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86231374740601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94349145889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04090738296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79195785522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71618986129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80819272994995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58089208602905</t>
   </si>
   <si>
     <t xml:space="preserve">7.01925897598267</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93266868591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07878971099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11126232147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18702840805054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77031183242798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74325227737427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89478492736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78113603591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53759813308716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2778263092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29406118392944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91522598266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3102970123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46183109283447</t>
+    <t xml:space="preserve">6.93266916275024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07879018783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11126184463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18702793121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77030992507935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74325084686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89478540420532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78113412857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53759860992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27782583236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29406213760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91522693634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31029748916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46183156967163</t>
   </si>
   <si>
     <t xml:space="preserve">6.41312456130981</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61877775192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47806739807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45100688934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68372011184692</t>
+    <t xml:space="preserve">6.61877632141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47806644439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45100784301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68372106552124</t>
   </si>
   <si>
     <t xml:space="preserve">6.37524127960205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54300975799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87854814529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00843477249146</t>
+    <t xml:space="preserve">6.54300928115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87855052947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00843381881714</t>
   </si>
   <si>
     <t xml:space="preserve">7.22491312026978</t>
@@ -158,136 +158,136 @@
     <t xml:space="preserve">7.27903127670288</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37644481658936</t>
+    <t xml:space="preserve">7.3764443397522</t>
   </si>
   <si>
     <t xml:space="preserve">7.32773780822754</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35480117797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1707911491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25197219848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00302410125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20867490768433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24656009674072</t>
+    <t xml:space="preserve">7.35479784011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17079305648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25197076797485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00302314758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20867586135864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24656057357788</t>
   </si>
   <si>
     <t xml:space="preserve">7.14373350143433</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23573398590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36562347412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43056344985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46844911575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28985691070557</t>
+    <t xml:space="preserve">7.23573684692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36562204360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43056488037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4684476852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28985452651978</t>
   </si>
   <si>
     <t xml:space="preserve">7.1166729927063</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3169150352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19785070419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92184257507324</t>
+    <t xml:space="preserve">7.31691360473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19785261154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92184638977051</t>
   </si>
   <si>
     <t xml:space="preserve">6.90560865402222</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73242664337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80278348922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66748428344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95431613922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9759635925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01384735107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29526805877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42515277862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30609035491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39809322357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51715612411499</t>
+    <t xml:space="preserve">6.7324275970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80278396606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66748380661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95431709289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97596216201782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01384782791138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29526710510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42515182495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30608892440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39809274673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51715469360352</t>
   </si>
   <si>
     <t xml:space="preserve">7.61457061767578</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65786361694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61998081207275</t>
+    <t xml:space="preserve">7.65786647796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61998128890991</t>
   </si>
   <si>
     <t xml:space="preserve">7.65245389938354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72280740737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79316329956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6849250793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54962825775146</t>
+    <t xml:space="preserve">7.72280836105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79316377639771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68492603302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54962778091431</t>
   </si>
   <si>
     <t xml:space="preserve">7.39268350601196</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24114894866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34397411346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40891695022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13832235336304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22407960891724</t>
+    <t xml:space="preserve">7.24114561080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34397506713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40891742706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13832139968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22407817840576</t>
   </si>
   <si>
     <t xml:space="preserve">7.44721841812134</t>
@@ -296,121 +296,121 @@
     <t xml:space="preserve">7.70382452011108</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74287223815918</t>
+    <t xml:space="preserve">7.74287366867065</t>
   </si>
   <si>
     <t xml:space="preserve">7.71498107910156</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77634572982788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65919733047485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55320644378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54762840270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48626661300659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68151140213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86001968383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88233280181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84328413009644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50300025939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3635401725769</t>
+    <t xml:space="preserve">7.77634525299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65919589996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55320596694946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5476279258728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48626518249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68151187896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86002159118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88233518600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84328556060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50300168991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36354064941406</t>
   </si>
   <si>
     <t xml:space="preserve">7.45837450027466</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38027429580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67035531997681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89907073974609</t>
+    <t xml:space="preserve">7.38027477264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67035388946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89907169342041</t>
   </si>
   <si>
     <t xml:space="preserve">7.99948358535767</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8767557144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13336563110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38585519790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62014770507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97716760635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09989547729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26724720001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03853225708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88791275024414</t>
+    <t xml:space="preserve">7.87675619125366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13336658477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38585376739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62015056610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97716903686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09989452362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26724815368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03853034973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88791418075562</t>
   </si>
   <si>
     <t xml:space="preserve">7.93254137039185</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08873558044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18356990814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26167011260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16125774383545</t>
+    <t xml:space="preserve">8.08873653411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18357086181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26166915893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16125679016113</t>
   </si>
   <si>
     <t xml:space="preserve">8.31187534332275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21146392822266</t>
+    <t xml:space="preserve">8.21146297454834</t>
   </si>
   <si>
     <t xml:space="preserve">8.12220764160156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09431648254395</t>
+    <t xml:space="preserve">8.09431552886963</t>
   </si>
   <si>
     <t xml:space="preserve">8.01621723175049</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97159051895142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93811798095703</t>
+    <t xml:space="preserve">7.97159099578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93811941146851</t>
   </si>
   <si>
     <t xml:space="preserve">7.82655000686646</t>
@@ -419,85 +419,85 @@
     <t xml:space="preserve">7.83212995529175</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62572622299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63130235671997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4806866645813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32449102401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37469911575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39143133163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56994247436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55878782272339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53646993637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64246273040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66477632522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51415967941284</t>
+    <t xml:space="preserve">7.62572526931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63130712509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48068523406982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32449054718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3746976852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39143323898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56994295120239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5587854385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53647375106812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64246225357056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66477489471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51415777206421</t>
   </si>
   <si>
     <t xml:space="preserve">7.49742269515991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59783315658569</t>
+    <t xml:space="preserve">7.5978364944458</t>
   </si>
   <si>
     <t xml:space="preserve">7.59225654602051</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65361928939819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5643630027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31333446502686</t>
+    <t xml:space="preserve">7.65361785888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56436395645142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31333303451538</t>
   </si>
   <si>
     <t xml:space="preserve">7.33564758300781</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36911773681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20176649093628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3111457824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17873859405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20176410675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28236103057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25357675552368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12117099761963</t>
+    <t xml:space="preserve">7.36911964416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20176696777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31114530563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17873907089233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2017650604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28236055374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25357627868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12117004394531</t>
   </si>
   <si>
     <t xml:space="preserve">7.08662986755371</t>
@@ -506,46 +506,46 @@
     <t xml:space="preserve">7.10965824127197</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43779611587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38022565841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42052507400513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46657800674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63928413391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65079498291016</t>
+    <t xml:space="preserve">7.43779516220093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38022518157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42052221298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4665789604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63928365707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65079689025879</t>
   </si>
   <si>
     <t xml:space="preserve">7.82925748825073</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67957782745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62776803970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57595682144165</t>
+    <t xml:space="preserve">7.67958068847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.627769947052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57595729827881</t>
   </si>
   <si>
     <t xml:space="preserve">7.72563552856445</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6623101234436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80047559738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82349967956543</t>
+    <t xml:space="preserve">7.66231203079224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8004732131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8235011100769</t>
   </si>
   <si>
     <t xml:space="preserve">7.90409564971924</t>
@@ -554,112 +554,112 @@
     <t xml:space="preserve">7.92712354660034</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87530899047852</t>
+    <t xml:space="preserve">7.8753137588501</t>
   </si>
   <si>
     <t xml:space="preserve">7.79471588134766</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91561079025269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77744436264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60474109649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48385000228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37447261810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31690073013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2478199005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35144472122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39749717712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36871385574341</t>
+    <t xml:space="preserve">7.91560840606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77744913101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60474300384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48384952545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37447071075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31690311431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24782037734985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35144424438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3974986076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36871194839478</t>
   </si>
   <si>
     <t xml:space="preserve">7.33992910385132</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22479295730591</t>
+    <t xml:space="preserve">7.22479248046875</t>
   </si>
   <si>
     <t xml:space="preserve">7.05784559249878</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19600915908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1499547958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12692928314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23630619049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24206352233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28811645507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56444406509399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83501482009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88106918334961</t>
+    <t xml:space="preserve">7.19600772857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14995384216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12692737579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23630809783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24206161499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28811502456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56444454193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83501434326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88106822967529</t>
   </si>
   <si>
     <t xml:space="preserve">8.03650188446045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11709785461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19193458557129</t>
+    <t xml:space="preserve">8.11709594726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19193553924561</t>
   </si>
   <si>
     <t xml:space="preserve">8.20345020294189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50856304168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59491443634033</t>
+    <t xml:space="preserve">8.50856018066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5949125289917</t>
   </si>
   <si>
     <t xml:space="preserve">8.56613063812256</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61794090270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66399478912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61218452453613</t>
+    <t xml:space="preserve">8.61793804168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66399574279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6121826171875</t>
   </si>
   <si>
     <t xml:space="preserve">8.72156238555908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73307800292969</t>
+    <t xml:space="preserve">8.73307418823242</t>
   </si>
   <si>
     <t xml:space="preserve">8.83094310760498</t>
@@ -668,97 +668,97 @@
     <t xml:space="preserve">8.81367206573486</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88851070404053</t>
+    <t xml:space="preserve">8.88850975036621</t>
   </si>
   <si>
     <t xml:space="preserve">8.90577983856201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00364589691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99788951873779</t>
+    <t xml:space="preserve">9.00364685058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99788856506348</t>
   </si>
   <si>
     <t xml:space="preserve">9.03242969512939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0496997833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85972785949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95183563232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94607830047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90002536773682</t>
+    <t xml:space="preserve">9.04970169067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85972690582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9518346786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94607925415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9000244140625</t>
   </si>
   <si>
     <t xml:space="preserve">9.02091693878174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86548328399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96334934234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92880630493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83670043945312</t>
+    <t xml:space="preserve">8.86548233032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96334743499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92880821228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83669853210449</t>
   </si>
   <si>
     <t xml:space="preserve">8.60642623901367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50280475616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28404521942139</t>
+    <t xml:space="preserve">8.50280380249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28404426574707</t>
   </si>
   <si>
     <t xml:space="preserve">8.18042278289795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13436603546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15163898468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3646411895752</t>
+    <t xml:space="preserve">8.13436889648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15163993835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36463928222656</t>
   </si>
   <si>
     <t xml:space="preserve">8.17466640472412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14012432098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26677417755127</t>
+    <t xml:space="preserve">8.14012622833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26677513122559</t>
   </si>
   <si>
     <t xml:space="preserve">8.28980159759521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37039947509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27828884124756</t>
+    <t xml:space="preserve">8.37039756774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27828979492188</t>
   </si>
   <si>
     <t xml:space="preserve">8.12861061096191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39342498779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29555988311768</t>
+    <t xml:space="preserve">8.39342594146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29555702209473</t>
   </si>
   <si>
     <t xml:space="preserve">8.23223304748535</t>
@@ -770,145 +770,145 @@
     <t xml:space="preserve">8.63521099090576</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64096641540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79064464569092</t>
+    <t xml:space="preserve">8.64096736907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7906436920166</t>
   </si>
   <si>
     <t xml:space="preserve">8.68702220916748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52007389068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4625072479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42220973968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4337215423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33010005950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44523525238037</t>
+    <t xml:space="preserve">8.52007675170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46250629425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42220783233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43372344970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33009910583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44523620605469</t>
   </si>
   <si>
     <t xml:space="preserve">8.58915615081787</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54885768890381</t>
+    <t xml:space="preserve">8.54885864257812</t>
   </si>
   <si>
     <t xml:space="preserve">8.57188701629639</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65248203277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62945556640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70429039001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81942844390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76761531829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76186084747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77337265014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45099258422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45674896240234</t>
+    <t xml:space="preserve">8.65248107910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62945461273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70429229736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81942749023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76761722564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76185894012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7733736038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45099544525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45675086975098</t>
   </si>
   <si>
     <t xml:space="preserve">8.60751914978027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57200050354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47728061676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44768142700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46544075012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42992210388184</t>
+    <t xml:space="preserve">8.57199954986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47727966308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44768238067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46544170379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42992305755615</t>
   </si>
   <si>
     <t xml:space="preserve">8.42400169372559</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63712024688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72591781616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77327537536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82063579559326</t>
+    <t xml:space="preserve">8.63711833953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72591686248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77327728271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82063293457031</t>
   </si>
   <si>
     <t xml:space="preserve">8.81471538543701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87983512878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90943336486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79695510864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90351486206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89167499542236</t>
+    <t xml:space="preserve">8.87983322143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90943431854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79695320129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90351390838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89167404174805</t>
   </si>
   <si>
     <t xml:space="preserve">8.87391471862793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83839416503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67263889312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.471360206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45359992980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3411226272583</t>
+    <t xml:space="preserve">8.83839511871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67263793945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47136402130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4536018371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34112358093262</t>
   </si>
   <si>
     <t xml:space="preserve">8.4417610168457</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31744480133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2641658782959</t>
+    <t xml:space="preserve">8.31744384765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26416492462158</t>
   </si>
   <si>
     <t xml:space="preserve">8.32928371429443</t>
@@ -917,64 +917,64 @@
     <t xml:space="preserve">8.16352653503418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22272682189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22864627838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28784561157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19904613494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15168952941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23456764221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06880760192871</t>
+    <t xml:space="preserve">8.22272491455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22864532470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28784465789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19904708862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15168857574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23456573486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06880855560303</t>
   </si>
   <si>
     <t xml:space="preserve">8.11024761199951</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08656978607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03920841217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05105018615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00368976593018</t>
+    <t xml:space="preserve">8.08657073974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03921031951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05104827880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00368881225586</t>
   </si>
   <si>
     <t xml:space="preserve">8.02736949920654</t>
   </si>
   <si>
-    <t xml:space="preserve">7.873450756073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79057359695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8852915763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90897226333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7964940071106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74913692474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67217588424683</t>
+    <t xml:space="preserve">7.87345361709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7905740737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88529348373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90897274017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79649448394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74913454055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67217683792114</t>
   </si>
   <si>
     <t xml:space="preserve">7.69585657119751</t>
@@ -983,25 +983,25 @@
     <t xml:space="preserve">7.67809629440308</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80833387374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82017374038696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83793497085571</t>
+    <t xml:space="preserve">7.80833435058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82017421722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83793306350708</t>
   </si>
   <si>
     <t xml:space="preserve">7.77873468399048</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77281522750854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78465414047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71953535079956</t>
+    <t xml:space="preserve">7.77281427383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7846531867981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7195348739624</t>
   </si>
   <si>
     <t xml:space="preserve">7.73137474060059</t>
@@ -1010,25 +1010,25 @@
     <t xml:space="preserve">7.84977293014526</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82609510421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91489171981812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97409057617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00961017608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99185085296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02145099639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03328800201416</t>
+    <t xml:space="preserve">7.82609462738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91489410400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97409009933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00960922241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99184894561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02145004272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03329086303711</t>
   </si>
   <si>
     <t xml:space="preserve">8.01552867889404</t>
@@ -1037,97 +1037,97 @@
     <t xml:space="preserve">7.98593044281006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90305185317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93857288360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84385347366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7609748840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87937211990356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89121294021606</t>
+    <t xml:space="preserve">7.90305328369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93856954574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84385395050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76097440719604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8793740272522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89121150970459</t>
   </si>
   <si>
     <t xml:space="preserve">7.92673206329346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98001098632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96817207336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99777126312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07472991943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17536735534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20585155487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24852466583252</t>
+    <t xml:space="preserve">7.98001050949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96817255020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99777269363403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07472896575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17536640167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20584869384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2485237121582</t>
   </si>
   <si>
     <t xml:space="preserve">8.31558704376221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37655067443848</t>
+    <t xml:space="preserve">8.37654972076416</t>
   </si>
   <si>
     <t xml:space="preserve">8.4009370803833</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49847984313965</t>
+    <t xml:space="preserve">8.49847888946533</t>
   </si>
   <si>
     <t xml:space="preserve">8.52896213531494</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49238300323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5045747756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53505897521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51676845550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57773303985596</t>
+    <t xml:space="preserve">8.4923849105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50457668304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53505802154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.516770362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57773399353027</t>
   </si>
   <si>
     <t xml:space="preserve">8.47409343719482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55334949493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44361019134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48628902435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44970798492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46799850463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46189880371094</t>
+    <t xml:space="preserve">8.55334758758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44361114501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48628807067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44970893859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46799564361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46190166473389</t>
   </si>
   <si>
     <t xml:space="preserve">8.39484024047852</t>
@@ -1136,133 +1136,133 @@
     <t xml:space="preserve">8.43141841888428</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41313076019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43751525878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55944442749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66918087005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71795272827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76672458648682</t>
+    <t xml:space="preserve">8.41312789916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43751430511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55944633483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66918182373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71795177459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76672649383545</t>
   </si>
   <si>
     <t xml:space="preserve">8.83988189697266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97400569915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91303825378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84597873687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78501510620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72404861450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62040901184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37045478820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38874435424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4558048248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48019123077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42532157897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34606838226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41922664642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5472526550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57163619995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52286720275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51067161560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68747043609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79720783233643</t>
+    <t xml:space="preserve">8.9740047454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91304016113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84597778320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78501224517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7240514755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6204080581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37045383453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3887414932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45580291748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48018932342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42532253265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34606742858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41922569274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54725170135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57163715362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52286434173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51067352294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68746757507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79720592498779</t>
   </si>
   <si>
     <t xml:space="preserve">8.85207557678223</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96181297302246</t>
+    <t xml:space="preserve">8.96181106567383</t>
   </si>
   <si>
     <t xml:space="preserve">9.09593391418457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08983993530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05935478210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11422157287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04106712341309</t>
+    <t xml:space="preserve">9.08983898162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05935382843018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11422348022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04106521606445</t>
   </si>
   <si>
     <t xml:space="preserve">9.10812664031982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12032032012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10203075408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01668167114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86670684814453</t>
+    <t xml:space="preserve">9.12032127380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10202980041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01667976379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86670780181885</t>
   </si>
   <si>
     <t xml:space="preserve">8.8313455581665</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89475059509277</t>
+    <t xml:space="preserve">8.89475154876709</t>
   </si>
   <si>
     <t xml:space="preserve">8.74721527099609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62894439697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38508415222168</t>
+    <t xml:space="preserve">8.62894535064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38508605957031</t>
   </si>
   <si>
     <t xml:space="preserve">8.3350944519043</t>
@@ -1271,10 +1271,10 @@
     <t xml:space="preserve">8.16805076599121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21926021575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1400089263916</t>
+    <t xml:space="preserve">8.21926116943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14000797271729</t>
   </si>
   <si>
     <t xml:space="preserve">8.1924352645874</t>
@@ -1283,115 +1283,115 @@
     <t xml:space="preserve">8.23267459869385</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31070995330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35704326629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3594799041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33996963500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40703296661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.450927734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36069965362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27412891387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15585803985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12659645080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23876953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28022766113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2863245010376</t>
+    <t xml:space="preserve">8.31070804595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35704231262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35948181152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3399715423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40703201293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45092868804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36069774627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27412796020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15585899353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12659549713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23877143859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2802267074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28632354736328</t>
   </si>
   <si>
     <t xml:space="preserve">8.36313819885254</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42776107788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.596022605896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49725914001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61431217193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68137264251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63869953155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60090160369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5704174041748</t>
+    <t xml:space="preserve">8.42776203155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59602165222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49726009368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61431312561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68137454986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63869857788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60089874267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57041931152344</t>
   </si>
   <si>
     <t xml:space="preserve">8.6569881439209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63382244110107</t>
+    <t xml:space="preserve">8.63382148742676</t>
   </si>
   <si>
     <t xml:space="preserve">8.71063899993896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79842662811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87402248382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06057357788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07642459869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13739013671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22639751434326</t>
+    <t xml:space="preserve">8.79842567443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8740234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06057548522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07642650604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13738918304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22639942169189</t>
   </si>
   <si>
     <t xml:space="preserve">9.28370571136475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3458890914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40807342529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41782760620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55926704406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62998485565186</t>
+    <t xml:space="preserve">9.34589004516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40807437896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41782665252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55926513671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62998580932617</t>
   </si>
   <si>
     <t xml:space="preserve">9.75435256958008</t>
@@ -1400,97 +1400,97 @@
     <t xml:space="preserve">9.72509098052979</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80800151824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77142333984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6629056930542</t>
+    <t xml:space="preserve">9.8080005645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77142429351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66290378570557</t>
   </si>
   <si>
     <t xml:space="preserve">9.85799121856689</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85067844390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87628173828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95065784454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83238697052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96773052215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1591577529907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89822959899902</t>
+    <t xml:space="preserve">9.85067749023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87628078460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95065879821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83238887786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96772766113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1591606140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89823055267334</t>
   </si>
   <si>
     <t xml:space="preserve">10.172571182251</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0030889511108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0225982666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1664762496948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2201242446899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0823440551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1213607788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.090877532959</t>
+    <t xml:space="preserve">10.0030899047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0225963592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1664743423462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2201232910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0823421478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.12135887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0908784866333</t>
   </si>
   <si>
     <t xml:space="preserve">10.0109119415283</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0596408843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94843769073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85722160339355</t>
+    <t xml:space="preserve">10.0596399307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94843578338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85722255706787</t>
   </si>
   <si>
     <t xml:space="preserve">9.61232280731201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41740417480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42989826202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6772985458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8284854888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73727226257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65355587005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65230846405029</t>
+    <t xml:space="preserve">9.41740322113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42989730834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67729663848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82848453521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73727416992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65355777740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65230751037598</t>
   </si>
   <si>
     <t xml:space="preserve">9.76476192474365</t>
@@ -1499,598 +1499,598 @@
     <t xml:space="preserve">9.5111141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78850173950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6910400390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87971305847168</t>
+    <t xml:space="preserve">9.78850364685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69104099273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.879714012146</t>
   </si>
   <si>
     <t xml:space="preserve">9.70353603363037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70853519439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64231204986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47238254547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76850891113281</t>
+    <t xml:space="preserve">9.70853233337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64231014251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47237968444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76850986480713</t>
   </si>
   <si>
     <t xml:space="preserve">9.54734992980957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6410608291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90720272064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93969058990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93719100952148</t>
+    <t xml:space="preserve">9.64106273651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90720367431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93968963623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93719005584717</t>
   </si>
   <si>
     <t xml:space="preserve">9.8547248840332</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0933790206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0871286392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1308612823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1083717346191</t>
+    <t xml:space="preserve">10.0933752059937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0871324539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1308631896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1083726882935</t>
   </si>
   <si>
     <t xml:space="preserve">10.1933364868164</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3270320892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1533517837524</t>
+    <t xml:space="preserve">10.3270301818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1533536911011</t>
   </si>
   <si>
     <t xml:space="preserve">10.1583499908447</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1708450317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.029655456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0821323394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0808839797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0458974838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0496444702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0771312713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1446084976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1383581161499</t>
+    <t xml:space="preserve">10.1708459854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0296516418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0821304321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0808820724487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0458955764771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0496454238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0771341323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.144606590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1383600234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1895866394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.120867729187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1745948791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2857990264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2095785140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.123363494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1783428192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.377010345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3082895278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2370691299438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96842861175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96967792510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0671367645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94093990325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88596248626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0034151077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1046237945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1958360671997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1421070098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2458152770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2658052444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2483139038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98342132568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.048397064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0733861923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97092723846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88721084594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82473754882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9022045135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92094707489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0071620941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98841953277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9871711730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0783815383911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2070827484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.360161781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6115350723267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6423168182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6012763977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4409599304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4653291702271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4794368743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5012407302856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4383964538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4319849014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1613721847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4281349182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3588800430298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.074161529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0164480209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1075067520142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1523942947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99336242675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80611705780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86895847320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73044681549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58680534362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.440598487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60219573974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70479869842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8510046005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86639308929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0715970993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8920431137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84972095489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90871620178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83561611175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0254259109497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98694896697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91128253936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93180274963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71377277374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57141494750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60347652435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55474376678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43931674957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26746082305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38032150268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18024730682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01608657836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1674222946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10201454162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07636260986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11612319946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1353588104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30593395233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24309062957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16357707977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87116146087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05071258544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93913555145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01993465423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12894821166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14561939239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07251453399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95196056365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85833549499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94554615020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86603164672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83268547058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66980743408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81601238250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83653354644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87500858306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19563865661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11483955383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05841159820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14177227020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1327953338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08662509918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05456352233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13792610168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15716171264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11740493774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36749649047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32773685455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28285026550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2443733215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34440898895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25463485717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31234741210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39058017730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49446296691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47266101837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48163890838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58039093017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52909278869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32004356384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30849933624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39442729949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46239948272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52652549743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47779178619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69581985473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73173046112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74583530426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7804651260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79200744628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80354976654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75481510162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75353336334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76122760772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72531509399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.643235206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6894063949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73686027526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79842090606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59834766387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69710159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72403335571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96771335601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96386528015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99592781066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0959634780884</t>
   </si>
   <si>
     <t xml:space="preserve">10.1895875930786</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1208667755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1745939254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2857990264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2095804214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.123366355896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1783409118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3770132064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3082914352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2370691299438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96842861175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96967792510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0671367645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94093894958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88596248626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0034151077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1046228408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1958360671997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1421070098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2458152770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2658071517944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2483110427856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98342418670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.048397064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0733871459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97092533111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88721179962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82473754882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9022045135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92094707489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0071601867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98842239379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98717021942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0783843994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2070808410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.360164642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.611536026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6423168182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6012735366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4409627914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4653291702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4794368743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5012369155884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4383964538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4319839477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1613721847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4281349182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3588790893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0741596221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0164499282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1075048446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1523952484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9933614730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80611515045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86895942687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73044776916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58680534362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.440598487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60219669342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70479774475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8510046005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86639308929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0715961456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89204406738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84972190856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90871524810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83561515808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0254259109497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98695087432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91128253936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93179988861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71377468109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5714168548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60347843170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55474281311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43931674957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26745986938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38032054901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18024730682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01608467102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16742134094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10201549530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07636547088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11611938476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13536167144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30593299865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24309253692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87116050720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05071449279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93913459777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01993370056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12894535064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14561939239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07251644134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95195960998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85833644866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94554805755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86603164672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83268451690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66980743408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81601142883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83653354644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8750114440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19563865661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11483860015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05840969085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.141770362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1327953338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08662414550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05456161499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13792514801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15716075897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11740398406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36749458312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32773685455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2828483581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2443733215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34440803527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25463390350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31234645843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39058017730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49446487426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4726619720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48163890838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58039093017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52909183502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32004261016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30850124359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39442729949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46240043640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52652645111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47779178619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6958179473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73173046112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74583721160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78046607971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79200839996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80355072021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75481510162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75353145599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76122665405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72531604766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64323711395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6894063949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73685836791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79842090606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59834957122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69710254669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72403144836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96771049499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96386528015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99592876434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.095965385437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1895885467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1164846420288</t>
+    <t xml:space="preserve">10.1164855957031</t>
   </si>
   <si>
     <t xml:space="preserve">10.1511125564575</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0677499771118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0190124511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0138854980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99721050262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92667102813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1023759841919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1254606246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1985664367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1036605834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1626558303833</t>
+    <t xml:space="preserve">10.0677490234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0190114974976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0138826370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99720859527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92667198181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1023750305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1254625320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1985654830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1036596298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1626539230347</t>
   </si>
   <si>
     <t xml:space="preserve">10.140851020813</t>
@@ -2099,205 +2099,205 @@
     <t xml:space="preserve">10.188304901123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2216510772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2113924026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1421346664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.048511505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89460849761963</t>
+    <t xml:space="preserve">10.2216491699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2113904953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1421356201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0485105514526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89461040496826</t>
   </si>
   <si>
     <t xml:space="preserve">9.8958911895752</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1305923461914</t>
+    <t xml:space="preserve">10.1305904388428</t>
   </si>
   <si>
     <t xml:space="preserve">9.97156047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94334506988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83817863464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68171119689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75866222381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6406717300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67529964447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53678894042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29182624816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28541374206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18537712097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14818668365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24822235107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36493015289307</t>
+    <t xml:space="preserve">9.94334316253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83817768096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68170928955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75866317749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64067077636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67530059814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53678798675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29182720184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28541469573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.185378074646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14818477630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24822044372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3649320602417</t>
   </si>
   <si>
     <t xml:space="preserve">9.30978202819824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4585542678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51626873016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50703525543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58880996704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5083532333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17993259429932</t>
+    <t xml:space="preserve">9.45855331420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51626968383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50703620910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5888090133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50835132598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17993354797363</t>
   </si>
   <si>
     <t xml:space="preserve">9.26830387115479</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27885437011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24983978271484</t>
+    <t xml:space="preserve">9.2788553237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24983692169189</t>
   </si>
   <si>
     <t xml:space="preserve">9.05727005004883</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02957248687744</t>
+    <t xml:space="preserve">9.02957153320312</t>
   </si>
   <si>
     <t xml:space="preserve">8.95571041107178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11398410797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24456024169922</t>
+    <t xml:space="preserve">9.11398506164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24456119537354</t>
   </si>
   <si>
     <t xml:space="preserve">9.14563941955566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16674327850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20631122589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23269176483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26302719116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1693811416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19576263427734</t>
+    <t xml:space="preserve">9.16674423217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20631217956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23269271850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26302814483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16938209533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19575977325439</t>
   </si>
   <si>
     <t xml:space="preserve">9.14695835113525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33557033538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37909412384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46878433227539</t>
+    <t xml:space="preserve">9.3355712890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37909603118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46878337860107</t>
   </si>
   <si>
     <t xml:space="preserve">9.6323356628418</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57693767547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52286148071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56770801544189</t>
+    <t xml:space="preserve">9.57693958282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52286052703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56770610809326</t>
   </si>
   <si>
     <t xml:space="preserve">9.54000759124756</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65475749969482</t>
+    <t xml:space="preserve">9.65475559234619</t>
   </si>
   <si>
     <t xml:space="preserve">9.56111145019531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60727787017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65871524810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59540462493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66399097442627</t>
+    <t xml:space="preserve">9.60727310180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65871429443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59540367126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66399002075195</t>
   </si>
   <si>
     <t xml:space="preserve">9.69828319549561</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76027297973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77742004394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70223903656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67190361022949</t>
+    <t xml:space="preserve">9.76027393341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.777419090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70223808288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67190551757812</t>
   </si>
   <si>
     <t xml:space="preserve">9.50571537017822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43053436279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37777709960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44108581542969</t>
+    <t xml:space="preserve">9.43053531646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37777519226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44108390808105</t>
   </si>
   <si>
     <t xml:space="preserve">9.48988819122314</t>
@@ -2309,40 +2309,40 @@
     <t xml:space="preserve">9.45559501647949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39624309539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29468250274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36722469329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29599952697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02165699005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88976287841797</t>
+    <t xml:space="preserve">9.39624118804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29467964172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36722660064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29600238800049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02165985107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88976383209229</t>
   </si>
   <si>
     <t xml:space="preserve">8.82645320892334</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70114994049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85942649841309</t>
+    <t xml:space="preserve">8.70115184783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8594274520874</t>
   </si>
   <si>
     <t xml:space="preserve">8.69983386993408</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68532562255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85019397735596</t>
+    <t xml:space="preserve">8.68532466888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85019302368164</t>
   </si>
   <si>
     <t xml:space="preserve">8.64048004150391</t>
@@ -2351,46 +2351,46 @@
     <t xml:space="preserve">8.5995922088623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75391006469727</t>
+    <t xml:space="preserve">8.75391101837158</t>
   </si>
   <si>
     <t xml:space="preserve">8.66817760467529</t>
   </si>
   <si>
-    <t xml:space="preserve">8.804030418396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77896976470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66685962677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71698093414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77237415313721</t>
+    <t xml:space="preserve">8.80403137207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77897167205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6668586730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71697998046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77237319946289</t>
   </si>
   <si>
     <t xml:space="preserve">8.83700370788574</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9807710647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04275989532471</t>
+    <t xml:space="preserve">8.98076915740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04276180267334</t>
   </si>
   <si>
     <t xml:space="preserve">8.97021961212158</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01506423950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08101081848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18125057220459</t>
+    <t xml:space="preserve">9.01506233215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08101272583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18125247955322</t>
   </si>
   <si>
     <t xml:space="preserve">9.29995822906494</t>
@@ -2399,85 +2399,85 @@
     <t xml:space="preserve">9.28149223327637</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2617073059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4397668838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.332932472229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44636249542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59672355651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60895442962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51109790802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42003726959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46896648406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55051326751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53692150115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50022602081299</t>
+    <t xml:space="preserve">9.26170825958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43976974487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33293151855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44636154174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59672451019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60895538330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5110969543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4200382232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46896553039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55051231384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53692054748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50022411346436</t>
   </si>
   <si>
     <t xml:space="preserve">9.2120943069458</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11151885986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20393562316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27732944488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1971435546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24199295043945</t>
+    <t xml:space="preserve">9.11151790618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20393753051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27733135223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19714260101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24199199676514</t>
   </si>
   <si>
     <t xml:space="preserve">9.29771709442139</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40236949920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33985042572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40372943878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3887767791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3643159866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48255729675293</t>
+    <t xml:space="preserve">9.40236854553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33985137939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40372657775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38877773284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36431503295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48255825042725</t>
   </si>
   <si>
     <t xml:space="preserve">9.56274509429932</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60759735107422</t>
+    <t xml:space="preserve">9.60759449005127</t>
   </si>
   <si>
     <t xml:space="preserve">9.5409984588623</t>
@@ -2486,91 +2486,91 @@
     <t xml:space="preserve">9.47168445587158</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39693260192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30858898162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22160530090332</t>
+    <t xml:space="preserve">9.39693164825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30859088897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22160720825195</t>
   </si>
   <si>
     <t xml:space="preserve">9.31266784667969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49615001678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64837074279785</t>
+    <t xml:space="preserve">9.49614810943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64836978912354</t>
   </si>
   <si>
     <t xml:space="preserve">9.62526321411133</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63342094421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64293384552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60623836517334</t>
+    <t xml:space="preserve">9.63341903686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6429328918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60623741149902</t>
   </si>
   <si>
     <t xml:space="preserve">9.68642425537109</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63749504089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66332054138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58856773376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49342918395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52197170257568</t>
+    <t xml:space="preserve">9.63749694824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66331768035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58856868743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49343109130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52196979522705</t>
   </si>
   <si>
     <t xml:space="preserve">9.5423583984375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54643630981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46760559082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43906497955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37790775299072</t>
+    <t xml:space="preserve">9.54643535614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46760845184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43906593322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37790489196777</t>
   </si>
   <si>
     <t xml:space="preserve">9.31946277618408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22296524047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16044616699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27189350128174</t>
+    <t xml:space="preserve">9.2229642868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16044521331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27189540863037</t>
   </si>
   <si>
     <t xml:space="preserve">9.35751819610596</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25966167449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28684425354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23655700683594</t>
+    <t xml:space="preserve">9.25965976715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28684520721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23655796051025</t>
   </si>
   <si>
     <t xml:space="preserve">9.27597045898438</t>
@@ -2582,16 +2582,16 @@
     <t xml:space="preserve">9.25830268859863</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31130886077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39013576507568</t>
+    <t xml:space="preserve">9.31130790710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39013862609863</t>
   </si>
   <si>
     <t xml:space="preserve">9.40916442871094</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52468967437744</t>
+    <t xml:space="preserve">9.52469062805176</t>
   </si>
   <si>
     <t xml:space="preserve">9.51381683349609</t>
@@ -2600,73 +2600,73 @@
     <t xml:space="preserve">9.51925373077393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58585071563721</t>
+    <t xml:space="preserve">9.58584976196289</t>
   </si>
   <si>
     <t xml:space="preserve">9.72855663299561</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73127365112305</t>
+    <t xml:space="preserve">9.73127555847168</t>
   </si>
   <si>
     <t xml:space="preserve">9.65380668640137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58177185058594</t>
+    <t xml:space="preserve">9.58177280426025</t>
   </si>
   <si>
     <t xml:space="preserve">9.42819309234619</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37654590606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43770790100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45673561096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43362712860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21345043182373</t>
+    <t xml:space="preserve">9.37654685974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43770503997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4567346572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43362903594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21345138549805</t>
   </si>
   <si>
     <t xml:space="preserve">9.1454963684082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15365028381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96745109558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10472393035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0299711227417</t>
+    <t xml:space="preserve">9.15365219116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96745014190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10472202301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02997016906738</t>
   </si>
   <si>
     <t xml:space="preserve">8.78397178649902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60185050964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56923198699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69019317626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85328578948975</t>
+    <t xml:space="preserve">8.60184955596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56923007965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69019222259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85328769683838</t>
   </si>
   <si>
     <t xml:space="preserve">8.81387042999268</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7703800201416</t>
+    <t xml:space="preserve">8.77037811279297</t>
   </si>
   <si>
     <t xml:space="preserve">8.68475532531738</t>
@@ -2675,106 +2675,106 @@
     <t xml:space="preserve">8.90221500396729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82610321044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76086521148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77309703826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7921257019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76630401611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67388153076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26886558532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13838958740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19819068908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99024772644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58251094818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55532932281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5566873550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57843399047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4533953666687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95460033416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50442266464233</t>
+    <t xml:space="preserve">8.82610416412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76086711883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77309799194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79212379455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76630306243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67388248443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26886653900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13839054107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19819164276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9902458190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58251333236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55532884597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55668830871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57843351364136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45339584350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95459985733032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50442314147949</t>
   </si>
   <si>
     <t xml:space="preserve">5.54859399795532</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47044467926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47964906692505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69642782211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41169166564941</t>
+    <t xml:space="preserve">5.47044515609741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47964859008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69642686843872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41169261932373</t>
   </si>
   <si>
     <t xml:space="preserve">4.66584777832031</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54896306991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73312473297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95601940155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95194244384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6913013458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92778635025024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91963243484497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58393144607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83944511413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26552820205688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25193643569946</t>
+    <t xml:space="preserve">4.54896402359009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73312377929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95601892471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9519419670105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69130086898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9277868270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91963386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58393096923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8394455909729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26552867889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2519359588623</t>
   </si>
   <si>
     <t xml:space="preserve">6.68549585342407</t>
@@ -2786,160 +2786,160 @@
     <t xml:space="preserve">6.33008623123169</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4068775177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31649398803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32532978057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22951078414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83196926116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74498653411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83536720275879</t>
+    <t xml:space="preserve">6.40687704086304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31649494171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3253288269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22951126098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83197021484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74498701095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83536672592163</t>
   </si>
   <si>
     <t xml:space="preserve">5.73139524459839</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40928506851196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67295122146606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75721883773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60635566711426</t>
+    <t xml:space="preserve">5.40928411483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67295265197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75721836090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60635662078857</t>
   </si>
   <si>
     <t xml:space="preserve">5.71100807189941</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90128421783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08680391311646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92167091369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57985401153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90332317352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72391939163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81430101394653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86526727676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79323482513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78575944900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78983783721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19562482833862</t>
+    <t xml:space="preserve">5.90128469467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08680438995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92167234420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57985353469849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90332412719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72391986846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81430196762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86526775360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79323530197144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78575992584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78983688354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19562673568726</t>
   </si>
   <si>
     <t xml:space="preserve">6.00024557113647</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03245258331299</t>
+    <t xml:space="preserve">6.03245067596436</t>
   </si>
   <si>
     <t xml:space="preserve">5.88430643081665</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84995460510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91150236129761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92152214050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04748153686523</t>
+    <t xml:space="preserve">5.84995365142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91150283813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92152261734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04748106002808</t>
   </si>
   <si>
     <t xml:space="preserve">6.07753992080688</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81345415115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96875762939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27721357345581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44038867950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41533946990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80323791503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91631269454956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71020078659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60570955276489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14123439788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14552927017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14051866531372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39458560943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36667346954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32301712036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35092830657959</t>
+    <t xml:space="preserve">5.81345462799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96875715255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27721405029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44038724899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41533899307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80323696136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91631412506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71020030975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60571002960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1412353515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1455283164978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14051818847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39458608627319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3666729927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32301664352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35092782974243</t>
   </si>
   <si>
     <t xml:space="preserve">6.30011606216431</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06322574615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06966686248779</t>
+    <t xml:space="preserve">6.06322622299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06966733932495</t>
   </si>
   <si>
     <t xml:space="preserve">6.00955009460449</t>
@@ -2957,13 +2957,13 @@
     <t xml:space="preserve">6.24071502685547</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20779228210449</t>
+    <t xml:space="preserve">6.20779323577881</t>
   </si>
   <si>
     <t xml:space="preserve">6.26791048049927</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31228160858154</t>
+    <t xml:space="preserve">6.3122820854187</t>
   </si>
   <si>
     <t xml:space="preserve">6.2249698638916</t>
@@ -2972,49 +2972,49 @@
     <t xml:space="preserve">6.03603029251099</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1977744102478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28580093383789</t>
+    <t xml:space="preserve">6.19777297973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28580141067505</t>
   </si>
   <si>
     <t xml:space="preserve">6.32373332977295</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36595726013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30727100372314</t>
+    <t xml:space="preserve">6.36595869064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30727243423462</t>
   </si>
   <si>
     <t xml:space="preserve">6.28437042236328</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3902907371521</t>
+    <t xml:space="preserve">6.39029264450073</t>
   </si>
   <si>
     <t xml:space="preserve">6.23141050338745</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15554857254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09757900238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05678606033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06680488586426</t>
+    <t xml:space="preserve">6.15554809570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09757852554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05678558349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06680393218994</t>
   </si>
   <si>
     <t xml:space="preserve">6.01885414123535</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59517097473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39692878723145</t>
+    <t xml:space="preserve">5.59517288208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39692974090576</t>
   </si>
   <si>
     <t xml:space="preserve">5.39191913604736</t>
@@ -3023,52 +3023,52 @@
     <t xml:space="preserve">5.62451505661011</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79412984848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68391561508179</t>
+    <t xml:space="preserve">5.79413080215454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68391609191895</t>
   </si>
   <si>
     <t xml:space="preserve">5.58658409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71540689468384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90005111694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99237442016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90076684951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85353231430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79699373245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76407194137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81703329086304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67890644073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63453578948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86212062835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78124904632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69823026657104</t>
+    <t xml:space="preserve">5.71540641784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90005159378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99237394332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90076637268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85353183746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79699420928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76407146453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81703233718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67890691757202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63453483581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86212015151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78124952316284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69822931289673</t>
   </si>
   <si>
     <t xml:space="preserve">5.5822901725769</t>
@@ -3077,22 +3077,22 @@
     <t xml:space="preserve">5.56511354446411</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49354648590088</t>
+    <t xml:space="preserve">5.49354696273804</t>
   </si>
   <si>
     <t xml:space="preserve">5.50785970687866</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47135925292969</t>
+    <t xml:space="preserve">5.471360206604</t>
   </si>
   <si>
     <t xml:space="preserve">5.56296682357788</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38118457794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45919370651245</t>
+    <t xml:space="preserve">5.38118505477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45919275283813</t>
   </si>
   <si>
     <t xml:space="preserve">5.45776176452637</t>
@@ -3101,19 +3101,19 @@
     <t xml:space="preserve">5.43843936920166</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35040998458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44774389266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47565507888794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43486022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28743076324463</t>
+    <t xml:space="preserve">5.35041046142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44774293899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47565412521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4348611831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28743124008179</t>
   </si>
   <si>
     <t xml:space="preserve">5.05608797073364</t>
@@ -3125,7 +3125,7 @@
     <t xml:space="preserve">5.0400824546814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95569372177124</t>
+    <t xml:space="preserve">4.95569276809692</t>
   </si>
   <si>
     <t xml:space="preserve">4.86621189117432</t>
@@ -3134,58 +3134,58 @@
     <t xml:space="preserve">4.99061346054077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84875106811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8654842376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7010703086853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72653245925903</t>
+    <t xml:space="preserve">4.84875154495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86548376083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70106983184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72653293609619</t>
   </si>
   <si>
     <t xml:space="preserve">4.86693859100342</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03280830383301</t>
+    <t xml:space="preserve">5.03280782699585</t>
   </si>
   <si>
     <t xml:space="preserve">4.89603805541992</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00880098342896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99206686019897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96078443527222</t>
+    <t xml:space="preserve">5.0088005065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99206829071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96078538894653</t>
   </si>
   <si>
     <t xml:space="preserve">4.86402893066406</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87275886535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66905975341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77454662322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79127979278564</t>
+    <t xml:space="preserve">4.87275838851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66906070709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7745475769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79127931594849</t>
   </si>
   <si>
     <t xml:space="preserve">4.77381992340088</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61231470108032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61304330825806</t>
+    <t xml:space="preserve">4.6123161315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6130428314209</t>
   </si>
   <si>
     <t xml:space="preserve">4.68797492980957</t>
@@ -3194,40 +3194,40 @@
     <t xml:space="preserve">4.54320430755615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43771648406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28130626678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3053126335144</t>
+    <t xml:space="preserve">4.43771696090698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28130578994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30531215667725</t>
   </si>
   <si>
     <t xml:space="preserve">4.37297058105469</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62832021713257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73889923095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79928207397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79855537414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75927019119263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36745452880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58570432662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52313947677612</t>
+    <t xml:space="preserve">4.62832069396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73890066146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79928159713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79855489730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75926923751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36745595932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58570289611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52313899993896</t>
   </si>
   <si>
     <t xml:space="preserve">5.54205322265625</t>
@@ -3236,244 +3236,244 @@
     <t xml:space="preserve">5.57260894775391</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79667711257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88252115249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96109056472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87597370147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91089344024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06002902984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27100324630737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30883312225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22589874267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24335861206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04038763046265</t>
+    <t xml:space="preserve">5.7966775894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88252210617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9610915184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87597322463989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91089391708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06002950668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27100419998169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30883407592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22589826583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24335908889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04038858413696</t>
   </si>
   <si>
     <t xml:space="preserve">6.12186765670776</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18297624588013</t>
+    <t xml:space="preserve">6.1829776763916</t>
   </si>
   <si>
     <t xml:space="preserve">6.14878463745117</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36121273040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3779468536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39467811584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43323469161987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50089311599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40777111053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31319952011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36703300476074</t>
+    <t xml:space="preserve">6.36121368408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37794494628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39467716217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43323612213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50089168548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4077730178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31319808959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36703252792358</t>
   </si>
   <si>
     <t xml:space="preserve">6.36994218826294</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33720588684082</t>
+    <t xml:space="preserve">6.33720636367798</t>
   </si>
   <si>
     <t xml:space="preserve">6.27173137664795</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99746465682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08185386657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2448148727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25354337692261</t>
+    <t xml:space="preserve">5.99746608734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08185434341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24481344223022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25354385375977</t>
   </si>
   <si>
     <t xml:space="preserve">6.22880887985229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21862506866455</t>
+    <t xml:space="preserve">6.21862459182739</t>
   </si>
   <si>
     <t xml:space="preserve">6.14587497711182</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37357997894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58237028121948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59692096710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56927680969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53144598007202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58673572540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59110260009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55108880996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42450475692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44269132614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42159461975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47542858123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30592393875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21425914764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07676219940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20407342910767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21789646148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0760350227356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96545648574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04620695114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17570161819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23462820053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26445579528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31538200378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38376522064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43396329879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38522148132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45942497253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63693428039551</t>
+    <t xml:space="preserve">6.37357950210571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58236980438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59692144393921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56927490234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53144645690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58673620223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59110069274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55108976364136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42450523376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44269227981567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42159509658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47542905807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30592489242554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21425867080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07676076889038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20407390594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2178955078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07603645324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96545553207397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04620790481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17570209503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23462963104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26445722579956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31538057327271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38376426696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43396091461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38522100448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45942401885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63693332672119</t>
   </si>
   <si>
     <t xml:space="preserve">6.60492420196533</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66603374481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61801767349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69149494171143</t>
+    <t xml:space="preserve">6.66603422164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61801862716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6914963722229</t>
   </si>
   <si>
     <t xml:space="preserve">6.80643939971924</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8559103012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96721458435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04214906692505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89810419082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95557451248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90537881851196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02759742736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18473672866821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3200511932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40589570999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37679529190063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43499565124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49319505691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57903861999512</t>
+    <t xml:space="preserve">6.85590887069702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96721649169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04214811325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89810514450073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95557546615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9053783416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02759790420532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18473815917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32005214691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40589475631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37679719924927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4349946975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49319458007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57904100418091</t>
   </si>
   <si>
     <t xml:space="preserve">7.5179295539856</t>
@@ -3482,10 +3482,10 @@
     <t xml:space="preserve">7.44954490661621</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52083778381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40152978897095</t>
+    <t xml:space="preserve">7.52083969116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40152931213379</t>
   </si>
   <si>
     <t xml:space="preserve">7.38115930557251</t>
@@ -3494,37 +3494,37 @@
     <t xml:space="preserve">7.26039695739746</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4539098739624</t>
+    <t xml:space="preserve">7.45391082763672</t>
   </si>
   <si>
     <t xml:space="preserve">7.3564248085022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44372415542603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52811479568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57467555999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63432884216309</t>
+    <t xml:space="preserve">7.44372653961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5281138420105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57467460632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63432836532593</t>
   </si>
   <si>
     <t xml:space="preserve">7.68961811065674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61977910995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6066837310791</t>
+    <t xml:space="preserve">7.61977767944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60668325424194</t>
   </si>
   <si>
     <t xml:space="preserve">7.46409511566162</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42044448852539</t>
+    <t xml:space="preserve">7.42044544219971</t>
   </si>
   <si>
     <t xml:space="preserve">7.39279937744141</t>
@@ -3533,28 +3533,28 @@
     <t xml:space="preserve">7.43935966491699</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62996387481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53975439071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52957057952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51065397262573</t>
+    <t xml:space="preserve">7.62996292114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53975343704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52956867218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51065301895142</t>
   </si>
   <si>
     <t xml:space="preserve">7.32878112792969</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3840708732605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39716577529907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34915065765381</t>
+    <t xml:space="preserve">7.38407135009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39716672897339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34915018081665</t>
   </si>
   <si>
     <t xml:space="preserve">7.3826150894165</t>
@@ -3563,49 +3563,49 @@
     <t xml:space="preserve">7.35496950149536</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42335557937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42189979553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22402095794678</t>
+    <t xml:space="preserve">7.4233546257019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42190027236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22402143478394</t>
   </si>
   <si>
     <t xml:space="preserve">7.34769678115845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49901437759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51211023330688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50774335861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57176494598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60813999176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49610328674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58776807785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61250257492065</t>
+    <t xml:space="preserve">7.49901294708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51210927963257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50774478912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5717625617981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60813856124878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49610376358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58776950836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61250448226929</t>
   </si>
   <si>
     <t xml:space="preserve">7.59068059921265</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41753578186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48155450820923</t>
+    <t xml:space="preserve">7.41753482818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4815559387207</t>
   </si>
   <si>
     <t xml:space="preserve">7.53071594238281</t>
@@ -3617,43 +3617,43 @@
     <t xml:space="preserve">7.47112607955933</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52326917648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51879787445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49049282073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66777372360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72438621520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77652597427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73183298110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78695678710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81824064254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77950429916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83164691925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8822979927063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99105262756348</t>
+    <t xml:space="preserve">7.523268699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.518798828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4904932975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66777324676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72438383102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.776526927948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73183584213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78695487976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81824111938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77950620651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8316478729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88229942321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99105072021484</t>
   </si>
   <si>
     <t xml:space="preserve">7.99552011489868</t>
@@ -3662,229 +3662,229 @@
     <t xml:space="preserve">8.00148105621338</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91805267333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68267107009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76013946533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7571587562561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76311683654785</t>
+    <t xml:space="preserve">7.91805410385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68267297744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76014041900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75716018676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76311731338501</t>
   </si>
   <si>
     <t xml:space="preserve">7.85101413726807</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86293172836304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70352935791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70054721832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64989900588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79142427444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74524021148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78844451904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57540988922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42121934890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50837135314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45175981521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46665668487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38174057006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3236403465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04207706451416</t>
+    <t xml:space="preserve">7.86293315887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70352792739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70054864883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64989709854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79142332077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74524259567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78844356536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57540941238403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42121887207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50836944580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45175838470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46665716171265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38174200057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32363939285278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04207754135132</t>
   </si>
   <si>
     <t xml:space="preserve">7.07857608795166</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26255941390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18360471725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20222520828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34896659851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30576181411743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38695430755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45920753479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42792415618896</t>
+    <t xml:space="preserve">7.26256084442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18360233306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20222568511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34896612167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30576276779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38695526123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4592080116272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42792463302612</t>
   </si>
   <si>
     <t xml:space="preserve">7.55008363723755</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53816652297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59775495529175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67373275756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.660325050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70948839187622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75864934921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80483102798462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83462619781494</t>
+    <t xml:space="preserve">7.53816413879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59775543212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67373418807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66032695770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7094874382019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75864791870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80483150482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83462810516357</t>
   </si>
   <si>
     <t xml:space="preserve">7.72587442398071</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72885513305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72140502929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50539207458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4949631690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62308120727539</t>
+    <t xml:space="preserve">7.72885274887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72140693664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50539064407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49496412277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62308216094971</t>
   </si>
   <si>
     <t xml:space="preserve">7.68565225601196</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69458913803101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67671060562134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76758718490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77056837081909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91954135894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84356594085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88527774810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88825845718384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85399389266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04915428161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12215042114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18620777130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21153736114502</t>
+    <t xml:space="preserve">7.69458818435669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67671394348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76758909225464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77056789398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91954278945923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84356737136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88527822494507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88825750350952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85399293899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04915142059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12214946746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18620872497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21153450012207</t>
   </si>
   <si>
     <t xml:space="preserve">8.15045547485352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07447338104248</t>
+    <t xml:space="preserve">8.07447242736816</t>
   </si>
   <si>
     <t xml:space="preserve">8.22333812713623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4404354095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45284271240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47610092163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67304039001465</t>
+    <t xml:space="preserve">8.44043445587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45284175872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47610187530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67303848266602</t>
   </si>
   <si>
     <t xml:space="preserve">8.73351669311523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82966041564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95216464996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90254211425781</t>
+    <t xml:space="preserve">8.8296594619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95216369628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90254402160645</t>
   </si>
   <si>
     <t xml:space="preserve">9.02659797668457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18632030487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04520606994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98473072052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19407367706299</t>
+    <t xml:space="preserve">9.18632125854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04520797729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98472785949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19407272338867</t>
   </si>
   <si>
     <t xml:space="preserve">9.30882453918457</t>
@@ -3893,40 +3893,40 @@
     <t xml:space="preserve">9.28401374816895</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16616058349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28866577148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46544551849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48715496063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43753147125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55073356628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40806770324707</t>
+    <t xml:space="preserve">9.16615962982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28866481781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46544456481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48715400695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43753242492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55073165893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40806865692139</t>
   </si>
   <si>
     <t xml:space="preserve">9.36465072631836</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51972007751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58174705505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51196479797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43133068084717</t>
+    <t xml:space="preserve">9.51971912384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58174419403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51196575164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43132972717285</t>
   </si>
   <si>
     <t xml:space="preserve">9.61741352081299</t>
@@ -3935,16 +3935,16 @@
     <t xml:space="preserve">9.88258266448975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72286033630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59880352020264</t>
+    <t xml:space="preserve">9.72285842895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59880447387695</t>
   </si>
   <si>
     <t xml:space="preserve">9.73836803436279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82520771026611</t>
+    <t xml:space="preserve">9.82520484924316</t>
   </si>
   <si>
     <t xml:space="preserve">9.83296012878418</t>
@@ -3953,22 +3953,22 @@
     <t xml:space="preserve">9.78488826751709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81900215148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80504703521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70114994049072</t>
+    <t xml:space="preserve">9.81900405883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8050479888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70115184783936</t>
   </si>
   <si>
     <t xml:space="preserve">9.72751235961914</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76782989501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76317691802979</t>
+    <t xml:space="preserve">9.76783084869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76317882537842</t>
   </si>
   <si>
     <t xml:space="preserve">9.63757228851318</t>
@@ -3977,7 +3977,7 @@
     <t xml:space="preserve">9.4344310760498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55848503112793</t>
+    <t xml:space="preserve">9.55848789215088</t>
   </si>
   <si>
     <t xml:space="preserve">9.59105110168457</t>
@@ -3986,64 +3986,64 @@
     <t xml:space="preserve">9.53367519378662</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93975830078125</t>
+    <t xml:space="preserve">8.93976020812988</t>
   </si>
   <si>
     <t xml:space="preserve">9.14910316467285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22973823547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25765323638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31192588806152</t>
+    <t xml:space="preserve">9.22973918914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25765037536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31192684173584</t>
   </si>
   <si>
     <t xml:space="preserve">9.53057479858398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74456882476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60655879974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51041316986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46389579772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31968116760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41892433166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30417060852051</t>
+    <t xml:space="preserve">9.74456977844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60655784606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51041507720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46389293670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31967926025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41892528533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30417251586914</t>
   </si>
   <si>
     <t xml:space="preserve">9.45769214630127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34449195861816</t>
+    <t xml:space="preserve">9.34448909759521</t>
   </si>
   <si>
     <t xml:space="preserve">9.17546463012695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44373607635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43908309936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49025535583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53212356567383</t>
+    <t xml:space="preserve">9.44373512268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43908214569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49025630950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53212547302246</t>
   </si>
   <si>
     <t xml:space="preserve">9.52126979827881</t>
@@ -4052,10 +4052,10 @@
     <t xml:space="preserve">9.47475051879883</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62051391601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77713489532471</t>
+    <t xml:space="preserve">9.62051486968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77713394165039</t>
   </si>
   <si>
     <t xml:space="preserve">9.89033508300781</t>
@@ -4064,67 +4064,67 @@
     <t xml:space="preserve">9.80814743041992</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91669845581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83451175689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.932204246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1198387145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0981292724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2035751342773</t>
+    <t xml:space="preserve">9.91669750213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83450889587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93220710754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.119836807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0981283187866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2035760879517</t>
   </si>
   <si>
     <t xml:space="preserve">10.2438936233521</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2888660430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4051656723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3043699264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1617069244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83606147766113</t>
+    <t xml:space="preserve">10.2888641357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4051666259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3043718338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1617078781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83606052398682</t>
   </si>
   <si>
     <t xml:space="preserve">10.1524038314819</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4547901153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7091007232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5245695114136</t>
+    <t xml:space="preserve">10.4547891616821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7091026306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5245704650879</t>
   </si>
   <si>
     <t xml:space="preserve">10.3183279037476</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4330797195435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3555450439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3028202056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4516878128052</t>
+    <t xml:space="preserve">10.4330806732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.355544090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3028211593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4516859054565</t>
   </si>
   <si>
     <t xml:space="preserve">10.2237358093262</t>
@@ -4133,25 +4133,25 @@
     <t xml:space="preserve">10.1074333190918</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2749080657959</t>
+    <t xml:space="preserve">10.2749071121216</t>
   </si>
   <si>
     <t xml:space="preserve">10.3105745315552</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4889030456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3307332992554</t>
+    <t xml:space="preserve">10.4889039993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3307342529297</t>
   </si>
   <si>
     <t xml:space="preserve">10.2128801345825</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3384876251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4439344406128</t>
+    <t xml:space="preserve">10.3384857177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4439353942871</t>
   </si>
   <si>
     <t xml:space="preserve">10.3229789733887</t>
@@ -4160,22 +4160,22 @@
     <t xml:space="preserve">10.4609909057617</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4098196029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3601980209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.684289932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7246103286743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.050253868103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2658023834229</t>
+    <t xml:space="preserve">10.4098167419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3601970672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6842918395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.724609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0502557754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2658014297485</t>
   </si>
   <si>
     <t xml:space="preserve">10.7509717941284</t>
@@ -4184,124 +4184,124 @@
     <t xml:space="preserve">9.9663200378418</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3943109512329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5990037918091</t>
+    <t xml:space="preserve">10.3943119049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5990047454834</t>
   </si>
   <si>
     <t xml:space="preserve">10.5462808609009</t>
   </si>
   <si>
-    <t xml:space="preserve">10.16015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0624628067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0205936431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90118885040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1648082733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86862468719482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2516469955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.439281463623</t>
+    <t xml:space="preserve">10.1601552963257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0624618530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0205945968628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90119075775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1648092269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86862659454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2516479492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4392805099487</t>
   </si>
   <si>
     <t xml:space="preserve">10.290415763855</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1539554595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3757019042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3074731826782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4005146026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4222240447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4733963012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3803558349609</t>
+    <t xml:space="preserve">10.1539535522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3757028579712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3074712753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4005136489868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4222249984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4733982086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3803539276123</t>
   </si>
   <si>
     <t xml:space="preserve">10.2826614379883</t>
   </si>
   <si>
-    <t xml:space="preserve">10.713755607605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6966943740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9897785186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0099382400513</t>
+    <t xml:space="preserve">10.7137565612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6966953277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9897794723511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0099353790283</t>
   </si>
   <si>
     <t xml:space="preserve">10.971170425415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0316476821899</t>
+    <t xml:space="preserve">11.0316457748413</t>
   </si>
   <si>
     <t xml:space="preserve">10.8548679351807</t>
   </si>
   <si>
-    <t xml:space="preserve">10.529221534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0252447128296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0469570159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2020263671875</t>
+    <t xml:space="preserve">10.5292224884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0252456665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0469560623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2020254135132</t>
   </si>
   <si>
     <t xml:space="preserve">10.3819065093994</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2345895767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5447282791138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4749479293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5478286743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1399974822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2795581817627</t>
+    <t xml:space="preserve">10.2345886230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5447292327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4749488830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5478296279907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1399984359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2795600891113</t>
   </si>
   <si>
     <t xml:space="preserve">10.5602350234985</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5757427215576</t>
+    <t xml:space="preserve">10.5757436752319</t>
   </si>
   <si>
     <t xml:space="preserve">10.7199583053589</t>
@@ -4310,31 +4310,31 @@
     <t xml:space="preserve">10.8021450042725</t>
   </si>
   <si>
-    <t xml:space="preserve">10.688943862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7695798873901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9728088378906</t>
+    <t xml:space="preserve">10.6889429092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7695789337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9728097915649</t>
   </si>
   <si>
     <t xml:space="preserve">10.8895978927612</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2976551055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3984718322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3552656173706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.361665725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3600654602051</t>
+    <t xml:space="preserve">11.2976570129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3984708786011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3552665710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3616647720337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3600664138794</t>
   </si>
   <si>
     <t xml:space="preserve">11.2800540924072</t>
@@ -4346,28 +4346,28 @@
     <t xml:space="preserve">11.4080743789673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5472936630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5440921783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5152893066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2224454879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5935525894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3839235305786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5375461578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6047563552856</t>
+    <t xml:space="preserve">11.5472955703735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.544093132019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5152912139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2224464416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5935535430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3839225769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5375442504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6047554016113</t>
   </si>
   <si>
     <t xml:space="preserve">10.0862789154053</t>
@@ -4376,34 +4376,34 @@
     <t xml:space="preserve">9.60941028594971</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6366138458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66541862487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32936763763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14534091949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33416938781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20134830474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28296279907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06373023986816</t>
+    <t xml:space="preserve">9.63661289215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6654167175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32936859130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14534282684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3341703414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20134925842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28296089172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06372928619385</t>
   </si>
   <si>
     <t xml:space="preserve">8.983717918396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19974899291992</t>
+    <t xml:space="preserve">9.19975185394287</t>
   </si>
   <si>
     <t xml:space="preserve">8.6668701171875</t>
@@ -4412,37 +4412,37 @@
     <t xml:space="preserve">8.6060619354248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83809661865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98211669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96131420135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91170692443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89410305023193</t>
+    <t xml:space="preserve">8.83809566497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98211765289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9613151550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91170597076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89410400390625</t>
   </si>
   <si>
     <t xml:space="preserve">8.51644992828369</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67167282104492</t>
+    <t xml:space="preserve">8.67167186737061</t>
   </si>
   <si>
     <t xml:space="preserve">8.81249237060547</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04452610015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94051170349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80129146575928</t>
+    <t xml:space="preserve">9.04452705383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94051265716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80129241943359</t>
   </si>
   <si>
     <t xml:space="preserve">8.77728843688965</t>
@@ -4454,22 +4454,22 @@
     <t xml:space="preserve">8.81729221343994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87490177154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37417507171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36297416687012</t>
+    <t xml:space="preserve">8.87490272521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37417602539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36297130584717</t>
   </si>
   <si>
     <t xml:space="preserve">9.15654373168945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12133693695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11333656311035</t>
+    <t xml:space="preserve">9.12133884429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11333751678467</t>
   </si>
   <si>
     <t xml:space="preserve">9.16614532470703</t>
@@ -4478,10 +4478,10 @@
     <t xml:space="preserve">9.15814399719238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19494915008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14054203033447</t>
+    <t xml:space="preserve">9.19494819641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14054012298584</t>
   </si>
   <si>
     <t xml:space="preserve">9.27336120605469</t>
@@ -4490,70 +4490,70 @@
     <t xml:space="preserve">9.30536556243896</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26375865936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35497188568115</t>
+    <t xml:space="preserve">9.26375961303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35497283935547</t>
   </si>
   <si>
     <t xml:space="preserve">9.54860019683838</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41738128662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56940364837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92785549163818</t>
+    <t xml:space="preserve">9.41738224029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56940460205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9278564453125</t>
   </si>
   <si>
     <t xml:space="preserve">9.80463790893555</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0062685012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85424518585205</t>
+    <t xml:space="preserve">10.0062694549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85424613952637</t>
   </si>
   <si>
     <t xml:space="preserve">10.0014686584473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79023742675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44778537750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38217639923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6702184677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83344173431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56300258636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29576396942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26695919036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34697151184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55660343170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47018909454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44938659667969</t>
+    <t xml:space="preserve">9.79023551940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44778633117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38217735290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67021751403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8334436416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56300163269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29576301574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26696109771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34697246551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55660247802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47018814086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44938468933105</t>
   </si>
   <si>
     <t xml:space="preserve">9.23335361480713</t>
@@ -4562,55 +4562,55 @@
     <t xml:space="preserve">9.15654277801514</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08801651000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25117683410645</t>
+    <t xml:space="preserve">9.08801746368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25117492675781</t>
   </si>
   <si>
     <t xml:space="preserve">8.81227493286133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75679969787598</t>
+    <t xml:space="preserve">8.75680160522461</t>
   </si>
   <si>
     <t xml:space="preserve">8.77148532867432</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79922389984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90038013458252</t>
+    <t xml:space="preserve">8.79922008514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90038108825684</t>
   </si>
   <si>
     <t xml:space="preserve">9.17122745513916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41433525085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56444358825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56933784484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65907573699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61175918579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43880939483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29685974121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53507614135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67865562438965</t>
+    <t xml:space="preserve">9.41433620452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5644416809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56933689117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65907669067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61176013946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43880844116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29686164855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53507328033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67865657806396</t>
   </si>
   <si>
     <t xml:space="preserve">9.68028736114502</t>
@@ -4619,10 +4619,10 @@
     <t xml:space="preserve">9.86628913879395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83692169189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0783977508545</t>
+    <t xml:space="preserve">9.83692073822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0783967971802</t>
   </si>
   <si>
     <t xml:space="preserve">10.0522918701172</t>
@@ -4631,34 +4631,34 @@
     <t xml:space="preserve">10.1844511032104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5385103225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7163543701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8126192092896</t>
+    <t xml:space="preserve">10.5385074615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7163534164429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8126173019409</t>
   </si>
   <si>
     <t xml:space="preserve">10.9839353561401</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0377788543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1927804946899</t>
+    <t xml:space="preserve">11.0377769470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1927824020386</t>
   </si>
   <si>
     <t xml:space="preserve">11.4293632507324</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6398391723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5957860946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4391527175903</t>
+    <t xml:space="preserve">11.639838218689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5957880020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.439151763916</t>
   </si>
   <si>
     <t xml:space="preserve">11.4783096313477</t>
@@ -4667,37 +4667,37 @@
     <t xml:space="preserve">11.6479978561401</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8078927993774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8095245361328</t>
+    <t xml:space="preserve">11.8078956604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8095254898071</t>
   </si>
   <si>
     <t xml:space="preserve">11.7132616043091</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4913644790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.57457447052</t>
+    <t xml:space="preserve">11.4913625717163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5745754241943</t>
   </si>
   <si>
     <t xml:space="preserve">11.140362739563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6441841125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7005300521851</t>
+    <t xml:space="preserve">11.6441822052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7005319595337</t>
   </si>
   <si>
     <t xml:space="preserve">11.7535638809204</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8480310440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6160068511963</t>
+    <t xml:space="preserve">11.848030090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6160078048706</t>
   </si>
   <si>
     <t xml:space="preserve">11.7635068893433</t>
@@ -4706,46 +4706,46 @@
     <t xml:space="preserve">11.8695755004883</t>
   </si>
   <si>
-    <t xml:space="preserve">11.675669670105</t>
+    <t xml:space="preserve">11.6756715774536</t>
   </si>
   <si>
     <t xml:space="preserve">11.5115985870361</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4635353088379</t>
+    <t xml:space="preserve">11.4635362625122</t>
   </si>
   <si>
     <t xml:space="preserve">11.3044366836548</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1337356567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2066564559937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2083120346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2762613296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4469661712646</t>
+    <t xml:space="preserve">11.133734703064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.206654548645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2083129882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2762622833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4469633102417</t>
   </si>
   <si>
     <t xml:space="preserve">11.2779197692871</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8138751983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6895771026611</t>
+    <t xml:space="preserve">10.8138761520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6895761489868</t>
   </si>
   <si>
     <t xml:space="preserve">10.7641563415527</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7724418640137</t>
+    <t xml:space="preserve">10.772442817688</t>
   </si>
   <si>
     <t xml:space="preserve">11.1552782058716</t>
@@ -4754,28 +4754,28 @@
     <t xml:space="preserve">11.0840158462524</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1668796539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2248859405518</t>
+    <t xml:space="preserve">11.166880607605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2248849868774</t>
   </si>
   <si>
     <t xml:space="preserve">11.1933975219727</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2630043029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0094366073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3591270446777</t>
+    <t xml:space="preserve">11.2630033493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0094356536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3591279983521</t>
   </si>
   <si>
     <t xml:space="preserve">11.4237613677979</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2497444152832</t>
+    <t xml:space="preserve">11.2497453689575</t>
   </si>
   <si>
     <t xml:space="preserve">11.466851234436</t>
@@ -4784,37 +4784,37 @@
     <t xml:space="preserve">11.5546894073486</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5795497894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7999687194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9458122253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9507818222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8728904724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9093503952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9822702407837</t>
+    <t xml:space="preserve">11.5795478820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7999668121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9458112716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9507827758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8728895187378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9093494415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.982271194458</t>
   </si>
   <si>
     <t xml:space="preserve">11.8115692138672</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9789552688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9325504302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7502508163452</t>
+    <t xml:space="preserve">11.9789581298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9325532913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7502470016479</t>
   </si>
   <si>
     <t xml:space="preserve">11.6640691757202</t>
@@ -4823,22 +4823,22 @@
     <t xml:space="preserve">11.7651643753052</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8430576324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7419624328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7137870788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4734811782837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3939304351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4718227386475</t>
+    <t xml:space="preserve">11.843056678772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.741961479187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7137908935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4734802246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3939294815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4718236923218</t>
   </si>
   <si>
     <t xml:space="preserve">11.3491840362549</t>
@@ -4847,16 +4847,16 @@
     <t xml:space="preserve">11.5232000350952</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7336759567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8861484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2225780487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2374963760376</t>
+    <t xml:space="preserve">11.7336750030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8861465454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2225799560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2374935150146</t>
   </si>
   <si>
     <t xml:space="preserve">12.2855567932129</t>
@@ -4868,43 +4868,43 @@
     <t xml:space="preserve">12.1927480697632</t>
   </si>
   <si>
-    <t xml:space="preserve">11.849684715271</t>
+    <t xml:space="preserve">11.8496875762939</t>
   </si>
   <si>
     <t xml:space="preserve">11.8911190032959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8231706619263</t>
+    <t xml:space="preserve">11.823169708252</t>
   </si>
   <si>
     <t xml:space="preserve">11.6955595016479</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0691003799438</t>
+    <t xml:space="preserve">11.0690984725952</t>
   </si>
   <si>
     <t xml:space="preserve">10.931544303894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1039018630981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0757274627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9133138656616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0574989318848</t>
+    <t xml:space="preserve">11.1039028167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0757293701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9133148193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0574979782104</t>
   </si>
   <si>
     <t xml:space="preserve">11.1320772171021</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2166004180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1221342086792</t>
+    <t xml:space="preserve">11.2165985107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1221332550049</t>
   </si>
   <si>
     <t xml:space="preserve">11.1188182830811</t>
@@ -4919,46 +4919,46 @@
     <t xml:space="preserve">10.7094650268555</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8055877685547</t>
+    <t xml:space="preserve">10.8055896759033</t>
   </si>
   <si>
     <t xml:space="preserve">10.2006759643555</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0780334472656</t>
+    <t xml:space="preserve">10.0780344009399</t>
   </si>
   <si>
     <t xml:space="preserve">10.3008279800415</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5185594558716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5303735733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5101184844971</t>
+    <t xml:space="preserve">10.5185575485229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5303726196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5101194381714</t>
   </si>
   <si>
     <t xml:space="preserve">10.2721357345581</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3869066238403</t>
+    <t xml:space="preserve">10.386908531189</t>
   </si>
   <si>
     <t xml:space="preserve">10.5877599716187</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6957817077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8746900558472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8915700912476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3354682922363</t>
+    <t xml:space="preserve">10.695779800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8746891021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8915691375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.335467338562</t>
   </si>
   <si>
     <t xml:space="preserve">11.2325105667114</t>
@@ -4970,16 +4970,16 @@
     <t xml:space="preserve">11.4266109466553</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6325273513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5329437255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7000398635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6477174758911</t>
+    <t xml:space="preserve">11.6325263977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5329465866089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7000408172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6477155685425</t>
   </si>
   <si>
     <t xml:space="preserve">11.7135419845581</t>
@@ -4988,13 +4988,13 @@
     <t xml:space="preserve">11.7219820022583</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6072072982788</t>
+    <t xml:space="preserve">11.6072082519531</t>
   </si>
   <si>
     <t xml:space="preserve">11.4637441635132</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6173334121704</t>
+    <t xml:space="preserve">11.6173362731934</t>
   </si>
   <si>
     <t xml:space="preserve">11.6612186431885</t>
@@ -5006,7 +5006,7 @@
     <t xml:space="preserve">11.6004571914673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3776636123657</t>
+    <t xml:space="preserve">11.3776626586914</t>
   </si>
   <si>
     <t xml:space="preserve">11.1143627166748</t>
@@ -5015,16 +5015,16 @@
     <t xml:space="preserve">11.002965927124</t>
   </si>
   <si>
-    <t xml:space="preserve">10.94895362854</t>
+    <t xml:space="preserve">10.9489555358887</t>
   </si>
   <si>
     <t xml:space="preserve">11.4519281387329</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5143785476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4097347259521</t>
+    <t xml:space="preserve">11.5143795013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4097328186035</t>
   </si>
   <si>
     <t xml:space="preserve">11.1346168518066</t>
@@ -5033,94 +5033,94 @@
     <t xml:space="preserve">11.2966480255127</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2628917694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1649961471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3050870895386</t>
+    <t xml:space="preserve">11.2628908157349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1649971008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3050880432129</t>
   </si>
   <si>
     <t xml:space="preserve">11.2578277587891</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3506574630737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3849773406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4656238555908</t>
+    <t xml:space="preserve">11.3506593704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3849782943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4656229019165</t>
   </si>
   <si>
     <t xml:space="preserve">11.4690551757812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1927976608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3180570602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3386478424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0726823806763</t>
+    <t xml:space="preserve">11.1927947998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.318058013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3386468887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0726842880249</t>
   </si>
   <si>
     <t xml:space="preserve">10.6814584732056</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9714460372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2751598358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2408418655396</t>
+    <t xml:space="preserve">10.9714441299438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2751588821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2408409118652</t>
   </si>
   <si>
     <t xml:space="preserve">11.1396036148071</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2219667434692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2528533935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0074787139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1190137863159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.141318321228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1962280273438</t>
+    <t xml:space="preserve">11.2219657897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2528514862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0074806213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1190128326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1413202285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1962289810181</t>
   </si>
   <si>
     <t xml:space="preserve">11.1344547271729</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1447515487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9954681396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2099561691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0555248260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.978307723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.100136756897</t>
+    <t xml:space="preserve">11.1447505950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9954671859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2099552154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0555229187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9783086776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1001377105713</t>
   </si>
   <si>
     <t xml:space="preserve">10.9354124069214</t>
@@ -5129,34 +5129,34 @@
     <t xml:space="preserve">10.9834566116333</t>
   </si>
   <si>
-    <t xml:space="preserve">11.057240486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3094787597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5068054199219</t>
+    <t xml:space="preserve">11.0572395324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.309476852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5068044662476</t>
   </si>
   <si>
     <t xml:space="preserve">11.5514183044434</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4707708358765</t>
+    <t xml:space="preserve">11.4707727432251</t>
   </si>
   <si>
     <t xml:space="preserve">11.1825008392334</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1979427337646</t>
+    <t xml:space="preserve">11.1979446411133</t>
   </si>
   <si>
     <t xml:space="preserve">11.2562847137451</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3540906906128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.611475944519</t>
+    <t xml:space="preserve">11.3540916442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6114768981934</t>
   </si>
   <si>
     <t xml:space="preserve">11.6852588653564</t>
@@ -5165,10 +5165,10 @@
     <t xml:space="preserve">11.518816947937</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4055662155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5222482681274</t>
+    <t xml:space="preserve">11.4055671691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5222492218018</t>
   </si>
   <si>
     <t xml:space="preserve">11.6166219711304</t>
@@ -5177,10 +5177,10 @@
     <t xml:space="preserve">11.7024173736572</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8465518951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7624750137329</t>
+    <t xml:space="preserve">11.8465528488159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7624740600586</t>
   </si>
   <si>
     <t xml:space="preserve">11.6595191955566</t>
@@ -5189,22 +5189,22 @@
     <t xml:space="preserve">11.7796325683594</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7178611755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9117565155029</t>
+    <t xml:space="preserve">11.7178592681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9117574691772</t>
   </si>
   <si>
     <t xml:space="preserve">11.8190984725952</t>
   </si>
   <si>
-    <t xml:space="preserve">11.724723815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7744846343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7350206375122</t>
+    <t xml:space="preserve">11.7247247695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7744855880737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7350196838379</t>
   </si>
   <si>
     <t xml:space="preserve">11.6904048919678</t>
@@ -5213,31 +5213,31 @@
     <t xml:space="preserve">12.069619178772</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1193809509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0524616241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0232906341553</t>
+    <t xml:space="preserve">12.1193819046021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0524597167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.023289680481</t>
   </si>
   <si>
     <t xml:space="preserve">11.9512233734131</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9889736175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0404481887817</t>
+    <t xml:space="preserve">11.9889726638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0404491424561</t>
   </si>
   <si>
     <t xml:space="preserve">12.0884943008423</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1090850830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0747671127319</t>
+    <t xml:space="preserve">12.1090860366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0747661590576</t>
   </si>
   <si>
     <t xml:space="preserve">12.1210975646973</t>
@@ -5246,49 +5246,49 @@
     <t xml:space="preserve">12.1434030532837</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2669477462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3167095184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3270034790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.254937171936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4728546142578</t>
+    <t xml:space="preserve">12.2669467926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3167085647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3270053863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2549362182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4728555679321</t>
   </si>
   <si>
     <t xml:space="preserve">12.5277643203735</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7268085479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6907730102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6461620330811</t>
+    <t xml:space="preserve">12.726806640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6907749176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6461610794067</t>
   </si>
   <si>
     <t xml:space="preserve">12.6959218978882</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9138412475586</t>
+    <t xml:space="preserve">12.9138402938843</t>
   </si>
   <si>
     <t xml:space="preserve">12.9567394256592</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9738960266113</t>
+    <t xml:space="preserve">12.9738969802856</t>
   </si>
   <si>
     <t xml:space="preserve">13.1866683959961</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1574993133545</t>
+    <t xml:space="preserve">13.1574983596802</t>
   </si>
   <si>
     <t xml:space="preserve">13.0511646270752</t>
@@ -5297,25 +5297,25 @@
     <t xml:space="preserve">13.3353023529053</t>
   </si>
   <si>
-    <t xml:space="preserve">13.27952003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0877714157104</t>
+    <t xml:space="preserve">13.2795209884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0877695083618</t>
   </si>
   <si>
     <t xml:space="preserve">13.2812643051147</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2638320922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2289686203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3980560302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4398918151855</t>
+    <t xml:space="preserve">13.2638330459595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2289695739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3980569839478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4398927688599</t>
   </si>
   <si>
     <t xml:space="preserve">13.2969512939453</t>
@@ -5324,13 +5324,13 @@
     <t xml:space="preserve">12.9866666793823</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8367538452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6362886428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5857353210449</t>
+    <t xml:space="preserve">12.8367528915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.636287689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5857362747192</t>
   </si>
   <si>
     <t xml:space="preserve">12.7600545883179</t>
@@ -5345,76 +5345,76 @@
     <t xml:space="preserve">13.1487827301025</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3318157196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5078763961792</t>
+    <t xml:space="preserve">13.3318147659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5078773498535</t>
   </si>
   <si>
     <t xml:space="preserve">13.4921875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5375099182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6316423416138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4677820205688</t>
+    <t xml:space="preserve">13.5375108718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6316413879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4677839279175</t>
   </si>
   <si>
     <t xml:space="preserve">13.4207181930542</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4538383483887</t>
+    <t xml:space="preserve">13.453839302063</t>
   </si>
   <si>
     <t xml:space="preserve">13.4276905059814</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4939308166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5183372497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3910837173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4468660354614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6874227523804</t>
+    <t xml:space="preserve">13.4939317703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5183353424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3910846710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4468669891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6874237060547</t>
   </si>
   <si>
     <t xml:space="preserve">13.3928270339966</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4259471893311</t>
+    <t xml:space="preserve">13.4259481430054</t>
   </si>
   <si>
     <t xml:space="preserve">13.0842847824097</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9221696853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0180435180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0720834732056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2760353088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2917222976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2394256591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9518022537231</t>
+    <t xml:space="preserve">12.9221687316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0180444717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0720825195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2760343551636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2917232513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2394275665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9518032073975</t>
   </si>
   <si>
     <t xml:space="preserve">13.2843284606934</t>
@@ -5426,37 +5426,37 @@
     <t xml:space="preserve">13.0329465866089</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2205982208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3374376296997</t>
+    <t xml:space="preserve">13.2205972671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3374366760254</t>
   </si>
   <si>
     <t xml:space="preserve">13.3038015365601</t>
   </si>
   <si>
-    <t xml:space="preserve">13.452507019043</t>
+    <t xml:space="preserve">13.4525079727173</t>
   </si>
   <si>
     <t xml:space="preserve">13.3728437423706</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4259519577026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.49853515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2418403625488</t>
+    <t xml:space="preserve">13.425952911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4985342025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2418413162231</t>
   </si>
   <si>
     <t xml:space="preserve">13.3569107055664</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1993532180786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0736637115479</t>
+    <t xml:space="preserve">13.1993551254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0736627578735</t>
   </si>
   <si>
     <t xml:space="preserve">13.2860984802246</t>
@@ -5465,22 +5465,22 @@
     <t xml:space="preserve">13.2630844116211</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1037588119507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0559616088867</t>
+    <t xml:space="preserve">13.1037578582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0559606552124</t>
   </si>
   <si>
     <t xml:space="preserve">13.1427049636841</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1126089096069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2701663970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3002614974976</t>
+    <t xml:space="preserve">13.1126079559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2701654434204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3002605438232</t>
   </si>
   <si>
     <t xml:space="preserve">13.4578170776367</t>
@@ -5498,22 +5498,22 @@
     <t xml:space="preserve">13.5941305160522</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5852794647217</t>
+    <t xml:space="preserve">13.5852785110474</t>
   </si>
   <si>
     <t xml:space="preserve">13.7693910598755</t>
   </si>
   <si>
-    <t xml:space="preserve">13.664942741394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7375268936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7552280426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3480587005615</t>
+    <t xml:space="preserve">13.6649436950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7375259399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7552270889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3480596542358</t>
   </si>
   <si>
     <t xml:space="preserve">13.2099761962891</t>
@@ -5522,16 +5522,16 @@
     <t xml:space="preserve">13.1745700836182</t>
   </si>
   <si>
-    <t xml:space="preserve">13.11083984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3144245147705</t>
+    <t xml:space="preserve">13.1108388900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3144226074219</t>
   </si>
   <si>
     <t xml:space="preserve">13.2737073898315</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2170572280884</t>
+    <t xml:space="preserve">13.2170562744141</t>
   </si>
   <si>
     <t xml:space="preserve">12.9692153930664</t>
@@ -5543,22 +5543,22 @@
     <t xml:space="preserve">12.7904148101807</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6930494308472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7089815139771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8258209228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8930931091309</t>
+    <t xml:space="preserve">12.6930484771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7089805603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8258199691772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8930921554565</t>
   </si>
   <si>
     <t xml:space="preserve">13.0612707138062</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2064361572266</t>
+    <t xml:space="preserve">13.2064352035522</t>
   </si>
   <si>
     <t xml:space="preserve">13.0984468460083</t>
@@ -5567,37 +5567,37 @@
     <t xml:space="preserve">12.910795211792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7231426239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9249582290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7196035385132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.716064453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6523313522339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7797937393188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8081169128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8364429473877</t>
+    <t xml:space="preserve">12.7231435775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9249572753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7196025848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7160634994507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6523303985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7797927856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8081188201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.836443901062</t>
   </si>
   <si>
     <t xml:space="preserve">12.9267282485962</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5284118652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.542573928833</t>
+    <t xml:space="preserve">12.5284109115601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5425720214844</t>
   </si>
   <si>
     <t xml:space="preserve">12.508936882019</t>
@@ -5609,19 +5609,19 @@
     <t xml:space="preserve">12.595682144165</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6186971664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6151552200317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7284536361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7072114944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6116142272949</t>
+    <t xml:space="preserve">12.6186952590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6151533126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7284545898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7072105407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6116151809692</t>
   </si>
   <si>
     <t xml:space="preserve">12.6824264526367</t>
@@ -5630,52 +5630,52 @@
     <t xml:space="preserve">12.7355356216431</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8417549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9479722976685</t>
+    <t xml:space="preserve">12.8417539596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9479713439941</t>
   </si>
   <si>
     <t xml:space="preserve">12.951512336731</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0134735107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8860111236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.004620552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.257773399353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8541450500488</t>
+    <t xml:space="preserve">13.0134725570679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8860101699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0046215057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2577743530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8541460037231</t>
   </si>
   <si>
     <t xml:space="preserve">12.8399829864502</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7949819564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1009960174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8939867019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9245862960815</t>
+    <t xml:space="preserve">12.7949810028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1009941101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.893985748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9245882034302</t>
   </si>
   <si>
     <t xml:space="preserve">12.9191865921021</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0991954803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0955944061279</t>
+    <t xml:space="preserve">13.0991945266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0955953598022</t>
   </si>
   <si>
     <t xml:space="preserve">13.1135950088501</t>
@@ -5687,49 +5687,49 @@
     <t xml:space="preserve">13.5276145935059</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6590204238892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8138284683228</t>
+    <t xml:space="preserve">13.6590194702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8138275146484</t>
   </si>
   <si>
     <t xml:space="preserve">13.9578342437744</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9632329940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9020328521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8390293121338</t>
+    <t xml:space="preserve">13.9632349014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9020309448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8390302658081</t>
   </si>
   <si>
     <t xml:space="preserve">13.786826133728</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1576414108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9812355041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6806211471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7976264953613</t>
+    <t xml:space="preserve">14.157642364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9812345504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6806221008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.79762840271</t>
   </si>
   <si>
     <t xml:space="preserve">13.7076225280762</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7328243255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8066282272339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.968635559082</t>
+    <t xml:space="preserve">13.7328252792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8066272735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9686346054077</t>
   </si>
   <si>
     <t xml:space="preserve">13.71302318573</t>
@@ -5744,7 +5744,7 @@
     <t xml:space="preserve">13.7472248077393</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6230182647705</t>
+    <t xml:space="preserve">13.6230173110962</t>
   </si>
   <si>
     <t xml:space="preserve">13.3422060012817</t>
@@ -5753,10 +5753,10 @@
     <t xml:space="preserve">13.2378015518188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3692073822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4718112945557</t>
+    <t xml:space="preserve">13.3692083358765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.47181224823</t>
   </si>
   <si>
     <t xml:space="preserve">13.4430112838745</t>
@@ -5765,76 +5765,76 @@
     <t xml:space="preserve">13.5294141769409</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6626205444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7148237228394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6014184951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3026037216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3458061218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4024887084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3366651535034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2105026245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2452421188354</t>
+    <t xml:space="preserve">13.6626214981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.714822769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6014175415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.302604675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3458070755005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4024877548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3366641998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2105016708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2452430725098</t>
   </si>
   <si>
     <t xml:space="preserve">13.1501636505127</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3311786651611</t>
+    <t xml:space="preserve">13.3311796188354</t>
   </si>
   <si>
     <t xml:space="preserve">13.3092374801636</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1519908905029</t>
+    <t xml:space="preserve">13.1519918441772</t>
   </si>
   <si>
     <t xml:space="preserve">13.1355352401733</t>
   </si>
   <si>
-    <t xml:space="preserve">13.252555847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.181245803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.811900138855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7497339248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8630981445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7917881011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8978366851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7881307601929</t>
+    <t xml:space="preserve">13.2525548934937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1812477111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8119010925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7497329711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8630971908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.791787147522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.897837638855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7881317138672</t>
   </si>
   <si>
     <t xml:space="preserve">12.7460775375366</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5412921905518</t>
+    <t xml:space="preserve">12.5412912368774</t>
   </si>
   <si>
     <t xml:space="preserve">12.3493051528931</t>
@@ -5846,16 +5846,16 @@
     <t xml:space="preserve">12.6016302108765</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7058525085449</t>
+    <t xml:space="preserve">12.7058515548706</t>
   </si>
   <si>
     <t xml:space="preserve">12.9197797775269</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7405920028687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9124660491943</t>
+    <t xml:space="preserve">12.7405910491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9124641418457</t>
   </si>
   <si>
     <t xml:space="preserve">13.0148582458496</t>
@@ -5867,13 +5867,13 @@
     <t xml:space="preserve">13.0861682891846</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1227350234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2854681015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2818117141724</t>
+    <t xml:space="preserve">13.1227369308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2854671478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.281810760498</t>
   </si>
   <si>
     <t xml:space="preserve">13.221471786499</t>
@@ -5885,10 +5885,10 @@
     <t xml:space="preserve">13.2141590118408</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0751981735229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9014949798584</t>
+    <t xml:space="preserve">13.0751962661743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9014959335327</t>
   </si>
   <si>
     <t xml:space="preserve">12.963662147522</t>
@@ -5897,31 +5897,31 @@
     <t xml:space="preserve">12.9819469451904</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0678825378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0166873931885</t>
+    <t xml:space="preserve">13.0678834915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0166854858398</t>
   </si>
   <si>
     <t xml:space="preserve">12.8100728988647</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9216079711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0642261505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8722400665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8649263381958</t>
+    <t xml:space="preserve">12.9216070175171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.064227104187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8722410202026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8649253845215</t>
   </si>
   <si>
     <t xml:space="preserve">12.8228721618652</t>
   </si>
   <si>
-    <t xml:space="preserve">12.852126121521</t>
+    <t xml:space="preserve">12.8521270751953</t>
   </si>
   <si>
     <t xml:space="preserve">12.8173866271973</t>
@@ -5933,10 +5933,10 @@
     <t xml:space="preserve">13.384204864502</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5286502838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3019227981567</t>
+    <t xml:space="preserve">13.5286512374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3019247055054</t>
   </si>
   <si>
     <t xml:space="preserve">12.9965734481812</t>
@@ -5951,28 +5951,28 @@
     <t xml:space="preserve">13.0441131591797</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2159872055054</t>
+    <t xml:space="preserve">13.2159881591797</t>
   </si>
   <si>
     <t xml:space="preserve">13.0971393585205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2543849945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3640909194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2507286071777</t>
+    <t xml:space="preserve">13.2543840408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3640918731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2507276535034</t>
   </si>
   <si>
     <t xml:space="preserve">13.2708406448364</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1666193008423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4719686508179</t>
+    <t xml:space="preserve">13.1666202545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4719696044922</t>
   </si>
   <si>
     <t xml:space="preserve">13.4408855438232</t>
@@ -5996,19 +5996,19 @@
     <t xml:space="preserve">12.9490346908569</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5815172195435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5540914535522</t>
+    <t xml:space="preserve">12.5815162658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5540904998779</t>
   </si>
   <si>
     <t xml:space="preserve">12.6619691848755</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8064165115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9033241271973</t>
+    <t xml:space="preserve">12.8064155578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9033231735229</t>
   </si>
   <si>
     <t xml:space="preserve">13.0002317428589</t>
@@ -6017,16 +6017,16 @@
     <t xml:space="preserve">13.0276575088501</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0569124221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.122049331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1778783798218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0234155654907</t>
+    <t xml:space="preserve">13.0569114685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1220483779907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1778793334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0234146118164</t>
   </si>
   <si>
     <t xml:space="preserve">12.6270170211792</t>
@@ -6035,7 +6035,7 @@
     <t xml:space="preserve">12.7200679779053</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7312345504761</t>
+    <t xml:space="preserve">12.7312335968018</t>
   </si>
   <si>
     <t xml:space="preserve">12.9247808456421</t>
@@ -6044,16 +6044,16 @@
     <t xml:space="preserve">13.1369361877441</t>
   </si>
   <si>
-    <t xml:space="preserve">13.125771522522</t>
+    <t xml:space="preserve">13.1257705688477</t>
   </si>
   <si>
     <t xml:space="preserve">13.3286218643188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4961128234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2076559066772</t>
+    <t xml:space="preserve">13.4961137771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2076549530029</t>
   </si>
   <si>
     <t xml:space="preserve">13.181601524353</t>
@@ -6065,7 +6065,7 @@
     <t xml:space="preserve">13.3267602920532</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3565359115601</t>
+    <t xml:space="preserve">13.3565378189087</t>
   </si>
   <si>
     <t xml:space="preserve">12.9936380386353</t>
@@ -6074,34 +6074,34 @@
     <t xml:space="preserve">13.0606355667114</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2653465270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2858180999756</t>
+    <t xml:space="preserve">13.2653474807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2858190536499</t>
   </si>
   <si>
     <t xml:space="preserve">13.1946287155151</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2374315261841</t>
+    <t xml:space="preserve">13.2374324798584</t>
   </si>
   <si>
     <t xml:space="preserve">13.4253950119019</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0196924209595</t>
+    <t xml:space="preserve">13.0196914672852</t>
   </si>
   <si>
     <t xml:space="preserve">13.0383024215698</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0587739944458</t>
+    <t xml:space="preserve">13.0587749481201</t>
   </si>
   <si>
     <t xml:space="preserve">13.0476083755493</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1350755691528</t>
+    <t xml:space="preserve">13.1350765228271</t>
   </si>
   <si>
     <t xml:space="preserve">13.0308589935303</t>
@@ -6113,13 +6113,13 @@
     <t xml:space="preserve">12.9620008468628</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0364408493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8522005081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7647333145142</t>
+    <t xml:space="preserve">13.0364418029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.852201461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7647323608398</t>
   </si>
   <si>
     <t xml:space="preserve">13.1164655685425</t>
@@ -6149,7 +6149,7 @@
     <t xml:space="preserve">12.7091226577759</t>
   </si>
   <si>
-    <t xml:space="preserve">12.716700553894</t>
+    <t xml:space="preserve">12.7166996002197</t>
   </si>
   <si>
     <t xml:space="preserve">12.6996488571167</t>
@@ -6161,7 +6161,7 @@
     <t xml:space="preserve">12.7602767944336</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7754335403442</t>
+    <t xml:space="preserve">12.7754344940186</t>
   </si>
   <si>
     <t xml:space="preserve">12.7451200485229</t>
@@ -6170,10 +6170,10 @@
     <t xml:space="preserve">12.712911605835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7830123901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6977548599243</t>
+    <t xml:space="preserve">12.783013343811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.69775390625</t>
   </si>
   <si>
     <t xml:space="preserve">12.6693344116211</t>
@@ -6182,10 +6182,10 @@
     <t xml:space="preserve">12.6181793212891</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5954446792603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4097728729248</t>
+    <t xml:space="preserve">12.5954437255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4097719192505</t>
   </si>
   <si>
     <t xml:space="preserve">12.1104221343994</t>
@@ -6206,13 +6206,13 @@
     <t xml:space="preserve">12.2714643478394</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4002990722656</t>
+    <t xml:space="preserve">12.4003000259399</t>
   </si>
   <si>
     <t xml:space="preserve">12.7526979446411</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9213199615479</t>
+    <t xml:space="preserve">12.9213209152222</t>
   </si>
   <si>
     <t xml:space="preserve">12.9421606063843</t>
@@ -6260,10 +6260,10 @@
     <t xml:space="preserve">12.7242794036865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7413311004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9175300598145</t>
+    <t xml:space="preserve">12.7413301467896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9175291061401</t>
   </si>
   <si>
     <t xml:space="preserve">12.9781579971313</t>
@@ -6281,22 +6281,22 @@
     <t xml:space="preserve">13.1316232681274</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1543569564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3210849761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2869825363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2547731399536</t>
+    <t xml:space="preserve">13.1543579101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3210859298706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2869815826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2547721862793</t>
   </si>
   <si>
     <t xml:space="preserve">13.2983493804932</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3343477249146</t>
+    <t xml:space="preserve">13.3343467712402</t>
   </si>
   <si>
     <t xml:space="preserve">13.3513994216919</t>
@@ -6308,7 +6308,7 @@
     <t xml:space="preserve">13.3154001235962</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2263536453247</t>
+    <t xml:space="preserve">13.2263526916504</t>
   </si>
   <si>
     <t xml:space="preserve">13.2964553833008</t>
@@ -6332,34 +6332,34 @@
     <t xml:space="preserve">12.5651302337646</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4514541625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5196599960327</t>
+    <t xml:space="preserve">12.4514532089233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5196590423584</t>
   </si>
   <si>
     <t xml:space="preserve">12.8227996826172</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8322715759277</t>
+    <t xml:space="preserve">12.8322725296021</t>
   </si>
   <si>
     <t xml:space="preserve">12.9307928085327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9364757537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.995210647583</t>
+    <t xml:space="preserve">12.9364767074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9952096939087</t>
   </si>
   <si>
     <t xml:space="preserve">13.2850875854492</t>
   </si>
   <si>
-    <t xml:space="preserve">13.404447555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5806484222412</t>
+    <t xml:space="preserve">13.4044485092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5806474685669</t>
   </si>
   <si>
     <t xml:space="preserve">13.6848516464233</t>
@@ -6852,6 +6852,9 @@
   </si>
   <si>
     <t xml:space="preserve">16.2180004119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2959995269775</t>
   </si>
 </sst>
 </file>
@@ -72554,7 +72557,7 @@
     </row>
     <row r="2515">
       <c r="A2515" s="1" t="n">
-        <v>45980.6937268519</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B2515" t="n">
         <v>8051185</v>
@@ -72575,6 +72578,32 @@
         <v>2279</v>
       </c>
       <c r="H2515" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2516">
+      <c r="A2516" s="1" t="n">
+        <v>45981.6932175926</v>
+      </c>
+      <c r="B2516" t="n">
+        <v>7107536</v>
+      </c>
+      <c r="C2516" t="n">
+        <v>16.4080009460449</v>
+      </c>
+      <c r="D2516" t="n">
+        <v>16.2800006866455</v>
+      </c>
+      <c r="E2516" t="n">
+        <v>16.3239994049072</v>
+      </c>
+      <c r="F2516" t="n">
+        <v>16.2959995269775</v>
+      </c>
+      <c r="G2516" t="s">
+        <v>2280</v>
+      </c>
+      <c r="H2516" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ENI.MI.xlsx
+++ b/data/ENI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2300" uniqueCount="2300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2301" uniqueCount="2301">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,349 +38,349 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15080308914185</t>
+    <t xml:space="preserve">7.15080261230469</t>
   </si>
   <si>
     <t xml:space="preserve">ENI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21469736099243</t>
+    <t xml:space="preserve">7.21469640731812</t>
   </si>
   <si>
     <t xml:space="preserve">7.01236629486084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95911931991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76211500167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73549222946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75146484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83133125305176</t>
+    <t xml:space="preserve">6.95912027359009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76211452484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73549175262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75146532058716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83133363723755</t>
   </si>
   <si>
     <t xml:space="preserve">6.92717409133911</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68224620819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60770416259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69822120666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47459268569946</t>
+    <t xml:space="preserve">6.68224573135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60770273208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69821929931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47459030151367</t>
   </si>
   <si>
     <t xml:space="preserve">6.90587520599365</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82068347930908</t>
+    <t xml:space="preserve">6.82068490982056</t>
   </si>
   <si>
     <t xml:space="preserve">6.96444511413574</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99639320373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07093524932861</t>
+    <t xml:space="preserve">6.99639272689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07093477249146</t>
   </si>
   <si>
     <t xml:space="preserve">6.66095018386841</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63432598114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78341341018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67159795761108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43199491500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17641973495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19239282608032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81967830657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2083683013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35745239257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30953311920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51186418533325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37342739105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34680366516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57575845718384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27226161956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43732023239136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76743745803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89522647857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10820627212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.161452293396</t>
+    <t xml:space="preserve">6.63432741165161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78341293334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67159748077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43199634552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17642021179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19239187240601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81967735290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20836687088013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35745286941528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30953216552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51186275482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37342643737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34680461883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57575750350952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27225971221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43732118606567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7674388885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89522504806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1082067489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16145277023315</t>
   </si>
   <si>
     <t xml:space="preserve">7.25729417800903</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20937204360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23599481582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05496168136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13483047485352</t>
+    <t xml:space="preserve">7.20937252044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23599338531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05496263504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13483142852783</t>
   </si>
   <si>
     <t xml:space="preserve">6.88990259170532</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09223413467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1295051574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0283408164978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11885547637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24664402008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31053829193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34781122207642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17210102081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00171613693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19872379302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08158493041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81003379821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79406213760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62367582321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69289541244507</t>
+    <t xml:space="preserve">7.0922327041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12950658798218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02833795547485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11885595321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24664449691772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31053733825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34780931472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17210149765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00171661376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19872522354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08158445358276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81003475189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79406261444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62367725372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69289493560791</t>
   </si>
   <si>
     <t xml:space="preserve">6.55978298187256</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84198379516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86328077316284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90055227279663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17742538452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30521249771118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18807411193848</t>
+    <t xml:space="preserve">6.84198141098022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86328029632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90055131912231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17742443084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30521440505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.188072681427</t>
   </si>
   <si>
     <t xml:space="preserve">7.27859115600586</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39573001861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49157047271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53416633605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49689388275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52884197235107</t>
+    <t xml:space="preserve">7.39573049545288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49157094955444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53416728973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49689674377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52884292602539</t>
   </si>
   <si>
     <t xml:space="preserve">7.59806251525879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66728162765503</t>
+    <t xml:space="preserve">7.66728067398071</t>
   </si>
   <si>
     <t xml:space="preserve">7.56079006195068</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42767763137817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27326679229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12418127059937</t>
+    <t xml:space="preserve">7.42767667770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27326536178589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12417888641357</t>
   </si>
   <si>
     <t xml:space="preserve">7.22534704208374</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28923940658569</t>
+    <t xml:space="preserve">7.28924036026001</t>
   </si>
   <si>
     <t xml:space="preserve">7.02301406860352</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10738658905029</t>
+    <t xml:space="preserve">7.10738754272461</t>
   </si>
   <si>
     <t xml:space="preserve">7.3269214630127</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5793833732605</t>
+    <t xml:space="preserve">7.57938480377197</t>
   </si>
   <si>
     <t xml:space="preserve">7.6178035736084</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59036016464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65073251724243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53547811508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43119812011719</t>
+    <t xml:space="preserve">7.59035968780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65073442459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.535475730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43119955062866</t>
   </si>
   <si>
     <t xml:space="preserve">7.42571115493774</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36534070968628</t>
+    <t xml:space="preserve">7.36533880233765</t>
   </si>
   <si>
     <t xml:space="preserve">7.5574312210083</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73305654525757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75501155853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71659374237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3818039894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24459648132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33789825439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.261061668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54645442962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77147483825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87026596069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74952268600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00198650360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26655006408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49706077575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84831237792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96905469894409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13370800018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90868377685547</t>
+    <t xml:space="preserve">7.7330584526062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7550106048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71659278869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38180541992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24459552764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33789777755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26106071472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54645490646362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77147674560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87026691436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74952363967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00198554992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26655054092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49705791473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84831380844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96905565261841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13370704650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90868282318115</t>
   </si>
   <si>
     <t xml:space="preserve">7.76049900054932</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80440521240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95808029174805</t>
+    <t xml:space="preserve">7.80440616607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95807933807373</t>
   </si>
   <si>
     <t xml:space="preserve">8.05138111114502</t>
@@ -389,49 +389,49 @@
     <t xml:space="preserve">8.12821865081787</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02942657470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17761421203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07882022857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99100828170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96356773376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88673067092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84282541275024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80989170074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70012807846069</t>
+    <t xml:space="preserve">8.02942752838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1776123046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07882308959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99100923538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96356534957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88672876358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84282445907593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80989551544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70012617111206</t>
   </si>
   <si>
     <t xml:space="preserve">7.70561647415161</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50254774093628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50803709030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35985279083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20617866516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25557231903076</t>
+    <t xml:space="preserve">7.50254821777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50803518295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35985040664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20617771148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25557518005371</t>
   </si>
   <si>
     <t xml:space="preserve">7.27203845977783</t>
@@ -440,109 +440,109 @@
     <t xml:space="preserve">7.44766521453857</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43668746948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41473436355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51901245117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54096698760986</t>
+    <t xml:space="preserve">7.43668842315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41473388671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51901388168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54096555709839</t>
   </si>
   <si>
     <t xml:space="preserve">7.39278030395508</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37631559371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47510576248169</t>
+    <t xml:space="preserve">7.37631511688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47510623931885</t>
   </si>
   <si>
     <t xml:space="preserve">7.46961784362793</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52998733520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44217729568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19520282745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21715497970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25008487701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08543491363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19304752349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06278085708618</t>
+    <t xml:space="preserve">7.52998924255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44217824935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19520044326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21715354919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25008249282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0854344367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19304609298706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06278038024902</t>
   </si>
   <si>
     <t xml:space="preserve">7.16472864151001</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13640928268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00614070892334</t>
+    <t xml:space="preserve">7.1364107131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00614213943481</t>
   </si>
   <si>
     <t xml:space="preserve">6.97215843200684</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99481534957886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31764984130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26101398468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30066013336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34596967697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51588487625122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52721166610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70279121398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55553007125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50455665588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45358180999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60084342956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53854036331177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6744704246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69712543487549</t>
+    <t xml:space="preserve">6.99481296539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31765270233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2610125541687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3006591796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34597110748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51588582992554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52721118927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70278978347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55553102493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50455808639526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45358276367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60084247589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53853988647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67447137832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6971263885498</t>
   </si>
   <si>
     <t xml:space="preserve">7.77642107009888</t>
@@ -557,16 +557,16 @@
     <t xml:space="preserve">7.66880798339844</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78774833679199</t>
+    <t xml:space="preserve">7.78774929046631</t>
   </si>
   <si>
     <t xml:space="preserve">7.65181732177734</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48190212249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36296224594116</t>
+    <t xml:space="preserve">7.48190259933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36296272277832</t>
   </si>
   <si>
     <t xml:space="preserve">7.25534868240356</t>
@@ -578,19 +578,19 @@
     <t xml:space="preserve">7.13074541091919</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23269462585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27800512313843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2496862411499</t>
+    <t xml:space="preserve">7.23269414901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27800416946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24968385696411</t>
   </si>
   <si>
     <t xml:space="preserve">7.22136640548706</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10808944702148</t>
+    <t xml:space="preserve">7.1080904006958</t>
   </si>
   <si>
     <t xml:space="preserve">6.94383907318115</t>
@@ -599,73 +599,73 @@
     <t xml:space="preserve">7.07977056503296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03446102142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01180553436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11941766738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12508153915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17039346694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4422550201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70845460891724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75376272201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90668964385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98598194122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05960941314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0709400177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37112236022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45607948303223</t>
+    <t xml:space="preserve">7.03445816040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01180458068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11941719055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12507915496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17039060592651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44225597381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7084527015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75376510620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90668869018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98598289489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05961132049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07093906402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37112140655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45607852935791</t>
   </si>
   <si>
     <t xml:space="preserve">8.42776012420654</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47873210906982</t>
+    <t xml:space="preserve">8.47873306274414</t>
   </si>
   <si>
     <t xml:space="preserve">8.52404499053955</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47307109832764</t>
+    <t xml:space="preserve">8.47307014465332</t>
   </si>
   <si>
     <t xml:space="preserve">8.58068180084229</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59201145172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68829345703125</t>
+    <t xml:space="preserve">8.59200859069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6882963180542</t>
   </si>
   <si>
     <t xml:space="preserve">8.67130374908447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74493408203125</t>
+    <t xml:space="preserve">8.74493217468262</t>
   </si>
   <si>
     <t xml:space="preserve">8.76192569732666</t>
@@ -674,34 +674,34 @@
     <t xml:space="preserve">8.85820960998535</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85254573822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88652801513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90351963043213</t>
+    <t xml:space="preserve">8.85254383087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8865270614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90352058410645</t>
   </si>
   <si>
     <t xml:space="preserve">8.71661376953125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8072338104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80157089233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75626182556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87520122528076</t>
+    <t xml:space="preserve">8.80723476409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8015718460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75625991821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87519836425781</t>
   </si>
   <si>
     <t xml:space="preserve">8.72227764129639</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81856155395508</t>
+    <t xml:space="preserve">8.81856346130371</t>
   </si>
   <si>
     <t xml:space="preserve">8.78458118438721</t>
@@ -710,94 +710,94 @@
     <t xml:space="preserve">8.69395923614502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46740436553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36545848846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15023136138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04828453063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00297451019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01996231079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22952365875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0426197052002</t>
+    <t xml:space="preserve">8.46740531921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36545658111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15023326873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04828262329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00297355651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01996326446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22952461242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04261875152588</t>
   </si>
   <si>
     <t xml:space="preserve">8.00863647460938</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13324165344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15589714050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23518848419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14457035064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99730920791626</t>
+    <t xml:space="preserve">8.1332426071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1558952331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23518943786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14456844329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99731111526489</t>
   </si>
   <si>
     <t xml:space="preserve">8.25784492492676</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16155910491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09925842285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22386264801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4957275390625</t>
+    <t xml:space="preserve">8.16156101226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09925937652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22386169433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49572658538818</t>
   </si>
   <si>
     <t xml:space="preserve">8.50138854980469</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64864826202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54669857025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38245010375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32581233978271</t>
+    <t xml:space="preserve">8.64864921569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54669952392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38244915008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3258113861084</t>
   </si>
   <si>
     <t xml:space="preserve">8.28616428375244</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29749011993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19554424285889</t>
+    <t xml:space="preserve">8.29749202728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19554138183594</t>
   </si>
   <si>
     <t xml:space="preserve">8.30881977081299</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45041370391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41076755523682</t>
+    <t xml:space="preserve">8.45041465759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41076850891113</t>
   </si>
   <si>
     <t xml:space="preserve">8.433424949646</t>
@@ -806,58 +806,58 @@
     <t xml:space="preserve">8.51271629333496</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49005889892578</t>
+    <t xml:space="preserve">8.49006175994873</t>
   </si>
   <si>
     <t xml:space="preserve">8.56369018554688</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67696571350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62599277496338</t>
+    <t xml:space="preserve">8.67696762084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6259937286377</t>
   </si>
   <si>
     <t xml:space="preserve">8.62032794952393</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6316556930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31448268890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32014656066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46847915649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43353652954102</t>
+    <t xml:space="preserve">8.63165760040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31448173522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32014751434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46848011016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43353462219238</t>
   </si>
   <si>
     <t xml:space="preserve">8.34034824371338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31122779846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32869815826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29375457763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28792667388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49760341644287</t>
+    <t xml:space="preserve">8.31122589111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32870006561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29375267028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28792858123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49760055541992</t>
   </si>
   <si>
     <t xml:space="preserve">8.58496475219727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63156223297119</t>
+    <t xml:space="preserve">8.63156127929688</t>
   </si>
   <si>
     <t xml:space="preserve">8.67815399169922</t>
@@ -866,28 +866,28 @@
     <t xml:space="preserve">8.67233180999756</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73639869689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76551914215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65485668182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7596960067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74804782867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73056983947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69562816619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53254699707031</t>
+    <t xml:space="preserve">8.7363977432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76551818847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65485763549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75969409942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74804592132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73057270050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69562721252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53254890441895</t>
   </si>
   <si>
     <t xml:space="preserve">8.33452224731445</t>
@@ -902,13 +902,13 @@
     <t xml:space="preserve">8.3054027557373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18309211730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13067531585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19474029541016</t>
+    <t xml:space="preserve">8.18309307098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13067436218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19474124908447</t>
   </si>
   <si>
     <t xml:space="preserve">8.03166103363037</t>
@@ -917,190 +917,190 @@
     <t xml:space="preserve">8.08990383148193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09572792053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15397262573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06660556793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02001190185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1015510559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93847322463989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97924184799194</t>
+    <t xml:space="preserve">8.09572696685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15397071838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06660652160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02001285552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10155200958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93847179412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97924280166626</t>
   </si>
   <si>
     <t xml:space="preserve">7.95594596862793</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90935039520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92100095748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87440633773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89770221710205</t>
+    <t xml:space="preserve">7.90935134887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92099905014038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87440824508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89770412445068</t>
   </si>
   <si>
     <t xml:space="preserve">7.74627208709717</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66473054885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7579197883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78121614456177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67055702209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62396097183228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54824686050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5715446472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55407047271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68220567703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69385385513306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71132707595825</t>
+    <t xml:space="preserve">7.66473245620728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75792169570923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78121852874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6705584526062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62396192550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54824829101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57154512405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55407238006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68220472335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69385480880737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71132612228394</t>
   </si>
   <si>
     <t xml:space="preserve">7.65308427810669</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64725971221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65890884399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5948429107666</t>
+    <t xml:space="preserve">7.64726066589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65890789031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59484004974365</t>
   </si>
   <si>
     <t xml:space="preserve">7.6064887046814</t>
   </si>
   <si>
-    <t xml:space="preserve">7.722975730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69967794418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78704118728638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84528493881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88023090362549</t>
+    <t xml:space="preserve">7.72297430038452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69967985153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78704214096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84528398513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8802318572998</t>
   </si>
   <si>
     <t xml:space="preserve">7.86275720596313</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8918776512146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9035267829895</t>
+    <t xml:space="preserve">7.89187860488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90352773666382</t>
   </si>
   <si>
     <t xml:space="preserve">7.88605499267578</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85693454742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77539253234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81034088134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71714973449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63561296463013</t>
+    <t xml:space="preserve">7.85693311691284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77539348602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81033897399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7171516418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63561105728149</t>
   </si>
   <si>
     <t xml:space="preserve">7.75209665298462</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76374435424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7986912727356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85110855102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83945846557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86858177185059</t>
+    <t xml:space="preserve">7.76374530792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79869031906128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85110950469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83946132659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8685827255249</t>
   </si>
   <si>
     <t xml:space="preserve">7.94429779052734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04331016540527</t>
+    <t xml:space="preserve">8.04331111907959</t>
   </si>
   <si>
     <t xml:space="preserve">8.07329845428467</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11528587341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18126392364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24124336242676</t>
+    <t xml:space="preserve">8.11528491973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1812629699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24124526977539</t>
   </si>
   <si>
     <t xml:space="preserve">8.26523494720459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36120414733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39119434356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35520648956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3671989440918</t>
+    <t xml:space="preserve">8.36120319366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39119243621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35520553588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36720085144043</t>
   </si>
   <si>
     <t xml:space="preserve">8.39719295501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37919616699219</t>
+    <t xml:space="preserve">8.3791971206665</t>
   </si>
   <si>
     <t xml:space="preserve">8.43917655944824</t>
@@ -1109,28 +1109,28 @@
     <t xml:space="preserve">8.33721160888672</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41518592834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30722236633301</t>
+    <t xml:space="preserve">8.41518497467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30722332000732</t>
   </si>
   <si>
     <t xml:space="preserve">8.34920692443848</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31321907043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33121299743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32521533966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25923824310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29522609710693</t>
+    <t xml:space="preserve">8.31321716308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33121204376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32521629333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25923728942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29522514343262</t>
   </si>
   <si>
     <t xml:space="preserve">8.27723217010498</t>
@@ -1139,73 +1139,73 @@
     <t xml:space="preserve">8.30122375488281</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42118453979492</t>
+    <t xml:space="preserve">8.42118358612061</t>
   </si>
   <si>
     <t xml:space="preserve">8.52914714813232</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57712841033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62511539459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69709014892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82904624938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76906776428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70309066772461</t>
+    <t xml:space="preserve">8.5771312713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6251163482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69708919525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82904815673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76906681060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70308780670166</t>
   </si>
   <si>
     <t xml:space="preserve">8.64310836791992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58312797546387</t>
+    <t xml:space="preserve">8.5831298828125</t>
   </si>
   <si>
     <t xml:space="preserve">8.48116207122803</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2352466583252</t>
+    <t xml:space="preserve">8.23524475097656</t>
   </si>
   <si>
     <t xml:space="preserve">8.25324058532715</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31921577453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34320831298828</t>
+    <t xml:space="preserve">8.31921482086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34320735931396</t>
   </si>
   <si>
     <t xml:space="preserve">8.28922748565674</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21125316619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28322887420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40918922424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43317890167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3851957321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37319946289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54713821411133</t>
+    <t xml:space="preserve">8.21125411987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28322792053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40918731689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43317985534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38519477844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37320041656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54714202880859</t>
   </si>
   <si>
     <t xml:space="preserve">8.65510559082031</t>
@@ -1214,13 +1214,13 @@
     <t xml:space="preserve">8.70908641815186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81704902648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94900703430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94300937652588</t>
+    <t xml:space="preserve">8.81705093383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94900608062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94300842285156</t>
   </si>
   <si>
     <t xml:space="preserve">8.91301822662354</t>
@@ -1229,85 +1229,85 @@
     <t xml:space="preserve">8.96700096130371</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89502239227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96100234985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97300052642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95500564575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87103271484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72348213195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68869304656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75107192993164</t>
+    <t xml:space="preserve">8.8950252532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9610013961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97299861907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95500373840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87103176116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72348308563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68869495391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75107097625732</t>
   </si>
   <si>
     <t xml:space="preserve">8.60591983795166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48956108093262</t>
+    <t xml:space="preserve">8.4895601272583</t>
   </si>
   <si>
     <t xml:space="preserve">8.24964046478271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20045757293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03611087799072</t>
+    <t xml:space="preserve">8.20045566558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03611278533936</t>
   </si>
   <si>
     <t xml:space="preserve">8.08649444580078</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00852203369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06010437011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09969139099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17646598815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2220516204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22444915771484</t>
+    <t xml:space="preserve">8.00852108001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06010341644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09968948364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17646408081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22205066680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22445011138916</t>
   </si>
   <si>
     <t xml:space="preserve">8.20525646209717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2712345123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31441879272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22564792633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14047813415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02411651611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99532413482666</t>
+    <t xml:space="preserve">8.27123260498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31441974639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2256498336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14047622680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02411556243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99532604217529</t>
   </si>
   <si>
     <t xml:space="preserve">8.10568809509277</t>
@@ -1316,40 +1316,40 @@
     <t xml:space="preserve">8.14647579193115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15247344970703</t>
+    <t xml:space="preserve">8.1524715423584</t>
   </si>
   <si>
     <t xml:space="preserve">8.22804832458496</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29162788391113</t>
+    <t xml:space="preserve">8.29162979125977</t>
   </si>
   <si>
     <t xml:space="preserve">8.45717144012451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36000347137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47516632080078</t>
+    <t xml:space="preserve">8.36000442504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47516345977783</t>
   </si>
   <si>
     <t xml:space="preserve">8.54114437103271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49915981292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46196842193604</t>
+    <t xml:space="preserve">8.49915790557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46196937561035</t>
   </si>
   <si>
     <t xml:space="preserve">8.43198013305664</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51715183258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49435901641846</t>
+    <t xml:space="preserve">8.51714992523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49435806274414</t>
   </si>
   <si>
     <t xml:space="preserve">8.56993389129639</t>
@@ -1358,37 +1358,37 @@
     <t xml:space="preserve">8.65630531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73068046569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91421890258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92981433868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98979091644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07736396789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13374614715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19492530822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.256103515625</t>
+    <t xml:space="preserve">8.73067951202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91421985626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92981243133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98979377746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07736492156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13374328613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19492244720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25610446929932</t>
   </si>
   <si>
     <t xml:space="preserve">9.265700340271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40485572814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47443199157715</t>
+    <t xml:space="preserve">9.40485382080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47443103790283</t>
   </si>
   <si>
     <t xml:space="preserve">9.5967903137207</t>
@@ -1400,16 +1400,16 @@
     <t xml:space="preserve">9.64957141876221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6135835647583</t>
+    <t xml:space="preserve">9.61358451843262</t>
   </si>
   <si>
     <t xml:space="preserve">9.50682067871094</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69875717163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69155883789062</t>
+    <t xml:space="preserve">9.69875431060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69155693054199</t>
   </si>
   <si>
     <t xml:space="preserve">9.7167501449585</t>
@@ -1421,118 +1421,118 @@
     <t xml:space="preserve">9.67356395721436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80671977996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99505519866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73834323883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0082530975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84150981903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86070346832275</t>
+    <t xml:space="preserve">9.80671787261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99505615234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73834228515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0082521438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84150791168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86070251464844</t>
   </si>
   <si>
     <t xml:space="preserve">10.002254486084</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0550346374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91948127746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9578685760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92787837982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84920406341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8971471786499</t>
+    <t xml:space="preserve">10.0550374984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91947937011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95787143707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92787933349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84920310974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89714622497559</t>
   </si>
   <si>
     <t xml:space="preserve">9.78773784637451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.697998046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45705318450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26528358459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2775764465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52097988128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66972541809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57998561859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49762058258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49639129638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60702896118164</t>
+    <t xml:space="preserve">9.69799900054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45705413818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26528263092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27757453918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52097797393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66972637176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57998657226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4976224899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49639320373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60703086853027</t>
   </si>
   <si>
     <t xml:space="preserve">9.35748100280762</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6303882598877</t>
+    <t xml:space="preserve">9.63038921356201</t>
   </si>
   <si>
     <t xml:space="preserve">9.53450107574463</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72012615203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54679393768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55171203613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48655796051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31937217712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61071872711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3931303024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48532772064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74716949462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77913188934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77667427062988</t>
+    <t xml:space="preserve">9.72012519836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54679298400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55171298980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48655891418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31937313079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6107177734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39313125610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48532962799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74717235565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77913379669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7766752243042</t>
   </si>
   <si>
     <t xml:space="preserve">9.69554042816162</t>
@@ -1541,61 +1541,61 @@
     <t xml:space="preserve">9.93033981323242</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92419147491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96721649169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94508934020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0286808013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1602182388306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98934650421143</t>
+    <t xml:space="preserve">9.92419242858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9672155380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94509124755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0286827087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1602172851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98934459686279</t>
   </si>
   <si>
     <t xml:space="preserve">9.99426174163818</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0065565109253</t>
+    <t xml:space="preserve">10.0065546035767</t>
   </si>
   <si>
     <t xml:space="preserve">9.86764335632324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91927528381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.918044090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88362598419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8873119354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91435527801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98074054718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97459316253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0249938964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95738315582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0102424621582</t>
+    <t xml:space="preserve">9.91927433013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91804504394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88362503051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88731098175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91435813903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98073959350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97459411621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0249929428101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95738410949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0102443695068</t>
   </si>
   <si>
     <t xml:space="preserve">10.1196527481079</t>
@@ -1616,37 +1616,37 @@
     <t xml:space="preserve">10.1417789459229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0717096328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80740928649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80863571166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9045238494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78036403656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7262716293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84182739257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94140148162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0311403274536</t>
+    <t xml:space="preserve">10.0717067718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80740642547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80863475799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90452194213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78036308288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72627258300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84182929992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94140338897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0311412811279</t>
   </si>
   <si>
     <t xml:space="preserve">9.97828006744385</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0803127288818</t>
+    <t xml:space="preserve">10.0803136825562</t>
   </si>
   <si>
     <t xml:space="preserve">10.0999813079834</t>
@@ -1658,16 +1658,16 @@
     <t xml:space="preserve">9.82215881347656</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88608264923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91066837310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80986499786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72750377655029</t>
+    <t xml:space="preserve">9.88608169555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91066932678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80986404418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72750091552734</t>
   </si>
   <si>
     <t xml:space="preserve">9.66603755950928</t>
@@ -1676,13 +1676,13 @@
     <t xml:space="preserve">9.74225521087646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76069450378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84551811218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82707500457764</t>
+    <t xml:space="preserve">9.7606954574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8455171585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82707595825195</t>
   </si>
   <si>
     <t xml:space="preserve">9.82584762573242</t>
@@ -1694,10 +1694,10 @@
     <t xml:space="preserve">10.0422048568726</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1928157806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4401273727417</t>
+    <t xml:space="preserve">10.192813873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4401254653931</t>
   </si>
   <si>
     <t xml:space="preserve">10.4704103469849</t>
@@ -1712,142 +1712,142 @@
     <t xml:space="preserve">10.2962808609009</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3101606369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3316097259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2697820663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2634725570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99723434448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2596864700317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1915512084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91143131256104</t>
+    <t xml:space="preserve">10.3101596832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3316116333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2697839736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2634754180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99723529815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2596893310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1915521621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91143226623535</t>
   </si>
   <si>
     <t xml:space="preserve">9.85465049743652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94424152374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98840236663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83193874359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6477165222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70954418182373</t>
+    <t xml:space="preserve">9.94423961639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98840141296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83193969726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64771556854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70954322814941</t>
   </si>
   <si>
     <t xml:space="preserve">9.57326984405518</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4319486618042</t>
+    <t xml:space="preserve">9.43194770812988</t>
   </si>
   <si>
     <t xml:space="preserve">9.2881031036377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4470911026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54803466796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69187927246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7070198059082</t>
+    <t xml:space="preserve">9.44709014892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54803371429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69188022613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70702075958252</t>
   </si>
   <si>
     <t xml:space="preserve">9.90890884399414</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73225688934326</t>
+    <t xml:space="preserve">9.73225593566895</t>
   </si>
   <si>
     <t xml:space="preserve">9.69061660766602</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74865913391113</t>
+    <t xml:space="preserve">9.74866104125977</t>
   </si>
   <si>
     <t xml:space="preserve">9.67673778533936</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86348247528076</t>
+    <t xml:space="preserve">9.86348342895508</t>
   </si>
   <si>
     <t xml:space="preserve">9.8256311416626</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75118350982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77137184143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55686569213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41680717468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44835090637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40040588378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28684043884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11775970458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22879981994629</t>
+    <t xml:space="preserve">9.75118446350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7713737487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55686664581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41680526733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44835186004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40040493011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28684329986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11776161193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22879886627197</t>
   </si>
   <si>
     <t xml:space="preserve">9.03195858001709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87044715881348</t>
+    <t xml:space="preserve">8.87044906616211</t>
   </si>
   <si>
     <t xml:space="preserve">9.01934051513672</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95498752593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92975425720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96886920928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98779678344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15561771392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09378433227539</t>
+    <t xml:space="preserve">8.95498943328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92975330352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96886825561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98779487609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15561580657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09378528594971</t>
   </si>
   <si>
     <t xml:space="preserve">9.01555633544922</t>
@@ -1862,7 +1862,7 @@
     <t xml:space="preserve">8.79474258422852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87423610687256</t>
+    <t xml:space="preserve">8.87423324584961</t>
   </si>
   <si>
     <t xml:space="preserve">8.98148727416992</t>
@@ -1877,232 +1877,232 @@
     <t xml:space="preserve">8.80735778808594</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71524620056152</t>
+    <t xml:space="preserve">8.71524715423584</t>
   </si>
   <si>
     <t xml:space="preserve">8.80104732513428</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72281837463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69001007080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52976131439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67360687255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69379615783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73165035247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04709911346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96760654449463</t>
+    <t xml:space="preserve">8.72281742095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6900110244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52976322174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67360782623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69379711151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73165130615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04710102081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96760749816895</t>
   </si>
   <si>
     <t xml:space="preserve">8.91208744049072</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99410438537598</t>
+    <t xml:space="preserve">8.99410343170166</t>
   </si>
   <si>
     <t xml:space="preserve">8.98527240753174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93984889984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90830039978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99031734466553</t>
+    <t xml:space="preserve">8.93984699249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90830326080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99031925201416</t>
   </si>
   <si>
     <t xml:space="preserve">9.00924587249756</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97012996673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21617889404297</t>
+    <t xml:space="preserve">8.97012901306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21618175506592</t>
   </si>
   <si>
     <t xml:space="preserve">9.17706394195557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13290309906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09504795074463</t>
+    <t xml:space="preserve">9.13290119171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09504699707031</t>
   </si>
   <si>
     <t xml:space="preserve">9.1934700012207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10514354705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1619234085083</t>
+    <t xml:space="preserve">9.10514163970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16192245483398</t>
   </si>
   <si>
     <t xml:space="preserve">9.23889255523682</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34109973907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31964778900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3284797668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42564010620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37516689300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16949367523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1581392288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24267673492432</t>
+    <t xml:space="preserve">9.34110069274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31964874267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32848262786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42563819885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37516593933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16949272155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15813732147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24267959594727</t>
   </si>
   <si>
     <t xml:space="preserve">9.30955505371094</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37264633178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32469654083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53919982910156</t>
+    <t xml:space="preserve">9.37264442443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3246955871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5392017364502</t>
   </si>
   <si>
     <t xml:space="preserve">9.5745325088501</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58841228485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62248134613037</t>
+    <t xml:space="preserve">9.58841323852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62247943878174</t>
   </si>
   <si>
     <t xml:space="preserve">9.63383674621582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64519309997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59724521636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59598350524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60355472564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56822204589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48746681213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53289222717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57957935333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64014530181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44330406188965</t>
+    <t xml:space="preserve">9.64519214630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59724426269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59598541259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60355377197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56822490692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48746871948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53289318084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57958030700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64014720916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44330596923828</t>
   </si>
   <si>
     <t xml:space="preserve">9.54046440124512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56696319580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80670166015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80291748046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83446216583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93288326263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0249948501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9530725479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98714065551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90512371063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85717678070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85212707519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83572387695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76632499694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93919277191162</t>
+    <t xml:space="preserve">9.56696128845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80670261383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80291652679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83446407318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93288230895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.024995803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95307159423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98713970184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90512275695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85717487335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85212802886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83572578430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76632595062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93919086456299</t>
   </si>
   <si>
     <t xml:space="preserve">9.96190547943115</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0338277816772</t>
+    <t xml:space="preserve">10.0338268280029</t>
   </si>
   <si>
     <t xml:space="preserve">9.94045352935791</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99849796295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97704601287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0237321853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0565395355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.046443939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97830772399902</t>
+    <t xml:space="preserve">9.99849510192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9770450592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0237331390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0565385818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0464448928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97830963134766</t>
   </si>
   <si>
     <t xml:space="preserve">9.88619613647461</t>
@@ -2114,16 +2114,16 @@
     <t xml:space="preserve">9.73604202270508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96695232391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81048774719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78272819519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67926120758057</t>
+    <t xml:space="preserve">9.96695137023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8104887008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78272914886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6792631149292</t>
   </si>
   <si>
     <t xml:space="preserve">9.5253210067749</t>
@@ -2132,19 +2132,19 @@
     <t xml:space="preserve">9.60103130340576</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48494529724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51901531219482</t>
+    <t xml:space="preserve">9.48494434356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51901149749756</t>
   </si>
   <si>
     <t xml:space="preserve">9.38273811340332</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14173412322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13542461395264</t>
+    <t xml:space="preserve">9.1417350769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13542652130127</t>
   </si>
   <si>
     <t xml:space="preserve">9.03700542449951</t>
@@ -2153,142 +2153,142 @@
     <t xml:space="preserve">9.00041484832764</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09883308410645</t>
+    <t xml:space="preserve">9.09883403778076</t>
   </si>
   <si>
     <t xml:space="preserve">9.21365833282471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15939998626709</t>
+    <t xml:space="preserve">9.15940093994141</t>
   </si>
   <si>
     <t xml:space="preserve">9.30576801300049</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36255073547363</t>
+    <t xml:space="preserve">9.36255168914795</t>
   </si>
   <si>
     <t xml:space="preserve">9.35346698760986</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43392181396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35476303100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03164863586426</t>
+    <t xml:space="preserve">9.43391990661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35476398468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03164958953857</t>
   </si>
   <si>
     <t xml:space="preserve">9.11859130859375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12897205352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10042285919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91096973419189</t>
+    <t xml:space="preserve">9.1289701461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10042381286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91096782684326</t>
   </si>
   <si>
     <t xml:space="preserve">8.88371753692627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81104946136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96676731109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09523391723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99790954589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01867389678955</t>
+    <t xml:space="preserve">8.81104755401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96676635742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09523582458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99791145324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01867198944092</t>
   </si>
   <si>
     <t xml:space="preserve">9.0576000213623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08355712890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11339950561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02126789093018</t>
+    <t xml:space="preserve">9.08355522155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11340045928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02126598358154</t>
   </si>
   <si>
     <t xml:space="preserve">9.04722118377686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99920654296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18476963043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22759437561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31583690643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47674179077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4222412109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36903953552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41315841674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38590526580811</t>
+    <t xml:space="preserve">8.99920463562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18477153778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22759532928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31583404541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4767427444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42223930358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36903858184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41315746307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38590812683105</t>
   </si>
   <si>
     <t xml:space="preserve">9.49880409240723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4066686630249</t>
+    <t xml:space="preserve">9.40666961669922</t>
   </si>
   <si>
     <t xml:space="preserve">9.45208740234375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50269603729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44040966033936</t>
+    <t xml:space="preserve">9.5026969909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44040870666504</t>
   </si>
   <si>
     <t xml:space="preserve">9.50788688659668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54162693023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60261535644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61948585510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54551792144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51567459106445</t>
+    <t xml:space="preserve">9.5416259765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60261631011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61948490142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54551887512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5156717300415</t>
   </si>
   <si>
     <t xml:space="preserve">9.35216808319092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27820301055908</t>
+    <t xml:space="preserve">9.27820205688477</t>
   </si>
   <si>
     <t xml:space="preserve">9.22629642486572</t>
@@ -2297,40 +2297,40 @@
     <t xml:space="preserve">9.28858375549316</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33659553527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31064224243164</t>
+    <t xml:space="preserve">9.33659744262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31064319610596</t>
   </si>
   <si>
     <t xml:space="preserve">9.30285739898682</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24446392059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14454364776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21591472625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14584255218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87593078613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74616527557373</t>
+    <t xml:space="preserve">9.24446582794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14454460144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21591567993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14584064483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87593173980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74616718292236</t>
   </si>
   <si>
     <t xml:space="preserve">8.68387699127197</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56060123443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7163200378418</t>
+    <t xml:space="preserve">8.56060218811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71631717681885</t>
   </si>
   <si>
     <t xml:space="preserve">8.55930328369141</t>
@@ -2339,31 +2339,31 @@
     <t xml:space="preserve">8.54502964019775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70723628997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50090980529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4606819152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61250877380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52816104888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66181945800781</t>
+    <t xml:space="preserve">8.70723724365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50091171264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46068286895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61250782012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52816009521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66181755065918</t>
   </si>
   <si>
     <t xml:space="preserve">8.63716411590576</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52686405181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57617282867432</t>
+    <t xml:space="preserve">8.52686214447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57617378234863</t>
   </si>
   <si>
     <t xml:space="preserve">8.63067531585693</t>
@@ -2372,19 +2372,19 @@
     <t xml:space="preserve">8.694260597229</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8357048034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89669418334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82532119750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86944389343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93432521820068</t>
+    <t xml:space="preserve">8.83570384979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89669227600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82532215118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86944198608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93432426452637</t>
   </si>
   <si>
     <t xml:space="preserve">9.03294563293457</t>
@@ -2393,25 +2393,25 @@
     <t xml:space="preserve">9.14973545074463</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13156604766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11210155487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28728580474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18217754364014</t>
+    <t xml:space="preserve">9.13156795501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11210250854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28728485107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18217468261719</t>
   </si>
   <si>
     <t xml:space="preserve">9.29377460479736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4417085647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45373916625977</t>
+    <t xml:space="preserve">9.44170761108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45374011993408</t>
   </si>
   <si>
     <t xml:space="preserve">9.35746479034424</t>
@@ -2420,43 +2420,43 @@
     <t xml:space="preserve">9.2678747177124</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31601333618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39624404907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38287258148193</t>
+    <t xml:space="preserve">9.31601238250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39624118804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3828706741333</t>
   </si>
   <si>
     <t xml:space="preserve">9.34676742553711</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06328678131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96433734893799</t>
+    <t xml:space="preserve">9.06328773498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9643383026123</t>
   </si>
   <si>
     <t xml:space="preserve">9.05526638031006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12747192382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04858016967773</t>
+    <t xml:space="preserve">9.12747383117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04858112335205</t>
   </si>
   <si>
     <t xml:space="preserve">9.09270763397217</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14752864837646</t>
+    <t xml:space="preserve">9.1475305557251</t>
   </si>
   <si>
     <t xml:space="preserve">9.25049114227295</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18898391723633</t>
+    <t xml:space="preserve">9.1889820098877</t>
   </si>
   <si>
     <t xml:space="preserve">9.25182914733887</t>
@@ -2465,103 +2465,103 @@
     <t xml:space="preserve">9.23711967468262</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21305274963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32938575744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40827655792236</t>
+    <t xml:space="preserve">9.21305179595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32938766479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40827751159668</t>
   </si>
   <si>
     <t xml:space="preserve">9.45240306854248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38688087463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31868934631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24514484405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15822601318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07265090942383</t>
+    <t xml:space="preserve">9.38688278198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31868648529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24514293670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15822792053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07264804840088</t>
   </si>
   <si>
     <t xml:space="preserve">9.16223907470703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34275722503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49251747131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46978569030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47780990600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48716926574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45106601715088</t>
+    <t xml:space="preserve">9.34275436401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49251651763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46978759765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47780895233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48716831207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45106506347656</t>
   </si>
   <si>
     <t xml:space="preserve">9.52995777130127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48181915283203</t>
+    <t xml:space="preserve">9.48182010650635</t>
   </si>
   <si>
     <t xml:space="preserve">9.50722694396973</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43368339538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34008121490479</t>
+    <t xml:space="preserve">9.43368244171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3400821685791</t>
   </si>
   <si>
     <t xml:space="preserve">9.36816310882568</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38821983337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39223003387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31467628479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28659725189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22642517089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16892433166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0739860534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01247692108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12212467193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20636463165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11008930206299</t>
+    <t xml:space="preserve">9.38821792602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39223194122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31467723846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28659534454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2264232635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16892337799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07398700714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01247787475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12212562561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20636367797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11009120941162</t>
   </si>
   <si>
     <t xml:space="preserve">9.13683223724365</t>
@@ -2573,7 +2573,7 @@
     <t xml:space="preserve">9.12613487243652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09537887573242</t>
+    <t xml:space="preserve">9.09538173675537</t>
   </si>
   <si>
     <t xml:space="preserve">9.10875225067139</t>
@@ -2582,67 +2582,67 @@
     <t xml:space="preserve">9.16090202331543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23845672607422</t>
+    <t xml:space="preserve">9.23845767974854</t>
   </si>
   <si>
     <t xml:space="preserve">9.25717735290527</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37083625793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36013984680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36548805236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43100833892822</t>
+    <t xml:space="preserve">9.37083721160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36013793945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36548709869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43100929260254</t>
   </si>
   <si>
     <t xml:space="preserve">9.57141017913818</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57408332824707</t>
+    <t xml:space="preserve">9.57408428192139</t>
   </si>
   <si>
     <t xml:space="preserve">9.49786758422852</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42699813842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27589702606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22508525848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28525829315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30398082733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28124713897705</t>
+    <t xml:space="preserve">9.4269962310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27589893341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2250862121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28525924682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30397891998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28124618530273</t>
   </si>
   <si>
     <t xml:space="preserve">9.06462574005127</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99776840209961</t>
+    <t xml:space="preserve">8.99777030944824</t>
   </si>
   <si>
     <t xml:space="preserve">9.00579166412354</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82259941101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9576530456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.884108543396</t>
+    <t xml:space="preserve">8.82260036468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95765399932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88410949707031</t>
   </si>
   <si>
     <t xml:space="preserve">8.64208316802979</t>
@@ -2651,34 +2651,34 @@
     <t xml:space="preserve">8.46290302276611</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43081188201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54981803894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71027851104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67150115966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62871170043945</t>
+    <t xml:space="preserve">8.43081092834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54981994628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71027946472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67150020599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62871074676514</t>
   </si>
   <si>
     <t xml:space="preserve">8.54446887969971</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75841426849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68353366851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61935043334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63138580322266</t>
+    <t xml:space="preserve">8.75841617584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68353462219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61934947967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63138484954834</t>
   </si>
   <si>
     <t xml:space="preserve">8.65010547637939</t>
@@ -2687,37 +2687,37 @@
     <t xml:space="preserve">8.62469863891602</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53377151489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13529968261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00692939758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06576728820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86117792129517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46003007888794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43328666687012</t>
+    <t xml:space="preserve">8.53377246856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13529777526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00693035125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06576442718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86118078231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46003103256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43328714370728</t>
   </si>
   <si>
     <t xml:space="preserve">7.43462467193604</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45601844787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33300113677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84226322174072</t>
+    <t xml:space="preserve">7.45601987838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33299970626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84226226806641</t>
   </si>
   <si>
     <t xml:space="preserve">5.41550874710083</t>
@@ -2726,28 +2726,28 @@
     <t xml:space="preserve">5.4589672088623</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38207960128784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40728902816772</t>
+    <t xml:space="preserve">5.38208103179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40728712081909</t>
   </si>
   <si>
     <t xml:space="preserve">4.62056589126587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34043025970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59048080444336</t>
+    <t xml:space="preserve">4.34042978286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59047985076904</t>
   </si>
   <si>
     <t xml:space="preserve">4.47548341751099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65666913986206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87596321105957</t>
+    <t xml:space="preserve">4.65667009353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87596368789673</t>
   </si>
   <si>
     <t xml:space="preserve">4.87195301055908</t>
@@ -2756,16 +2756,16 @@
     <t xml:space="preserve">5.59936857223511</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83203458786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8240122795105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49373245239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74512100219727</t>
+    <t xml:space="preserve">5.83203554153442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82401275634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49373340606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74511957168579</t>
   </si>
   <si>
     <t xml:space="preserve">6.16431999206543</t>
@@ -2774,16 +2774,16 @@
     <t xml:space="preserve">6.1509485244751</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57750415802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23452043533325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22783613204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30338525772095</t>
+    <t xml:space="preserve">6.5775032043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23452091217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22783327102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30338621139526</t>
   </si>
   <si>
     <t xml:space="preserve">6.21446418762207</t>
@@ -2792,40 +2792,40 @@
     <t xml:space="preserve">6.22315549850464</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1288857460022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73776531219482</t>
+    <t xml:space="preserve">6.12888526916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73776578903198</t>
   </si>
   <si>
     <t xml:space="preserve">5.65218734741211</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7411093711853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6388144493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32190704345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58131790161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66422176361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51579618453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61875820159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80596017837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98848295211792</t>
+    <t xml:space="preserve">5.74110889434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63881540298462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32190752029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58131694793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.664222240448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51579570770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61875772476196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80595970153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98848390579224</t>
   </si>
   <si>
     <t xml:space="preserve">5.82601833343506</t>
@@ -2834,25 +2834,25 @@
     <t xml:space="preserve">5.48972225189209</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8079662322998</t>
+    <t xml:space="preserve">5.80796718597412</t>
   </si>
   <si>
     <t xml:space="preserve">5.63146114349365</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72038173675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77052640914917</t>
+    <t xml:space="preserve">5.72038125991821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77052545547485</t>
   </si>
   <si>
     <t xml:space="preserve">5.69965600967407</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69230175018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69631385803223</t>
+    <t xml:space="preserve">5.69230222702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69631338119507</t>
   </si>
   <si>
     <t xml:space="preserve">6.09554767608643</t>
@@ -2861,151 +2861,151 @@
     <t xml:space="preserve">5.90332365036011</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93500995635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78925752639771</t>
+    <t xml:space="preserve">5.93500852584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78925704956055</t>
   </si>
   <si>
     <t xml:space="preserve">5.75545930862427</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8160138130188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82587099075317</t>
+    <t xml:space="preserve">5.81601333618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82587051391602</t>
   </si>
   <si>
     <t xml:space="preserve">5.94979524612427</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97936820983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71955013275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87234210968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17581605911255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33635568618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31171274185181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69334411621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80459356307983</t>
+    <t xml:space="preserve">5.97936868667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71954917907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87234258651733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17581701278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33635520935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31171226501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69334268569946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80459403991699</t>
   </si>
   <si>
     <t xml:space="preserve">6.60180902481079</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49900674819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0420355796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04626083374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04133081436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29129219055176</t>
+    <t xml:space="preserve">6.49900770187378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04203653335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04626035690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04133129119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29129266738892</t>
   </si>
   <si>
     <t xml:space="preserve">6.26383209228516</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22088146209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24834299087524</t>
+    <t xml:space="preserve">6.22088050842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24834156036377</t>
   </si>
   <si>
     <t xml:space="preserve">6.19834899902344</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96528673171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97162246704102</t>
+    <t xml:space="preserve">5.96528720855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97162294387817</t>
   </si>
   <si>
     <t xml:space="preserve">5.91247701644897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07301664352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97796010971069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96739816665649</t>
+    <t xml:space="preserve">6.07301616668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97796058654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96739864349365</t>
   </si>
   <si>
     <t xml:space="preserve">6.13990831375122</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10751867294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.166663646698</t>
+    <t xml:space="preserve">6.10751819610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16666412353516</t>
   </si>
   <si>
     <t xml:space="preserve">6.21031856536865</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12441682815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9385290145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09766101837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18426656723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22158479690552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26312685012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20538997650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18285846710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28706789016724</t>
+    <t xml:space="preserve">6.12441730499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93852996826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09766006469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18426609039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22158432006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26313018798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20539045333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18285894393921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28706741333008</t>
   </si>
   <si>
     <t xml:space="preserve">6.13075399398804</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05611705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99908447265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95894956588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96880769729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92163133621216</t>
+    <t xml:space="preserve">6.05611610412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99908399581909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95894813537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96880722045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92163038253784</t>
   </si>
   <si>
     <t xml:space="preserve">5.5047926902771</t>
@@ -3017,25 +3017,25 @@
     <t xml:space="preserve">5.30482387542725</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53366231918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70053815841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59210443496704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49634313583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62308502197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80474758148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89557838439941</t>
+    <t xml:space="preserve">5.53366184234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70053720474243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59210395812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49634408950806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62308597564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80474662780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89557933807373</t>
   </si>
   <si>
     <t xml:space="preserve">5.80545091629028</t>
@@ -3047,13 +3047,13 @@
     <t xml:space="preserve">5.70335388183594</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67096567153931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.723069190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58717489242554</t>
+    <t xml:space="preserve">5.67096424102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72307014465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58717393875122</t>
   </si>
   <si>
     <t xml:space="preserve">5.54351949691772</t>
@@ -3062,85 +3062,85 @@
     <t xml:space="preserve">5.76742887496948</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68786478042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6061863899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49211931228638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4752197265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40480756759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41889142990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.382981300354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4731068611145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29426145553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37100982666016</t>
+    <t xml:space="preserve">5.68786334991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60618543624878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49211883544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47522068023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40480947494507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41889047622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38298034667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47310733795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29426240921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37101078033447</t>
   </si>
   <si>
     <t xml:space="preserve">5.3696026802063</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35059118270874</t>
+    <t xml:space="preserve">5.3505916595459</t>
   </si>
   <si>
     <t xml:space="preserve">5.26398420333862</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35974502563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38720464706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34707021713257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20202159881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97441577911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05028486251831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95866918563843</t>
+    <t xml:space="preserve">5.35974359512329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38720512390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34707069396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20202302932739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97441625595093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05028533935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95867013931274</t>
   </si>
   <si>
     <t xml:space="preserve">4.87564373016357</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78760766983032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90999937057495</t>
+    <t xml:space="preserve">4.78760623931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90999984741211</t>
   </si>
   <si>
     <t xml:space="preserve">4.77042961120605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78689098358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62513303756714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65018558502197</t>
+    <t xml:space="preserve">4.78689193725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62513256072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65018510818481</t>
   </si>
   <si>
     <t xml:space="preserve">4.78832292556763</t>
@@ -3149,22 +3149,22 @@
     <t xml:space="preserve">4.9515118598938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8169527053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92789220809937</t>
+    <t xml:space="preserve">4.81695222854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92789268493652</t>
   </si>
   <si>
     <t xml:space="preserve">4.91143083572388</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88065385818481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78545951843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79404878616333</t>
+    <t xml:space="preserve">4.8806529045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78545999526978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79404926300049</t>
   </si>
   <si>
     <t xml:space="preserve">4.59364080429077</t>
@@ -3173,28 +3173,28 @@
     <t xml:space="preserve">4.69742393493652</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71388578414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69670724868774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53781318664551</t>
+    <t xml:space="preserve">4.71388530731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69670677185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53781270980835</t>
   </si>
   <si>
     <t xml:space="preserve">4.53852844238281</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61224985122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4698166847229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36603450775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21214962005615</t>
+    <t xml:space="preserve">4.61224937438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46981620788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36603355407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21215009689331</t>
   </si>
   <si>
     <t xml:space="preserve">4.23576974868774</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">4.30233335494995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55355978012085</t>
+    <t xml:space="preserve">4.55355882644653</t>
   </si>
   <si>
     <t xml:space="preserve">4.66235208511353</t>
@@ -3218,25 +3218,25 @@
     <t xml:space="preserve">4.68239259719849</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28075313568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49547719955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43392372131348</t>
+    <t xml:space="preserve">5.28075456619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4954776763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43392324447632</t>
   </si>
   <si>
     <t xml:space="preserve">5.45253229141235</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48259353637695</t>
+    <t xml:space="preserve">5.48259305953979</t>
   </si>
   <si>
     <t xml:space="preserve">5.70304203033447</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78750038146973</t>
+    <t xml:space="preserve">5.78749990463257</t>
   </si>
   <si>
     <t xml:space="preserve">5.86480140686035</t>
@@ -3245,49 +3245,49 @@
     <t xml:space="preserve">5.78105878829956</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81541538238525</t>
+    <t xml:space="preserve">5.81541442871094</t>
   </si>
   <si>
     <t xml:space="preserve">5.96214151382446</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16970729827881</t>
+    <t xml:space="preserve">6.16970682144165</t>
   </si>
   <si>
     <t xml:space="preserve">6.20692682266235</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12533092498779</t>
+    <t xml:space="preserve">6.12533044815063</t>
   </si>
   <si>
     <t xml:space="preserve">6.14250898361206</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94281721115112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02297973632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08310270309448</t>
+    <t xml:space="preserve">5.94281673431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02298021316528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08310174942017</t>
   </si>
   <si>
     <t xml:space="preserve">6.04946231842041</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25845956802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2749228477478</t>
+    <t xml:space="preserve">6.25846004486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27492237091064</t>
   </si>
   <si>
     <t xml:space="preserve">6.29138326644897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32931804656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39588260650635</t>
+    <t xml:space="preserve">6.32931756973267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39588117599487</t>
   </si>
   <si>
     <t xml:space="preserve">6.30426692962646</t>
@@ -3296,157 +3296,157 @@
     <t xml:space="preserve">6.21122026443481</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26418542861938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26704883575439</t>
+    <t xml:space="preserve">6.26418447494507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26704788208008</t>
   </si>
   <si>
     <t xml:space="preserve">6.23483991622925</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17042255401611</t>
+    <t xml:space="preserve">6.17042398452759</t>
   </si>
   <si>
     <t xml:space="preserve">5.9005880355835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98361396789551</t>
+    <t xml:space="preserve">5.98361444473267</t>
   </si>
   <si>
     <t xml:space="preserve">6.14394044876099</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15252876281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12819528579712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11817455291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04660081863403</t>
+    <t xml:space="preserve">6.15252923965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12819337844849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11817407608032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0465989112854</t>
   </si>
   <si>
     <t xml:space="preserve">6.27062702178955</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47604608535767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49036026000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46316194534302</t>
+    <t xml:space="preserve">6.47604560852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49036073684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46316242218018</t>
   </si>
   <si>
     <t xml:space="preserve">6.42594337463379</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48034000396729</t>
+    <t xml:space="preserve">6.48034048080444</t>
   </si>
   <si>
     <t xml:space="preserve">6.48463487625122</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44526958465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32072973251343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33862257003784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31786680221558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37083196640015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20406246185303</t>
+    <t xml:space="preserve">6.44526767730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32072830200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33862352371216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3178653717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37083148956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20406436920166</t>
   </si>
   <si>
     <t xml:space="preserve">6.11387920379639</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97860479354858</t>
+    <t xml:space="preserve">5.97860383987427</t>
   </si>
   <si>
     <t xml:space="preserve">6.10385847091675</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11745738983154</t>
+    <t xml:space="preserve">6.11745834350586</t>
   </si>
   <si>
     <t xml:space="preserve">5.97788763046265</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86909532546997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94854307174683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07594537734985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13392114639282</t>
+    <t xml:space="preserve">5.86909627914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94854211807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07594585418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13392019271851</t>
   </si>
   <si>
     <t xml:space="preserve">6.1632661819458</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21336650848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28064775466919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33003425598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28207921981812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35508441925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5297269821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49823331832886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55835676193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51111745834351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58340692520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6964955329895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74516487121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8546724319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92839765548706</t>
+    <t xml:space="preserve">6.21336698532104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28064727783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33003377914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28208017349243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35508489608765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52972745895386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49823474884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55835819244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51111793518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58340740203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69649505615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74516534805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85467338562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9283971786499</t>
   </si>
   <si>
     <t xml:space="preserve">6.78667831420898</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84322118759155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79383611679077</t>
+    <t xml:space="preserve">6.84322071075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79383563995361</t>
   </si>
   <si>
     <t xml:space="preserve">6.9140796661377</t>
@@ -3455,10 +3455,10 @@
     <t xml:space="preserve">7.06868076324463</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20180797576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28626871109009</t>
+    <t xml:space="preserve">7.20181083679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2862663269043</t>
   </si>
   <si>
     <t xml:space="preserve">7.25763845443726</t>
@@ -3467,52 +3467,52 @@
     <t xml:space="preserve">7.31489658355713</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37215662002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45661544799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3964900970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32920980453491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39935350418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28197240829468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26193046569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14311790466309</t>
+    <t xml:space="preserve">7.37215709686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45661449432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39649152755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32921171188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39935636520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28197193145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2619309425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14311838150024</t>
   </si>
   <si>
     <t xml:space="preserve">7.33350563049316</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23759698867798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32348823547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40651321411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45232057571411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51101160049438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56540775299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49669694900513</t>
+    <t xml:space="preserve">7.23759794235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32348585128784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40651226043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45232009887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51101112365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56540632247925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49669647216797</t>
   </si>
   <si>
     <t xml:space="preserve">7.48381233215332</t>
@@ -3521,133 +3521,133 @@
     <t xml:space="preserve">7.34352588653564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30058097839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27338361740112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31919097900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50671625137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4179630279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40794324874878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38933563232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21039915084839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26479530334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27767944335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23043966293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26336288452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23616313934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3034462928772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3020133972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10733222961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22900915145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37788152694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39076614379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38647174835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44945764541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48524522781372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37501955032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46520328521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48953914642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46806716918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29771947860718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3607029914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40907144546509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31746625900269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35044574737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40174388885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39734649658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36949777603149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54391670227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59961175918579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6509108543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60693979263306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66117238998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69194984436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65384292602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7051420211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75497627258301</t>
+    <t xml:space="preserve">7.30058145523071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27338314056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31919145584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50671577453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41796445846558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40794229507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38933324813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21039867401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26479434967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27767753601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23044061660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2633638381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23616409301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30344724655151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30201196670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1073317527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22900819778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37788200378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39076519012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38646984100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44945430755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4852442741394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37501859664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46520233154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48953819274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46806621551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2977180480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36070394515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40907287597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31746673583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35044479370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4017448425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39734697341919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36949729919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54391527175903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59961128234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65091228485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60694026947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66117286682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69195175170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65384244918823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70514345169067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75497436523438</t>
   </si>
   <si>
     <t xml:space="preserve">7.86196899414062</t>
@@ -3656,109 +3656,109 @@
     <t xml:space="preserve">7.86636781692505</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87222862243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79015207290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5585732460022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63478851318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63185787200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63771915435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.724196434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73592185974121</t>
+    <t xml:space="preserve">7.87223100662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79015064239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55857229232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63478994369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63185596466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63771963119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72419500350952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73592233657837</t>
   </si>
   <si>
     <t xml:space="preserve">7.57909345626831</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57616090774536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52632617950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66556739807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62013053894043</t>
+    <t xml:space="preserve">7.57616186141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52632761001587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66556882858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6201319694519</t>
   </si>
   <si>
     <t xml:space="preserve">7.66263628005981</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45304346084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.301344871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38708829879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33139085769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34604787826538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26250219345093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20534086227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92832517623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96423625946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14524745941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06756687164307</t>
+    <t xml:space="preserve">7.45304298400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30134534835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38708639144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3313889503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34604644775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26250505447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20534181594849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92832469940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96423578262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14524841308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06756544113159</t>
   </si>
   <si>
     <t xml:space="preserve">7.08588790893555</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23025894165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18775272369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26763343811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33871936798096</t>
+    <t xml:space="preserve">7.23025703430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18775177001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26763200759888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3387188911438</t>
   </si>
   <si>
     <t xml:space="preserve">7.3079400062561</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42812728881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4164023399353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4750280380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54977703094482</t>
+    <t xml:space="preserve">7.42812776565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41640043258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47502946853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54977893829346</t>
   </si>
   <si>
     <t xml:space="preserve">7.53658723831177</t>
@@ -3767,133 +3767,133 @@
     <t xml:space="preserve">7.58495473861694</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63332414627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67876005172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70807361602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60107755661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6040096282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59668016433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38415431976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37389421463013</t>
+    <t xml:space="preserve">7.63332319259644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67875909805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70807313919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60107898712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60401058197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59668207168579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3841552734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37389755249023</t>
   </si>
   <si>
     <t xml:space="preserve">7.49994659423828</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56150436401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57029867172241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55270957946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64211654663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64504957199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79161691665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71686887741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75790739059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76083898544312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72712850570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91913223266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99095249176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05397796630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07889270782471</t>
+    <t xml:space="preserve">7.56150484085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57030010223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55270862579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64211702346802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64504766464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79161787033081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71686792373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75790691375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76083755493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.727126121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91913318634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9909520149231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05397701263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07889366149902</t>
   </si>
   <si>
     <t xml:space="preserve">8.01880073547363</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94404411315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09050559997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3040943145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31630229949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33918857574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53294372558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59244441986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68703460693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80756092071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75873947143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8807897567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03793239593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89909839630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83960056304932</t>
+    <t xml:space="preserve">7.94404363632202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09050750732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30409526824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31630039215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33918571472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53294277191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59244537353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68703556060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8075590133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75873851776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88079071044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03793048858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89909934997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83959770202637</t>
   </si>
   <si>
     <t xml:space="preserve">9.04556179046631</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15845680236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13404846191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01809978485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13862609863281</t>
+    <t xml:space="preserve">9.15845775604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13404941558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01809883117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13862323760986</t>
   </si>
   <si>
     <t xml:space="preserve">9.31254863739014</t>
@@ -3902,121 +3902,121 @@
     <t xml:space="preserve">9.333909034729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2850866317749</t>
+    <t xml:space="preserve">9.28508567810059</t>
   </si>
   <si>
     <t xml:space="preserve">9.39645862579346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25609970092773</t>
+    <t xml:space="preserve">9.25609874725342</t>
   </si>
   <si>
     <t xml:space="preserve">9.21338081359863</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36594772338867</t>
+    <t xml:space="preserve">9.36594486236572</t>
   </si>
   <si>
     <t xml:space="preserve">9.42697238922119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35831737518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27898502349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46206188201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72294902801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56580543518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44375610351562</t>
+    <t xml:space="preserve">9.35831832885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2789831161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46206283569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72294616699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56580448150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44375419616699</t>
   </si>
   <si>
     <t xml:space="preserve">9.58106231689453</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66649913787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67412662506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6268310546875</t>
+    <t xml:space="preserve">9.6664981842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67412853240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62683200836182</t>
   </si>
   <si>
     <t xml:space="preserve">9.66039562225342</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64666366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54444789886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57038307189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61005020141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60547351837158</t>
+    <t xml:space="preserve">9.64666557312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54444694519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57038021087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61004829406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60547256469727</t>
   </si>
   <si>
     <t xml:space="preserve">9.48189449310303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28203678131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40408897399902</t>
+    <t xml:space="preserve">9.2820348739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40408611297607</t>
   </si>
   <si>
     <t xml:space="preserve">9.43612480163574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37967681884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79535484313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00131607055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08065128326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10811138153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16151142120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37662506103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58716583251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45138263702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35679244995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31102180480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1691370010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26678085327148</t>
+    <t xml:space="preserve">9.37967777252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79535579681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00131702423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08065032958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10811042785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16150951385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37662696838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58716678619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45138359069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35679149627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3110237121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16913795471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26677799224854</t>
   </si>
   <si>
     <t xml:space="preserve">9.15388202667236</t>
@@ -4025,109 +4025,109 @@
     <t xml:space="preserve">9.3049201965332</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19354915618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02725315093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2911901473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28661251068115</t>
+    <t xml:space="preserve">9.19354629516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02725219726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29118824005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28661155700684</t>
   </si>
   <si>
     <t xml:space="preserve">9.33695888519287</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37814998626709</t>
+    <t xml:space="preserve">9.37815189361572</t>
   </si>
   <si>
     <t xml:space="preserve">9.36747169494629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.321702003479</t>
+    <t xml:space="preserve">9.32170295715332</t>
   </si>
   <si>
     <t xml:space="preserve">9.46511268615723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61920356750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73057460784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6497163772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75651168823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67565059661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77176952362061</t>
+    <t xml:space="preserve">9.61920166015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73057556152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64971733093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75651359558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67565155029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77176856994629</t>
   </si>
   <si>
     <t xml:space="preserve">9.95637226104736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93501281738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0387563705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.078423500061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1226682662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2370920181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1379241943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99756336212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67717838287354</t>
+    <t xml:space="preserve">9.9350118637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0387554168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0784244537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1226663589478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2370901107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1379222869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99756240844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67717933654785</t>
   </si>
   <si>
     <t xml:space="preserve">9.98840999603271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2859125137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5361175537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3545665740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1516523361206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2645540237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.188271522522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1363973617554</t>
+    <t xml:space="preserve">10.2859115600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5361185073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.354564666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1516542434692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.264552116394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1882705688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1363983154297</t>
   </si>
   <si>
     <t xml:space="preserve">10.2828607559204</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0585927963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94416809082031</t>
+    <t xml:space="preserve">10.0585880279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.944167137146</t>
   </si>
   <si>
     <t xml:space="preserve">10.1089353561401</t>
@@ -4136,37 +4136,37 @@
     <t xml:space="preserve">10.1440258026123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3194751739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1638603210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0479106903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1714887619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2752332687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1562299728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2920122146606</t>
+    <t xml:space="preserve">10.3194770812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1638593673706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0479116439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1714897155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2752323150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.156231880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2920141220093</t>
   </si>
   <si>
     <t xml:space="preserve">10.2416667938232</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1928472518921</t>
+    <t xml:space="preserve">10.1928462982178</t>
   </si>
   <si>
     <t xml:space="preserve">10.5117073059082</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5513725280762</t>
+    <t xml:space="preserve">10.5513744354248</t>
   </si>
   <si>
     <t xml:space="preserve">10.8717594146729</t>
@@ -4175,16 +4175,16 @@
     <t xml:space="preserve">11.0838232040405</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5773096084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80533218383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2264099121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4277982711792</t>
+    <t xml:space="preserve">10.5773105621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80533313751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2264108657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4277954101562</t>
   </si>
   <si>
     <t xml:space="preserve">10.3759250640869</t>
@@ -4193,25 +4193,25 @@
     <t xml:space="preserve">9.99603843688965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89992332458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85873126983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74125576019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0006170272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7092170715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.086051940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2706537246704</t>
+    <t xml:space="preserve">9.89992141723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85872936248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74125480651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0006151199341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70921611785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0860528945923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2706546783447</t>
   </si>
   <si>
     <t xml:space="preserve">10.1241912841797</t>
@@ -4220,145 +4220,145 @@
     <t xml:space="preserve">9.98993682861328</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2081022262573</t>
+    <t xml:space="preserve">10.208104133606</t>
   </si>
   <si>
     <t xml:space="preserve">10.1409730911255</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2325134277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2538728713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3042192459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2126798629761</t>
+    <t xml:space="preserve">10.2325124740601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2538709640503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.304220199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2126808166504</t>
   </si>
   <si>
     <t xml:space="preserve">10.1165647506714</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5406942367554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5239105224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8122596740723</t>
+    <t xml:space="preserve">10.540696144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5239114761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8122587203979</t>
   </si>
   <si>
     <t xml:space="preserve">10.8320932388306</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7939519882202</t>
+    <t xml:space="preserve">10.7939510345459</t>
   </si>
   <si>
     <t xml:space="preserve">10.8534517288208</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6795301437378</t>
+    <t xml:space="preserve">10.6795282363892</t>
   </si>
   <si>
     <t xml:space="preserve">10.3591432571411</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86330699920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88466644287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0372304916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2142066955566</t>
+    <t xml:space="preserve">9.86330890655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88466739654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0372314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2142057418823</t>
   </si>
   <si>
     <t xml:space="preserve">10.0692701339722</t>
   </si>
   <si>
-    <t xml:space="preserve">10.374400138855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3057460784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3774490356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97620487213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1135129928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3896560668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4049129486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5467967987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6276559829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.516284942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5956172943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7955636978149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7136974334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1151647567749</t>
+    <t xml:space="preserve">10.3743991851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3057451248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3774499893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97620582580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1135139465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3896551132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4049139022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5467977523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6276578903198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5162839889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5956153869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7955646514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7136964797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1151657104492</t>
   </si>
   <si>
     <t xml:space="preserve">11.2143526077271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1718435287476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1781396865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1765651702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0978469848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0773801803589</t>
+    <t xml:space="preserve">11.1718416213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1781406402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1765670776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.097846031189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0773792266846</t>
   </si>
   <si>
     <t xml:space="preserve">11.2237968444824</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3607702255249</t>
+    <t xml:space="preserve">11.3607692718506</t>
   </si>
   <si>
     <t xml:space="preserve">11.3576211929321</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3292818069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0411672592163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4224348068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2161912918091</t>
+    <t xml:space="preserve">11.3292808532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0411691665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.422435760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2161893844604</t>
   </si>
   <si>
     <t xml:space="preserve">10.3673324584961</t>
@@ -4370,34 +4370,34 @@
     <t xml:space="preserve">9.92335414886475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45418834686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4809513092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50929164886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17867088317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9976167678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18339347839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05272006988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13301277160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91732120513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83860111236572</t>
+    <t xml:space="preserve">9.45418739318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48095226287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50929260253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17866992950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99761486053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18339443206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05271911621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13301467895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91732311248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83860397338867</t>
   </si>
   <si>
     <t xml:space="preserve">9.05114555358887</t>
@@ -4406,19 +4406,19 @@
     <t xml:space="preserve">8.52687549591064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46704769134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69533443450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83702850341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81656074523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76775360107422</t>
+    <t xml:space="preserve">8.4670467376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69533252716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83702945709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81656265258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76775455474854</t>
   </si>
   <si>
     <t xml:space="preserve">8.75043678283691</t>
@@ -4427,28 +4427,28 @@
     <t xml:space="preserve">8.37888240814209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5315990447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67014503479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89842796325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7960958480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65912055969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63550758361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70793056488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67486667633057</t>
+    <t xml:space="preserve">8.53159809112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67014217376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89842987060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79609394073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65912246704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63550853729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70792961120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67486572265625</t>
   </si>
   <si>
     <t xml:space="preserve">8.73154354095459</t>
@@ -4457,70 +4457,70 @@
     <t xml:space="preserve">9.22275161743164</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21173095703125</t>
+    <t xml:space="preserve">9.21173191070557</t>
   </si>
   <si>
     <t xml:space="preserve">9.00863647460938</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9739990234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9661283493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0180835723877</t>
+    <t xml:space="preserve">8.97399997711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96613025665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01808261871338</t>
   </si>
   <si>
     <t xml:space="preserve">9.01021099090576</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04642105102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99289131164551</t>
+    <t xml:space="preserve">9.04642200469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99289321899414</t>
   </si>
   <si>
     <t xml:space="preserve">9.12356758117676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15505599975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11411952972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20385932922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.394362449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26526165008545</t>
+    <t xml:space="preserve">9.15505409240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11412143707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20386123657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39436149597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26526260375977</t>
   </si>
   <si>
     <t xml:space="preserve">9.41482830047607</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76749134063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64626216888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84463500976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.695068359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83991050720215</t>
+    <t xml:space="preserve">9.76749038696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64626121520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84463405609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69506740570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83991241455078</t>
   </si>
   <si>
     <t xml:space="preserve">9.63209438323975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29517364501953</t>
+    <t xml:space="preserve">9.29517555236816</t>
   </si>
   <si>
     <t xml:space="preserve">9.23062610626221</t>
@@ -4529,70 +4529,70 @@
     <t xml:space="preserve">9.51401615142822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67460060119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40853118896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14560794830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11726856231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19598770141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4022331237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31721687316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29675102233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08420562744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00863742828369</t>
+    <t xml:space="preserve">9.67460250854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40853023529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14560890197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11726760864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19598960876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40223407745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31721591949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2967472076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08420753479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00863838195801</t>
   </si>
   <si>
     <t xml:space="preserve">8.94121646881104</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10174083709717</t>
+    <t xml:space="preserve">9.10173892974854</t>
   </si>
   <si>
     <t xml:space="preserve">8.66993045806885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6153507232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62979698181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65708827972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75661277770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02308464050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26226425170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40994834899902</t>
+    <t xml:space="preserve">8.61535167694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62979793548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6570873260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75661087036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0230827331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26226615905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40994644165039</t>
   </si>
   <si>
     <t xml:space="preserve">9.41476345062256</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50305271148682</t>
+    <t xml:space="preserve">9.5030517578125</t>
   </si>
   <si>
     <t xml:space="preserve">9.45650100708008</t>
@@ -4601,55 +4601,55 @@
     <t xml:space="preserve">9.28634452819824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14668846130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38105297088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52231597900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5239200592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70691680908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67802429199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91560173034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88991737365723</t>
+    <t xml:space="preserve">9.14668750762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38105392456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52231407165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52391910552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70691871643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67802333831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91560077667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88991641998291</t>
   </si>
   <si>
     <t xml:space="preserve">10.0199413299561</t>
   </si>
   <si>
-    <t xml:space="preserve">10.368278503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5432500839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.63796043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.806510925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8594856262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0119829177856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2447414398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4518203735352</t>
+    <t xml:space="preserve">10.3682794570923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5432510375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6379594802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8065099716187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8594846725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.01198387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.244743347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4518213272095</t>
   </si>
   <si>
     <t xml:space="preserve">11.4084777832031</t>
@@ -4658,64 +4658,64 @@
     <t xml:space="preserve">11.2543745040894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2929000854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4598474502563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6171598434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6187658309937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5240573883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3057432174683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3876085281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9604139328003</t>
+    <t xml:space="preserve">11.2929010391235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4598455429077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6171607971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6187648773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5240564346313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3057441711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3876123428345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9604120254517</t>
   </si>
   <si>
     <t xml:space="preserve">11.4560928344727</t>
   </si>
   <si>
-    <t xml:space="preserve">11.511528968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5637083053589</t>
+    <t xml:space="preserve">11.5115308761597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5637063980103</t>
   </si>
   <si>
     <t xml:space="preserve">11.6566476821899</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4283742904663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5734901428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6778450012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4870738983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3256492614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2783660888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1218338012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9538908004761</t>
+    <t xml:space="preserve">11.4283761978149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5734882354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.677845954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4870748519897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3256511688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2783641815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1218347549438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9538879394531</t>
   </si>
   <si>
     <t xml:space="preserve">11.0256328582764</t>
@@ -4727,22 +4727,22 @@
     <t xml:space="preserve">11.0941152572632</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2620601654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0957450866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6392002105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5169076919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5902833938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5984354019165</t>
+    <t xml:space="preserve">11.262059211731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0957469940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6391983032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5169067382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5902814865112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5984344482422</t>
   </si>
   <si>
     <t xml:space="preserve">10.9750871658325</t>
@@ -4751,19 +4751,19 @@
     <t xml:space="preserve">10.904974937439</t>
   </si>
   <si>
-    <t xml:space="preserve">10.986499786377</t>
+    <t xml:space="preserve">10.9865007400513</t>
   </si>
   <si>
     <t xml:space="preserve">11.043568611145</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0125894546509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0810718536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8316020965576</t>
+    <t xml:space="preserve">11.0125904083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0810689926147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8316011428833</t>
   </si>
   <si>
     <t xml:space="preserve">11.1756429672241</t>
@@ -4772,40 +4772,40 @@
     <t xml:space="preserve">11.2392320632935</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0680274963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2816257476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3680438995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3925018310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6093626022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7528486251831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7577381134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6811065673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7169780731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7887210845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6207761764526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7854585647583</t>
+    <t xml:space="preserve">11.0680284500122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.281626701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3680429458618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3925008773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6093635559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7528495788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7577419281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6811056137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7169771194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.788722038269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.620777130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7854604721069</t>
   </si>
   <si>
     <t xml:space="preserve">11.7398052215576</t>
@@ -4820,28 +4820,28 @@
     <t xml:space="preserve">11.5751209259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6517543792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5522937774658</t>
+    <t xml:space="preserve">11.6517562866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5522947311401</t>
   </si>
   <si>
     <t xml:space="preserve">11.5245742797852</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2881488800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2098817825317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2865180969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1658592224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3370628356934</t>
+    <t xml:space="preserve">11.2881479263306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2098827362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2865171432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1658582687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3370637893677</t>
   </si>
   <si>
     <t xml:space="preserve">11.5441408157349</t>
@@ -4853,31 +4853,31 @@
     <t xml:space="preserve">12.025146484375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0398206710815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0871076583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9762315750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9957981109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.658278465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6990423202515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6321887969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5066394805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8902997970581</t>
+    <t xml:space="preserve">12.0398216247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0871067047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9762306213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9957962036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6582794189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6990413665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6321907043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5066385269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8902988433838</t>
   </si>
   <si>
     <t xml:space="preserve">10.7549657821655</t>
@@ -4886,49 +4886,49 @@
     <t xml:space="preserve">10.9245414733887</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8968200683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7370290756226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8788871765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9522590637207</t>
+    <t xml:space="preserve">10.8968210220337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7370309829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.878885269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.952260017395</t>
   </si>
   <si>
     <t xml:space="preserve">11.0354156494141</t>
   </si>
   <si>
-    <t xml:space="preserve">10.942476272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9392137527466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9180192947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9490003585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5364761352539</t>
+    <t xml:space="preserve">10.9424753189087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9392147064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9180183410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9489984512329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.536473274231</t>
   </si>
   <si>
     <t xml:space="preserve">10.6310453414917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0359010696411</t>
+    <t xml:space="preserve">10.0359029769897</t>
   </si>
   <si>
     <t xml:space="preserve">9.91524314880371</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1344375610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3486528396606</t>
+    <t xml:space="preserve">10.1344394683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3486499786377</t>
   </si>
   <si>
     <t xml:space="preserve">10.3602752685547</t>
@@ -4937,58 +4937,58 @@
     <t xml:space="preserve">10.3403482437134</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1062088012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2191257476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4167346954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5230102539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6990299224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7156352996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1523656845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0510721206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1540260314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2420358657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4446249008179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3466520309448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5110483169556</t>
+    <t xml:space="preserve">10.1062078475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2191276550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4167327880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5230112075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.699028968811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7156362533569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.152364730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0510702133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1540269851685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2420349121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4446268081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3466510772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5110473632812</t>
   </si>
   <si>
     <t xml:space="preserve">11.4595699310303</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5243339538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5326366424561</t>
+    <t xml:space="preserve">11.5243330001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5326337814331</t>
   </si>
   <si>
     <t xml:space="preserve">11.419716835022</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2785682678223</t>
+    <t xml:space="preserve">11.2785673141479</t>
   </si>
   <si>
     <t xml:space="preserve">11.4296798706055</t>
@@ -4997,19 +4997,19 @@
     <t xml:space="preserve">11.4728546142578</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3034763336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4130744934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1938810348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9348306655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.825234413147</t>
+    <t xml:space="preserve">11.3034772872925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4130764007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1938791275024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9348316192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8252353668213</t>
   </si>
   <si>
     <t xml:space="preserve">10.7720956802368</t>
@@ -5018,55 +5018,55 @@
     <t xml:space="preserve">11.2669429779053</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3283863067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2254304885864</t>
+    <t xml:space="preserve">11.3283843994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2254314422607</t>
   </si>
   <si>
     <t xml:space="preserve">10.954758644104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1141719818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.080961227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9846477508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1224746704102</t>
+    <t xml:space="preserve">11.1141729354858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0809593200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9846467971802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1224756240845</t>
   </si>
   <si>
     <t xml:space="preserve">11.0759782791138</t>
   </si>
   <si>
-    <t xml:space="preserve">11.167308807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2010746002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2804183959961</t>
+    <t xml:space="preserve">11.1673097610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2010736465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2804193496704</t>
   </si>
   <si>
     <t xml:space="preserve">11.2837953567505</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0119972229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1352367401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1554946899414</t>
+    <t xml:space="preserve">11.0119962692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1352348327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1554927825928</t>
   </si>
   <si>
     <t xml:space="preserve">10.8938255310059</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5089197158813</t>
+    <t xml:space="preserve">10.5089206695557</t>
   </si>
   <si>
     <t xml:space="preserve">10.7942218780518</t>
@@ -5078,25 +5078,25 @@
     <t xml:space="preserve">11.0592679977417</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9596652984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0406980514526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0710830688477</t>
+    <t xml:space="preserve">10.9596643447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0406970977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0710821151733</t>
   </si>
   <si>
     <t xml:space="preserve">10.8296737670898</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9394063949585</t>
+    <t xml:space="preserve">10.9394054412842</t>
   </si>
   <si>
     <t xml:space="preserve">10.9613523483276</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0153741836548</t>
+    <t xml:space="preserve">11.0153751373291</t>
   </si>
   <si>
     <t xml:space="preserve">10.9545993804932</t>
@@ -5105,43 +5105,43 @@
     <t xml:space="preserve">10.964729309082</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8178558349609</t>
+    <t xml:space="preserve">10.8178567886353</t>
   </si>
   <si>
     <t xml:space="preserve">11.028881072998</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8769445419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8009767532349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9208345413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7587728500366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8060398101807</t>
+    <t xml:space="preserve">10.8769426345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8009738922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9208354949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.758770942688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8060388565063</t>
   </si>
   <si>
     <t xml:space="preserve">10.8786306381226</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1267938613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.32093334198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3648262023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2854814529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0018682479858</t>
+    <t xml:space="preserve">11.1267948150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3209352493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3648271560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2854833602905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0018692016602</t>
   </si>
   <si>
     <t xml:space="preserve">11.0170621871948</t>
@@ -5150,7 +5150,7 @@
     <t xml:space="preserve">11.0744600296021</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1706886291504</t>
+    <t xml:space="preserve">11.1706867218018</t>
   </si>
   <si>
     <t xml:space="preserve">11.4239139556885</t>
@@ -5159,7 +5159,7 @@
     <t xml:space="preserve">11.4965057373047</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3327522277832</t>
+    <t xml:space="preserve">11.3327503204346</t>
   </si>
   <si>
     <t xml:space="preserve">11.2213315963745</t>
@@ -5168,25 +5168,25 @@
     <t xml:space="preserve">11.3361282348633</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4289789199829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.513388633728</t>
+    <t xml:space="preserve">11.4289770126343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5133895874023</t>
   </si>
   <si>
     <t xml:space="preserve">11.6551933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5724725723267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4711828231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5893564224243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5285806655884</t>
+    <t xml:space="preserve">11.5724744796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4711818695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5893545150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5285816192627</t>
   </si>
   <si>
     <t xml:space="preserve">11.7193450927734</t>
@@ -5195,19 +5195,19 @@
     <t xml:space="preserve">11.6281843185425</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5353345870972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5842914581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5454635620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5015687942505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8746585845947</t>
+    <t xml:space="preserve">11.5353326797485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5842905044556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5454626083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5015697479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8746576309204</t>
   </si>
   <si>
     <t xml:space="preserve">11.9236154556274</t>
@@ -5216,37 +5216,37 @@
     <t xml:space="preserve">11.8577756881714</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8290777206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7581739425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7953128814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8459577560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8932275772095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9134855270386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8797225952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9253034591675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9472503662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0687990188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1177558898926</t>
+    <t xml:space="preserve">11.8290767669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7581748962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7953119277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8459596633911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8932294845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9134874343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8797235488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9253015518188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9472494125366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0687980651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1177539825439</t>
   </si>
   <si>
     <t xml:space="preserve">12.1278839111328</t>
@@ -5255,46 +5255,46 @@
     <t xml:space="preserve">12.0569820404053</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2713804244995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.325403213501</t>
+    <t xml:space="preserve">12.2713794708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3254022598267</t>
   </si>
   <si>
     <t xml:space="preserve">12.5212306976318</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4857788085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4418849945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4908447265625</t>
+    <t xml:space="preserve">12.4857797622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4418869018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4908437728882</t>
   </si>
   <si>
     <t xml:space="preserve">12.7052421569824</t>
   </si>
   <si>
-    <t xml:space="preserve">12.747447013855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.764328956604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9736623764038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9449634552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8403482437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1198949813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0650157928467</t>
+    <t xml:space="preserve">12.7474479675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7643280029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9736642837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9449663162231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8403472900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1198959350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0650148391724</t>
   </si>
   <si>
     <t xml:space="preserve">12.8763628005981</t>
@@ -5303,25 +5303,25 @@
     <t xml:space="preserve">13.0667304992676</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0495805740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0152816772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1816358566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2227983474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.08216381073</t>
+    <t xml:space="preserve">13.049578666687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0152797698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1816368103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2227964401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0821657180786</t>
   </si>
   <si>
     <t xml:space="preserve">12.7768907546997</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6294012069702</t>
+    <t xml:space="preserve">12.6294002532959</t>
   </si>
   <si>
     <t xml:space="preserve">12.4321737289429</t>
@@ -5330,7 +5330,7 @@
     <t xml:space="preserve">12.3824377059937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5539407730103</t>
+    <t xml:space="preserve">12.5539417266846</t>
   </si>
   <si>
     <t xml:space="preserve">12.8386325836182</t>
@@ -5345,22 +5345,22 @@
     <t xml:space="preserve">13.1164655685425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2896814346313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2742481231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3188371658325</t>
+    <t xml:space="preserve">13.28968334198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2742490768433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3188381195068</t>
   </si>
   <si>
     <t xml:space="preserve">13.4114503860474</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2502355575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2039318084717</t>
+    <t xml:space="preserve">13.2502374649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2039308547974</t>
   </si>
   <si>
     <t xml:space="preserve">13.2365159988403</t>
@@ -5369,13 +5369,13 @@
     <t xml:space="preserve">13.2107925415039</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2759628295898</t>
+    <t xml:space="preserve">13.2759618759155</t>
   </si>
   <si>
     <t xml:space="preserve">13.299973487854</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1747770309448</t>
+    <t xml:space="preserve">13.1747760772705</t>
   </si>
   <si>
     <t xml:space="preserve">13.2296571731567</t>
@@ -5384,22 +5384,22 @@
     <t xml:space="preserve">13.466329574585</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1764907836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2090768814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8729333877563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7134380340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8077630996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8609294891357</t>
+    <t xml:space="preserve">13.17649269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.209077835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8729343414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7134370803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8077621459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8609285354614</t>
   </si>
   <si>
     <t xml:space="preserve">13.0615854263306</t>
@@ -5408,22 +5408,22 @@
     <t xml:space="preserve">13.0770206451416</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0255680084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7425918579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0697450637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0053033828735</t>
+    <t xml:space="preserve">13.0255689620972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7425909042358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0697469711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0053024291992</t>
   </si>
   <si>
     <t xml:space="preserve">12.8224239349365</t>
   </si>
   <si>
-    <t xml:space="preserve">13.007043838501</t>
+    <t xml:space="preserve">13.0070447921753</t>
   </si>
   <si>
     <t xml:space="preserve">13.1219968795776</t>
@@ -5438,40 +5438,40 @@
     <t xml:space="preserve">13.1568307876587</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2090816497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2804918289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.027946472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1411552429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9861431121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8624830245972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0714864730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0488452911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8920927047729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8450651168823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9304113388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9008007049561</t>
+    <t xml:space="preserve">13.2090826034546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2804927825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0279445648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1411561965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9861440658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8624839782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0714883804321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0488443374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8920917510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8450660705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9304084777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9008016586304</t>
   </si>
   <si>
     <t xml:space="preserve">13.055811882019</t>
@@ -5480,58 +5480,58 @@
     <t xml:space="preserve">13.0854206085205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2404327392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2369499206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3135843276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4424686431885</t>
+    <t xml:space="preserve">13.2404317855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.23694896698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3135833740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4424695968628</t>
   </si>
   <si>
     <t xml:space="preserve">13.3745441436768</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3658351898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5469732284546</t>
+    <t xml:space="preserve">13.365837097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5469722747803</t>
   </si>
   <si>
     <t xml:space="preserve">13.4442119598389</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5156211853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5330390930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1324462890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9965944290161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9617595672607</t>
+    <t xml:space="preserve">13.5156221389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5330381393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1324472427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9965934753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9617586135864</t>
   </si>
   <si>
     <t xml:space="preserve">12.8990592956543</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0993547439575</t>
+    <t xml:space="preserve">13.0993537902832</t>
   </si>
   <si>
     <t xml:space="preserve">13.0592956542969</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0035610198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7597217559814</t>
+    <t xml:space="preserve">13.0035619735718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7597236633301</t>
   </si>
   <si>
     <t xml:space="preserve">12.7214050292969</t>
@@ -5540,7 +5540,7 @@
     <t xml:space="preserve">12.5838098526001</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4880170822144</t>
+    <t xml:space="preserve">12.48801612854</t>
   </si>
   <si>
     <t xml:space="preserve">12.5036916732788</t>
@@ -5549,40 +5549,40 @@
     <t xml:space="preserve">12.6186447143555</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6848287582397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8502893447876</t>
+    <t xml:space="preserve">12.6848297119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8502902984619</t>
   </si>
   <si>
     <t xml:space="preserve">12.9931106567383</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8868684768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7022466659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5176248550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7161808013916</t>
+    <t xml:space="preserve">12.886866569519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7022457122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5176239013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7161798477173</t>
   </si>
   <si>
     <t xml:space="preserve">12.514142036438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5106582641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4479560852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5733604431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6012268066406</t>
+    <t xml:space="preserve">12.5106592178345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4479579925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5733585357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6012277603149</t>
   </si>
   <si>
     <t xml:space="preserve">12.6290950775146</t>
@@ -5597,46 +5597,46 @@
     <t xml:space="preserve">12.3399715423584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3068799972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4549236297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3922214508057</t>
+    <t xml:space="preserve">12.3068790435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4549245834351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.39222240448</t>
   </si>
   <si>
     <t xml:space="preserve">12.4148654937744</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4113807678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5228509902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5019512176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4078979492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4775657653809</t>
+    <t xml:space="preserve">12.4113817214966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5228500366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5019483566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4078989028931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4775667190552</t>
   </si>
   <si>
     <t xml:space="preserve">12.5298175811768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6343193054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7388219833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7423038482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8032636642456</t>
+    <t xml:space="preserve">12.6343202590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7388229370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7423048019409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8032646179199</t>
   </si>
   <si>
     <t xml:space="preserve">12.6778621673584</t>
@@ -5645,22 +5645,22 @@
     <t xml:space="preserve">12.7945575714111</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0436201095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6465110778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6325778961182</t>
+    <t xml:space="preserve">13.0436191558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6465101242065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6325769424438</t>
   </si>
   <si>
     <t xml:space="preserve">12.5883026123047</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8893737792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6857080459595</t>
+    <t xml:space="preserve">12.8893728256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6857089996338</t>
   </si>
   <si>
     <t xml:space="preserve">12.7158145904541</t>
@@ -5669,13 +5669,13 @@
     <t xml:space="preserve">12.7105016708374</t>
   </si>
   <si>
-    <t xml:space="preserve">12.887601852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8840627670288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9017696380615</t>
+    <t xml:space="preserve">12.8876028060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8840608596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9017705917358</t>
   </si>
   <si>
     <t xml:space="preserve">12.9708395004272</t>
@@ -5684,19 +5684,19 @@
     <t xml:space="preserve">13.3091011047363</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4383840560913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5906896591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7323713302612</t>
+    <t xml:space="preserve">13.4383850097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5906915664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7323722839355</t>
   </si>
   <si>
     <t xml:space="preserve">13.7376842498779</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6774711608887</t>
+    <t xml:space="preserve">13.677472114563</t>
   </si>
   <si>
     <t xml:space="preserve">13.6154851913452</t>
@@ -5708,16 +5708,16 @@
     <t xml:space="preserve">13.9289522171021</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7553958892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4596376419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5747518539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4862012863159</t>
+    <t xml:space="preserve">13.7553939819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4596385955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5747528076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4862022399902</t>
   </si>
   <si>
     <t xml:space="preserve">13.5109958648682</t>
@@ -5726,37 +5726,37 @@
     <t xml:space="preserve">13.583607673645</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7429971694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4915161132812</t>
+    <t xml:space="preserve">13.7429990768433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4915142059326</t>
   </si>
   <si>
     <t xml:space="preserve">13.507453918457</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5127668380737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5251636505127</t>
+    <t xml:space="preserve">13.512767791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5251655578613</t>
   </si>
   <si>
     <t xml:space="preserve">13.40296459198</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1266889572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0239686965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1532535552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2542018890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2258644104004</t>
+    <t xml:space="preserve">13.12668800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0239706039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1532526016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2542009353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2258653640747</t>
   </si>
   <si>
     <t xml:space="preserve">13.3108730316162</t>
@@ -5768,7 +5768,7 @@
     <t xml:space="preserve">13.4932861328125</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3817129135132</t>
+    <t xml:space="preserve">13.3817148208618</t>
   </si>
   <si>
     <t xml:space="preserve">13.0877256393433</t>
@@ -5777,7 +5777,7 @@
     <t xml:space="preserve">13.1302299499512</t>
   </si>
   <si>
-    <t xml:space="preserve">13.185996055603</t>
+    <t xml:space="preserve">13.1859970092773</t>
   </si>
   <si>
     <t xml:space="preserve">13.1212348937988</t>
@@ -5792,7 +5792,7 @@
     <t xml:space="preserve">12.9377470016479</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1158380508423</t>
+    <t xml:space="preserve">13.1158399581909</t>
   </si>
   <si>
     <t xml:space="preserve">13.0942525863647</t>
@@ -5801,13 +5801,13 @@
     <t xml:space="preserve">12.939546585083</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9233551025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0384864807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9683284759521</t>
+    <t xml:space="preserve">12.9233560562134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0384855270386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9683294296265</t>
   </si>
   <si>
     <t xml:space="preserve">12.6049489974976</t>
@@ -5816,7 +5816,7 @@
     <t xml:space="preserve">12.5437860488892</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6553182601929</t>
+    <t xml:space="preserve">12.6553192138672</t>
   </si>
   <si>
     <t xml:space="preserve">12.5851602554321</t>
@@ -5828,88 +5828,88 @@
     <t xml:space="preserve">12.5815629959106</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5401887893677</t>
+    <t xml:space="preserve">12.540189743042</t>
   </si>
   <si>
     <t xml:space="preserve">12.3387117385864</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1498250961304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1732120513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3980741500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5006132125854</t>
+    <t xml:space="preserve">12.149827003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1732110977173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3980751037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5006122589111</t>
   </si>
   <si>
     <t xml:space="preserve">12.711085319519</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5347900390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7038898468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8046283721924</t>
+    <t xml:space="preserve">12.5347929000854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7038879394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8046293258667</t>
   </si>
   <si>
     <t xml:space="preserve">12.8082256317139</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8747854232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9107627868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0708656311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.067268371582</t>
+    <t xml:space="preserve">12.8747863769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9107646942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0708665847778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0672674179077</t>
   </si>
   <si>
     <t xml:space="preserve">13.0079040527344</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1374273300171</t>
+    <t xml:space="preserve">13.1374263763428</t>
   </si>
   <si>
     <t xml:space="preserve">13.0007095336914</t>
   </si>
   <si>
-    <t xml:space="preserve">12.86399269104</t>
+    <t xml:space="preserve">12.8639917373657</t>
   </si>
   <si>
     <t xml:space="preserve">12.6930961608887</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7542581558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7722482681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8567972183228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8064260482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6031513214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7128829956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8531980514526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6643133163452</t>
+    <t xml:space="preserve">12.7542591094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7722473144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8567962646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8064270019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6031503677368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7128839492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.853199005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6643123626709</t>
   </si>
   <si>
     <t xml:space="preserve">12.6571168899536</t>
@@ -5918,58 +5918,58 @@
     <t xml:space="preserve">12.615743637085</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6445245742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6103458404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1590118408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1680088043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3101215362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0870590209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.786639213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5329933166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.522198677063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8334112167358</t>
+    <t xml:space="preserve">12.6445255279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6103467941284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1590127944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.168007850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3101205825806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0870580673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7866382598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5329923629761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5221996307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8334102630615</t>
   </si>
   <si>
     <t xml:space="preserve">13.0025091171265</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8855781555176</t>
+    <t xml:space="preserve">12.8855791091919</t>
   </si>
   <si>
     <t xml:space="preserve">13.0402851104736</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1482200622559</t>
+    <t xml:space="preserve">13.1482191085815</t>
   </si>
   <si>
     <t xml:space="preserve">13.0366868972778</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0564746856689</t>
+    <t xml:space="preserve">13.0564756393433</t>
   </si>
   <si>
     <t xml:space="preserve">12.9539375305176</t>
   </si>
   <si>
-    <t xml:space="preserve">13.254355430603</t>
+    <t xml:space="preserve">13.2543544769287</t>
   </si>
   <si>
     <t xml:space="preserve">13.2237730026245</t>
@@ -5978,13 +5978,13 @@
     <t xml:space="preserve">13.1967887878418</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3173170089722</t>
+    <t xml:space="preserve">13.3173179626465</t>
   </si>
   <si>
     <t xml:space="preserve">13.1985893249512</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2219743728638</t>
+    <t xml:space="preserve">13.2219753265381</t>
   </si>
   <si>
     <t xml:space="preserve">12.8891763687134</t>
@@ -5993,31 +5993,31 @@
     <t xml:space="preserve">12.7398672103882</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3782873153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3513031005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4574403762817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.599552154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6948938369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7902374267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8172197341919</t>
+    <t xml:space="preserve">12.3782863616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3513040542603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4574394226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5995531082153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6948947906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7902364730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8172206878662</t>
   </si>
   <si>
     <t xml:space="preserve">12.8460025787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9100866317749</t>
+    <t xml:space="preserve">12.9100856781006</t>
   </si>
   <si>
     <t xml:space="preserve">12.965015411377</t>
@@ -6026,16 +6026,16 @@
     <t xml:space="preserve">12.8130474090576</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4230518341064</t>
+    <t xml:space="preserve">12.4230508804321</t>
   </si>
   <si>
     <t xml:space="preserve">12.5145998001099</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5255851745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7160053253174</t>
+    <t xml:space="preserve">12.5255861282349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7160062789917</t>
   </si>
   <si>
     <t xml:space="preserve">12.9247350692749</t>
@@ -6053,10 +6053,10 @@
     <t xml:space="preserve">12.9943113327026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.968677520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0565633773804</t>
+    <t xml:space="preserve">12.9686784744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0565643310547</t>
   </si>
   <si>
     <t xml:space="preserve">13.1114921569824</t>
@@ -6074,7 +6074,7 @@
     <t xml:space="preserve">13.0510692596436</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0712118148804</t>
+    <t xml:space="preserve">13.0712108612061</t>
   </si>
   <si>
     <t xml:space="preserve">12.9814949035645</t>
@@ -6101,25 +6101,25 @@
     <t xml:space="preserve">12.9229040145874</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8203706741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8991012573242</t>
+    <t xml:space="preserve">12.820369720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8991003036499</t>
   </si>
   <si>
     <t xml:space="preserve">12.7526245117188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8258638381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6445980072021</t>
+    <t xml:space="preserve">12.8258628845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6445970535278</t>
   </si>
   <si>
     <t xml:space="preserve">12.5585422515869</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9045934677124</t>
+    <t xml:space="preserve">12.9045925140381</t>
   </si>
   <si>
     <t xml:space="preserve">12.9511947631836</t>
@@ -6128,7 +6128,7 @@
     <t xml:space="preserve">12.8002099990845</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7946176528931</t>
+    <t xml:space="preserve">12.7946166992188</t>
   </si>
   <si>
     <t xml:space="preserve">12.8747701644897</t>
@@ -6140,13 +6140,13 @@
     <t xml:space="preserve">12.8058004379272</t>
   </si>
   <si>
-    <t xml:space="preserve">12.541111946106</t>
+    <t xml:space="preserve">12.5411109924316</t>
   </si>
   <si>
     <t xml:space="preserve">12.503830909729</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5112857818604</t>
+    <t xml:space="preserve">12.5112867355347</t>
   </si>
   <si>
     <t xml:space="preserve">12.4945116043091</t>
@@ -6164,16 +6164,16 @@
     <t xml:space="preserve">12.5392475128174</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5075588226318</t>
+    <t xml:space="preserve">12.5075578689575</t>
   </si>
   <si>
     <t xml:space="preserve">12.57652759552</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4926452636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4646854400635</t>
+    <t xml:space="preserve">12.4926462173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4646863937378</t>
   </si>
   <si>
     <t xml:space="preserve">12.4143571853638</t>
@@ -6182,10 +6182,10 @@
     <t xml:space="preserve">12.3919887542725</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2093152999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9148015975952</t>
+    <t xml:space="preserve">12.2093162536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9148006439209</t>
   </si>
   <si>
     <t xml:space="preserve">12.0154581069946</t>
@@ -6197,13 +6197,13 @@
     <t xml:space="preserve">11.8588800430298</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8383760452271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0732412338257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1999950408936</t>
+    <t xml:space="preserve">11.8383769989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0732421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1999959945679</t>
   </si>
   <si>
     <t xml:space="preserve">12.5467023849487</t>
@@ -6233,7 +6233,7 @@
     <t xml:space="preserve">12.9959316253662</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1338682174683</t>
+    <t xml:space="preserve">13.1338672637939</t>
   </si>
   <si>
     <t xml:space="preserve">12.9474668502808</t>
@@ -6251,13 +6251,13 @@
     <t xml:space="preserve">12.496374130249</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4982395172119</t>
+    <t xml:space="preserve">12.4982385635376</t>
   </si>
   <si>
     <t xml:space="preserve">12.5187425613403</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5355186462402</t>
+    <t xml:space="preserve">12.5355176925659</t>
   </si>
   <si>
     <t xml:space="preserve">12.7088718414307</t>
@@ -6281,19 +6281,19 @@
     <t xml:space="preserve">12.9418745040894</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1059083938599</t>
+    <t xml:space="preserve">13.1059074401855</t>
   </si>
   <si>
     <t xml:space="preserve">13.0723552703857</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0406665802002</t>
+    <t xml:space="preserve">13.0406675338745</t>
   </si>
   <si>
     <t xml:space="preserve">13.0835399627686</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1189565658569</t>
+    <t xml:space="preserve">13.1189556121826</t>
   </si>
   <si>
     <t xml:space="preserve">13.1357316970825</t>
@@ -6320,7 +6320,7 @@
     <t xml:space="preserve">13.1170921325684</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9120502471924</t>
+    <t xml:space="preserve">12.9120492935181</t>
   </si>
   <si>
     <t xml:space="preserve">12.9083223342896</t>
@@ -6332,7 +6332,7 @@
     <t xml:space="preserve">12.2503232955933</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3174285888672</t>
+    <t xml:space="preserve">12.3174295425415</t>
   </si>
   <si>
     <t xml:space="preserve">12.6156721115112</t>
@@ -6362,7 +6362,7 @@
     <t xml:space="preserve">13.4637994766235</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3985595703125</t>
+    <t xml:space="preserve">13.3985586166382</t>
   </si>
   <si>
     <t xml:space="preserve">13.337854385376</t>
@@ -6912,6 +6912,9 @@
   </si>
   <si>
     <t xml:space="preserve">15.7220001220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8979997634888</t>
   </si>
 </sst>
 </file>
@@ -73160,7 +73163,7 @@
     </row>
     <row r="2536">
       <c r="A2536" s="1" t="n">
-        <v>46009.6929166667</v>
+        <v>46009.3333333333</v>
       </c>
       <c r="B2536" t="n">
         <v>9078392</v>
@@ -73181,6 +73184,32 @@
         <v>2299</v>
       </c>
       <c r="H2536" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2537">
+      <c r="A2537" s="1" t="n">
+        <v>46010.6924074074</v>
+      </c>
+      <c r="B2537" t="n">
+        <v>19410242</v>
+      </c>
+      <c r="C2537" t="n">
+        <v>15.9379997253418</v>
+      </c>
+      <c r="D2537" t="n">
+        <v>15.6239995956421</v>
+      </c>
+      <c r="E2537" t="n">
+        <v>15.6239995956421</v>
+      </c>
+      <c r="F2537" t="n">
+        <v>15.8979997634888</v>
+      </c>
+      <c r="G2537" t="s">
+        <v>2300</v>
+      </c>
+      <c r="H2537" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ENI.MI.xlsx
+++ b/data/ENI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2304" uniqueCount="2304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2305" uniqueCount="2305">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,91 +38,91 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15080404281616</t>
+    <t xml:space="preserve">7.150803565979</t>
   </si>
   <si>
     <t xml:space="preserve">ENI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21469831466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01236486434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9591236114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76211500167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7354907989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75146532058716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83133029937744</t>
+    <t xml:space="preserve">7.21469783782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.012366771698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95912218093872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76211452484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73549222946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75146627426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83133554458618</t>
   </si>
   <si>
     <t xml:space="preserve">6.92717409133911</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68224811553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6077036857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69821977615356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47459077835083</t>
+    <t xml:space="preserve">6.68224763870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60770511627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69822216033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47459268569946</t>
   </si>
   <si>
     <t xml:space="preserve">6.90587711334229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82068347930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96444606781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99639415740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07093572616577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66094923019409</t>
+    <t xml:space="preserve">6.82068490982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96444654464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99639272689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07093667984009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66094732284546</t>
   </si>
   <si>
     <t xml:space="preserve">6.63432741165161</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78341245651245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6715989112854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43199729919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17642068862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19239282608032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81967782974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20836734771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35745048522949</t>
+    <t xml:space="preserve">6.78341197967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67159748077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43199491500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17641973495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1923942565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81967973709106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20836687088013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35745286941528</t>
   </si>
   <si>
     <t xml:space="preserve">6.30953311920166</t>
@@ -131,238 +131,238 @@
     <t xml:space="preserve">6.51186275482178</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37342691421509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34680366516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57575750350952</t>
+    <t xml:space="preserve">6.37342596054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34680461883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57575607299805</t>
   </si>
   <si>
     <t xml:space="preserve">6.27226066589355</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43732070922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76743936538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89522743225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10820770263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16145277023315</t>
+    <t xml:space="preserve">6.43732023239136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76743984222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89522695541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10820817947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16145420074463</t>
   </si>
   <si>
     <t xml:space="preserve">7.25729417800903</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20937299728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23599481582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05496263504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1348295211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88990068435669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09223508834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1295051574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02833938598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11885690689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24664402008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31053781509399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34781074523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17210245132446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00171709060669</t>
+    <t xml:space="preserve">7.20937395095825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23599433898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05496311187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13482999801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88990116119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09223461151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12950468063354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02833986282349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11885643005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24664211273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31053733825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3478102684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17210149765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00171661376953</t>
   </si>
   <si>
     <t xml:space="preserve">7.1987247467041</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08158540725708</t>
+    <t xml:space="preserve">7.08158445358276</t>
   </si>
   <si>
     <t xml:space="preserve">6.81003570556641</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79406261444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62367630004883</t>
+    <t xml:space="preserve">6.7940616607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62367677688599</t>
   </si>
   <si>
     <t xml:space="preserve">6.69289636611938</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55978441238403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84198045730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86327934265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90055179595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17742586135864</t>
+    <t xml:space="preserve">6.55978393554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84198141098022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86327791213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90055131912231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17742490768433</t>
   </si>
   <si>
     <t xml:space="preserve">7.30521440505981</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18807315826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27859163284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39572906494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49156999588013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53416728973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49689483642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52884292602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59806108474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66728019714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56079006195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4276762008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27326726913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12417984008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22534561157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28923988342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02301359176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10738801956177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3269214630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57938528060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6178035736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59036016464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65073108673096</t>
+    <t xml:space="preserve">7.18807554244995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27859115600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39573097229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49157285690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5341682434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49689817428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52884340286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59806203842163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6672797203064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56079149246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42767572402954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27326583862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12417936325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22534608840942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28923940658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02301549911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10738658905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32692050933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5793833732605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61780166625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59036254882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65073347091675</t>
   </si>
   <si>
     <t xml:space="preserve">7.53547716140747</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43119955062866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42571115493774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3653392791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55743026733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73305749893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75501203536987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71658945083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38180494308472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24459600448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33789825439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26106071472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54645490646362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77147579193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87026691436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74952268600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00198650360107</t>
+    <t xml:space="preserve">7.4311990737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4257116317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36534023284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55743265151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73305892944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75501155853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71659421920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38180637359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24459552764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3378963470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.261061668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54645442962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77147483825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8702654838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74952220916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00198554992676</t>
   </si>
   <si>
     <t xml:space="preserve">7.26654863357544</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49705982208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84831142425537</t>
+    <t xml:space="preserve">7.49705839157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84831285476685</t>
   </si>
   <si>
     <t xml:space="preserve">7.96905469894409</t>
@@ -371,13 +371,13 @@
     <t xml:space="preserve">8.13370513916016</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90868043899536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76049947738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80440711975098</t>
+    <t xml:space="preserve">7.90868425369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76050043106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8044056892395</t>
   </si>
   <si>
     <t xml:space="preserve">7.95807981491089</t>
@@ -386,226 +386,226 @@
     <t xml:space="preserve">8.05137920379639</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12821769714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02942562103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17761421203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07882308959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9910101890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96356964111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88673114776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84282398223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8098931312561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70012760162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70561647415161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50254821777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50803565979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35984992980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20617818832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25557231903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27203798294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4476637840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4366888999939</t>
+    <t xml:space="preserve">8.12821865081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02942848205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1776123046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07882213592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99100732803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9635648727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8867301940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84282350540161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80989217758179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70012807846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70561695098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5025486946106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5080361366272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3598518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20617914199829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25557422637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27203845977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44766521453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43668794631958</t>
   </si>
   <si>
     <t xml:space="preserve">7.41473436355591</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51901245117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54096555709839</t>
+    <t xml:space="preserve">7.51901149749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54096460342407</t>
   </si>
   <si>
     <t xml:space="preserve">7.39278221130371</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3763165473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47510671615601</t>
+    <t xml:space="preserve">7.37631511688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47510528564453</t>
   </si>
   <si>
     <t xml:space="preserve">7.46961736679077</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52999019622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44217729568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19520235061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21715450286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25008296966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08543539047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19304752349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06278038024902</t>
+    <t xml:space="preserve">7.52998781204224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4421763420105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1952018737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21715593338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.250084400177</t>
   </si>
   <si>
     <t xml:space="preserve">7.08543491363525</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16472721099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13640975952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00614309310913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97215986251831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99481344223022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31764984130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26101303100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3006591796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34597110748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51588439941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52721214294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70279264450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55553293228149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50455760955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45358180999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60084199905396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53854036331177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67447233200073</t>
+    <t xml:space="preserve">7.19304847717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06277847290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08543300628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16472816467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1364107131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00613975524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97215938568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9948148727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31765174865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26101207733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30065727233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34597206115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5158839225769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52721357345581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70279169082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5555305480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50455665588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45358228683472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60084295272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53854084014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67447376251221</t>
   </si>
   <si>
     <t xml:space="preserve">7.69712734222412</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77641916275024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79907655715942</t>
+    <t xml:space="preserve">7.77641868591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79907512664795</t>
   </si>
   <si>
     <t xml:space="preserve">7.74810171127319</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66880750656128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78774785995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65181589126587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4819016456604</t>
+    <t xml:space="preserve">7.66880702972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78774642944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65181636810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48190116882324</t>
   </si>
   <si>
     <t xml:space="preserve">7.36296033859253</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25534820556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19871091842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13074445724487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23269319534302</t>
+    <t xml:space="preserve">7.25534915924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19871187210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13074493408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23269414901733</t>
   </si>
   <si>
     <t xml:space="preserve">7.27800321578979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24968814849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22136735916138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10809135437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9438419342041</t>
+    <t xml:space="preserve">7.24968671798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22136545181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10808944702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94383859634399</t>
   </si>
   <si>
     <t xml:space="preserve">7.07977247238159</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03446006774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01180458068848</t>
+    <t xml:space="preserve">7.03445911407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01180648803711</t>
   </si>
   <si>
     <t xml:space="preserve">7.11941719055176</t>
@@ -614,25 +614,25 @@
     <t xml:space="preserve">7.12508106231689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17039394378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44225645065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70845365524292</t>
+    <t xml:space="preserve">7.17039155960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44225549697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70845460891724</t>
   </si>
   <si>
     <t xml:space="preserve">7.7537636756897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90668678283691</t>
+    <t xml:space="preserve">7.90668869018555</t>
   </si>
   <si>
     <t xml:space="preserve">7.98598146438599</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05960941314697</t>
+    <t xml:space="preserve">8.05961036682129</t>
   </si>
   <si>
     <t xml:space="preserve">8.07093715667725</t>
@@ -641,172 +641,172 @@
     <t xml:space="preserve">8.37112045288086</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45608043670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42775821685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47873306274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52404403686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47307014465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5806827545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59201145172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68829536437988</t>
+    <t xml:space="preserve">8.45607852935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42776012420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47873401641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52404308319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.473069190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58068370819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59201049804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68829441070557</t>
   </si>
   <si>
     <t xml:space="preserve">8.67130374908447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74493217468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76192283630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85820865631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85254383087158</t>
+    <t xml:space="preserve">8.74493312835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76192378997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85821056365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85254287719727</t>
   </si>
   <si>
     <t xml:space="preserve">8.8865270614624</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90352153778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71661472320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80723476409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80156993865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75626182556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87520217895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72227764129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81856250762939</t>
+    <t xml:space="preserve">8.90351963043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71661376953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80723571777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80157089233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75626087188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87520027160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7222785949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81856346130371</t>
   </si>
   <si>
     <t xml:space="preserve">8.78457927703857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69395923614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46740531921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36545658111572</t>
+    <t xml:space="preserve">8.6939582824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4674072265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36545753479004</t>
   </si>
   <si>
     <t xml:space="preserve">8.15023136138916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04828453063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00297451019287</t>
+    <t xml:space="preserve">8.04828357696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00297260284424</t>
   </si>
   <si>
     <t xml:space="preserve">8.01996421813965</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22952556610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0426197052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00863647460938</t>
+    <t xml:space="preserve">8.22952651977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04262065887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00863838195801</t>
   </si>
   <si>
     <t xml:space="preserve">8.13324069976807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15589618682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23519134521484</t>
+    <t xml:space="preserve">8.15589427947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23519039154053</t>
   </si>
   <si>
     <t xml:space="preserve">8.14456844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99731111526489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25784492492676</t>
+    <t xml:space="preserve">7.99730634689331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25784683227539</t>
   </si>
   <si>
     <t xml:space="preserve">8.16155910491943</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09925651550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22386074066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49572467803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50138759613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64864826202393</t>
+    <t xml:space="preserve">8.09925746917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22386264801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49572277069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.501389503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64864921569824</t>
   </si>
   <si>
     <t xml:space="preserve">8.54669857025146</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38244724273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32580947875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28616237640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29749011993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19554138183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30881690979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45041561126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41076850891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43342304229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51271820068359</t>
+    <t xml:space="preserve">8.38244915008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3258113861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28616428375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2974910736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19554233551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30881881713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45041465759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41077041625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43342399597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51271629333496</t>
   </si>
   <si>
     <t xml:space="preserve">8.49006271362305</t>
@@ -815,40 +815,40 @@
     <t xml:space="preserve">8.56369113922119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67696857452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62599086761475</t>
+    <t xml:space="preserve">8.67696571350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6259937286377</t>
   </si>
   <si>
     <t xml:space="preserve">8.62032890319824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63165855407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31448364257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32014656066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46848201751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4335355758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34034729003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31122589111328</t>
+    <t xml:space="preserve">8.6316556930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31448459625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32014560699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46848011016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43353462219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34034633636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31122779846191</t>
   </si>
   <si>
     <t xml:space="preserve">8.32869815826416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2937536239624</t>
+    <t xml:space="preserve">8.29375267028809</t>
   </si>
   <si>
     <t xml:space="preserve">8.28792667388916</t>
@@ -857,10 +857,10 @@
     <t xml:space="preserve">8.49760055541992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58496761322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63156032562256</t>
+    <t xml:space="preserve">8.58496570587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63155841827393</t>
   </si>
   <si>
     <t xml:space="preserve">8.67815399169922</t>
@@ -869,43 +869,43 @@
     <t xml:space="preserve">8.67233085632324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7363977432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76551818847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65485858917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75969314575195</t>
+    <t xml:space="preserve">8.73639488220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76551723480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65485763549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75969219207764</t>
   </si>
   <si>
     <t xml:space="preserve">8.74804592132568</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73057556152344</t>
+    <t xml:space="preserve">8.73057460784912</t>
   </si>
   <si>
     <t xml:space="preserve">8.69562721252441</t>
   </si>
   <si>
-    <t xml:space="preserve">8.532546043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33452320098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31705188751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20638942718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3054027557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18309116363525</t>
+    <t xml:space="preserve">8.53254795074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33452415466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31704998016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20638847351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30540180206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18309307098389</t>
   </si>
   <si>
     <t xml:space="preserve">8.13067436218262</t>
@@ -917,37 +917,37 @@
     <t xml:space="preserve">8.03166103363037</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08990383148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09572696685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15397071838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06660461425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02001094818115</t>
+    <t xml:space="preserve">8.08990287780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09572887420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15397262573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06660842895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02001190185547</t>
   </si>
   <si>
     <t xml:space="preserve">8.1015510559082</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93847322463989</t>
+    <t xml:space="preserve">7.93847417831421</t>
   </si>
   <si>
     <t xml:space="preserve">7.97924280166626</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95594549179077</t>
+    <t xml:space="preserve">7.95594453811646</t>
   </si>
   <si>
     <t xml:space="preserve">7.90935087203979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92100095748901</t>
+    <t xml:space="preserve">7.9210000038147</t>
   </si>
   <si>
     <t xml:space="preserve">7.87440586090088</t>
@@ -956,103 +956,103 @@
     <t xml:space="preserve">7.89770317077637</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74627208709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66473197937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75792217254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78121852874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67055511474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62396287918091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54824733734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57154273986816</t>
+    <t xml:space="preserve">7.74627304077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66473150253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7579197883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78121757507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67055654525757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62396430969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54824590682983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57154369354248</t>
   </si>
   <si>
     <t xml:space="preserve">7.55407285690308</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68220472335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69385290145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71132516860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65308523178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64725971221924</t>
+    <t xml:space="preserve">7.68220567703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6938533782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71132612228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65308332443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6472601890564</t>
   </si>
   <si>
     <t xml:space="preserve">7.6589093208313</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59484052658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60648918151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72297382354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69967889785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78704166412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84528493881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88023090362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86275577545166</t>
+    <t xml:space="preserve">7.59484195709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60649013519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72297525405884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69967842102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78704214096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8452844619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88022994995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86275815963745</t>
   </si>
   <si>
     <t xml:space="preserve">7.89188003540039</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9035267829895</t>
+    <t xml:space="preserve">7.90352773666382</t>
   </si>
   <si>
     <t xml:space="preserve">7.88605403900146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85693502426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77539300918579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81033754348755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71714973449707</t>
+    <t xml:space="preserve">7.85693120956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77539253234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81033897399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71715021133423</t>
   </si>
   <si>
     <t xml:space="preserve">7.63561058044434</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75209617614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76374483108521</t>
+    <t xml:space="preserve">7.75209665298462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76374578475952</t>
   </si>
   <si>
     <t xml:space="preserve">7.79869079589844</t>
@@ -1061,16 +1061,16 @@
     <t xml:space="preserve">7.85110855102539</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83945894241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86858177185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9442982673645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04330921173096</t>
+    <t xml:space="preserve">7.8394603729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86858129501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94429540634155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04330825805664</t>
   </si>
   <si>
     <t xml:space="preserve">8.07329940795898</t>
@@ -1079,79 +1079,79 @@
     <t xml:space="preserve">8.11528587341309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18126392364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24124336242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26523399353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36120319366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39119052886963</t>
+    <t xml:space="preserve">8.18126201629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24124240875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26523494720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36120510101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39119243621826</t>
   </si>
   <si>
     <t xml:space="preserve">8.35520553588867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36720275878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39719009399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37919807434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43917655944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3372106552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41518497467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30722045898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34920883178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31322002410889</t>
+    <t xml:space="preserve">8.36720180511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39719200134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37919616699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43917560577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33721160888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41518592834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30722141265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34920787811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31321907043457</t>
   </si>
   <si>
     <t xml:space="preserve">8.33121299743652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32521533966064</t>
+    <t xml:space="preserve">8.32521629333496</t>
   </si>
   <si>
     <t xml:space="preserve">8.25923728942871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2952241897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2772331237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30122375488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42118263244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52914714813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57713031768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62511444091797</t>
+    <t xml:space="preserve">8.29522609710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27723121643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3012228012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42118358612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52914905548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5771312713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62511539459229</t>
   </si>
   <si>
     <t xml:space="preserve">8.69709205627441</t>
@@ -1160,25 +1160,25 @@
     <t xml:space="preserve">8.82904624938965</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76906681060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70308971405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64310741424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58313083648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48116302490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2352466583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25324058532715</t>
+    <t xml:space="preserve">8.76906585693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70308780670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64310836791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58313179016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48116397857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23524475097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25323963165283</t>
   </si>
   <si>
     <t xml:space="preserve">8.31921863555908</t>
@@ -1187,58 +1187,58 @@
     <t xml:space="preserve">8.3432092666626</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28922843933105</t>
+    <t xml:space="preserve">8.28922653198242</t>
   </si>
   <si>
     <t xml:space="preserve">8.21125316619873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28322982788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40918827056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43317794799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3851957321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37320041656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54714107513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65510559082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70908641815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81704998016357</t>
+    <t xml:space="preserve">8.28322887420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40918636322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.433180809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38519477844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37319850921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54713916778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65510368347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70908737182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81705093383789</t>
   </si>
   <si>
     <t xml:space="preserve">8.94900703430176</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94300937652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91301822662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96700191497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89502334594727</t>
+    <t xml:space="preserve">8.94300746917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91301727294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96700000762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89502429962158</t>
   </si>
   <si>
     <t xml:space="preserve">8.96100330352783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97299957275391</t>
+    <t xml:space="preserve">8.97299861907959</t>
   </si>
   <si>
     <t xml:space="preserve">8.95500564575195</t>
@@ -1247,97 +1247,97 @@
     <t xml:space="preserve">8.87103271484375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72348022460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68869495391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75107383728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60592174530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48955917358398</t>
+    <t xml:space="preserve">8.72348308563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68869400024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75107192993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60591983795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48956108093262</t>
   </si>
   <si>
     <t xml:space="preserve">8.24964237213135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20045757293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03611183166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08649635314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00852298736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06010437011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09969043731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17646503448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22205066680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22444820404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20525646209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2712345123291</t>
+    <t xml:space="preserve">8.2004566192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03611087799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0864953994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00852108001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0601053237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09968948364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17646312713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2220516204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22444915771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20525455474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27123355865479</t>
   </si>
   <si>
     <t xml:space="preserve">8.31441783905029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22565078735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14047622680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02411651611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99532508850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10568618774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14647579193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15247249603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22804641723633</t>
+    <t xml:space="preserve">8.22564792633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14047908782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02411556243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99532604217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10568809509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14647483825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15247344970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22804832458496</t>
   </si>
   <si>
     <t xml:space="preserve">8.29162788391113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45717144012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36000156402588</t>
+    <t xml:space="preserve">8.45717239379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3600025177002</t>
   </si>
   <si>
     <t xml:space="preserve">8.47516441345215</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54114246368408</t>
+    <t xml:space="preserve">8.54114437103271</t>
   </si>
   <si>
     <t xml:space="preserve">8.49915790557861</t>
@@ -1346,16 +1346,16 @@
     <t xml:space="preserve">8.46197032928467</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43198013305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51715183258057</t>
+    <t xml:space="preserve">8.43197917938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51715087890625</t>
   </si>
   <si>
     <t xml:space="preserve">8.49435901641846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56993389129639</t>
+    <t xml:space="preserve">8.56993293762207</t>
   </si>
   <si>
     <t xml:space="preserve">8.65630340576172</t>
@@ -1364,22 +1364,22 @@
     <t xml:space="preserve">8.73068046569824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91421890258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92981338500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9897928237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07736396789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13374519348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19492435455322</t>
+    <t xml:space="preserve">8.91421794891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92981624603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98979187011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07736301422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13374328613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19492340087891</t>
   </si>
   <si>
     <t xml:space="preserve">9.256103515625</t>
@@ -1388,7 +1388,7 @@
     <t xml:space="preserve">9.265700340271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40485572814941</t>
+    <t xml:space="preserve">9.40485382080078</t>
   </si>
   <si>
     <t xml:space="preserve">9.47443103790283</t>
@@ -1403,13 +1403,13 @@
     <t xml:space="preserve">9.64957237243652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61358547210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50681972503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69875431060791</t>
+    <t xml:space="preserve">9.61358451843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50682258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69875621795654</t>
   </si>
   <si>
     <t xml:space="preserve">9.69155883789062</t>
@@ -1418,88 +1418,88 @@
     <t xml:space="preserve">9.7167501449585</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78992748260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67356395721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80671977996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99505519866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73834228515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0082540512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84150695800781</t>
+    <t xml:space="preserve">9.78992462158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67356491088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80672073364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99505615234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73834133148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0082550048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84150886535645</t>
   </si>
   <si>
     <t xml:space="preserve">9.86070156097412</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0022563934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0550384521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91948223114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95787048339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92788028717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84920406341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89714527130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78773784637451</t>
+    <t xml:space="preserve">10.002254486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0550365447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91948413848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95786952972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92787933349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84920310974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89714813232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78773880004883</t>
   </si>
   <si>
     <t xml:space="preserve">9.697998046875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45705413818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26528072357178</t>
+    <t xml:space="preserve">9.45705509185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26528167724609</t>
   </si>
   <si>
     <t xml:space="preserve">9.27757549285889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52097988128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66972541809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57998371124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4976224899292</t>
+    <t xml:space="preserve">9.5209789276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66972637176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57998657226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49762058258057</t>
   </si>
   <si>
     <t xml:space="preserve">9.49639320373535</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60702991485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35748291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6303882598877</t>
+    <t xml:space="preserve">9.60703182220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35748195648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63038730621338</t>
   </si>
   <si>
     <t xml:space="preserve">9.53450107574463</t>
@@ -1508,31 +1508,31 @@
     <t xml:space="preserve">9.72012615203857</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54679298400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55171203613281</t>
+    <t xml:space="preserve">9.54679489135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55171012878418</t>
   </si>
   <si>
     <t xml:space="preserve">9.48655891418457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31937408447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6107177734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3931303024292</t>
+    <t xml:space="preserve">9.31937313079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61071872711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39313125610352</t>
   </si>
   <si>
     <t xml:space="preserve">9.48532867431641</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74717044830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77913284301758</t>
+    <t xml:space="preserve">9.74717235565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77913379669189</t>
   </si>
   <si>
     <t xml:space="preserve">9.7766752243042</t>
@@ -1544,61 +1544,61 @@
     <t xml:space="preserve">9.93033790588379</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92419147491455</t>
+    <t xml:space="preserve">9.92419052124023</t>
   </si>
   <si>
     <t xml:space="preserve">9.9672155380249</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94509124755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0286827087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1602172851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98934555053711</t>
+    <t xml:space="preserve">9.94508934020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0286836624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1602182388306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98934459686279</t>
   </si>
   <si>
     <t xml:space="preserve">9.9942626953125</t>
   </si>
   <si>
-    <t xml:space="preserve">10.006555557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86764621734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91927433013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.918044090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88362503051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88731098175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91435813903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98074054718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97459316253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0249938964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95738220214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0102443695068</t>
+    <t xml:space="preserve">10.0065536499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86764335632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91927528381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91804599761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88362407684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88731288909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91435623168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98073959350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97459411621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0249929428101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95738315582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0102434158325</t>
   </si>
   <si>
     <t xml:space="preserve">10.1196508407593</t>
@@ -1607,7 +1607,7 @@
     <t xml:space="preserve">10.0446634292603</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95983982086182</t>
+    <t xml:space="preserve">9.95984077453613</t>
   </si>
   <si>
     <t xml:space="preserve">10.0139312744141</t>
@@ -1619,16 +1619,16 @@
     <t xml:space="preserve">10.1417779922485</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0717086791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80740737915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80863666534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90452289581299</t>
+    <t xml:space="preserve">10.0717077255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80740833282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80863761901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90452480316162</t>
   </si>
   <si>
     <t xml:space="preserve">9.78036308288574</t>
@@ -1640,70 +1640,70 @@
     <t xml:space="preserve">9.84182643890381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94140148162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0311441421509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97828006744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0803136825562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0999803543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0827713012695</t>
+    <t xml:space="preserve">9.94140243530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0311412811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97828197479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0803127288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0999841690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0827722549438</t>
   </si>
   <si>
     <t xml:space="preserve">9.82215976715088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88608551025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91067028045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80986499786377</t>
+    <t xml:space="preserve">9.88608264923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91066932678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8098669052124</t>
   </si>
   <si>
     <t xml:space="preserve">9.72750091552734</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66603851318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74225521087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76069259643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84551429748535</t>
+    <t xml:space="preserve">9.66603755950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74225234985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76069355010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84551620483398</t>
   </si>
   <si>
     <t xml:space="preserve">9.82707595825195</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82584953308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91558742523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0422039031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1928129196167</t>
+    <t xml:space="preserve">9.82584857940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9155855178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0422058105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1928148269653</t>
   </si>
   <si>
     <t xml:space="preserve">10.4401264190674</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4704084396362</t>
+    <t xml:space="preserve">10.4704093933105</t>
   </si>
   <si>
     <t xml:space="preserve">10.4300308227539</t>
@@ -1712,145 +1712,145 @@
     <t xml:space="preserve">10.2723064422607</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2962837219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3101606369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3316097259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2697830200195</t>
+    <t xml:space="preserve">10.2962799072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3101625442505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3316106796265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2697839736938</t>
   </si>
   <si>
     <t xml:space="preserve">10.2634763717651</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99723339080811</t>
+    <t xml:space="preserve">9.99723434448242</t>
   </si>
   <si>
     <t xml:space="preserve">10.2596883773804</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1915512084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91143321990967</t>
+    <t xml:space="preserve">10.1915521621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91143226623535</t>
   </si>
   <si>
     <t xml:space="preserve">9.85465240478516</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94423961639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9884033203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83194065093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6477165222168</t>
+    <t xml:space="preserve">9.94423770904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98840236663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83193969726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64771556854248</t>
   </si>
   <si>
     <t xml:space="preserve">9.70954513549805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57326889038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43194961547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28810405731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44709205627441</t>
+    <t xml:space="preserve">9.57326984405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4319486618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28810501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44708919525146</t>
   </si>
   <si>
     <t xml:space="preserve">9.54803466796875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69187831878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7070198059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90890789031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73225688934326</t>
+    <t xml:space="preserve">9.69188117980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70702075958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90891075134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73225593566895</t>
   </si>
   <si>
     <t xml:space="preserve">9.69061756134033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74866008758545</t>
+    <t xml:space="preserve">9.74865818023682</t>
   </si>
   <si>
     <t xml:space="preserve">9.67673778533936</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86348438262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82563209533691</t>
+    <t xml:space="preserve">9.86348533630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82562923431396</t>
   </si>
   <si>
     <t xml:space="preserve">9.75118446350098</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77137279510498</t>
+    <t xml:space="preserve">9.7713737487793</t>
   </si>
   <si>
     <t xml:space="preserve">9.5568675994873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41680717468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44835186004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40040397644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28684329986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11776065826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22880077362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03195858001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87044811248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01934051513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95498847961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92975234985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96886825561523</t>
+    <t xml:space="preserve">9.4168062210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44835090637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40040493011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28684425354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11775970458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22879886627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03195953369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87044906616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01934146881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95498943328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92975330352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96886920928955</t>
   </si>
   <si>
     <t xml:space="preserve">8.98779678344727</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15561294555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09378623962402</t>
+    <t xml:space="preserve">9.15561389923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09378528594971</t>
   </si>
   <si>
     <t xml:space="preserve">9.0155553817749</t>
@@ -1859,37 +1859,37 @@
     <t xml:space="preserve">8.72786331176758</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90451526641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79473781585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87423133850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98148632049561</t>
+    <t xml:space="preserve">8.90451622009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7947416305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87423419952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98148822784424</t>
   </si>
   <si>
     <t xml:space="preserve">8.99789047241211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92596626281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80735969543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71524620056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80104732513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72282028198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69000911712646</t>
+    <t xml:space="preserve">8.9259672164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80735778808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71524715423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80105018615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72281932830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69001197814941</t>
   </si>
   <si>
     <t xml:space="preserve">8.52976226806641</t>
@@ -1898,100 +1898,100 @@
     <t xml:space="preserve">8.67360782623291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69379425048828</t>
+    <t xml:space="preserve">8.69379711151123</t>
   </si>
   <si>
     <t xml:space="preserve">8.73165035247803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04710006713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96760845184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91209030151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99410343170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98527240753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93984699249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90830039978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99032115936279</t>
+    <t xml:space="preserve">9.0471019744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96760749816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91208648681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99410724639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98527050018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93984508514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90830230712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99032020568848</t>
   </si>
   <si>
     <t xml:space="preserve">9.00924587249756</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97013092041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21618175506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1770658493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13290119171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09504985809326</t>
+    <t xml:space="preserve">8.97012996673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21618270874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17706489562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13290405273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09504795074463</t>
   </si>
   <si>
     <t xml:space="preserve">9.19346809387207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10514354705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16192245483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23889636993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34109973907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31964778900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32848072052002</t>
+    <t xml:space="preserve">9.10514068603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16192531585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23889350891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34109878540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3196496963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32848167419434</t>
   </si>
   <si>
     <t xml:space="preserve">9.42564010620117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.375168800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16949462890625</t>
+    <t xml:space="preserve">9.37516784667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16949653625488</t>
   </si>
   <si>
     <t xml:space="preserve">9.15813732147217</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24267864227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3095531463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37264347076416</t>
+    <t xml:space="preserve">9.24267768859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30955219268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37264442443848</t>
   </si>
   <si>
     <t xml:space="preserve">9.3246955871582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53919982910156</t>
+    <t xml:space="preserve">9.53920269012451</t>
   </si>
   <si>
     <t xml:space="preserve">9.5745325088501</t>
@@ -2003,43 +2003,43 @@
     <t xml:space="preserve">9.62248134613037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63383674621582</t>
+    <t xml:space="preserve">9.63383769989014</t>
   </si>
   <si>
     <t xml:space="preserve">9.64519214630127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59724426269531</t>
+    <t xml:space="preserve">9.597243309021</t>
   </si>
   <si>
     <t xml:space="preserve">9.59598445892334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60355377197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56822395324707</t>
+    <t xml:space="preserve">9.60355281829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56822490692139</t>
   </si>
   <si>
     <t xml:space="preserve">9.48746871948242</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53289318084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5795783996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64014434814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4433069229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54046440124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56695938110352</t>
+    <t xml:space="preserve">9.53289222717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57957935333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64014625549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44330406188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5404634475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56696128845215</t>
   </si>
   <si>
     <t xml:space="preserve">9.80670261383057</t>
@@ -2048,19 +2048,19 @@
     <t xml:space="preserve">9.80291843414307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8344612121582</t>
+    <t xml:space="preserve">9.83446311950684</t>
   </si>
   <si>
     <t xml:space="preserve">9.93288421630859</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0249948501587</t>
+    <t xml:space="preserve">10.024995803833</t>
   </si>
   <si>
     <t xml:space="preserve">9.95307159423828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98714065551758</t>
+    <t xml:space="preserve">9.98714256286621</t>
   </si>
   <si>
     <t xml:space="preserve">9.90512275695801</t>
@@ -2069,37 +2069,37 @@
     <t xml:space="preserve">9.8571720123291</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85212898254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83572196960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76632404327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93919277191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96190452575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0338268280029</t>
+    <t xml:space="preserve">9.85212707519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83572483062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76632690429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93919086456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96190357208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0338277816772</t>
   </si>
   <si>
     <t xml:space="preserve">9.94045543670654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99849605560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97704601287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0237331390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0565395355225</t>
+    <t xml:space="preserve">9.99849700927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97704696655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0237321853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0565404891968</t>
   </si>
   <si>
     <t xml:space="preserve">10.046443939209</t>
@@ -2117,28 +2117,28 @@
     <t xml:space="preserve">9.73604202270508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96695232391357</t>
+    <t xml:space="preserve">9.96695137023926</t>
   </si>
   <si>
     <t xml:space="preserve">9.8104887008667</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78272914886475</t>
+    <t xml:space="preserve">9.78272819519043</t>
   </si>
   <si>
     <t xml:space="preserve">9.67926216125488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52532196044922</t>
+    <t xml:space="preserve">9.52532291412354</t>
   </si>
   <si>
     <t xml:space="preserve">9.60103034973145</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48494338989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51901149749756</t>
+    <t xml:space="preserve">9.48494434356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51901340484619</t>
   </si>
   <si>
     <t xml:space="preserve">9.38273906707764</t>
@@ -2147,76 +2147,76 @@
     <t xml:space="preserve">9.1417350769043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13542652130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03700733184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00041389465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09883499145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21365928649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15940093994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30576992034912</t>
+    <t xml:space="preserve">9.13542556762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03700542449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00041580200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09883308410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21365737915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15939712524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3057689666748</t>
   </si>
   <si>
     <t xml:space="preserve">9.36254978179932</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35346603393555</t>
+    <t xml:space="preserve">9.35346508026123</t>
   </si>
   <si>
     <t xml:space="preserve">9.43392086029053</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35476398468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03164958953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11859035491943</t>
+    <t xml:space="preserve">9.35476207733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03164863586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11859130859375</t>
   </si>
   <si>
     <t xml:space="preserve">9.12897300720215</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10042381286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91096687316895</t>
+    <t xml:space="preserve">9.10042285919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91096591949463</t>
   </si>
   <si>
     <t xml:space="preserve">8.88371849060059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8110466003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96676540374756</t>
+    <t xml:space="preserve">8.81104850769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96676635742188</t>
   </si>
   <si>
     <t xml:space="preserve">9.09523487091064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99791049957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01867198944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05760288238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0835542678833</t>
+    <t xml:space="preserve">8.99790859222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0186710357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0576000213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08355522155762</t>
   </si>
   <si>
     <t xml:space="preserve">9.11339855194092</t>
@@ -2228,76 +2228,76 @@
     <t xml:space="preserve">9.04722118377686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99920749664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18477249145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2275915145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31583404541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47674083709717</t>
+    <t xml:space="preserve">8.99920654296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18477058410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22759437561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31583499908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47674179077148</t>
   </si>
   <si>
     <t xml:space="preserve">9.42224216461182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36903762817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41315841674805</t>
+    <t xml:space="preserve">9.36903858184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41315937042236</t>
   </si>
   <si>
     <t xml:space="preserve">9.38590717315674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49880313873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40667152404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45208644866943</t>
+    <t xml:space="preserve">9.49880409240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40666961669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45208740234375</t>
   </si>
   <si>
     <t xml:space="preserve">9.50269603729248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44040775299072</t>
+    <t xml:space="preserve">9.44041156768799</t>
   </si>
   <si>
     <t xml:space="preserve">9.50788688659668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54162693023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.602614402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61948490142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54551696777344</t>
+    <t xml:space="preserve">9.54162406921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60261535644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61948299407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54551982879639</t>
   </si>
   <si>
     <t xml:space="preserve">9.5156717300415</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35216617584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2782039642334</t>
+    <t xml:space="preserve">9.35216808319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27820014953613</t>
   </si>
   <si>
     <t xml:space="preserve">9.22629642486572</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28858280181885</t>
+    <t xml:space="preserve">9.28858470916748</t>
   </si>
   <si>
     <t xml:space="preserve">9.33659744262695</t>
@@ -2306,55 +2306,55 @@
     <t xml:space="preserve">9.31064319610596</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30285739898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24446296691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14454364776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21591377258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14584255218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87593173980713</t>
+    <t xml:space="preserve">9.3028564453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24446392059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14454460144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21591567993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14584064483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87593078613281</t>
   </si>
   <si>
     <t xml:space="preserve">8.74616718292236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68387985229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56060314178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71631908416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55930519104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54502868652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70723533630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50091075897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46068286895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61250782012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52816009521484</t>
+    <t xml:space="preserve">8.68387699127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56060123443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7163200378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55930423736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54503154754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70723628997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50090980529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4606819152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61250686645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52816295623779</t>
   </si>
   <si>
     <t xml:space="preserve">8.6618185043335</t>
@@ -2366,142 +2366,142 @@
     <t xml:space="preserve">8.52686214447021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57617378234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63067626953125</t>
+    <t xml:space="preserve">8.57617092132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63067436218262</t>
   </si>
   <si>
     <t xml:space="preserve">8.69425964355469</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83570384979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89669418334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82532119750977</t>
+    <t xml:space="preserve">8.83570289611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89669227600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82532215118408</t>
   </si>
   <si>
     <t xml:space="preserve">8.86944389343262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93432521820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03294658660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14973545074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13156890869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11210250854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28728675842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18217658996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29377460479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4417085647583</t>
+    <t xml:space="preserve">8.93432426452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03294563293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14973640441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13156795501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11210155487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28728485107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1821756362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29377365112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44170475006104</t>
   </si>
   <si>
     <t xml:space="preserve">9.45374202728271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35746479034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26787662506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31601238250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39624309539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38287353515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34676742553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06328868865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96433734893799</t>
+    <t xml:space="preserve">9.35746383666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26787567138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31601333618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39624214172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3828706741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34676647186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06328964233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96434020996094</t>
   </si>
   <si>
     <t xml:space="preserve">9.05526542663574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12747383117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04858016967773</t>
+    <t xml:space="preserve">9.12747192382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04857921600342</t>
   </si>
   <si>
     <t xml:space="preserve">9.09270763397217</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14752960205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25049304962158</t>
+    <t xml:space="preserve">9.14753246307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25049209594727</t>
   </si>
   <si>
     <t xml:space="preserve">9.18898296356201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25182914733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23712062835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21305084228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32938385009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40827465057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45240211486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38688182830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31868743896484</t>
+    <t xml:space="preserve">9.2518310546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23711967468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21305179595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32938480377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40827751159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45240306854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38688087463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31868648529053</t>
   </si>
   <si>
     <t xml:space="preserve">9.24514293670654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15822887420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07264995574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16224002838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34275531768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49251937866211</t>
+    <t xml:space="preserve">9.15822601318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0726490020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16223907470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34275722503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49251747131348</t>
   </si>
   <si>
     <t xml:space="preserve">9.46978664398193</t>
@@ -2510,52 +2510,52 @@
     <t xml:space="preserve">9.47780895233154</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48717021942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45106506347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5299596786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48182106018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50722694396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43368339538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34008121490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36816310882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38821983337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39223194122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31467437744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28659534454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22642230987549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16892528533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07398509979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01247596740723</t>
+    <t xml:space="preserve">9.48716735839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45106410980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52995681762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48182010650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50722789764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43368244171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3400821685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36816215515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38822078704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39223098754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31467628479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28659725189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22642135620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16892433166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07398700714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01247787475586</t>
   </si>
   <si>
     <t xml:space="preserve">9.12212467193604</t>
@@ -2564,64 +2564,64 @@
     <t xml:space="preserve">9.20636558532715</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11008930206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13683223724365</t>
+    <t xml:space="preserve">9.11009120941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13683414459229</t>
   </si>
   <si>
     <t xml:space="preserve">9.08735847473145</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12613582611084</t>
+    <t xml:space="preserve">9.12613677978516</t>
   </si>
   <si>
     <t xml:space="preserve">9.09537887573242</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10875129699707</t>
+    <t xml:space="preserve">9.10875225067139</t>
   </si>
   <si>
     <t xml:space="preserve">9.16090202331543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23845767974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25717830657959</t>
+    <t xml:space="preserve">9.23845672607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25717735290527</t>
   </si>
   <si>
     <t xml:space="preserve">9.37083530426025</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36013984680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36548805236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43101024627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57141208648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57408428192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4978666305542</t>
+    <t xml:space="preserve">9.36013889312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36548709869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43100833892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5714111328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5740852355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49786853790283</t>
   </si>
   <si>
     <t xml:space="preserve">9.42699909210205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27589797973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22508430480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28525543212891</t>
+    <t xml:space="preserve">9.27589702606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22508525848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28525924682617</t>
   </si>
   <si>
     <t xml:space="preserve">9.30397796630859</t>
@@ -2630,61 +2630,61 @@
     <t xml:space="preserve">9.28124523162842</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06462574005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99776744842529</t>
+    <t xml:space="preserve">9.06462478637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99776935577393</t>
   </si>
   <si>
     <t xml:space="preserve">9.00579166412354</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82259941101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95765209197998</t>
+    <t xml:space="preserve">8.82260036468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95765399932861</t>
   </si>
   <si>
     <t xml:space="preserve">8.88410949707031</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64208221435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46290397644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43080997467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54981899261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71027660369873</t>
+    <t xml:space="preserve">8.64208030700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46290111541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43081283569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54981708526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71027755737305</t>
   </si>
   <si>
     <t xml:space="preserve">8.67150020599365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62871074676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54447078704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75841617584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68353652954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61935043334961</t>
+    <t xml:space="preserve">8.62871170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54446983337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75841808319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68353462219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61935234069824</t>
   </si>
   <si>
     <t xml:space="preserve">8.63138580322266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65010356903076</t>
+    <t xml:space="preserve">8.65010452270508</t>
   </si>
   <si>
     <t xml:space="preserve">8.62470054626465</t>
@@ -2699,22 +2699,22 @@
     <t xml:space="preserve">8.00693035125732</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06576633453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86118030548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46003198623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43328762054443</t>
+    <t xml:space="preserve">8.06576538085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8611798286438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46002960205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43328857421875</t>
   </si>
   <si>
     <t xml:space="preserve">7.43462419509888</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45601844787598</t>
+    <t xml:space="preserve">7.45602035522461</t>
   </si>
   <si>
     <t xml:space="preserve">7.33300018310547</t>
@@ -2726,7 +2726,7 @@
     <t xml:space="preserve">5.4155101776123</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45896768569946</t>
+    <t xml:space="preserve">5.45896673202515</t>
   </si>
   <si>
     <t xml:space="preserve">5.38208055496216</t>
@@ -2735,94 +2735,94 @@
     <t xml:space="preserve">4.40728855133057</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62056541442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34042978286743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59048080444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47548294067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6566686630249</t>
+    <t xml:space="preserve">4.62056636810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34043025970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59047937393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4754843711853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65666913986206</t>
   </si>
   <si>
     <t xml:space="preserve">4.8759651184082</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87195205688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59936904907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83203458786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82401275634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49373292922974</t>
+    <t xml:space="preserve">4.87195301055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59936809539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83203506469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8240122795105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49373340606689</t>
   </si>
   <si>
     <t xml:space="preserve">5.74511957168579</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16432094573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15094804763794</t>
+    <t xml:space="preserve">6.16432046890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15094947814941</t>
   </si>
   <si>
     <t xml:space="preserve">6.57750368118286</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23452091217041</t>
+    <t xml:space="preserve">6.23452138900757</t>
   </si>
   <si>
     <t xml:space="preserve">6.22783422470093</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30338621139526</t>
+    <t xml:space="preserve">6.30338430404663</t>
   </si>
   <si>
     <t xml:space="preserve">6.21446371078491</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22315645217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1288857460022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73776531219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65218639373779</t>
+    <t xml:space="preserve">6.22315549850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12888479232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73776483535767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65218687057495</t>
   </si>
   <si>
     <t xml:space="preserve">5.74110841751099</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6388144493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32190799713135</t>
+    <t xml:space="preserve">5.63881540298462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32190704345703</t>
   </si>
   <si>
     <t xml:space="preserve">5.58131694793701</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66422080993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51579618453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61875820159912</t>
+    <t xml:space="preserve">5.66422033309937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51579570770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6187572479248</t>
   </si>
   <si>
     <t xml:space="preserve">5.8059606552124</t>
@@ -2837,106 +2837,106 @@
     <t xml:space="preserve">5.48972177505493</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8079662322998</t>
+    <t xml:space="preserve">5.80796575546265</t>
   </si>
   <si>
     <t xml:space="preserve">5.63146066665649</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72038173675537</t>
+    <t xml:space="preserve">5.72038221359253</t>
   </si>
   <si>
     <t xml:space="preserve">5.77052545547485</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69965553283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69230127334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69631242752075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09554624557495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90332269668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93500900268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78925704956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75545883178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8160138130188</t>
+    <t xml:space="preserve">5.69965600967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69230175018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69631338119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09554815292358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90332317352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93500804901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78925657272339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75545930862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81601285934448</t>
   </si>
   <si>
     <t xml:space="preserve">5.82587099075317</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94979476928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97936820983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71954822540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87234258651733</t>
+    <t xml:space="preserve">5.94979524612427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97936725616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71954965591431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87234210968018</t>
   </si>
   <si>
     <t xml:space="preserve">6.17581796646118</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33635520935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31171178817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69334173202515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80459451675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60180997848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49900770187378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04203462600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04625988006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04133033752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29129409790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26383352279663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22088050842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24834108352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19834899902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9652853012085</t>
+    <t xml:space="preserve">6.33635425567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31171274185181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69334316253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80459499359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60180902481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49900722503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04203510284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04625940322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04133081436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29129314422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.263831615448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22088098526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24834060668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1983494758606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96528577804565</t>
   </si>
   <si>
     <t xml:space="preserve">5.97162294387817</t>
@@ -2945,7 +2945,7 @@
     <t xml:space="preserve">5.91247749328613</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07301664352417</t>
+    <t xml:space="preserve">6.07301473617554</t>
   </si>
   <si>
     <t xml:space="preserve">5.97796010971069</t>
@@ -2954,118 +2954,118 @@
     <t xml:space="preserve">5.96739864349365</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13990688323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1075177192688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16666412353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21031951904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12441682815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93852853775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09766101837158</t>
+    <t xml:space="preserve">6.1399073600769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10751724243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.166663646698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21031856536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12441730499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93852949142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09766054153442</t>
   </si>
   <si>
     <t xml:space="preserve">6.18426704406738</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22158479690552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26312971115112</t>
+    <t xml:space="preserve">6.2215838432312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26312828063965</t>
   </si>
   <si>
     <t xml:space="preserve">6.20539045333862</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18285942077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28706741333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1307520866394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05611705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99908399581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95894956588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96880722045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.921630859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50479316711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30975294113159</t>
+    <t xml:space="preserve">6.18285799026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28706789016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13075351715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05611753463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99908494949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95894861221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96880674362183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92163038253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50479364395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30975246429443</t>
   </si>
   <si>
     <t xml:space="preserve">5.30482387542725</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53366184234619</t>
+    <t xml:space="preserve">5.53366231918335</t>
   </si>
   <si>
     <t xml:space="preserve">5.70053720474243</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59210348129272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4963436126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62308359146118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80474758148193</t>
+    <t xml:space="preserve">5.59210395812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49634313583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62308502197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80474853515625</t>
   </si>
   <si>
     <t xml:space="preserve">5.89557838439941</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80545043945312</t>
+    <t xml:space="preserve">5.80545091629028</t>
   </si>
   <si>
     <t xml:space="preserve">5.75897884368896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70335483551025</t>
+    <t xml:space="preserve">5.7033543586731</t>
   </si>
   <si>
     <t xml:space="preserve">5.67096471786499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72307062149048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58717489242554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54351949691772</t>
+    <t xml:space="preserve">5.723069190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58717441558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54351902008057</t>
   </si>
   <si>
     <t xml:space="preserve">5.76742887496948</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68786334991455</t>
+    <t xml:space="preserve">5.68786430358887</t>
   </si>
   <si>
     <t xml:space="preserve">5.60618591308594</t>
@@ -3077,91 +3077,91 @@
     <t xml:space="preserve">5.47522020339966</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40480852127075</t>
+    <t xml:space="preserve">5.40480804443359</t>
   </si>
   <si>
     <t xml:space="preserve">5.41889095306396</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38297986984253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47310781478882</t>
+    <t xml:space="preserve">5.382981300354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47310829162598</t>
   </si>
   <si>
     <t xml:space="preserve">5.29426145553589</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37101030349731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3696026802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3505916595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26398420333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35974407196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38720560073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34707117080688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20202255249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97441530227661</t>
+    <t xml:space="preserve">5.37101078033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36960315704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35059118270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26398468017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35974550247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38720512390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34707069396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20202207565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97441577911377</t>
   </si>
   <si>
     <t xml:space="preserve">5.05028438568115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95866966247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87564277648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78760766983032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90999841690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7704291343689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7868914604187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62513303756714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65018463134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78832292556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9515118598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8169527053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92789268493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91143035888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88065338134766</t>
+    <t xml:space="preserve">4.95866918563843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87564325332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78760623931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90999937057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77042865753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78689098358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62513256072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6501841545105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78832244873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95151233673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81695318222046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92789316177368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91143131256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88065385818481</t>
   </si>
   <si>
     <t xml:space="preserve">4.78546047210693</t>
@@ -3176,40 +3176,40 @@
     <t xml:space="preserve">4.69742298126221</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71388483047485</t>
+    <t xml:space="preserve">4.71388530731201</t>
   </si>
   <si>
     <t xml:space="preserve">4.6967077255249</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53781318664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53852891921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61224985122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4698166847229</t>
+    <t xml:space="preserve">4.53781223297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53852844238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61225080490112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46981763839722</t>
   </si>
   <si>
     <t xml:space="preserve">4.36603450775146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21215057373047</t>
+    <t xml:space="preserve">4.21214962005615</t>
   </si>
   <si>
     <t xml:space="preserve">4.23576879501343</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30233287811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55355882644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66235256195068</t>
+    <t xml:space="preserve">4.30233383178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55355930328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66235113143921</t>
   </si>
   <si>
     <t xml:space="preserve">4.72175884246826</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">4.7210431098938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68239212036133</t>
+    <t xml:space="preserve">4.68239259719849</t>
   </si>
   <si>
     <t xml:space="preserve">5.28075408935547</t>
@@ -3230,31 +3230,31 @@
     <t xml:space="preserve">5.43392324447632</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45253276824951</t>
+    <t xml:space="preserve">5.45253229141235</t>
   </si>
   <si>
     <t xml:space="preserve">5.48259353637695</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70304346084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78750038146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86479997634888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78105878829956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81541442871094</t>
+    <t xml:space="preserve">5.70304250717163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7875018119812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86480093002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78105783462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81541395187378</t>
   </si>
   <si>
     <t xml:space="preserve">5.96214246749878</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16970777511597</t>
+    <t xml:space="preserve">6.16970729827881</t>
   </si>
   <si>
     <t xml:space="preserve">6.2069263458252</t>
@@ -3269,610 +3269,610 @@
     <t xml:space="preserve">5.94281768798828</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02298021316528</t>
+    <t xml:space="preserve">6.02297973632812</t>
   </si>
   <si>
     <t xml:space="preserve">6.08310222625732</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04946279525757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25846147537231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27492237091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29138326644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32931900024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39588260650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30426645278931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21122121810913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2641863822937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26704883575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23484086990356</t>
+    <t xml:space="preserve">6.04946231842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.258460521698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27492189407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29138422012329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3293194770813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39588356018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30426597595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21122074127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26418590545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26704835891724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23484039306641</t>
   </si>
   <si>
     <t xml:space="preserve">6.17042350769043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9005880355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98361301422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14394044876099</t>
+    <t xml:space="preserve">5.90058851242065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98361444473267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14393997192383</t>
   </si>
   <si>
     <t xml:space="preserve">6.15252923965454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12819480895996</t>
+    <t xml:space="preserve">6.12819528579712</t>
   </si>
   <si>
     <t xml:space="preserve">6.11817455291748</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04659938812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27062702178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47604560852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49035978317261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4631609916687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42594337463379</t>
+    <t xml:space="preserve">6.04659986495972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27062606811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47604513168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49036121368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46316242218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42594385147095</t>
   </si>
   <si>
     <t xml:space="preserve">6.4803409576416</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48463582992554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44526720046997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32072877883911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33862257003784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31786584854126</t>
+    <t xml:space="preserve">6.48463487625122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44526863098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32073068618774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33862352371216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31786632537842</t>
   </si>
   <si>
     <t xml:space="preserve">6.37083101272583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20406341552734</t>
+    <t xml:space="preserve">6.20406198501587</t>
   </si>
   <si>
     <t xml:space="preserve">6.11387920379639</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97860431671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10385942459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1174578666687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97788763046265</t>
+    <t xml:space="preserve">5.97860336303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10385894775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11745882034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97788906097412</t>
   </si>
   <si>
     <t xml:space="preserve">5.86909484863281</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94854307174683</t>
+    <t xml:space="preserve">5.94854211807251</t>
   </si>
   <si>
     <t xml:space="preserve">6.07594537734985</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13392019271851</t>
+    <t xml:space="preserve">6.13392066955566</t>
   </si>
   <si>
     <t xml:space="preserve">6.16326570510864</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21336650848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28064870834351</t>
+    <t xml:space="preserve">6.21336841583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28064727783203</t>
   </si>
   <si>
     <t xml:space="preserve">6.33003330230713</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28208017349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35508394241333</t>
+    <t xml:space="preserve">6.28207874298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35508489608765</t>
   </si>
   <si>
     <t xml:space="preserve">6.52972602844238</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49823474884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55835580825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51111698150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58340692520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69649505615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74516487121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85467481613159</t>
+    <t xml:space="preserve">6.49823522567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55835628509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51111650466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58340740203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69649457931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74516582489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85467338562012</t>
   </si>
   <si>
     <t xml:space="preserve">6.92839622497559</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78667879104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84322309494019</t>
+    <t xml:space="preserve">6.78667783737183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84322023391724</t>
   </si>
   <si>
     <t xml:space="preserve">6.79383516311646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91408014297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06868171691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20180988311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28626728057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25763750076294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3148980140686</t>
+    <t xml:space="preserve">6.91408061981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06868124008179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20181083679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28626775741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25763607025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31489610671997</t>
   </si>
   <si>
     <t xml:space="preserve">7.37215709686279</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45661401748657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39649105072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3292121887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39935493469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28197288513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26193046569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14311790466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33350610733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23759651184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32348728179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40650939941406</t>
+    <t xml:space="preserve">7.45661449432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3964900970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32921075820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39935302734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28197240829468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2619309425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14311838150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33350706100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23759794235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32348585128784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40651178359985</t>
   </si>
   <si>
     <t xml:space="preserve">7.45231962203979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51100921630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56540584564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49669456481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48381090164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34352540969849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30058240890503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27338361740112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31919193267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50671720504761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41796445846558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40794515609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38933420181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21040010452271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26479387283325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27767753601074</t>
+    <t xml:space="preserve">7.51101112365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56540679931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49669599533081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48381233215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3435263633728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30058193206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27338218688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31919097900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50671482086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4179630279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40794324874878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3893346786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2103967666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26479530334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27767848968506</t>
   </si>
   <si>
     <t xml:space="preserve">7.23043918609619</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26336336135864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23616409301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30344486236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30201292037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10733079910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22900629043579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37788248062134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39076566696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38647031784058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44945764541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48524284362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37501859664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46520280838013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48953914642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46806526184082</t>
+    <t xml:space="preserve">7.26336193084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23616504669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30344438552856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30201387405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10733222961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22900772094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37788057327271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39076662063599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38647127151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44945621490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48524379730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3750205039978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46520233154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48953866958618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46806573867798</t>
   </si>
   <si>
     <t xml:space="preserve">7.2977180480957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36070346832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40907192230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31746578216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3504433631897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40174293518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39734745025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36949825286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54391527175903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59961271286011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65091037750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60694122314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66117191314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69195032119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65384197235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70514297485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75497531890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8619704246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86636972427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.872230052948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79015302658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55857181549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63478946685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63185739517212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63772058486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72419738769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73592281341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57909250259399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57616090774536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52632808685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66556835174561</t>
+    <t xml:space="preserve">7.36070489883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4090723991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31746673583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35044527053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40174341201782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39734601974487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36949920654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54391574859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59961318969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6509108543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60694074630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66117143630981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69195079803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65384292602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7051420211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75497484207153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86197090148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86636686325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87223100662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79015254974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55857229232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63478994369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63185882568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63771867752075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.724196434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73591995239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57909202575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57616233825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5263295173645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66556930541992</t>
   </si>
   <si>
     <t xml:space="preserve">7.6201319694519</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6626353263855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45304346084595</t>
+    <t xml:space="preserve">7.66263914108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45304441452026</t>
   </si>
   <si>
     <t xml:space="preserve">7.30134439468384</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38708686828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33138990402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34604787826538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2625036239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20534181594849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92832660675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96423435211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14524793624878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06756448745728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08588790893555</t>
+    <t xml:space="preserve">7.38708639144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33139085769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34604835510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26250171661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20534038543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92832612991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96423387527466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14524841308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06756591796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08588743209839</t>
   </si>
   <si>
     <t xml:space="preserve">7.23025846481323</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18775367736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26763200759888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33871936798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30794095993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42812633514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41640043258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47503042221069</t>
+    <t xml:space="preserve">7.18775224685669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26763343811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3387188911438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30793857574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42812776565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41640186309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47502851486206</t>
   </si>
   <si>
     <t xml:space="preserve">7.54977893829346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53658676147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58495664596558</t>
+    <t xml:space="preserve">7.53658723831177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58495569229126</t>
   </si>
   <si>
     <t xml:space="preserve">7.63332414627075</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67875909805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70807409286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60107755661011</t>
+    <t xml:space="preserve">7.67876052856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70807313919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60107803344727</t>
   </si>
   <si>
     <t xml:space="preserve">7.60401058197021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59668064117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38415431976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37389659881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49994373321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56150341033936</t>
+    <t xml:space="preserve">7.59668111801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38415765762329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37389707565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49994421005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56150436401367</t>
   </si>
   <si>
     <t xml:space="preserve">7.5702977180481</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55270862579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64211797714233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64504718780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79161643981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71686840057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75790739059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7608380317688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72712659835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91913223266602</t>
+    <t xml:space="preserve">7.55270957946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64211845397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64504909515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79161834716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71686601638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75790786743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76083755493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72712564468384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91913414001465</t>
   </si>
   <si>
     <t xml:space="preserve">7.99095296859741</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05397701263428</t>
+    <t xml:space="preserve">8.05397510528564</t>
   </si>
   <si>
     <t xml:space="preserve">8.07889461517334</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01879978179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94404363632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0905065536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30409526824951</t>
+    <t xml:space="preserve">8.01880073547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94404268264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09050559997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30409336090088</t>
   </si>
   <si>
     <t xml:space="preserve">8.3163013458252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.339186668396</t>
+    <t xml:space="preserve">8.33918571472168</t>
   </si>
   <si>
     <t xml:space="preserve">8.53294372558594</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59244346618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68703365325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80755805969238</t>
+    <t xml:space="preserve">8.59244441986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68703460693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80755996704102</t>
   </si>
   <si>
     <t xml:space="preserve">8.75873947143555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88079071044922</t>
+    <t xml:space="preserve">8.8807897567749</t>
   </si>
   <si>
     <t xml:space="preserve">9.03793239593506</t>
@@ -3881,10 +3881,10 @@
     <t xml:space="preserve">8.89909934997559</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83959770202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04555988311768</t>
+    <t xml:space="preserve">8.83959865570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04555892944336</t>
   </si>
   <si>
     <t xml:space="preserve">9.15845680236816</t>
@@ -3893,157 +3893,157 @@
     <t xml:space="preserve">9.13404846191406</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01809692382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13862609863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31254959106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33390808105469</t>
+    <t xml:space="preserve">9.01809883117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1386251449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31254768371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33390712738037</t>
   </si>
   <si>
     <t xml:space="preserve">9.28508758544922</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39645957946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25609970092773</t>
+    <t xml:space="preserve">9.39645862579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25609874725342</t>
   </si>
   <si>
     <t xml:space="preserve">9.21338176727295</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36594581604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42697238922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35831642150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27898502349854</t>
+    <t xml:space="preserve">9.36594772338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42697143554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35831832885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2789831161499</t>
   </si>
   <si>
     <t xml:space="preserve">9.46206188201904</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72294902801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56580448150635</t>
+    <t xml:space="preserve">9.72294807434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56580543518066</t>
   </si>
   <si>
     <t xml:space="preserve">9.44375419616699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58106231689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66649723052979</t>
+    <t xml:space="preserve">9.58106327056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6664981842041</t>
   </si>
   <si>
     <t xml:space="preserve">9.67412757873535</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62683296203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66039562225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64666652679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54444885253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57038402557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61004829406738</t>
+    <t xml:space="preserve">9.62683200836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66039657592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6466646194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54444789886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5703821182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61004734039307</t>
   </si>
   <si>
     <t xml:space="preserve">9.60547351837158</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48189449310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28203773498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40408897399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43612575531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37967586517334</t>
+    <t xml:space="preserve">9.48189544677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28203582763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40408802032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43612766265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37967777252197</t>
   </si>
   <si>
     <t xml:space="preserve">8.79535388946533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00131893157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08065223693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10811138153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16150951385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37662601470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5871639251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45138359069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35679054260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31102561950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1691370010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26677894592285</t>
+    <t xml:space="preserve">9.00131607055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08065032958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10811233520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16150856018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37662792205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58716583251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45138263702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35679244995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3110237121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16913795471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26677799224854</t>
   </si>
   <si>
     <t xml:space="preserve">9.15388202667236</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30491924285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19354724884033</t>
+    <t xml:space="preserve">9.30492305755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19354915618896</t>
   </si>
   <si>
     <t xml:space="preserve">9.02725315093994</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29119110107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28661346435547</t>
+    <t xml:space="preserve">9.29118919372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28661251068115</t>
   </si>
   <si>
     <t xml:space="preserve">9.33695793151855</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37815284729004</t>
+    <t xml:space="preserve">9.37815093994141</t>
   </si>
   <si>
     <t xml:space="preserve">9.36747169494629</t>
@@ -4058,49 +4058,49 @@
     <t xml:space="preserve">9.61920261383057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73057556152344</t>
+    <t xml:space="preserve">9.73057651519775</t>
   </si>
   <si>
     <t xml:space="preserve">9.64971733093262</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75651168823242</t>
+    <t xml:space="preserve">9.75651359558105</t>
   </si>
   <si>
     <t xml:space="preserve">9.6756534576416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77176856994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95637226104736</t>
+    <t xml:space="preserve">9.77176761627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95637130737305</t>
   </si>
   <si>
     <t xml:space="preserve">9.93501281738281</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0387563705444</t>
+    <t xml:space="preserve">10.0387573242188</t>
   </si>
   <si>
     <t xml:space="preserve">10.0784244537354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1226692199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2370910644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1379232406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9975643157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67717838287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98841190338135</t>
+    <t xml:space="preserve">10.1226673126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2370891571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1379241943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99756336212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67717742919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98841094970703</t>
   </si>
   <si>
     <t xml:space="preserve">10.2859115600586</t>
@@ -4109,25 +4109,25 @@
     <t xml:space="preserve">10.5361185073853</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3545665740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1516542434692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2645530700684</t>
+    <t xml:space="preserve">10.3545637130737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1516551971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2645511627197</t>
   </si>
   <si>
     <t xml:space="preserve">10.1882696151733</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1363973617554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2828588485718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0585899353027</t>
+    <t xml:space="preserve">10.1363983154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2828598022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0585870742798</t>
   </si>
   <si>
     <t xml:space="preserve">9.944167137146</t>
@@ -4139,25 +4139,25 @@
     <t xml:space="preserve">10.1440258026123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3194742202759</t>
+    <t xml:space="preserve">10.3194751739502</t>
   </si>
   <si>
     <t xml:space="preserve">10.1638603210449</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0479097366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1714868545532</t>
+    <t xml:space="preserve">10.0479116439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1714878082275</t>
   </si>
   <si>
     <t xml:space="preserve">10.2752323150635</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1562309265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.292013168335</t>
+    <t xml:space="preserve">10.156231880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2920141220093</t>
   </si>
   <si>
     <t xml:space="preserve">10.2416667938232</t>
@@ -4166,79 +4166,79 @@
     <t xml:space="preserve">10.1928472518921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5117053985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5513744354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8717584609985</t>
+    <t xml:space="preserve">10.5117073059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5513725280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8717603683472</t>
   </si>
   <si>
     <t xml:space="preserve">11.0838251113892</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5773077011108</t>
+    <t xml:space="preserve">10.5773105621338</t>
   </si>
   <si>
     <t xml:space="preserve">9.80533218383789</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2264099121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4277963638306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3759241104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99603843688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89992141723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85873031616211</t>
+    <t xml:space="preserve">10.2264108657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4277982711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3759250640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99603939056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89992237091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85872936248779</t>
   </si>
   <si>
     <t xml:space="preserve">9.74125480651855</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0006151199341</t>
+    <t xml:space="preserve">10.0006160736084</t>
   </si>
   <si>
     <t xml:space="preserve">9.7092170715332</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0860500335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2706537246704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.124195098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98993492126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2081031799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1409730911255</t>
+    <t xml:space="preserve">10.0860509872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2706546783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1241941452026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98993682861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2081022262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1409759521484</t>
   </si>
   <si>
     <t xml:space="preserve">10.2325134277344</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2538719177246</t>
+    <t xml:space="preserve">10.2538728713989</t>
   </si>
   <si>
     <t xml:space="preserve">10.3042192459106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2126789093018</t>
+    <t xml:space="preserve">10.2126808166504</t>
   </si>
   <si>
     <t xml:space="preserve">10.1165637969971</t>
@@ -4247,16 +4247,16 @@
     <t xml:space="preserve">10.5406942367554</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5239124298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8122596740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8320932388306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7939519882202</t>
+    <t xml:space="preserve">10.5239114761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8122577667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8320941925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7939529418945</t>
   </si>
   <si>
     <t xml:space="preserve">10.8534517288208</t>
@@ -4265,55 +4265,55 @@
     <t xml:space="preserve">10.6795282363892</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3591423034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86330890655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88466548919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0372304916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.214204788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0692710876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.374397277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3057451248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3774509429932</t>
+    <t xml:space="preserve">10.3591413497925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86330795288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88466835021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0372314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2142086029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0692682266235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.374400138855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3057441711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3774518966675</t>
   </si>
   <si>
     <t xml:space="preserve">9.97620487213135</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1135120391846</t>
+    <t xml:space="preserve">10.1135129928589</t>
   </si>
   <si>
     <t xml:space="preserve">10.3896551132202</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4049139022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5467967987061</t>
+    <t xml:space="preserve">10.4049129486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5467977523804</t>
   </si>
   <si>
     <t xml:space="preserve">10.6276559829712</t>
   </si>
   <si>
-    <t xml:space="preserve">10.516284942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5956172943115</t>
+    <t xml:space="preserve">10.5162839889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5956182479858</t>
   </si>
   <si>
     <t xml:space="preserve">10.7955636978149</t>
@@ -4325,7 +4325,7 @@
     <t xml:space="preserve">11.1151647567749</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2143535614014</t>
+    <t xml:space="preserve">11.2143516540527</t>
   </si>
   <si>
     <t xml:space="preserve">11.1718444824219</t>
@@ -4334,10 +4334,10 @@
     <t xml:space="preserve">11.1781415939331</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1765661239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.097846031189</t>
+    <t xml:space="preserve">11.1765651702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0978469848633</t>
   </si>
   <si>
     <t xml:space="preserve">11.0773782730103</t>
@@ -4346,7 +4346,7 @@
     <t xml:space="preserve">11.2237987518311</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3607702255249</t>
+    <t xml:space="preserve">11.3607683181763</t>
   </si>
   <si>
     <t xml:space="preserve">11.3576211929321</t>
@@ -4355,31 +4355,31 @@
     <t xml:space="preserve">11.3292827606201</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0411701202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.422435760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2161893844604</t>
+    <t xml:space="preserve">11.0411682128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4224348068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2161903381348</t>
   </si>
   <si>
     <t xml:space="preserve">10.3673305511475</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4334564208984</t>
+    <t xml:space="preserve">10.4334545135498</t>
   </si>
   <si>
     <t xml:space="preserve">9.92335510253906</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45418834686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48095226287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50928974151611</t>
+    <t xml:space="preserve">9.45418643951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48095321655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50929355621338</t>
   </si>
   <si>
     <t xml:space="preserve">9.17866992950439</t>
@@ -4388,19 +4388,19 @@
     <t xml:space="preserve">8.99761581420898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18339157104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05271911621094</t>
+    <t xml:space="preserve">9.18339347839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0527172088623</t>
   </si>
   <si>
     <t xml:space="preserve">9.13301467895508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91732120513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83860206604004</t>
+    <t xml:space="preserve">8.91732215881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83860397338867</t>
   </si>
   <si>
     <t xml:space="preserve">9.05114459991455</t>
@@ -4409,46 +4409,46 @@
     <t xml:space="preserve">8.52687454223633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4670467376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69533252716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83702754974365</t>
+    <t xml:space="preserve">8.46704959869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69533443450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83702850341797</t>
   </si>
   <si>
     <t xml:space="preserve">8.81656169891357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76775741577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75043678283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37888240814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5315990447998</t>
+    <t xml:space="preserve">8.76775646209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75043773651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37888050079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53159809112549</t>
   </si>
   <si>
     <t xml:space="preserve">8.67014408111572</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89842891693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79609489440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6591215133667</t>
+    <t xml:space="preserve">8.89843082427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79609298706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65912342071533</t>
   </si>
   <si>
     <t xml:space="preserve">8.63550758361816</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70792961120605</t>
+    <t xml:space="preserve">8.70793056488037</t>
   </si>
   <si>
     <t xml:space="preserve">8.67486667633057</t>
@@ -4460,25 +4460,25 @@
     <t xml:space="preserve">9.22275352478027</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21173286437988</t>
+    <t xml:space="preserve">9.21173191070557</t>
   </si>
   <si>
     <t xml:space="preserve">9.00863742828369</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97399997711182</t>
+    <t xml:space="preserve">8.97400093078613</t>
   </si>
   <si>
     <t xml:space="preserve">8.96612930297852</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01808261871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01021289825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04642105102539</t>
+    <t xml:space="preserve">9.01808166503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01021194458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04642200469971</t>
   </si>
   <si>
     <t xml:space="preserve">8.99289131164551</t>
@@ -4487,10 +4487,10 @@
     <t xml:space="preserve">9.12356662750244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15505504608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11411952972412</t>
+    <t xml:space="preserve">9.15505599975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11412048339844</t>
   </si>
   <si>
     <t xml:space="preserve">9.20386028289795</t>
@@ -4499,85 +4499,85 @@
     <t xml:space="preserve">9.39436149597168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2652645111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41482925415039</t>
+    <t xml:space="preserve">9.26526260375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41482734680176</t>
   </si>
   <si>
     <t xml:space="preserve">9.76749038696289</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64626312255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84463596343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.695068359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83991241455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63209438323975</t>
+    <t xml:space="preserve">9.64626216888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84463310241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69506931304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83991050720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63209247589111</t>
   </si>
   <si>
     <t xml:space="preserve">9.29517459869385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23062419891357</t>
+    <t xml:space="preserve">9.23062515258789</t>
   </si>
   <si>
     <t xml:space="preserve">9.51401519775391</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67460155487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40853118896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14560890197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11726665496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19598960876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4022331237793</t>
+    <t xml:space="preserve">9.67460060119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40853023529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14560699462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11726951599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19598770141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40223217010498</t>
   </si>
   <si>
     <t xml:space="preserve">9.31721687316895</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29674816131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08420658111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94121551513672</t>
+    <t xml:space="preserve">9.29675102233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08420848846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94121742248535</t>
   </si>
   <si>
     <t xml:space="preserve">9.10174179077148</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66993045806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61535263061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62979793548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65708827972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75661277770996</t>
+    <t xml:space="preserve">8.66992855072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6153507232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62979888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65708923339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75661373138428</t>
   </si>
   <si>
     <t xml:space="preserve">9.02308368682861</t>
@@ -4586,40 +4586,40 @@
     <t xml:space="preserve">9.2622652053833</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40994834899902</t>
+    <t xml:space="preserve">9.40994739532471</t>
   </si>
   <si>
     <t xml:space="preserve">9.41476345062256</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5030517578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45649909973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28634452819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14668941497803</t>
+    <t xml:space="preserve">9.50305271148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45650100708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28634357452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14668560028076</t>
   </si>
   <si>
     <t xml:space="preserve">9.38105297088623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52231597900391</t>
+    <t xml:space="preserve">9.52231502532959</t>
   </si>
   <si>
     <t xml:space="preserve">9.52392101287842</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70691680908203</t>
+    <t xml:space="preserve">9.70691967010498</t>
   </si>
   <si>
     <t xml:space="preserve">9.67802333831787</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91560077667236</t>
+    <t xml:space="preserve">9.91559982299805</t>
   </si>
   <si>
     <t xml:space="preserve">9.88991641998291</t>
@@ -4628,16 +4628,16 @@
     <t xml:space="preserve">10.0199422836304</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3682813644409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.543251991272</t>
+    <t xml:space="preserve">10.3682804107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5432500839233</t>
   </si>
   <si>
     <t xml:space="preserve">10.63796043396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8065118789673</t>
+    <t xml:space="preserve">10.8065099716187</t>
   </si>
   <si>
     <t xml:space="preserve">10.8594837188721</t>
@@ -4646,19 +4646,19 @@
     <t xml:space="preserve">11.0119829177856</t>
   </si>
   <si>
-    <t xml:space="preserve">11.244743347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4518194198608</t>
+    <t xml:space="preserve">11.2447443008423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4518184661865</t>
   </si>
   <si>
     <t xml:space="preserve">11.4084777832031</t>
   </si>
   <si>
-    <t xml:space="preserve">11.254376411438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2928991317749</t>
+    <t xml:space="preserve">11.2543745040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2929000854492</t>
   </si>
   <si>
     <t xml:space="preserve">11.4598455429077</t>
@@ -4673,88 +4673,88 @@
     <t xml:space="preserve">11.5240564346313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3057413101196</t>
+    <t xml:space="preserve">11.3057432174683</t>
   </si>
   <si>
     <t xml:space="preserve">11.3876104354858</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9604120254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4560947418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5115299224854</t>
+    <t xml:space="preserve">10.960412979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4560928344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5115308761597</t>
   </si>
   <si>
     <t xml:space="preserve">11.5637083053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6566495895386</t>
+    <t xml:space="preserve">11.6566486358643</t>
   </si>
   <si>
     <t xml:space="preserve">11.428373336792</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5734901428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6778450012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4870738983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3256511688232</t>
+    <t xml:space="preserve">11.5734891891479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.677845954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4870719909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3256521224976</t>
   </si>
   <si>
     <t xml:space="preserve">11.2783641815186</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1218347549438</t>
+    <t xml:space="preserve">11.1218338012695</t>
   </si>
   <si>
     <t xml:space="preserve">10.9538888931274</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256338119507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0272636413574</t>
+    <t xml:space="preserve">11.025634765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0272626876831</t>
   </si>
   <si>
     <t xml:space="preserve">11.0941152572632</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2620601654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0957460403442</t>
+    <t xml:space="preserve">11.262059211731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0957441329956</t>
   </si>
   <si>
     <t xml:space="preserve">10.6391983032227</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5169067382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5902824401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5984354019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9750852584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9049739837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.986499786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0435676574707</t>
+    <t xml:space="preserve">10.5169076919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5902814865112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5984344482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9750862121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.904974937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9865007400513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.043568611145</t>
   </si>
   <si>
     <t xml:space="preserve">11.0125894546509</t>
@@ -4763,37 +4763,37 @@
     <t xml:space="preserve">11.0810708999634</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8315992355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1756391525269</t>
+    <t xml:space="preserve">10.831600189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1756410598755</t>
   </si>
   <si>
     <t xml:space="preserve">11.2392330169678</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0680265426636</t>
+    <t xml:space="preserve">11.0680255889893</t>
   </si>
   <si>
     <t xml:space="preserve">11.2816257476807</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3680448532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3925018310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6093626022339</t>
+    <t xml:space="preserve">11.3680438995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3925037384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6093635559082</t>
   </si>
   <si>
     <t xml:space="preserve">11.7528495788574</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7577381134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6811065673828</t>
+    <t xml:space="preserve">11.7577409744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6811046600342</t>
   </si>
   <si>
     <t xml:space="preserve">11.7169780731201</t>
@@ -4802,13 +4802,13 @@
     <t xml:space="preserve">11.7887201309204</t>
   </si>
   <si>
-    <t xml:space="preserve">11.620777130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7854595184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7398061752319</t>
+    <t xml:space="preserve">11.6207752227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7854614257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7398042678833</t>
   </si>
   <si>
     <t xml:space="preserve">11.5604467391968</t>
@@ -4820,19 +4820,19 @@
     <t xml:space="preserve">11.5751218795776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6517562866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5522937774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5245742797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2881488800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2098836898804</t>
+    <t xml:space="preserve">11.6517553329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5522928237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5245733261108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2881479263306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2098827362061</t>
   </si>
   <si>
     <t xml:space="preserve">11.2865180969238</t>
@@ -4847,76 +4847,76 @@
     <t xml:space="preserve">11.5441408157349</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6941509246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0251483917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0398216247559</t>
+    <t xml:space="preserve">11.694149017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.025146484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0398225784302</t>
   </si>
   <si>
     <t xml:space="preserve">12.0871076583862</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9762306213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9957990646362</t>
+    <t xml:space="preserve">11.9762287139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9957962036133</t>
   </si>
   <si>
     <t xml:space="preserve">11.658278465271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6990404129028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6321907043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5066375732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8902978897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7549657821655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9245386123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8968210220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7370309829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.878885269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.952260017395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0354175567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.942476272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9392166137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9180192947388</t>
+    <t xml:space="preserve">11.6990432739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6321887969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5066394805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8902997970581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7549667358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9245405197144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8968200683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7370300292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8788862228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9522609710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0354166030884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9424743652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9392156600952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9180183410645</t>
   </si>
   <si>
     <t xml:space="preserve">10.9489974975586</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5364742279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6310443878174</t>
+    <t xml:space="preserve">10.536473274231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6310453414917</t>
   </si>
   <si>
     <t xml:space="preserve">10.0359020233154</t>
@@ -4931,40 +4931,40 @@
     <t xml:space="preserve">10.3486499786377</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3602733612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3403472900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1062068939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2191276550293</t>
+    <t xml:space="preserve">10.3602743148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3403482437134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1062078475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.219126701355</t>
   </si>
   <si>
     <t xml:space="preserve">10.4167346954346</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5230102539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6990308761597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7156372070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.152364730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0510721206665</t>
+    <t xml:space="preserve">10.5230093002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6990299224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7156362533569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1523656845093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0510702133179</t>
   </si>
   <si>
     <t xml:space="preserve">11.1540260314941</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2420349121094</t>
+    <t xml:space="preserve">11.242036819458</t>
   </si>
   <si>
     <t xml:space="preserve">11.4446268081665</t>
@@ -4976,58 +4976,58 @@
     <t xml:space="preserve">11.5110473632812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4595708847046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5243320465088</t>
+    <t xml:space="preserve">11.4595699310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5243310928345</t>
   </si>
   <si>
     <t xml:space="preserve">11.5326356887817</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4197158813477</t>
+    <t xml:space="preserve">11.419716835022</t>
   </si>
   <si>
     <t xml:space="preserve">11.2785682678223</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4296817779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4728546142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3034763336182</t>
+    <t xml:space="preserve">11.4296798706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4728536605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3034782409668</t>
   </si>
   <si>
     <t xml:space="preserve">11.4130744934082</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1938781738281</t>
+    <t xml:space="preserve">11.1938800811768</t>
   </si>
   <si>
     <t xml:space="preserve">10.9348316192627</t>
   </si>
   <si>
-    <t xml:space="preserve">10.825234413147</t>
+    <t xml:space="preserve">10.8252334594727</t>
   </si>
   <si>
     <t xml:space="preserve">10.7720947265625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2669439315796</t>
+    <t xml:space="preserve">11.2669429779053</t>
   </si>
   <si>
     <t xml:space="preserve">11.3283853530884</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2254314422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9547576904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1141719818115</t>
+    <t xml:space="preserve">11.2254304885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.954758644104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1141729354858</t>
   </si>
   <si>
     <t xml:space="preserve">11.080961227417</t>
@@ -5036,31 +5036,31 @@
     <t xml:space="preserve">10.9846467971802</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1224746704102</t>
+    <t xml:space="preserve">11.1224756240845</t>
   </si>
   <si>
     <t xml:space="preserve">11.0759782791138</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1673097610474</t>
+    <t xml:space="preserve">11.167308807373</t>
   </si>
   <si>
     <t xml:space="preserve">11.2010746002197</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2804183959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2837953567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0119962692261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1352348327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1554918289185</t>
+    <t xml:space="preserve">11.2804193496704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2837944030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0119972229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.135235786438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1554927825928</t>
   </si>
   <si>
     <t xml:space="preserve">10.8938255310059</t>
@@ -5069,13 +5069,13 @@
     <t xml:space="preserve">10.5089206695557</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7942237854004</t>
+    <t xml:space="preserve">10.7942218780518</t>
   </si>
   <si>
     <t xml:space="preserve">11.0930309295654</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0592660903931</t>
+    <t xml:space="preserve">11.0592670440674</t>
   </si>
   <si>
     <t xml:space="preserve">10.9596643447876</t>
@@ -5084,55 +5084,55 @@
     <t xml:space="preserve">11.0406970977783</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0710821151733</t>
+    <t xml:space="preserve">11.0710830688477</t>
   </si>
   <si>
     <t xml:space="preserve">10.8296747207642</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9394073486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.961353302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0153751373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9545993804932</t>
+    <t xml:space="preserve">10.9394063949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9613523483276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0153741836548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9546003341675</t>
   </si>
   <si>
     <t xml:space="preserve">10.9647283554077</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8178577423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.028881072998</t>
+    <t xml:space="preserve">10.8178567886353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0288801193237</t>
   </si>
   <si>
     <t xml:space="preserve">10.8769435882568</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8009738922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9208354949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7587718963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8060398101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8786315917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1267938613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3209352493286</t>
+    <t xml:space="preserve">10.8009757995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9208364486694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7587699890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8060388565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8786306381226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1267929077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3209362030029</t>
   </si>
   <si>
     <t xml:space="preserve">11.3648281097412</t>
@@ -5153,25 +5153,25 @@
     <t xml:space="preserve">11.1706867218018</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4239139556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4965047836304</t>
+    <t xml:space="preserve">11.4239158630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.496506690979</t>
   </si>
   <si>
     <t xml:space="preserve">11.3327512741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2213315963745</t>
+    <t xml:space="preserve">11.2213306427002</t>
   </si>
   <si>
     <t xml:space="preserve">11.3361282348633</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4289779663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5133876800537</t>
+    <t xml:space="preserve">11.4289770126343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.513388633728</t>
   </si>
   <si>
     <t xml:space="preserve">11.6551942825317</t>
@@ -5180,28 +5180,28 @@
     <t xml:space="preserve">11.5724744796753</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4711837768555</t>
+    <t xml:space="preserve">11.4711818695068</t>
   </si>
   <si>
     <t xml:space="preserve">11.5893545150757</t>
   </si>
   <si>
-    <t xml:space="preserve">11.528582572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7193450927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6281824111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5353345870972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5842914581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5454626083374</t>
+    <t xml:space="preserve">11.5285797119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7193470001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6281833648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5353336334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5842905044556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5454635620117</t>
   </si>
   <si>
     <t xml:space="preserve">11.5015707015991</t>
@@ -5210,7 +5210,7 @@
     <t xml:space="preserve">11.8746585845947</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9236164093018</t>
+    <t xml:space="preserve">11.9236145019531</t>
   </si>
   <si>
     <t xml:space="preserve">11.8577756881714</t>
@@ -5222,7 +5222,7 @@
     <t xml:space="preserve">11.7581739425659</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7953128814697</t>
+    <t xml:space="preserve">11.795313835144</t>
   </si>
   <si>
     <t xml:space="preserve">11.8459596633911</t>
@@ -5237,13 +5237,13 @@
     <t xml:space="preserve">11.8797225952148</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9253025054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9472503662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0688009262085</t>
+    <t xml:space="preserve">11.9253053665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9472494125366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0687980651855</t>
   </si>
   <si>
     <t xml:space="preserve">12.1177558898926</t>
@@ -5252,25 +5252,25 @@
     <t xml:space="preserve">12.1278839111328</t>
   </si>
   <si>
-    <t xml:space="preserve">12.056981086731</t>
+    <t xml:space="preserve">12.0569820404053</t>
   </si>
   <si>
     <t xml:space="preserve">12.2713794708252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3254013061523</t>
+    <t xml:space="preserve">12.3254022598267</t>
   </si>
   <si>
     <t xml:space="preserve">12.5212306976318</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4857788085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4418859481812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4908437728882</t>
+    <t xml:space="preserve">12.4857797622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4418849945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4908447265625</t>
   </si>
   <si>
     <t xml:space="preserve">12.7052421569824</t>
@@ -5282,10 +5282,10 @@
     <t xml:space="preserve">12.7643280029297</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9736633300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9449653625488</t>
+    <t xml:space="preserve">12.9736623764038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9449644088745</t>
   </si>
   <si>
     <t xml:space="preserve">12.8403472900391</t>
@@ -5297,28 +5297,28 @@
     <t xml:space="preserve">13.0650157928467</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8763628005981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0667314529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0495805740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0152797698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1816358566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2227964401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0821647644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7768907546997</t>
+    <t xml:space="preserve">12.8763618469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0667295455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0495796203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0152788162231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1816349029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2227973937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.08216381073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.776891708374</t>
   </si>
   <si>
     <t xml:space="preserve">12.6294002532959</t>
@@ -5327,28 +5327,28 @@
     <t xml:space="preserve">12.4321737289429</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3824377059937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5539407730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8386316299438</t>
+    <t xml:space="preserve">12.382435798645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5539388656616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8386335372925</t>
   </si>
   <si>
     <t xml:space="preserve">12.9912691116333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9363899230957</t>
+    <t xml:space="preserve">12.9363889694214</t>
   </si>
   <si>
     <t xml:space="preserve">13.1164655685425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.28968334198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2742471694946</t>
+    <t xml:space="preserve">13.2896823883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2742481231689</t>
   </si>
   <si>
     <t xml:space="preserve">13.3188362121582</t>
@@ -5357,109 +5357,109 @@
     <t xml:space="preserve">13.4114484786987</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2502374649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2039308547974</t>
+    <t xml:space="preserve">13.2502365112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.203929901123</t>
   </si>
   <si>
     <t xml:space="preserve">13.236517906189</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2107906341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2759637832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2999725341797</t>
+    <t xml:space="preserve">13.2107915878296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2759628295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2999715805054</t>
   </si>
   <si>
     <t xml:space="preserve">13.1747770309448</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2296562194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4663286209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.17649269104</t>
+    <t xml:space="preserve">13.2296571731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.466329574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1764917373657</t>
   </si>
   <si>
     <t xml:space="preserve">13.2090768814087</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8729314804077</t>
+    <t xml:space="preserve">12.8729333877563</t>
   </si>
   <si>
     <t xml:space="preserve">12.7134370803833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8077630996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8609266281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0615844726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0770196914673</t>
+    <t xml:space="preserve">12.8077621459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8609275817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0615854263306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0770206451416</t>
   </si>
   <si>
     <t xml:space="preserve">13.0255680084229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7425918579102</t>
+    <t xml:space="preserve">12.7425909042358</t>
   </si>
   <si>
     <t xml:space="preserve">13.0697450637817</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0053014755249</t>
+    <t xml:space="preserve">13.0053033828735</t>
   </si>
   <si>
     <t xml:space="preserve">12.8224239349365</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0070447921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1219968795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0889043807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2352085113525</t>
+    <t xml:space="preserve">13.007043838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1219959259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.088903427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2352075576782</t>
   </si>
   <si>
     <t xml:space="preserve">13.1568307876587</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2090826034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2804908752441</t>
+    <t xml:space="preserve">13.2090816497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2804918289185</t>
   </si>
   <si>
     <t xml:space="preserve">13.0279445648193</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1411561965942</t>
+    <t xml:space="preserve">13.1411552429199</t>
   </si>
   <si>
     <t xml:space="preserve">12.9861431121826</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8624839782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0714874267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0488452911377</t>
+    <t xml:space="preserve">12.8624820709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0714864730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0488443374634</t>
   </si>
   <si>
     <t xml:space="preserve">12.8920917510986</t>
@@ -5477,73 +5477,73 @@
     <t xml:space="preserve">13.055811882019</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0854206085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2404317855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.23694896698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3135824203491</t>
+    <t xml:space="preserve">13.0854215621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2404327392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2369499206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3135833740234</t>
   </si>
   <si>
     <t xml:space="preserve">13.4424705505371</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3745431900024</t>
+    <t xml:space="preserve">13.3745422363281</t>
   </si>
   <si>
     <t xml:space="preserve">13.3658351898193</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5469722747803</t>
+    <t xml:space="preserve">13.5469732284546</t>
   </si>
   <si>
     <t xml:space="preserve">13.4442119598389</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5156221389771</t>
+    <t xml:space="preserve">13.5156230926514</t>
   </si>
   <si>
     <t xml:space="preserve">13.5330390930176</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1324472427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9965934753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9617595672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.89905834198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0993537902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0592947006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0035600662231</t>
+    <t xml:space="preserve">13.1324462890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9965925216675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9617605209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8990592956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0993547439575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0592956542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0035610198975</t>
   </si>
   <si>
     <t xml:space="preserve">12.7597227096558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7214050292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5838098526001</t>
+    <t xml:space="preserve">12.7214040756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5838108062744</t>
   </si>
   <si>
     <t xml:space="preserve">12.48801612854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5036907196045</t>
+    <t xml:space="preserve">12.5036916732788</t>
   </si>
   <si>
     <t xml:space="preserve">12.6186447143555</t>
@@ -5552,139 +5552,139 @@
     <t xml:space="preserve">12.6848287582397</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8502893447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9931116104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.886866569519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7022457122803</t>
+    <t xml:space="preserve">12.8502912521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9931106567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8868675231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7022466659546</t>
   </si>
   <si>
     <t xml:space="preserve">12.5176248550415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.716178894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5141429901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5106592178345</t>
+    <t xml:space="preserve">12.7161798477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.514142036438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5106582641602</t>
   </si>
   <si>
     <t xml:space="preserve">12.4479570388794</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5733594894409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6012268066406</t>
+    <t xml:space="preserve">12.5733604431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6012287139893</t>
   </si>
   <si>
     <t xml:space="preserve">12.6290950775146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7179222106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.32603931427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3399715423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3068799972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4549255371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3922214508057</t>
+    <t xml:space="preserve">12.7179203033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3260374069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3399724960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3068780899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4549245834351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.39222240448</t>
   </si>
   <si>
     <t xml:space="preserve">12.4148654937744</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4113807678223</t>
+    <t xml:space="preserve">12.4113798141479</t>
   </si>
   <si>
     <t xml:space="preserve">12.5228500366211</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5019493103027</t>
+    <t xml:space="preserve">12.5019502639771</t>
   </si>
   <si>
     <t xml:space="preserve">12.4078989028931</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4775667190552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5298185348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6343193054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7388210296631</t>
+    <t xml:space="preserve">12.4775657653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5298156738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6343183517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7388219833374</t>
   </si>
   <si>
     <t xml:space="preserve">12.7423057556152</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8032655715942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6778621673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7945566177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0436191558838</t>
+    <t xml:space="preserve">12.8032646179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6778631210327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7945556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0436201095581</t>
   </si>
   <si>
     <t xml:space="preserve">12.6465110778809</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6325769424438</t>
+    <t xml:space="preserve">12.6325778961182</t>
   </si>
   <si>
     <t xml:space="preserve">12.5883026123047</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8893737792969</t>
+    <t xml:space="preserve">12.8893718719482</t>
   </si>
   <si>
     <t xml:space="preserve">12.6857089996338</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7158164978027</t>
+    <t xml:space="preserve">12.7158145904541</t>
   </si>
   <si>
     <t xml:space="preserve">12.7105016708374</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8876037597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8840599060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9017705917358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9708385467529</t>
+    <t xml:space="preserve">12.887601852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8840608596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9017715454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9708395004272</t>
   </si>
   <si>
     <t xml:space="preserve">13.3091020584106</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4383840560913</t>
+    <t xml:space="preserve">13.4383859634399</t>
   </si>
   <si>
     <t xml:space="preserve">13.5906915664673</t>
@@ -5693,16 +5693,16 @@
     <t xml:space="preserve">13.7323722839355</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7376842498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6774711608887</t>
+    <t xml:space="preserve">13.7376861572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6774702072144</t>
   </si>
   <si>
     <t xml:space="preserve">13.6154870986938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5641250610352</t>
+    <t xml:space="preserve">13.5641260147095</t>
   </si>
   <si>
     <t xml:space="preserve">13.9289531707764</t>
@@ -5714,61 +5714,61 @@
     <t xml:space="preserve">13.4596366882324</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5747518539429</t>
+    <t xml:space="preserve">13.5747537612915</t>
   </si>
   <si>
     <t xml:space="preserve">13.4862022399902</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5109977722168</t>
+    <t xml:space="preserve">13.5109968185425</t>
   </si>
   <si>
     <t xml:space="preserve">13.583607673645</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7429990768433</t>
+    <t xml:space="preserve">13.7429981231689</t>
   </si>
   <si>
     <t xml:space="preserve">13.4915151596069</t>
   </si>
   <si>
-    <t xml:space="preserve">13.507453918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5127668380737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5251626968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4029655456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.12668800354</t>
+    <t xml:space="preserve">13.5074529647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.512767791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5251636505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4029636383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1266889572144</t>
   </si>
   <si>
     <t xml:space="preserve">13.0239696502686</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1532535552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2542009353638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2258653640747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3108720779419</t>
+    <t xml:space="preserve">13.1532526016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2541999816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2258634567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3108730316162</t>
   </si>
   <si>
     <t xml:space="preserve">13.4419269561768</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4932870864868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3817148208618</t>
+    <t xml:space="preserve">13.4932851791382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3817129135132</t>
   </si>
   <si>
     <t xml:space="preserve">13.0877256393433</t>
@@ -5777,16 +5777,16 @@
     <t xml:space="preserve">13.1302299499512</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1859970092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1212368011475</t>
+    <t xml:space="preserve">13.185996055603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1212358474731</t>
   </si>
   <si>
     <t xml:space="preserve">12.9971103668213</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0312900543213</t>
+    <t xml:space="preserve">13.0312910079956</t>
   </si>
   <si>
     <t xml:space="preserve">12.9377470016479</t>
@@ -5795,64 +5795,64 @@
     <t xml:space="preserve">13.1158390045166</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0942525863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9395456314087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9233560562134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0384874343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9683284759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6049489974976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5437860488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6553182601929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5851612091064</t>
+    <t xml:space="preserve">13.0942535400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.939546585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9233551025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0384855270386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9683294296265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6049499511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5437850952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6553192138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5851602554321</t>
   </si>
   <si>
     <t xml:space="preserve">12.6894979476929</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5815620422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5401887893677</t>
+    <t xml:space="preserve">12.581563949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5401906967163</t>
   </si>
   <si>
     <t xml:space="preserve">12.3387107849121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1498260498047</t>
+    <t xml:space="preserve">12.1498250961304</t>
   </si>
   <si>
     <t xml:space="preserve">12.1732120513916</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3980751037598</t>
+    <t xml:space="preserve">12.3980741500854</t>
   </si>
   <si>
     <t xml:space="preserve">12.5006122589111</t>
   </si>
   <si>
-    <t xml:space="preserve">12.711085319519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5347929000854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7038888931274</t>
+    <t xml:space="preserve">12.7110843658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5347919464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7038879394531</t>
   </si>
   <si>
     <t xml:space="preserve">12.8046283721924</t>
@@ -5861,31 +5861,31 @@
     <t xml:space="preserve">12.8082256317139</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8747854232788</t>
+    <t xml:space="preserve">12.8747863769531</t>
   </si>
   <si>
     <t xml:space="preserve">12.9107627868652</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0708665847778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0672693252563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0079050064087</t>
+    <t xml:space="preserve">13.0708656311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.067268371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0079040527344</t>
   </si>
   <si>
     <t xml:space="preserve">13.1374263763428</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0007085800171</t>
+    <t xml:space="preserve">13.0007095336914</t>
   </si>
   <si>
     <t xml:space="preserve">12.86399269104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6930952072144</t>
+    <t xml:space="preserve">12.6930961608887</t>
   </si>
   <si>
     <t xml:space="preserve">12.7542581558228</t>
@@ -5900,49 +5900,49 @@
     <t xml:space="preserve">12.8064270019531</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6031513214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7128839492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8531980514526</t>
+    <t xml:space="preserve">12.6031494140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7128829956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8531999588013</t>
   </si>
   <si>
     <t xml:space="preserve">12.6643142700195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6571178436279</t>
+    <t xml:space="preserve">12.6571168899536</t>
   </si>
   <si>
     <t xml:space="preserve">12.6157426834106</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6445255279541</t>
+    <t xml:space="preserve">12.6445245742798</t>
   </si>
   <si>
     <t xml:space="preserve">12.6103467941284</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1590137481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1680088043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3101215362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0870561599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.786639213562</t>
+    <t xml:space="preserve">13.1590147018433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.168007850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3101224899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0870571136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7866382598877</t>
   </si>
   <si>
     <t xml:space="preserve">12.5329933166504</t>
   </si>
   <si>
-    <t xml:space="preserve">12.522198677063</t>
+    <t xml:space="preserve">12.5221996307373</t>
   </si>
   <si>
     <t xml:space="preserve">12.8334102630615</t>
@@ -5954,25 +5954,25 @@
     <t xml:space="preserve">12.8855800628662</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0402860641479</t>
+    <t xml:space="preserve">13.0402851104736</t>
   </si>
   <si>
     <t xml:space="preserve">13.1482200622559</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0366878509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0564746856689</t>
+    <t xml:space="preserve">13.0366868972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0564756393433</t>
   </si>
   <si>
     <t xml:space="preserve">12.9539384841919</t>
   </si>
   <si>
-    <t xml:space="preserve">13.254355430603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2237730026245</t>
+    <t xml:space="preserve">13.2543544769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2237739562988</t>
   </si>
   <si>
     <t xml:space="preserve">13.1967897415161</t>
@@ -5984,70 +5984,70 @@
     <t xml:space="preserve">13.1985883712769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2219734191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8891773223877</t>
+    <t xml:space="preserve">13.2219743728638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8891763687134</t>
   </si>
   <si>
     <t xml:space="preserve">12.7398672103882</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3782873153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3513050079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4574394226074</t>
+    <t xml:space="preserve">12.3782863616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3513031005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4574384689331</t>
   </si>
   <si>
     <t xml:space="preserve">12.5995531082153</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6948947906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7902374267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8172216415405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.846001625061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9100875854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9650144577026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8130474090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4230518341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5145998001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5255861282349</t>
+    <t xml:space="preserve">12.6948938369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7902364730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8172206878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8460025787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9100866317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9650163650513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8130464553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4230508804321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5145988464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5255851745605</t>
   </si>
   <si>
     <t xml:space="preserve">12.7160053253174</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9247341156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9137496948242</t>
+    <t xml:space="preserve">12.9247350692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9137487411499</t>
   </si>
   <si>
     <t xml:space="preserve">13.1133232116699</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2781085968018</t>
+    <t xml:space="preserve">13.2781105041504</t>
   </si>
   <si>
     <t xml:space="preserve">12.9943113327026</t>
@@ -6056,37 +6056,37 @@
     <t xml:space="preserve">12.968677520752</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0565633773804</t>
+    <t xml:space="preserve">13.0565643310547</t>
   </si>
   <si>
     <t xml:space="preserve">13.1114921569824</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1407861709595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7837505340576</t>
+    <t xml:space="preserve">13.1407871246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7837514877319</t>
   </si>
   <si>
     <t xml:space="preserve">12.8496656417847</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0510702133179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0712108612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9814949035645</t>
+    <t xml:space="preserve">13.0510711669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0712118148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9814939498901</t>
   </si>
   <si>
     <t xml:space="preserve">13.023606300354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2085332870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8093843460083</t>
+    <t xml:space="preserve">13.208532333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.809383392334</t>
   </si>
   <si>
     <t xml:space="preserve">12.8276929855347</t>
@@ -6098,31 +6098,31 @@
     <t xml:space="preserve">12.8368492126465</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9229030609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8203706741333</t>
+    <t xml:space="preserve">12.9229049682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.820369720459</t>
   </si>
   <si>
     <t xml:space="preserve">12.8991003036499</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7526245117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8258619308472</t>
+    <t xml:space="preserve">12.7526254653931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8258628845215</t>
   </si>
   <si>
     <t xml:space="preserve">12.6445980072021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5585432052612</t>
+    <t xml:space="preserve">12.5585422515869</t>
   </si>
   <si>
     <t xml:space="preserve">12.9045944213867</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9511938095093</t>
+    <t xml:space="preserve">12.9511947631836</t>
   </si>
   <si>
     <t xml:space="preserve">12.8002090454102</t>
@@ -6134,10 +6134,10 @@
     <t xml:space="preserve">12.8747701644897</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9698343276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8058004379272</t>
+    <t xml:space="preserve">12.9698352813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8058013916016</t>
   </si>
   <si>
     <t xml:space="preserve">12.5411109924316</t>
@@ -6146,7 +6146,7 @@
     <t xml:space="preserve">12.503830909729</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5112867355347</t>
+    <t xml:space="preserve">12.5112857818604</t>
   </si>
   <si>
     <t xml:space="preserve">12.4945106506348</t>
@@ -6155,13 +6155,13 @@
     <t xml:space="preserve">12.4348611831665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5541591644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.56907081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5392465591431</t>
+    <t xml:space="preserve">12.5541582107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5690717697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5392475128174</t>
   </si>
   <si>
     <t xml:space="preserve">12.5075588226318</t>
@@ -6170,19 +6170,19 @@
     <t xml:space="preserve">12.57652759552</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4926471710205</t>
+    <t xml:space="preserve">12.4926452636719</t>
   </si>
   <si>
     <t xml:space="preserve">12.4646854400635</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4143562316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3919897079468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2093162536621</t>
+    <t xml:space="preserve">12.4143571853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3919878005981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2093152999878</t>
   </si>
   <si>
     <t xml:space="preserve">11.9148015975952</t>
@@ -6191,7 +6191,7 @@
     <t xml:space="preserve">12.0154581069946</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9129371643066</t>
+    <t xml:space="preserve">11.9129362106323</t>
   </si>
   <si>
     <t xml:space="preserve">11.8588800430298</t>
@@ -6209,7 +6209,7 @@
     <t xml:space="preserve">12.5467023849487</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7126007080078</t>
+    <t xml:space="preserve">12.7126016616821</t>
   </si>
   <si>
     <t xml:space="preserve">12.7331047058105</t>
@@ -6221,13 +6221,13 @@
     <t xml:space="preserve">12.803936958313</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8095293045044</t>
+    <t xml:space="preserve">12.8095302581787</t>
   </si>
   <si>
     <t xml:space="preserve">12.9288263320923</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0332107543945</t>
+    <t xml:space="preserve">13.0332117080688</t>
   </si>
   <si>
     <t xml:space="preserve">12.9959306716919</t>
@@ -6236,13 +6236,13 @@
     <t xml:space="preserve">13.1338682174683</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9474668502808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7927532196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7461519241333</t>
+    <t xml:space="preserve">12.9474658966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7927522659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7461528778076</t>
   </si>
   <si>
     <t xml:space="preserve">12.6697282791138</t>
@@ -6257,13 +6257,13 @@
     <t xml:space="preserve">12.5187425613403</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5355195999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7088718414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7685203552246</t>
+    <t xml:space="preserve">12.5355176925659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7088708877563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7685213088989</t>
   </si>
   <si>
     <t xml:space="preserve">12.7032804489136</t>
@@ -6272,34 +6272,34 @@
     <t xml:space="preserve">12.846809387207</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8729066848755</t>
+    <t xml:space="preserve">12.8729057312012</t>
   </si>
   <si>
     <t xml:space="preserve">12.9195070266724</t>
   </si>
   <si>
-    <t xml:space="preserve">12.941873550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1059083938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0723562240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0406675338745</t>
+    <t xml:space="preserve">12.9418745040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1059093475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0723552703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0406665802002</t>
   </si>
   <si>
     <t xml:space="preserve">13.0835399627686</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1189565658569</t>
+    <t xml:space="preserve">13.1189556121826</t>
   </si>
   <si>
     <t xml:space="preserve">13.1357326507568</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0984516143799</t>
+    <t xml:space="preserve">13.0984506607056</t>
   </si>
   <si>
     <t xml:space="preserve">13.1003150939941</t>
@@ -6311,55 +6311,55 @@
     <t xml:space="preserve">13.0816764831543</t>
   </si>
   <si>
-    <t xml:space="preserve">13.176739692688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3034944534302</t>
+    <t xml:space="preserve">13.1767406463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3034934997559</t>
   </si>
   <si>
     <t xml:space="preserve">13.1170921325684</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9120502471924</t>
+    <t xml:space="preserve">12.9120512008667</t>
   </si>
   <si>
     <t xml:space="preserve">12.9083223342896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3621644973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2503242492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3174285888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6156721115112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6249904632568</t>
+    <t xml:space="preserve">12.3621635437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2503232955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3174276351929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6156711578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6249923706055</t>
   </si>
   <si>
     <t xml:space="preserve">12.7219200134277</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7275114059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7852973937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0704927444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1879243850708</t>
+    <t xml:space="preserve">12.7275133132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7852964401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0704917907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1879253387451</t>
   </si>
   <si>
     <t xml:space="preserve">13.3612785339355</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4637985229492</t>
+    <t xml:space="preserve">13.4637994766235</t>
   </si>
   <si>
     <t xml:space="preserve">13.3985595703125</t>
@@ -6368,7 +6368,7 @@
     <t xml:space="preserve">13.3378553390503</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4877185821533</t>
+    <t xml:space="preserve">13.487717628479</t>
   </si>
   <si>
     <t xml:space="preserve">13.6451692581177</t>
@@ -6386,7 +6386,7 @@
     <t xml:space="preserve">13.6622428894043</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5749797821045</t>
+    <t xml:space="preserve">13.5749807357788</t>
   </si>
   <si>
     <t xml:space="preserve">12.9679384231567</t>
@@ -6398,10 +6398,10 @@
     <t xml:space="preserve">11.423773765564</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2777061462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6554870605469</t>
+    <t xml:space="preserve">11.2777051925659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6554861068726</t>
   </si>
   <si>
     <t xml:space="preserve">10.9628009796143</t>
@@ -6413,10 +6413,10 @@
     <t xml:space="preserve">11.1714725494385</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3440999984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5470790863037</t>
+    <t xml:space="preserve">11.3441009521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.547080039978</t>
   </si>
   <si>
     <t xml:space="preserve">11.6400337219238</t>
@@ -6428,7 +6428,7 @@
     <t xml:space="preserve">11.7898969650269</t>
   </si>
   <si>
-    <t xml:space="preserve">12.038405418396</t>
+    <t xml:space="preserve">12.0384044647217</t>
   </si>
   <si>
     <t xml:space="preserve">12.1010065078735</t>
@@ -6443,7 +6443,7 @@
     <t xml:space="preserve">12.0459928512573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0042591094971</t>
+    <t xml:space="preserve">12.0042581558228</t>
   </si>
   <si>
     <t xml:space="preserve">11.9264822006226</t>
@@ -6455,7 +6455,7 @@
     <t xml:space="preserve">11.9985675811768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0896234512329</t>
+    <t xml:space="preserve">12.0896244049072</t>
   </si>
   <si>
     <t xml:space="preserve">12.3305435180664</t>
@@ -6464,10 +6464,10 @@
     <t xml:space="preserve">12.5847425460815</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7801332473755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7535762786865</t>
+    <t xml:space="preserve">12.7801342010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7535772323608</t>
   </si>
   <si>
     <t xml:space="preserve">12.6378593444824</t>
@@ -6924,6 +6924,9 @@
   </si>
   <si>
     <t xml:space="preserve">15.9759998321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1399993896484</t>
   </si>
 </sst>
 </file>
@@ -73276,7 +73279,7 @@
     </row>
     <row r="2540">
       <c r="A2540" s="1" t="n">
-        <v>46020.6924768519</v>
+        <v>46020.3333333333</v>
       </c>
       <c r="B2540" t="n">
         <v>6624648</v>
@@ -73297,6 +73300,32 @@
         <v>2303</v>
       </c>
       <c r="H2540" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2541">
+      <c r="A2541" s="1" t="n">
+        <v>46021.6933680556</v>
+      </c>
+      <c r="B2541" t="n">
+        <v>8041391</v>
+      </c>
+      <c r="C2541" t="n">
+        <v>16.1639995574951</v>
+      </c>
+      <c r="D2541" t="n">
+        <v>16.007999420166</v>
+      </c>
+      <c r="E2541" t="n">
+        <v>16.0100002288818</v>
+      </c>
+      <c r="F2541" t="n">
+        <v>16.1399993896484</v>
+      </c>
+      <c r="G2541" t="s">
+        <v>2304</v>
+      </c>
+      <c r="H2541" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ENI.MI.xlsx
+++ b/data/ENI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2315" uniqueCount="2315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2316" uniqueCount="2316">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,211 +38,211 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15080308914185</t>
+    <t xml:space="preserve">7.15080213546753</t>
   </si>
   <si>
     <t xml:space="preserve">ENI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21469736099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01236534118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95912075042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76211500167847</t>
+    <t xml:space="preserve">7.21469688415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.012366771698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95912170410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76211595535278</t>
   </si>
   <si>
     <t xml:space="preserve">6.73549270629883</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75146627426147</t>
+    <t xml:space="preserve">6.75146818161011</t>
   </si>
   <si>
     <t xml:space="preserve">6.83133316040039</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92717599868774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68224811553955</t>
+    <t xml:space="preserve">6.92717361450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68224906921387</t>
   </si>
   <si>
     <t xml:space="preserve">6.60770511627197</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69821977615356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4745922088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90587711334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82068395614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96444463729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99639463424683</t>
+    <t xml:space="preserve">6.69822072982788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47459125518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90587663650513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82068300247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96444606781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99639129638672</t>
   </si>
   <si>
     <t xml:space="preserve">7.07093620300293</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66094875335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63432693481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78341150283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67159700393677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43199634552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17642021179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19239234924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81967878341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20836687088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35745286941528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30953311920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51186227798462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37342596054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34680414199829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57575798034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2722601890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43732070922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7674388885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89522552490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1082067489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16145324707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25729322433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20937204360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2359938621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05496025085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13483047485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88990163803101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09223318099976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12950611114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02834033966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11885499954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24664497375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31053924560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34780836105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17210054397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00171661376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19872426986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08158254623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81003475189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79406261444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62367630004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69289684295654</t>
+    <t xml:space="preserve">6.66094923019409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63432645797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78341341018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67159748077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43199586868286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17641973495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19239377975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81967830657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20836591720581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35745191574097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30953168869019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51186275482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37342405319214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34680366516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57575845718384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27226161956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4373197555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76744079589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89522695541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10820817947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.161452293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25729179382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20937252044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23599576950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05496263504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13483190536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88990306854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09223365783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12950372695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02833938598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11885643005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24664306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31053590774536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34780979156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17210102081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00171804428101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1987247467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08158588409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81003570556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7940616607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6236777305603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69289636611938</t>
   </si>
   <si>
     <t xml:space="preserve">6.55978441238403</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84198188781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86328172683716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90055131912231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17742586135864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30521535873413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18807744979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27859210968018</t>
+    <t xml:space="preserve">6.84198331832886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86328029632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.900550365448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1774263381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30521440505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18807363510132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27859020233154</t>
   </si>
   <si>
     <t xml:space="preserve">7.39573097229004</t>
@@ -251,223 +251,223 @@
     <t xml:space="preserve">7.49157047271729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53416728973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49689483642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52884244918823</t>
+    <t xml:space="preserve">7.53416681289673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49689674377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52884483337402</t>
   </si>
   <si>
     <t xml:space="preserve">7.59806251525879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66727781295776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56079006195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42767858505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27326631546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12418270111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22534465789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28923988342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02301645278931</t>
+    <t xml:space="preserve">7.66727924346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56078910827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4276762008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27326726913452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12417984008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22534418106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28924131393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02301502227783</t>
   </si>
   <si>
     <t xml:space="preserve">7.10738801956177</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32692003250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57938432693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61780309677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59036016464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65073156356812</t>
+    <t xml:space="preserve">7.32692337036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57938480377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61780405044556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59036064147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65073251724243</t>
   </si>
   <si>
     <t xml:space="preserve">7.535475730896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43119859695435</t>
+    <t xml:space="preserve">7.43119955062866</t>
   </si>
   <si>
     <t xml:space="preserve">7.42571067810059</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36533689498901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55743074417114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73305606842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7550106048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71659278869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38180589675903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24459552764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33789730072021</t>
+    <t xml:space="preserve">7.36533880233765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5574312210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73305702209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75500965118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71659183502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38180494308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24459600448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33789777755737</t>
   </si>
   <si>
     <t xml:space="preserve">7.26106023788452</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54645442962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77147769927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8702654838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74952125549316</t>
+    <t xml:space="preserve">7.54645299911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77147579193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87026596069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74952173233032</t>
   </si>
   <si>
     <t xml:space="preserve">8.00198459625244</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26654863357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49706029891968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84831476211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96905660629272</t>
+    <t xml:space="preserve">7.26654958724976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4970588684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84831190109253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96905517578125</t>
   </si>
   <si>
     <t xml:space="preserve">8.13370609283447</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9086856842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76049947738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80440711975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95807886123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0513801574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12821674346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02942848205566</t>
+    <t xml:space="preserve">7.90868425369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76050043106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80440473556519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95808029174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05138206481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12821865081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02942752838135</t>
   </si>
   <si>
     <t xml:space="preserve">8.17761325836182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07882118225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9910101890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96356773376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88673400878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84282445907593</t>
+    <t xml:space="preserve">8.07882213592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99100971221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96356725692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8867335319519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84282207489014</t>
   </si>
   <si>
     <t xml:space="preserve">7.80989503860474</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7001256942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70561695098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50254774093628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50803709030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35985279083252</t>
+    <t xml:space="preserve">7.70012760162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70561599731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50254678726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50803661346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35985088348389</t>
   </si>
   <si>
     <t xml:space="preserve">7.20617723464966</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25557279586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27203845977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44766330718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43668985366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41473436355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51901435852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54096508026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39278268814087</t>
+    <t xml:space="preserve">7.25557374954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27203893661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44766283035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43668651580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41473340988159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51901292800903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54096651077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39278030395508</t>
   </si>
   <si>
     <t xml:space="preserve">7.37631607055664</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47510623931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46961832046509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52998781204224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44217777252197</t>
+    <t xml:space="preserve">7.47510480880737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46961784362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52998924255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44217538833618</t>
   </si>
   <si>
     <t xml:space="preserve">7.19520044326782</t>
@@ -479,67 +479,67 @@
     <t xml:space="preserve">7.25008487701416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08543491363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19304609298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06278085708618</t>
-  </si>
-  <si>
     <t xml:space="preserve">7.08543539047241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16472959518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13640928268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00614023208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97215700149536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9948148727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31765079498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2610125541687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30065965652466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34597110748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5158863067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52721071243286</t>
+    <t xml:space="preserve">7.19304895401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06277990341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08543634414673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16472816467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1364107131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00613880157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97215795516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99481391906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3176531791687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26101446151733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30066061019897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34597015380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51588487625122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52721261978149</t>
   </si>
   <si>
     <t xml:space="preserve">7.70279169082642</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5555305480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50455808639526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45358276367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60084247589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53853797912598</t>
+    <t xml:space="preserve">7.55553197860718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50455665588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45358180999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60084104537964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53854036331177</t>
   </si>
   <si>
     <t xml:space="preserve">7.67447137832642</t>
@@ -548,25 +548,25 @@
     <t xml:space="preserve">7.69712781906128</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77641773223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79907464981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74809980392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6688084602356</t>
+    <t xml:space="preserve">7.77641868591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79907751083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74810171127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66880798339844</t>
   </si>
   <si>
     <t xml:space="preserve">7.78774738311768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65181589126587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48190021514893</t>
+    <t xml:space="preserve">7.65181684494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48190355300903</t>
   </si>
   <si>
     <t xml:space="preserve">7.36296319961548</t>
@@ -575,118 +575,118 @@
     <t xml:space="preserve">7.25534963607788</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19871091842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13074588775635</t>
+    <t xml:space="preserve">7.19870901107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13074493408203</t>
   </si>
   <si>
     <t xml:space="preserve">7.23269510269165</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2780065536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24968481063843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22136640548706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10809087753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94383955001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07977151870728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03446054458618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01180553436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1194167137146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12508201599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17039251327515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44225788116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7084527015686</t>
+    <t xml:space="preserve">7.27800416946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2496862411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22136545181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1080904006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94383859634399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07977104187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03446102142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01180458068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11941766738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12508153915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1703929901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44225549697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70845413208008</t>
   </si>
   <si>
     <t xml:space="preserve">7.75376319885254</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90668916702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98598289489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05961036682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07093811035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37111949920654</t>
+    <t xml:space="preserve">7.90669012069702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9859824180603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05961132049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07093906402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37112140655518</t>
   </si>
   <si>
     <t xml:space="preserve">8.45607757568359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42776012420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47873497009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52404403686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.473069190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5806827545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59201049804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68829536437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67130374908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74493312835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76192569732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85820770263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85254669189453</t>
+    <t xml:space="preserve">8.42775917053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47873306274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52404308319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47307109832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58068084716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59200859069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6882963180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67130470275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74493217468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76192474365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85820865631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85254573822021</t>
   </si>
   <si>
     <t xml:space="preserve">8.88652801513672</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90351867675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71661281585693</t>
+    <t xml:space="preserve">8.90351963043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71661472320557</t>
   </si>
   <si>
     <t xml:space="preserve">8.8072338104248</t>
@@ -695,106 +695,106 @@
     <t xml:space="preserve">8.80156993865967</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75625991821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87519931793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72227764129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81856250762939</t>
+    <t xml:space="preserve">8.75626182556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87520122528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7222785949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81856346130371</t>
   </si>
   <si>
     <t xml:space="preserve">8.78458023071289</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69395732879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4674072265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36545753479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15023326873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04828453063965</t>
+    <t xml:space="preserve">8.69395637512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46740627288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36545848846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15023231506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04828262329102</t>
   </si>
   <si>
     <t xml:space="preserve">8.00297355651855</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01996421813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22952747344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04262065887451</t>
+    <t xml:space="preserve">8.01996517181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22952651977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04262161254883</t>
   </si>
   <si>
     <t xml:space="preserve">8.00863742828369</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13323974609375</t>
+    <t xml:space="preserve">8.13324069976807</t>
   </si>
   <si>
     <t xml:space="preserve">8.1558952331543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23518943786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14456939697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99730920791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25784587860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16156196594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09925746917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22386169433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49572467803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.501389503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64864921569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54669952392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38244533538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32580947875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28616333007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2974910736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19554328918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30881786346436</t>
+    <t xml:space="preserve">8.23518848419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14456653594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99730825424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25784397125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16156101226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09925651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22386074066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49572658538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50138664245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64864826202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54670143127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38244915008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32581043243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28616428375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29749298095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19554424285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30881690979004</t>
   </si>
   <si>
     <t xml:space="preserve">8.45041370391846</t>
@@ -803,10 +803,10 @@
     <t xml:space="preserve">8.41076755523682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43342399597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51271533966064</t>
+    <t xml:space="preserve">8.43342208862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51271629333496</t>
   </si>
   <si>
     <t xml:space="preserve">8.49006080627441</t>
@@ -815,70 +815,70 @@
     <t xml:space="preserve">8.56369018554688</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67696475982666</t>
+    <t xml:space="preserve">8.67696571350098</t>
   </si>
   <si>
     <t xml:space="preserve">8.62599182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62032794952393</t>
+    <t xml:space="preserve">8.62032985687256</t>
   </si>
   <si>
     <t xml:space="preserve">8.6316556930542</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31448459625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32014751434326</t>
+    <t xml:space="preserve">8.31448173522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32014656066895</t>
   </si>
   <si>
     <t xml:space="preserve">8.46848106384277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43353462219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34034633636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31122779846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32869911193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2937536239624</t>
+    <t xml:space="preserve">8.4335355758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34034729003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31122589111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32869815826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29375171661377</t>
   </si>
   <si>
     <t xml:space="preserve">8.28792762756348</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49760341644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58496570587158</t>
+    <t xml:space="preserve">8.49760246276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5849666595459</t>
   </si>
   <si>
     <t xml:space="preserve">8.63155841827393</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67815494537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67233276367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73639869689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76551914215088</t>
+    <t xml:space="preserve">8.6781530380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67233085632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73639678955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76551723480225</t>
   </si>
   <si>
     <t xml:space="preserve">8.65485668182373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75969505310059</t>
+    <t xml:space="preserve">8.75969314575195</t>
   </si>
   <si>
     <t xml:space="preserve">8.74804592132568</t>
@@ -887,16 +887,16 @@
     <t xml:space="preserve">8.73057174682617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69562816619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53254699707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33452129364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31705188751221</t>
+    <t xml:space="preserve">8.6956262588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53254795074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33452224731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31704902648926</t>
   </si>
   <si>
     <t xml:space="preserve">8.20638751983643</t>
@@ -905,76 +905,76 @@
     <t xml:space="preserve">8.3054027557373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18309020996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1306734085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19473743438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03166103363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08990287780762</t>
+    <t xml:space="preserve">8.1830940246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13067531585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19474124908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03166007995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08990478515625</t>
   </si>
   <si>
     <t xml:space="preserve">8.09572601318359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15396976470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06660747528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02001190185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1015510559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93847227096558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97924423217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9559440612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90935039520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92099952697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87440729141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89770078659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74627351760864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66473293304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75792026519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78121662139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67055749893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62396287918091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54824829101562</t>
+    <t xml:space="preserve">8.15397071838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06660842895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02001571655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10155200958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93847322463989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97924375534058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95594453811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90935325622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92100095748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87440538406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89770364761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74627208709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66473054885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75792121887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7812180519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67055654525757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62396192550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54824590682983</t>
   </si>
   <si>
     <t xml:space="preserve">7.57154417037964</t>
@@ -983,157 +983,157 @@
     <t xml:space="preserve">7.55407094955444</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68220710754395</t>
+    <t xml:space="preserve">7.682204246521</t>
   </si>
   <si>
     <t xml:space="preserve">7.69385528564453</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71132564544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65308380126953</t>
+    <t xml:space="preserve">7.71132516860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65308332443237</t>
   </si>
   <si>
     <t xml:space="preserve">7.6472601890564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65890741348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59484195709229</t>
+    <t xml:space="preserve">7.65890979766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5948429107666</t>
   </si>
   <si>
     <t xml:space="preserve">7.60649061203003</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72297477722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69967937469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78704166412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84528541564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88022994995117</t>
+    <t xml:space="preserve">7.722975730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69967794418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78704309463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84528398513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88023090362549</t>
   </si>
   <si>
     <t xml:space="preserve">7.86275720596313</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89187908172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9035267829895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88605356216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85693359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77539396286011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81033802032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71715211868286</t>
+    <t xml:space="preserve">7.89187860488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90352535247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88605499267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85693311691284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77539348602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81033706665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71715068817139</t>
   </si>
   <si>
     <t xml:space="preserve">7.63561153411865</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75209760665894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76374387741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79869079589844</t>
+    <t xml:space="preserve">7.75209712982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76374340057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7986912727356</t>
   </si>
   <si>
     <t xml:space="preserve">7.85110902786255</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83945989608765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8685827255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94429588317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04331111907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0733003616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1152868270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18126487731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24124240875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26523399353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36120414733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39119243621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35520458221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36719989776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39719200134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3791971206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43917560577393</t>
+    <t xml:space="preserve">7.83946132659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86858081817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94429874420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04330921173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07329940795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11528587341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18126201629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24124431610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26523590087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36120319366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39119338989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35520553588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36720085144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39718914031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37919807434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43917751312256</t>
   </si>
   <si>
     <t xml:space="preserve">8.3372106552124</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41518497467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30722045898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34920692443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31322002410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33121299743652</t>
+    <t xml:space="preserve">8.41518592834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30722332000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34920597076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31321811676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33121395111084</t>
   </si>
   <si>
     <t xml:space="preserve">8.32521438598633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25923538208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29522609710693</t>
+    <t xml:space="preserve">8.25923824310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2952241897583</t>
   </si>
   <si>
     <t xml:space="preserve">8.27723217010498</t>
@@ -1142,25 +1142,25 @@
     <t xml:space="preserve">8.3012228012085</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42118167877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52914714813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57713222503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62511539459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69709205627441</t>
+    <t xml:space="preserve">8.42118358612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52914619445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57713031768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6251163482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69708919525146</t>
   </si>
   <si>
     <t xml:space="preserve">8.82904815673828</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76906681060791</t>
+    <t xml:space="preserve">8.76906585693359</t>
   </si>
   <si>
     <t xml:space="preserve">8.70308780670166</t>
@@ -1169,58 +1169,58 @@
     <t xml:space="preserve">8.64311027526855</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5831298828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48116397857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23524475097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25323963165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31921768188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3432092666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28922653198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21125411987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28322887420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40918636322021</t>
+    <t xml:space="preserve">8.58312892913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48116493225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23524570465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25323867797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31921577453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34320831298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28922557830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21125221252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28322982788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40918731689453</t>
   </si>
   <si>
     <t xml:space="preserve">8.433180809021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38519477844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37320041656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54714107513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.655104637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70908832550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81704902648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94900608062744</t>
+    <t xml:space="preserve">8.38519382476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37319850921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54714298248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65510559082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70908737182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81704998016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94900703430176</t>
   </si>
   <si>
     <t xml:space="preserve">8.94300746917725</t>
@@ -1229,19 +1229,19 @@
     <t xml:space="preserve">8.91301918029785</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96700000762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89502716064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96100330352783</t>
+    <t xml:space="preserve">8.96699905395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8950252532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96100234985352</t>
   </si>
   <si>
     <t xml:space="preserve">8.97299861907959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95500659942627</t>
+    <t xml:space="preserve">8.95500373840332</t>
   </si>
   <si>
     <t xml:space="preserve">8.87103366851807</t>
@@ -1250,16 +1250,16 @@
     <t xml:space="preserve">8.72348117828369</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68869209289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75107383728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60592079162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4895601272583</t>
+    <t xml:space="preserve">8.68869400024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75107192993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60592269897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48956108093262</t>
   </si>
   <si>
     <t xml:space="preserve">8.24964046478271</t>
@@ -1268,40 +1268,40 @@
     <t xml:space="preserve">8.20045757293701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03611373901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08649635314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00852298736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06010437011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09968948364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17646598815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22204875946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22444915771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20525646209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27123355865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31441974639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2256498336792</t>
+    <t xml:space="preserve">8.03611087799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0864953994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00852108001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06010341644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09969043731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17646408081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22205066680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22444725036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20525741577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27123260498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31441783905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22564792633057</t>
   </si>
   <si>
     <t xml:space="preserve">8.14047718048096</t>
@@ -1310,46 +1310,46 @@
     <t xml:space="preserve">8.02411651611328</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99532413482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10568904876709</t>
+    <t xml:space="preserve">7.99532604217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10569000244141</t>
   </si>
   <si>
     <t xml:space="preserve">8.14647483825684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15247344970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22804641723633</t>
+    <t xml:space="preserve">8.15247249603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22804737091064</t>
   </si>
   <si>
     <t xml:space="preserve">8.29162883758545</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45717144012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36000537872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47516632080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54114437103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49915599822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46196937561035</t>
+    <t xml:space="preserve">8.45717239379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36000442504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47516441345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5411434173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49915790557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46197128295898</t>
   </si>
   <si>
     <t xml:space="preserve">8.43197917938232</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51714992523193</t>
+    <t xml:space="preserve">8.51715278625488</t>
   </si>
   <si>
     <t xml:space="preserve">8.49435806274414</t>
@@ -1358,16 +1358,16 @@
     <t xml:space="preserve">8.56993293762207</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65630340576172</t>
+    <t xml:space="preserve">8.65630531311035</t>
   </si>
   <si>
     <t xml:space="preserve">8.73067951202393</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91421985626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92981243133545</t>
+    <t xml:space="preserve">8.91421794891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92981338500977</t>
   </si>
   <si>
     <t xml:space="preserve">8.98979091644287</t>
@@ -1376,91 +1376,91 @@
     <t xml:space="preserve">9.07736301422119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13374519348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19492435455322</t>
+    <t xml:space="preserve">9.13374328613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19492530822754</t>
   </si>
   <si>
     <t xml:space="preserve">9.25610160827637</t>
   </si>
   <si>
-    <t xml:space="preserve">9.265700340271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40485382080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4744291305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5967903137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56799697875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64957046508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61358451843262</t>
+    <t xml:space="preserve">9.26570129394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40485572814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47443008422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59678936004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56799793243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64957237243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6135835647583</t>
   </si>
   <si>
     <t xml:space="preserve">9.50682067871094</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69875431060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69155788421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71674823760986</t>
+    <t xml:space="preserve">9.69875526428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69155883789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7167501449585</t>
   </si>
   <si>
     <t xml:space="preserve">9.78992462158203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67356491088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80671977996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99505519866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73834419250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0082521438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84150886535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86070346832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0022554397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0550365447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91948318481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9578685760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92787933349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84920597076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89714622497559</t>
+    <t xml:space="preserve">9.67356300354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80671882629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99505615234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73834323883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0082530975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84151077270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86070156097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.002254486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0550374984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91948413848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95786571502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92788028717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84920406341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8971471786499</t>
   </si>
   <si>
     <t xml:space="preserve">9.78773784637451</t>
@@ -1469,10 +1469,10 @@
     <t xml:space="preserve">9.69799995422363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45705413818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26528263092041</t>
+    <t xml:space="preserve">9.45705318450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26528358459473</t>
   </si>
   <si>
     <t xml:space="preserve">9.27757549285889</t>
@@ -1481,58 +1481,58 @@
     <t xml:space="preserve">9.5209789276123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66972637176514</t>
+    <t xml:space="preserve">9.66972541809082</t>
   </si>
   <si>
     <t xml:space="preserve">9.57998561859131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4976224899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49639320373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60703086853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35748100280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63038635253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53450107574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72012519836426</t>
+    <t xml:space="preserve">9.49762153625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49639225006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60702896118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35747909545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63038444519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53450393676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72012710571289</t>
   </si>
   <si>
     <t xml:space="preserve">9.54679393768311</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55171203613281</t>
+    <t xml:space="preserve">9.5517110824585</t>
   </si>
   <si>
     <t xml:space="preserve">9.48655986785889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31937313079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61071968078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39313411712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48532962799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74717235565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77913379669189</t>
+    <t xml:space="preserve">9.31937217712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61071681976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39313220977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48532772064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74717140197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77913284301758</t>
   </si>
   <si>
     <t xml:space="preserve">9.7766752243042</t>
@@ -1541,97 +1541,97 @@
     <t xml:space="preserve">9.69554138183594</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93033599853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92419338226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96721744537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94508934020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0286808013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1602172851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98934459686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9942626953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0065536499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86764240264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91927433013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91804599761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88362312316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88731384277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91435432434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98074054718018</t>
+    <t xml:space="preserve">9.93033790588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92419147491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96721839904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94509029388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0286827087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1602182388306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98934555053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99426364898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.006555557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86764430999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91927528381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91804504394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88362407684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88731288909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91435623168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98073863983154</t>
   </si>
   <si>
     <t xml:space="preserve">9.97459316253662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0249938964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95738315582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0102415084839</t>
+    <t xml:space="preserve">10.0249929428101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95738410949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0102396011353</t>
   </si>
   <si>
     <t xml:space="preserve">10.1196517944336</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0446615219116</t>
+    <t xml:space="preserve">10.0446643829346</t>
   </si>
   <si>
     <t xml:space="preserve">9.95984172821045</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0139303207397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2093925476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1417789459229</t>
+    <t xml:space="preserve">10.0139312744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2093887329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1417798995972</t>
   </si>
   <si>
     <t xml:space="preserve">10.0717086791992</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80741024017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80863475799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90452194213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78036308288574</t>
+    <t xml:space="preserve">9.80740642547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80863666534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9045238494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78036212921143</t>
   </si>
   <si>
     <t xml:space="preserve">9.72627258300781</t>
@@ -1640,241 +1640,241 @@
     <t xml:space="preserve">9.84182834625244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94140434265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0311403274536</t>
+    <t xml:space="preserve">9.94140243530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0311412811279</t>
   </si>
   <si>
     <t xml:space="preserve">9.97828006744385</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0803117752075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0999822616577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0827713012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8221607208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88608264923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91066932678223</t>
+    <t xml:space="preserve">10.0803146362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0999813079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0827732086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82215881347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88608360290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91067028045654</t>
   </si>
   <si>
     <t xml:space="preserve">9.80986595153809</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72750282287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66603660583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74225425720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76069450378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8455171585083</t>
+    <t xml:space="preserve">9.72750186920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66603755950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74225521087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76069355010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84551525115967</t>
   </si>
   <si>
     <t xml:space="preserve">9.82707691192627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82584762573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91558647155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0422058105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1928119659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4401264190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4704084396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4300317764282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2723083496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2962808609009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3101596832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3316106796265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2697839736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2634735107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99723434448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2596883773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1915502548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91143226623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85465145111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94423866271973</t>
+    <t xml:space="preserve">9.82584667205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9155855178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0422048568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1928129196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4401245117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4704074859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4300327301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2723073959351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2962827682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3101606369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3316116333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2697811126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2634744644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99723339080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2596893310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1915531158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91143131256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85465240478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94423961639404</t>
   </si>
   <si>
     <t xml:space="preserve">9.98840236663818</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83193874359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6477165222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70954418182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57326889038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43194770812988</t>
+    <t xml:space="preserve">9.83193969726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64771556854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70954322814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57327175140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43194675445557</t>
   </si>
   <si>
     <t xml:space="preserve">9.28810501098633</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44708919525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54803562164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69188022613525</t>
+    <t xml:space="preserve">9.44709205627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54803466796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69188117980957</t>
   </si>
   <si>
     <t xml:space="preserve">9.7070198059082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90890884399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73225593566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69061851501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74865913391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67673873901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86348342895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82563018798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75118350982666</t>
+    <t xml:space="preserve">9.90890979766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73225688934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69061756134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74866008758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67673683166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86348438262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82563209533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75118446350098</t>
   </si>
   <si>
     <t xml:space="preserve">9.77137279510498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55686569213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4168062210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44835186004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40040588378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28684329986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11775970458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22879981994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03195762634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87044906616211</t>
+    <t xml:space="preserve">9.5568675994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41680812835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4483528137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40040397644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28684234619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11776065826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22879886627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03195953369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87044811248779</t>
   </si>
   <si>
     <t xml:space="preserve">9.0193395614624</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95498847961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92975234985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96886730194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98779582977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15561580657959</t>
+    <t xml:space="preserve">8.95498752593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92975330352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96886825561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98779678344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15561389923096</t>
   </si>
   <si>
     <t xml:space="preserve">9.09378623962402</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01555633544922</t>
+    <t xml:space="preserve">9.0155553817749</t>
   </si>
   <si>
     <t xml:space="preserve">8.72786426544189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90451622009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79473876953125</t>
+    <t xml:space="preserve">8.90451526641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79474067687988</t>
   </si>
   <si>
     <t xml:space="preserve">8.87423515319824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98148632049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99788951873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92596817016602</t>
+    <t xml:space="preserve">8.98148536682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99789047241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92596912384033</t>
   </si>
   <si>
     <t xml:space="preserve">8.80735969543457</t>
@@ -1886,43 +1886,43 @@
     <t xml:space="preserve">8.80104923248291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72281646728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69001007080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52976417541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67360973358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69379425048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73164844512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04709911346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96760654449463</t>
+    <t xml:space="preserve">8.72281742095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69001197814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52976226806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67360782623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69379711151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73165130615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04709815979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96760749816895</t>
   </si>
   <si>
     <t xml:space="preserve">8.91208839416504</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99410438537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98527145385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93984603881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90830230712891</t>
+    <t xml:space="preserve">8.99410247802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98527240753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93984794616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90830135345459</t>
   </si>
   <si>
     <t xml:space="preserve">8.99031925201416</t>
@@ -1931,88 +1931,88 @@
     <t xml:space="preserve">9.00924587249756</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97013282775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21617984771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17706394195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13290214538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09504795074463</t>
+    <t xml:space="preserve">8.97013187408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21618270874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1770658493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13290119171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09504985809326</t>
   </si>
   <si>
     <t xml:space="preserve">9.19346904754639</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10514354705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16192436218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23889350891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34109973907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3196496963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32848262786865</t>
+    <t xml:space="preserve">9.10514450073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1619234085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23889446258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34109878540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31964874267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32848358154297</t>
   </si>
   <si>
     <t xml:space="preserve">9.42563915252686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37516689300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16949653625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15813636779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24267864227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30955410003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37264442443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32469463348389</t>
+    <t xml:space="preserve">9.375168800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16949558258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15814018249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24268054962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30955505371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37264537811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32469654083252</t>
   </si>
   <si>
     <t xml:space="preserve">9.5392017364502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5745325088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58841323852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62248134613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63383865356445</t>
+    <t xml:space="preserve">9.57453155517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58841037750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62248039245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63383674621582</t>
   </si>
   <si>
     <t xml:space="preserve">9.64519309997559</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59724426269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59598350524902</t>
+    <t xml:space="preserve">9.597243309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59598255157471</t>
   </si>
   <si>
     <t xml:space="preserve">9.60355377197266</t>
@@ -2030,61 +2030,61 @@
     <t xml:space="preserve">9.57957935333252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64014434814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44330501556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54046249389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56696033477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80670356750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80291748046875</t>
+    <t xml:space="preserve">9.64014625549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44330596923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5404634475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56696224212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80670166015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80291843414307</t>
   </si>
   <si>
     <t xml:space="preserve">9.83446311950684</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93288230895996</t>
+    <t xml:space="preserve">9.93288421630859</t>
   </si>
   <si>
     <t xml:space="preserve">10.0249948501587</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9530725479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98713874816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90512466430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85717487335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85212898254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83572578430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76632308959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93919372558594</t>
+    <t xml:space="preserve">9.95307159423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98713970184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90512371063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85717391967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85212707519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83572387695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76632595062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93919086456299</t>
   </si>
   <si>
     <t xml:space="preserve">9.96190357208252</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0338277816772</t>
+    <t xml:space="preserve">10.0338268280029</t>
   </si>
   <si>
     <t xml:space="preserve">9.94045162200928</t>
@@ -2093,187 +2093,187 @@
     <t xml:space="preserve">9.99849605560303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9770450592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0237340927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0565385818481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0464448928833</t>
+    <t xml:space="preserve">9.97704792022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0237321853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0565366744995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.046443939209</t>
   </si>
   <si>
     <t xml:space="preserve">9.97830772399902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88619613647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73478221893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73604202270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96695232391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8104887008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78272914886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67926406860352</t>
+    <t xml:space="preserve">9.88619518280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73478126525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73604106903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96695137023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81048774719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78273010253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67926120758057</t>
   </si>
   <si>
     <t xml:space="preserve">9.52532196044922</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60103034973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48494434356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51901435852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38274002075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14173603057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13542556762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03700542449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.000412940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09883499145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21365833282471</t>
+    <t xml:space="preserve">9.60103130340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48494529724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51901340484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38273906707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1417350769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13542366027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03700637817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00041198730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09883403778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21365642547607</t>
   </si>
   <si>
     <t xml:space="preserve">9.15939998626709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30576801300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36255073547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35346508026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43392086029053</t>
+    <t xml:space="preserve">9.30576992034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36255168914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35346698760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43392276763916</t>
   </si>
   <si>
     <t xml:space="preserve">9.35476398468018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03164863586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11859321594238</t>
+    <t xml:space="preserve">9.03164958953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11859226226807</t>
   </si>
   <si>
     <t xml:space="preserve">9.12897205352783</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10042476654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91096782684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88371658325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81104755401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96676540374756</t>
+    <t xml:space="preserve">9.10042381286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91096687316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88371562957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8110466003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96676445007324</t>
   </si>
   <si>
     <t xml:space="preserve">9.09523296356201</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99791049957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0186710357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05760288238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08355331420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11340045928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02126789093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04722309112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99920654296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18477058410645</t>
+    <t xml:space="preserve">8.99790954589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01867294311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05760192871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08355522155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11340141296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02126693725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04722118377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99920558929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18477153778076</t>
   </si>
   <si>
     <t xml:space="preserve">9.22759437561035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31583404541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47674465179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42224216461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36903667449951</t>
+    <t xml:space="preserve">9.31583499908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47674179077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4222412109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36903858184814</t>
   </si>
   <si>
     <t xml:space="preserve">9.41315746307373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38590908050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49880313873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4066686630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45208835601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50269412994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44040966033936</t>
+    <t xml:space="preserve">9.38590621948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49880409240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40666961669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45208644866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50269508361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44040775299072</t>
   </si>
   <si>
     <t xml:space="preserve">9.50788593292236</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54162693023682</t>
+    <t xml:space="preserve">9.54162502288818</t>
   </si>
   <si>
     <t xml:space="preserve">9.60261344909668</t>
@@ -2282,28 +2282,28 @@
     <t xml:space="preserve">9.61948394775391</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54551792144775</t>
+    <t xml:space="preserve">9.54551696777344</t>
   </si>
   <si>
     <t xml:space="preserve">9.5156717300415</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35216808319092</t>
+    <t xml:space="preserve">9.3521671295166</t>
   </si>
   <si>
     <t xml:space="preserve">9.27820205688477</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22629642486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28858280181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33659648895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31064319610596</t>
+    <t xml:space="preserve">9.22629547119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28858375549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33659839630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31064510345459</t>
   </si>
   <si>
     <t xml:space="preserve">9.30285739898682</t>
@@ -2321,19 +2321,19 @@
     <t xml:space="preserve">9.14584159851074</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87592887878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74616718292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68387794494629</t>
+    <t xml:space="preserve">8.87593173980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74616622924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68387603759766</t>
   </si>
   <si>
     <t xml:space="preserve">8.56060028076172</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7163200378418</t>
+    <t xml:space="preserve">8.71631908416748</t>
   </si>
   <si>
     <t xml:space="preserve">8.55930519104004</t>
@@ -2342,73 +2342,73 @@
     <t xml:space="preserve">8.54502964019775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70723819732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50090789794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46068000793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61250686645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52815914154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66181945800781</t>
+    <t xml:space="preserve">8.70723628997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50091075897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46068477630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61250877380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52816200256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66181755065918</t>
   </si>
   <si>
     <t xml:space="preserve">8.63716220855713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5268611907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57617378234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63067436218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.694260597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83570289611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89669418334961</t>
+    <t xml:space="preserve">8.52686214447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57617282867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63067626953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69425964355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8357048034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89669227600098</t>
   </si>
   <si>
     <t xml:space="preserve">8.82532405853271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86944198608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93432331085205</t>
+    <t xml:space="preserve">8.8694429397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93432521820068</t>
   </si>
   <si>
     <t xml:space="preserve">9.03294658660889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14973449707031</t>
+    <t xml:space="preserve">9.14973545074463</t>
   </si>
   <si>
     <t xml:space="preserve">9.13156795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11210346221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28728485107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18217658996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29377365112305</t>
+    <t xml:space="preserve">9.11210250854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28728580474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1821756362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29377555847168</t>
   </si>
   <si>
     <t xml:space="preserve">9.44170665740967</t>
@@ -2417,16 +2417,16 @@
     <t xml:space="preserve">9.45374202728271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35746383666992</t>
+    <t xml:space="preserve">9.35746479034424</t>
   </si>
   <si>
     <t xml:space="preserve">9.26787567138672</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31601333618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39624404907227</t>
+    <t xml:space="preserve">9.31601428985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39624214172363</t>
   </si>
   <si>
     <t xml:space="preserve">9.38287258148193</t>
@@ -2435,157 +2435,157 @@
     <t xml:space="preserve">9.34676742553711</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06328868865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9643383026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05526638031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12747383117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04858112335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09270668029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1475305557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25049114227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18898391723633</t>
+    <t xml:space="preserve">9.06328964233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96433925628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05526542663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12747478485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04858207702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09270572662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14752960205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25049209594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18898296356201</t>
   </si>
   <si>
     <t xml:space="preserve">9.25182819366455</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23711967468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21305084228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32938671112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40827655792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45240306854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38688278198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31868743896484</t>
+    <t xml:space="preserve">9.23712158203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21305179595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32938385009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.408278465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4524040222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38688087463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31868648529053</t>
   </si>
   <si>
     <t xml:space="preserve">9.24514293670654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15822696685791</t>
+    <t xml:space="preserve">9.15822792053223</t>
   </si>
   <si>
     <t xml:space="preserve">9.0726490020752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16223907470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3427562713623</t>
+    <t xml:space="preserve">9.16224002838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34275531768799</t>
   </si>
   <si>
     <t xml:space="preserve">9.49251747131348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46978664398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47780895233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48716831207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45106601715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52995777130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48182010650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50722789764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43368339538574</t>
+    <t xml:space="preserve">9.46978569030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47780799865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48716926574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45106506347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5299596786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48181915283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50722599029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43368148803711</t>
   </si>
   <si>
     <t xml:space="preserve">9.34008312225342</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36816120147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38821887969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39223003387451</t>
+    <t xml:space="preserve">9.36816215515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38821983337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39223098754883</t>
   </si>
   <si>
     <t xml:space="preserve">9.31467533111572</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28659534454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2264232635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16892433166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07398509979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01247787475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12212467193604</t>
+    <t xml:space="preserve">9.28659629821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22642517089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16892623901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07398700714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01247596740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12212371826172</t>
   </si>
   <si>
     <t xml:space="preserve">9.20636463165283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11008930206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1368350982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08735847473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12613391876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09538173675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1087532043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16090106964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23845863342285</t>
+    <t xml:space="preserve">9.1100902557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13683319091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08735752105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12613582611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09538269042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10875129699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16090202331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2384557723999</t>
   </si>
   <si>
     <t xml:space="preserve">9.25717830657959</t>
@@ -2600,106 +2600,106 @@
     <t xml:space="preserve">9.36548900604248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43100833892822</t>
+    <t xml:space="preserve">9.43100929260254</t>
   </si>
   <si>
     <t xml:space="preserve">9.57141017913818</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57408428192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49786853790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42699718475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27589797973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22508430480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28525733947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30397796630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28124713897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06462669372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99776935577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00579166412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82259941101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95765399932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88410949707031</t>
+    <t xml:space="preserve">9.57408618927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4978666305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42699813842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27589702606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2250862121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28525829315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30397891998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28124618530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06462478637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99776744842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00579261779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82260036468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95765209197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88411045074463</t>
   </si>
   <si>
     <t xml:space="preserve">8.64208316802979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46290111541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43081188201904</t>
+    <t xml:space="preserve">8.4629020690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43081092834473</t>
   </si>
   <si>
     <t xml:space="preserve">8.54981803894043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71027660369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67150115966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62870979309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54446983337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7584171295166</t>
+    <t xml:space="preserve">8.71027755737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67149925231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62871170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54446792602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75841426849365</t>
   </si>
   <si>
     <t xml:space="preserve">8.68353366851807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61935329437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63138484954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65010452270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62469863891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53377437591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13529777526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00693130493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06576633453369</t>
+    <t xml:space="preserve">8.61935138702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63138675689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65010547637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62469959259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53377246856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13529872894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00693035125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06576538085938</t>
   </si>
   <si>
     <t xml:space="preserve">7.86117887496948</t>
@@ -2708,172 +2708,172 @@
     <t xml:space="preserve">7.4600305557251</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43328762054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43462514877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45602226257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33300065994263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84226083755493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41550970077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45896768569946</t>
+    <t xml:space="preserve">7.43328905105591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43462419509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45601892471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33300018310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84226274490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4155101776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4589672088623</t>
   </si>
   <si>
     <t xml:space="preserve">5.382080078125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40728855133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62056541442871</t>
+    <t xml:space="preserve">4.40728807449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62056589126587</t>
   </si>
   <si>
     <t xml:space="preserve">4.34043073654175</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59048080444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4754843711853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65666961669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87596321105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87195158004761</t>
+    <t xml:space="preserve">4.5904803276062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47548341751099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65667009353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87596464157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87195253372192</t>
   </si>
   <si>
     <t xml:space="preserve">5.59936857223511</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83203554153442</t>
+    <t xml:space="preserve">5.83203458786011</t>
   </si>
   <si>
     <t xml:space="preserve">5.8240122795105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49373292922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74511861801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16432094573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15094900131226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57750415802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23451948165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22783422470093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30338478088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21446371078491</t>
+    <t xml:space="preserve">5.49373340606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74512004852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16432046890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15094804763794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57750368118286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23452043533325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22783660888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30338621139526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21446418762207</t>
   </si>
   <si>
     <t xml:space="preserve">6.22315549850464</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12888526916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73776483535767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65218591690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74110889434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63881397247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32190752029419</t>
+    <t xml:space="preserve">6.1288857460022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73776531219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65218687057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74110794067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63881492614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32190799713135</t>
   </si>
   <si>
     <t xml:space="preserve">5.58131694793701</t>
   </si>
   <si>
-    <t xml:space="preserve">5.664222240448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51579666137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61875772476196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80595922470093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98848295211792</t>
+    <t xml:space="preserve">5.66422080993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51579618453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61875820159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8059606552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98848247528076</t>
   </si>
   <si>
     <t xml:space="preserve">5.82601737976074</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48972272872925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80796718597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63146066665649</t>
+    <t xml:space="preserve">5.48972177505493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80796575546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63146114349365</t>
   </si>
   <si>
     <t xml:space="preserve">5.72038269042969</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77052640914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69965600967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69230222702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69631433486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09554815292358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90332460403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93500947952271</t>
+    <t xml:space="preserve">5.77052545547485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69965553283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69230175018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69631338119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09554767608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90332412719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93500852584839</t>
   </si>
   <si>
     <t xml:space="preserve">5.78925752639771</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75545930862427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81601333618164</t>
+    <t xml:space="preserve">5.75545883178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81601285934448</t>
   </si>
   <si>
     <t xml:space="preserve">5.82587051391602</t>
@@ -2882,160 +2882,160 @@
     <t xml:space="preserve">5.94979667663574</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97936725616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71954917907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87234258651733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17581796646118</t>
+    <t xml:space="preserve">5.97936868667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71954870223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87234210968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17581701278687</t>
   </si>
   <si>
     <t xml:space="preserve">6.3363561630249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31171274185181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69334268569946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80459403991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60180997848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49900770187378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0420355796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04625988006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04133033752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29129314422607</t>
+    <t xml:space="preserve">6.31171226501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69334411621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80459356307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60180902481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49900722503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04203605651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0462589263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04133081436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29129266738892</t>
   </si>
   <si>
     <t xml:space="preserve">6.26383256912231</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22088098526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24834156036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19835042953491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96528720855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97162246704102</t>
+    <t xml:space="preserve">6.22088193893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24834108352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19834995269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9652853012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97162294387817</t>
   </si>
   <si>
     <t xml:space="preserve">5.91247701644897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07301664352417</t>
+    <t xml:space="preserve">6.07301712036133</t>
   </si>
   <si>
     <t xml:space="preserve">5.97796058654785</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96739864349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13990879058838</t>
+    <t xml:space="preserve">5.96739816665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13990783691406</t>
   </si>
   <si>
     <t xml:space="preserve">6.1075177192688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16666460037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21031761169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12441635131836</t>
+    <t xml:space="preserve">6.166663646698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21031713485718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12441682815552</t>
   </si>
   <si>
     <t xml:space="preserve">5.9385290145874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09765911102295</t>
+    <t xml:space="preserve">6.09766006469727</t>
   </si>
   <si>
     <t xml:space="preserve">6.18426656723022</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22158479690552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26312780380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20538997650146</t>
+    <t xml:space="preserve">6.22158575057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26312923431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20539045333862</t>
   </si>
   <si>
     <t xml:space="preserve">6.18285846710205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28706789016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13075304031372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05611848831177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99908399581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95894956588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96880722045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92162990570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5047926902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30975198745728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30482339859009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53366231918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70053672790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59210300445557</t>
+    <t xml:space="preserve">6.28706741333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13075399398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05611753463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99908447265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95894908905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96880674362183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.921630859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50479316711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30975151062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3048243522644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53366184234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70053720474243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59210395812988</t>
   </si>
   <si>
     <t xml:space="preserve">5.49634456634521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62308597564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80474805831909</t>
+    <t xml:space="preserve">5.62308549880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80474710464478</t>
   </si>
   <si>
     <t xml:space="preserve">5.89557838439941</t>
@@ -3047,121 +3047,121 @@
     <t xml:space="preserve">5.75897979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70335531234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67096519470215</t>
+    <t xml:space="preserve">5.7033543586731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67096567153931</t>
   </si>
   <si>
     <t xml:space="preserve">5.723069190979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58717489242554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54351949691772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76742839813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68786287307739</t>
+    <t xml:space="preserve">5.58717441558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54352045059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76742887496948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68786334991455</t>
   </si>
   <si>
     <t xml:space="preserve">5.6061863899231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49211931228638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4752197265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40480756759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41889047622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38298034667969</t>
+    <t xml:space="preserve">5.49211883544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47522068023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40480852127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41889142990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38298082351685</t>
   </si>
   <si>
     <t xml:space="preserve">5.47310781478882</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29426193237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37100982666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36960363388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3505916595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26398515701294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35974454879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38720607757568</t>
+    <t xml:space="preserve">5.29426288604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37101078033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36960172653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35059118270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26398468017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35974407196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38720560073853</t>
   </si>
   <si>
     <t xml:space="preserve">5.34707069396973</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20202255249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97441530227661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05028438568115</t>
+    <t xml:space="preserve">5.20202207565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97441625595093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05028486251831</t>
   </si>
   <si>
     <t xml:space="preserve">4.95867013931274</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87564373016357</t>
+    <t xml:space="preserve">4.8756422996521</t>
   </si>
   <si>
     <t xml:space="preserve">4.78760719299316</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90999889373779</t>
+    <t xml:space="preserve">4.90999937057495</t>
   </si>
   <si>
     <t xml:space="preserve">4.77042865753174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78689050674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62513446807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6501841545105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78832244873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95151233673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8169527053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92789220809937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91142988204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88065338134766</t>
+    <t xml:space="preserve">4.78689098358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62513303756714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65018463134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78832292556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95151281356812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81695175170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92789363861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91143035888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88065385818481</t>
   </si>
   <si>
     <t xml:space="preserve">4.78545999526978</t>
@@ -3170,19 +3170,19 @@
     <t xml:space="preserve">4.79404830932617</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59364032745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69742345809937</t>
+    <t xml:space="preserve">4.59364080429077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69742298126221</t>
   </si>
   <si>
     <t xml:space="preserve">4.71388530731201</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69670724868774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53781270980835</t>
+    <t xml:space="preserve">4.6967077255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53781318664551</t>
   </si>
   <si>
     <t xml:space="preserve">4.53852796554565</t>
@@ -3191,91 +3191,91 @@
     <t xml:space="preserve">4.61224985122681</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46981763839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36603498458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21215009689331</t>
+    <t xml:space="preserve">4.4698166847229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36603355407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21214962005615</t>
   </si>
   <si>
     <t xml:space="preserve">4.23576879501343</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30233287811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55355834960938</t>
+    <t xml:space="preserve">4.30233335494995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55355882644653</t>
   </si>
   <si>
     <t xml:space="preserve">4.66235160827637</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72175884246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72104406356812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68239164352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28075456619263</t>
+    <t xml:space="preserve">4.7217583656311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72104358673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68239307403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28075408935547</t>
   </si>
   <si>
     <t xml:space="preserve">5.49547719955444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43392324447632</t>
+    <t xml:space="preserve">5.43392372131348</t>
   </si>
   <si>
     <t xml:space="preserve">5.45253229141235</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48259305953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70304298400879</t>
+    <t xml:space="preserve">5.48259258270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70304346084595</t>
   </si>
   <si>
     <t xml:space="preserve">5.78750133514404</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86480093002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78105783462524</t>
+    <t xml:space="preserve">5.86480045318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7810583114624</t>
   </si>
   <si>
     <t xml:space="preserve">5.81541442871094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96214056015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16970729827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20692539215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12533092498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1425085067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94281816482544</t>
+    <t xml:space="preserve">5.96214151382446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16970777511597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20692586898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12533140182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14251041412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94281768798828</t>
   </si>
   <si>
     <t xml:space="preserve">6.02298021316528</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08310174942017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04946279525757</t>
+    <t xml:space="preserve">6.08310270309448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04946231842041</t>
   </si>
   <si>
     <t xml:space="preserve">6.25846004486084</t>
@@ -3284,82 +3284,82 @@
     <t xml:space="preserve">6.27492237091064</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29138422012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32931804656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39588308334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30426692962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21122121810913</t>
+    <t xml:space="preserve">6.29138517379761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32931900024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39588165283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30426788330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21122074127197</t>
   </si>
   <si>
     <t xml:space="preserve">6.26418542861938</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26704931259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23484039306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17042350769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90058851242065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98361444473267</t>
+    <t xml:space="preserve">6.26704835891724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23484134674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17042303085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90058708190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98361349105835</t>
   </si>
   <si>
     <t xml:space="preserve">6.14394044876099</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15252923965454</t>
+    <t xml:space="preserve">6.15252876281738</t>
   </si>
   <si>
     <t xml:space="preserve">6.12819480895996</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11817264556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04659938812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27062559127808</t>
+    <t xml:space="preserve">6.11817359924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04659843444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27062749862671</t>
   </si>
   <si>
     <t xml:space="preserve">6.47604656219482</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49036026000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46316242218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42594289779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48033905029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48463582992554</t>
+    <t xml:space="preserve">6.49036121368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4631609916687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42594337463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48033952713013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48463535308838</t>
   </si>
   <si>
     <t xml:space="preserve">6.4452691078186</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32072877883911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33862209320068</t>
+    <t xml:space="preserve">6.32072973251343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33862400054932</t>
   </si>
   <si>
     <t xml:space="preserve">6.31786584854126</t>
@@ -3371,136 +3371,136 @@
     <t xml:space="preserve">6.20406341552734</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11387920379639</t>
+    <t xml:space="preserve">6.11387825012207</t>
   </si>
   <si>
     <t xml:space="preserve">5.97860383987427</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10385942459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11745738983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97788858413696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86909532546997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94854211807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07594633102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13391971588135</t>
+    <t xml:space="preserve">6.10385847091675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11745929718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9778881072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86909580230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94854307174683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07594537734985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13391923904419</t>
   </si>
   <si>
     <t xml:space="preserve">6.16326570510864</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21336793899536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28064775466919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33003377914429</t>
+    <t xml:space="preserve">6.21336698532104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28064680099487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33003425598145</t>
   </si>
   <si>
     <t xml:space="preserve">6.28207969665527</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35508584976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52972602844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49823379516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55835580825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51111698150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58340740203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69649505615234</t>
+    <t xml:space="preserve">6.35508441925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52972555160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49823427200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55835485458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51111650466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58340692520142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69649457931519</t>
   </si>
   <si>
     <t xml:space="preserve">6.74516439437866</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85467338562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92839622497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78667783737183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84322118759155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79383563995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91408061981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0686821937561</t>
+    <t xml:space="preserve">6.85467386245728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92839431762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78667831420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84322166442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79383516311646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91407918930054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06868171691895</t>
   </si>
   <si>
     <t xml:space="preserve">7.20180940628052</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28626871109009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25763654708862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31489849090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37215566635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45661306381226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39649057388306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32921075820923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39935636520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28197336196899</t>
+    <t xml:space="preserve">7.28626489639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25763702392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31489753723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.372154712677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45661354064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39649248123169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32921266555786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39935445785522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28197240829468</t>
   </si>
   <si>
     <t xml:space="preserve">7.26193189620972</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14311695098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3335075378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2375955581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32348585128784</t>
+    <t xml:space="preserve">7.14311742782593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33350563049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23759603500366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32348537445068</t>
   </si>
   <si>
     <t xml:space="preserve">7.40651273727417</t>
@@ -3509,184 +3509,184 @@
     <t xml:space="preserve">7.45232009887695</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51100969314575</t>
+    <t xml:space="preserve">7.5110125541687</t>
   </si>
   <si>
     <t xml:space="preserve">7.56540584564209</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49669647216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48381185531616</t>
+    <t xml:space="preserve">7.49669599533081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48381328582764</t>
   </si>
   <si>
     <t xml:space="preserve">7.34352540969849</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30058288574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27338409423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31919145584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50671672821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41796350479126</t>
+    <t xml:space="preserve">7.30058145523071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27338314056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31919097900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50671434402466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41796255111694</t>
   </si>
   <si>
     <t xml:space="preserve">7.40794277191162</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38933372497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21039724349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26479482650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27767610549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23043823242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26336145401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23616504669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30344581604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30201196670532</t>
+    <t xml:space="preserve">7.3893346786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21039772033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26479387283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27767705917358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23043870925903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26336240768433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23616552352905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3034462928772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30201244354248</t>
   </si>
   <si>
     <t xml:space="preserve">7.1073317527771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22900772094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37788057327271</t>
+    <t xml:space="preserve">7.22900819778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37788105010986</t>
   </si>
   <si>
     <t xml:space="preserve">7.39076566696167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38647127151489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44945859909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48524379730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37501859664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46520376205444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48953628540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46806526184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29771900177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36070489883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40907192230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31746768951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35044527053833</t>
+    <t xml:space="preserve">7.38646984100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4494571685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48524284362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3750171661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46520328521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48953914642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46806573867798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29771947860718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36070537567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40907335281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31746673583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35044479370117</t>
   </si>
   <si>
     <t xml:space="preserve">7.4017448425293</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39734697341919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36949682235718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54391384124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59961271286011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65091037750244</t>
+    <t xml:space="preserve">7.39734745025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36949825286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54391527175903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59961223602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65091180801392</t>
   </si>
   <si>
     <t xml:space="preserve">7.60694026947021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66117191314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69195079803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65384149551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70514011383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75497484207153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86196947097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86636877059937</t>
+    <t xml:space="preserve">7.66117095947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69194984436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65384244918823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7051420211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75497436523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8619704246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86636972427368</t>
   </si>
   <si>
     <t xml:space="preserve">7.87222957611084</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79015159606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55857467651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63478899002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6318564414978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63772010803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72419452667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73592090606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57909250259399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57616233825684</t>
+    <t xml:space="preserve">7.79015254974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55857181549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63478755950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63185691833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63771963119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72419595718384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73592042922974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57909107208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57616138458252</t>
   </si>
   <si>
     <t xml:space="preserve">7.52632808685303</t>
@@ -3695,175 +3695,175 @@
     <t xml:space="preserve">7.66556835174561</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62013053894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66263771057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45304250717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30134391784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38708686828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33139085769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34604644775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26250267028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20534086227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9283242225647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96423530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14524984359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06756448745728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08588695526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23025798797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18775272369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26763343811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33871936798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30793952941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42812490463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4164023399353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47502899169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54977893829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53658771514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58495426177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63332509994507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67876005172729</t>
+    <t xml:space="preserve">7.62013149261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66263723373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45304489135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30134344100952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3870849609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33139228820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34604787826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26250219345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20534038543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92832469940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96423578262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14524793624878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06756544113159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08588790893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23025751113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18775224685669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26763296127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33871984481812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3079400062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42812728881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41640186309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4750280380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54978084564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53658676147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58495664596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63332366943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67875909805298</t>
   </si>
   <si>
     <t xml:space="preserve">7.70807409286499</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60107707977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60401010513306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59668207168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3841552734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3738956451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49994468688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56150484085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57029819488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55271005630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64211845397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64504909515381</t>
+    <t xml:space="preserve">7.60107851028442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60401058197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59668111801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38415670394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37389612197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49994516372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56150341033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57029914855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55271053314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64211702346802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64505052566528</t>
   </si>
   <si>
     <t xml:space="preserve">7.79161834716797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71686744689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75790739059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76083946228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72712850570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91913270950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99095249176025</t>
+    <t xml:space="preserve">7.71686697006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75790691375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76083850860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.727126121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91913175582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99095153808594</t>
   </si>
   <si>
     <t xml:space="preserve">8.05397701263428</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07889556884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01879978179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94404363632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09050750732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30409622192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31630325317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33918476104736</t>
+    <t xml:space="preserve">8.07889270782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01880073547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94404172897339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09050559997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30409526824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3163013458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33918571472168</t>
   </si>
   <si>
     <t xml:space="preserve">8.5329418182373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59244441986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68703365325928</t>
+    <t xml:space="preserve">8.59244346618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68703174591064</t>
   </si>
   <si>
     <t xml:space="preserve">8.8075590133667</t>
@@ -3875,55 +3875,55 @@
     <t xml:space="preserve">8.8807897567749</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03793239593506</t>
+    <t xml:space="preserve">9.03793334960938</t>
   </si>
   <si>
     <t xml:space="preserve">8.89909934997559</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83959865570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04556083679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15845775604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13404941558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01809883117676</t>
+    <t xml:space="preserve">8.83959674835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04555892944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15845680236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13404750823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01809978485107</t>
   </si>
   <si>
     <t xml:space="preserve">9.13862419128418</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31254959106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33390617370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28508758544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39645767211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25609874725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21338176727295</t>
+    <t xml:space="preserve">9.31255054473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33390808105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28508853912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39645862579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25609970092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21338272094727</t>
   </si>
   <si>
     <t xml:space="preserve">9.36594581604004</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42697334289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35831832885742</t>
+    <t xml:space="preserve">9.42697238922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35831737518311</t>
   </si>
   <si>
     <t xml:space="preserve">9.27898502349854</t>
@@ -3932,79 +3932,79 @@
     <t xml:space="preserve">9.46206283569336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72294807434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5658073425293</t>
+    <t xml:space="preserve">9.7229471206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56580638885498</t>
   </si>
   <si>
     <t xml:space="preserve">9.44375514984131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58106327056885</t>
+    <t xml:space="preserve">9.58106422424316</t>
   </si>
   <si>
     <t xml:space="preserve">9.66649913787842</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67412853240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62683296203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66039657592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64666557312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54444694519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5703821182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6100492477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6054744720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48189449310303</t>
+    <t xml:space="preserve">9.67412662506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6268310546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66039562225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64666652679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54444599151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57038307189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61005020141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60547256469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48189640045166</t>
   </si>
   <si>
     <t xml:space="preserve">9.28203678131104</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40408515930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43612575531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37967777252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79535484313965</t>
+    <t xml:space="preserve">9.40408802032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43612480163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37967586517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79535388946533</t>
   </si>
   <si>
     <t xml:space="preserve">9.00131702423096</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08065128326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10811233520508</t>
+    <t xml:space="preserve">9.08065032958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10811138153076</t>
   </si>
   <si>
     <t xml:space="preserve">9.16151142120361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37662601470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58716583251953</t>
+    <t xml:space="preserve">9.37662696838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5871639251709</t>
   </si>
   <si>
     <t xml:space="preserve">9.45138359069824</t>
@@ -4013,16 +4013,16 @@
     <t xml:space="preserve">9.35679340362549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31102180480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16913795471191</t>
+    <t xml:space="preserve">9.3110237121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1691370010376</t>
   </si>
   <si>
     <t xml:space="preserve">9.26677894592285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15388107299805</t>
+    <t xml:space="preserve">9.15388202667236</t>
   </si>
   <si>
     <t xml:space="preserve">9.30492115020752</t>
@@ -4034,37 +4034,37 @@
     <t xml:space="preserve">9.02725124359131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29118824005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28661155700684</t>
+    <t xml:space="preserve">9.29118919372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28661251068115</t>
   </si>
   <si>
     <t xml:space="preserve">9.33695793151855</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37815093994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36747169494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32170391082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46511268615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61920166015625</t>
+    <t xml:space="preserve">9.37814998626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36747264862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.321702003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46511173248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61920356750488</t>
   </si>
   <si>
     <t xml:space="preserve">9.73057556152344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64971733093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75651359558105</t>
+    <t xml:space="preserve">9.6497163772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75651168823242</t>
   </si>
   <si>
     <t xml:space="preserve">9.6756534576416</t>
@@ -4073,34 +4073,34 @@
     <t xml:space="preserve">9.77176952362061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95637130737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93501281738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0387563705444</t>
+    <t xml:space="preserve">9.95637226104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9350118637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0387554168701</t>
   </si>
   <si>
     <t xml:space="preserve">10.0784225463867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1226692199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2370901107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1379232406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9975643157959</t>
+    <t xml:space="preserve">10.1226673126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2370929718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1379241943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99756526947021</t>
   </si>
   <si>
     <t xml:space="preserve">9.67717838287354</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98840808868408</t>
+    <t xml:space="preserve">9.98841094970703</t>
   </si>
   <si>
     <t xml:space="preserve">10.2859106063843</t>
@@ -4112,10 +4112,10 @@
     <t xml:space="preserve">10.354564666748</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1516523361206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2645511627197</t>
+    <t xml:space="preserve">10.1516542434692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.264552116394</t>
   </si>
   <si>
     <t xml:space="preserve">10.1882696151733</t>
@@ -4124,19 +4124,19 @@
     <t xml:space="preserve">10.1363973617554</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2828607559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0585889816284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94416999816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1089363098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1440267562866</t>
+    <t xml:space="preserve">10.2828598022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0585918426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94416522979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1089372634888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1440258026123</t>
   </si>
   <si>
     <t xml:space="preserve">10.3194761276245</t>
@@ -4145,7 +4145,7 @@
     <t xml:space="preserve">10.1638612747192</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0479116439819</t>
+    <t xml:space="preserve">10.0479097366333</t>
   </si>
   <si>
     <t xml:space="preserve">10.1714868545532</t>
@@ -4157,43 +4157,43 @@
     <t xml:space="preserve">10.156231880188</t>
   </si>
   <si>
-    <t xml:space="preserve">10.292013168335</t>
+    <t xml:space="preserve">10.2920122146606</t>
   </si>
   <si>
     <t xml:space="preserve">10.2416667938232</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1928472518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5117063522339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5513725280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8717613220215</t>
+    <t xml:space="preserve">10.1928482055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5117073059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5513734817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8717594146729</t>
   </si>
   <si>
     <t xml:space="preserve">11.0838251113892</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5773096084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80533313751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2264137268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4277973175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3759241104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99603748321533</t>
+    <t xml:space="preserve">10.5773086547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80533218383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2264127731323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4277963638306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3759250640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99603843688965</t>
   </si>
   <si>
     <t xml:space="preserve">9.89992332458496</t>
@@ -4202,52 +4202,52 @@
     <t xml:space="preserve">9.85873222351074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74125576019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0006141662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70921802520752</t>
+    <t xml:space="preserve">9.74125480651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0006132125854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70921611785889</t>
   </si>
   <si>
     <t xml:space="preserve">10.086051940918</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2706546783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1241941452026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98993587493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.208104133606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1409749984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2325143814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2538719177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3042182922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2126798629761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1165647506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5406942367554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5239114761353</t>
+    <t xml:space="preserve">10.2706575393677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.124192237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9899377822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2081031799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1409740447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.232515335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2538728713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.304220199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2126779556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1165637969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5406932830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5239124298096</t>
   </si>
   <si>
     <t xml:space="preserve">10.8122606277466</t>
@@ -4256,130 +4256,130 @@
     <t xml:space="preserve">10.8320913314819</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7939529418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8534526824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6795282363892</t>
+    <t xml:space="preserve">10.7939519882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8534507751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6795301437378</t>
   </si>
   <si>
     <t xml:space="preserve">10.3591432571411</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86330699920654</t>
+    <t xml:space="preserve">9.86330795288086</t>
   </si>
   <si>
     <t xml:space="preserve">9.88466644287109</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0372314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2142038345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0692682266235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.374400138855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3057460784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3774509429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97620487213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1135139465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3896551132202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4049119949341</t>
+    <t xml:space="preserve">10.0372304916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2142057418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0692701339722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3743982315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3057451248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3774499893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97620677947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1135120391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3896541595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4049110412598</t>
   </si>
   <si>
     <t xml:space="preserve">10.5467977523804</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6276578903198</t>
+    <t xml:space="preserve">10.6276559829712</t>
   </si>
   <si>
     <t xml:space="preserve">10.5162839889526</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5956201553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7955636978149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7136964797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1151638031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2143507003784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1718416213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1781396865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.176568031311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0978450775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0773792266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2237968444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3607711791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3576211929321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3292827606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0411710739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4224348068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2161922454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3673334121704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4334554672241</t>
+    <t xml:space="preserve">10.5956163406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7955656051636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7136974334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1151647567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2143516540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1718425750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1781406402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1765661239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.097846031189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0773801803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2237987518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3607692718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3576202392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3292808532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0411691665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.422435760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2161903381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3673315048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4334545135498</t>
   </si>
   <si>
     <t xml:space="preserve">9.92335510253906</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45418834686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48095226287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50929260253906</t>
+    <t xml:space="preserve">9.45419025421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4809513092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50929355621338</t>
   </si>
   <si>
     <t xml:space="preserve">9.17866992950439</t>
@@ -4388,19 +4388,19 @@
     <t xml:space="preserve">8.99761581420898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18339252471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05272102355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13301372528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91732311248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83860301971436</t>
+    <t xml:space="preserve">9.18339538574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05272006988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13301467895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91732406616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83860111236572</t>
   </si>
   <si>
     <t xml:space="preserve">9.05114555358887</t>
@@ -4412,10 +4412,10 @@
     <t xml:space="preserve">8.46704864501953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69533443450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83702754974365</t>
+    <t xml:space="preserve">8.69533348083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83702850341797</t>
   </si>
   <si>
     <t xml:space="preserve">8.81656169891357</t>
@@ -4424,76 +4424,76 @@
     <t xml:space="preserve">8.76775455474854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75043869018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37888240814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53159618377686</t>
+    <t xml:space="preserve">8.75043678283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37888336181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53159713745117</t>
   </si>
   <si>
     <t xml:space="preserve">8.67014312744141</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89842796325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79609394073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65912437438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63550662994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70792865753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67486667633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73154354095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22275447845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21173191070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00863647460938</t>
+    <t xml:space="preserve">8.89842891693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79609489440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65912342071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63550853729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70792770385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67486763000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73154449462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22275257110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21173286437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00863552093506</t>
   </si>
   <si>
     <t xml:space="preserve">8.97399997711182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9661283493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01808452606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01021099090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04642200469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99289417266846</t>
+    <t xml:space="preserve">8.96612739562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01808166503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01021194458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04642105102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99289321899414</t>
   </si>
   <si>
     <t xml:space="preserve">9.12356662750244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15505504608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11411952972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20386123657227</t>
+    <t xml:space="preserve">9.15505409240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11412143707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20386219024658</t>
   </si>
   <si>
     <t xml:space="preserve">9.39436054229736</t>
@@ -4514,25 +4514,25 @@
     <t xml:space="preserve">9.84463405609131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.695068359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83991146087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63209247589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29517555236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23062610626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51401424407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67460250854492</t>
+    <t xml:space="preserve">9.69506931304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83991241455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6320915222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29517459869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23062419891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51401329040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67460155487061</t>
   </si>
   <si>
     <t xml:space="preserve">9.40853023529053</t>
@@ -4547,19 +4547,19 @@
     <t xml:space="preserve">9.19598770141602</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40223503112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31721687316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29675102233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08420562744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94121646881104</t>
+    <t xml:space="preserve">9.40223407745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31721782684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29675006866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08420848846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94121742248535</t>
   </si>
   <si>
     <t xml:space="preserve">9.10174179077148</t>
@@ -4574,46 +4574,46 @@
     <t xml:space="preserve">8.62979888916016</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65708923339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75661373138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0230827331543</t>
+    <t xml:space="preserve">8.65708637237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75661182403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02308368682861</t>
   </si>
   <si>
     <t xml:space="preserve">9.2622652053833</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40994930267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41476154327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50305271148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45650005340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28634262084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14668846130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3810510635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52231502532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5239200592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70691680908203</t>
+    <t xml:space="preserve">9.40994739532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41476249694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50305461883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45649909973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28634357452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14668560028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38105297088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52231597900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52392196655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70691776275635</t>
   </si>
   <si>
     <t xml:space="preserve">9.67802429199219</t>
@@ -4628,46 +4628,46 @@
     <t xml:space="preserve">10.0199413299561</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3682794570923</t>
+    <t xml:space="preserve">10.368278503418</t>
   </si>
   <si>
     <t xml:space="preserve">10.5432510375977</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6379594802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8065128326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.859486579895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.011981010437</t>
+    <t xml:space="preserve">10.6379613876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8065137863159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8594846725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0119819641113</t>
   </si>
   <si>
     <t xml:space="preserve">11.2447423934937</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4518213272095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4084777832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2543754577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2928991317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4598455429077</t>
+    <t xml:space="preserve">11.4518184661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4084768295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2543745040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2929000854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4598474502563</t>
   </si>
   <si>
     <t xml:space="preserve">11.6171607971191</t>
   </si>
   <si>
-    <t xml:space="preserve">11.618763923645</t>
+    <t xml:space="preserve">11.6187648773193</t>
   </si>
   <si>
     <t xml:space="preserve">11.5240564346313</t>
@@ -4676,64 +4676,64 @@
     <t xml:space="preserve">11.3057432174683</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3876104354858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9604110717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.456093788147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5115308761597</t>
+    <t xml:space="preserve">11.3876094818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.960412979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4560918807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5115299224854</t>
   </si>
   <si>
     <t xml:space="preserve">11.5637073516846</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6566467285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4283742904663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5734920501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6778440475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4870719909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3256492614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2783651351929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1218357086182</t>
+    <t xml:space="preserve">11.6566495895386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4283723831177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5734910964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.677845954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4870710372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3256511688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2783641815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1218328475952</t>
   </si>
   <si>
     <t xml:space="preserve">10.9538898468018</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256328582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0272626876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0941143035889</t>
+    <t xml:space="preserve">11.0256338119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0272636413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0941152572632</t>
   </si>
   <si>
     <t xml:space="preserve">11.262059211731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0957450866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6391973495483</t>
+    <t xml:space="preserve">11.0957469940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.639199256897</t>
   </si>
   <si>
     <t xml:space="preserve">10.5169086456299</t>
@@ -4745,121 +4745,121 @@
     <t xml:space="preserve">10.5984344482422</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9750862121582</t>
+    <t xml:space="preserve">10.9750871658325</t>
   </si>
   <si>
     <t xml:space="preserve">10.904974937439</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9865007400513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0435667037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0125885009766</t>
+    <t xml:space="preserve">10.986499786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0435695648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0125894546509</t>
   </si>
   <si>
     <t xml:space="preserve">11.0810708999634</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8315992355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1756429672241</t>
+    <t xml:space="preserve">10.831600189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1756420135498</t>
   </si>
   <si>
     <t xml:space="preserve">11.2392330169678</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0680265426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.281626701355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3680448532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.392502784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6093626022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7528486251831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.757740020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6811056137085</t>
+    <t xml:space="preserve">11.0680284500122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2816247940063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3680458068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3925018310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6093616485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7528495788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7577409744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6811075210571</t>
   </si>
   <si>
     <t xml:space="preserve">11.7169771194458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7887191772461</t>
+    <t xml:space="preserve">11.788722038269</t>
   </si>
   <si>
     <t xml:space="preserve">11.6207752227783</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7854604721069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7398042678833</t>
+    <t xml:space="preserve">11.7854614257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.739803314209</t>
   </si>
   <si>
     <t xml:space="preserve">11.5604467391968</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4756593704224</t>
+    <t xml:space="preserve">11.4756603240967</t>
   </si>
   <si>
     <t xml:space="preserve">11.5751218795776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6517553329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5522947311401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5245742797852</t>
+    <t xml:space="preserve">11.6517562866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5522956848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5245752334595</t>
   </si>
   <si>
     <t xml:space="preserve">11.2881488800049</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2098808288574</t>
+    <t xml:space="preserve">11.2098827362061</t>
   </si>
   <si>
     <t xml:space="preserve">11.2865161895752</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1658573150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3370628356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5441398620605</t>
+    <t xml:space="preserve">11.1658601760864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.337064743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5441417694092</t>
   </si>
   <si>
     <t xml:space="preserve">11.6941499710083</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0251474380493</t>
+    <t xml:space="preserve">12.025146484375</t>
   </si>
   <si>
     <t xml:space="preserve">12.0398216247559</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0871067047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9762296676636</t>
+    <t xml:space="preserve">12.0871076583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9762306213379</t>
   </si>
   <si>
     <t xml:space="preserve">11.9957971572876</t>
@@ -4871,37 +4871,37 @@
     <t xml:space="preserve">11.6990404129028</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6321897506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5066385269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8902978897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7549667358398</t>
+    <t xml:space="preserve">11.6321887969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5066404342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8902988433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7549657821655</t>
   </si>
   <si>
     <t xml:space="preserve">10.92453956604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8968210220337</t>
+    <t xml:space="preserve">10.8968229293823</t>
   </si>
   <si>
     <t xml:space="preserve">10.7370300292969</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8788862228394</t>
+    <t xml:space="preserve">10.8788871765137</t>
   </si>
   <si>
     <t xml:space="preserve">10.952260017395</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0354166030884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9424743652344</t>
+    <t xml:space="preserve">11.0354156494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9424753189087</t>
   </si>
   <si>
     <t xml:space="preserve">10.9392156600952</t>
@@ -4910,7 +4910,7 @@
     <t xml:space="preserve">10.9180173873901</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9489984512329</t>
+    <t xml:space="preserve">10.9489994049072</t>
   </si>
   <si>
     <t xml:space="preserve">10.5364751815796</t>
@@ -4919,109 +4919,109 @@
     <t xml:space="preserve">10.6310443878174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0359039306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91524314880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1344366073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3486490249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3602743148804</t>
+    <t xml:space="preserve">10.0359029769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91524410247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1344375610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3486499786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3602752685547</t>
   </si>
   <si>
     <t xml:space="preserve">10.3403482437134</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1062088012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2191247940063</t>
+    <t xml:space="preserve">10.1062078475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2191257476807</t>
   </si>
   <si>
     <t xml:space="preserve">10.4167337417603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5230121612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6990308761597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7156362533569</t>
+    <t xml:space="preserve">10.5230102539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.699028968811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7156352996826</t>
   </si>
   <si>
     <t xml:space="preserve">11.152364730835</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0510721206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1540241241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2420377731323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4446249008179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3466529846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5110483169556</t>
+    <t xml:space="preserve">11.0510702133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1540260314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2420349121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4446239471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3466539382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5110492706299</t>
   </si>
   <si>
     <t xml:space="preserve">11.4595708847046</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5243330001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5326366424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4197158813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2785682678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4296798706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4728546142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3034782409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4130735397339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1938800811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.934832572937</t>
+    <t xml:space="preserve">11.5243320465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5326356887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4197149276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2785692214966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4296789169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4728555679321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3034791946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4130754470825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1938810348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9348316192627</t>
   </si>
   <si>
     <t xml:space="preserve">10.8252334594727</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7720937728882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2669448852539</t>
+    <t xml:space="preserve">10.7720947265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2669439315796</t>
   </si>
   <si>
     <t xml:space="preserve">11.3283863067627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2254314422607</t>
+    <t xml:space="preserve">11.2254304885864</t>
   </si>
   <si>
     <t xml:space="preserve">10.9547576904297</t>
@@ -5030,55 +5030,55 @@
     <t xml:space="preserve">11.1141710281372</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0809602737427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9846477508545</t>
+    <t xml:space="preserve">11.080961227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9846487045288</t>
   </si>
   <si>
     <t xml:space="preserve">11.1224746704102</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0759782791138</t>
+    <t xml:space="preserve">11.0759792327881</t>
   </si>
   <si>
     <t xml:space="preserve">11.1673097610474</t>
   </si>
   <si>
-    <t xml:space="preserve">11.201075553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2804183959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2837934494019</t>
+    <t xml:space="preserve">11.2010736465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2804174423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2837953567505</t>
   </si>
   <si>
     <t xml:space="preserve">11.0119972229004</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1352367401123</t>
+    <t xml:space="preserve">11.135235786438</t>
   </si>
   <si>
     <t xml:space="preserve">11.1554927825928</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8938255310059</t>
+    <t xml:space="preserve">10.8938245773315</t>
   </si>
   <si>
     <t xml:space="preserve">10.5089206695557</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7942218780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0930290222168</t>
+    <t xml:space="preserve">10.7942237854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0930309295654</t>
   </si>
   <si>
     <t xml:space="preserve">11.0592670440674</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9596633911133</t>
+    <t xml:space="preserve">10.9596643447876</t>
   </si>
   <si>
     <t xml:space="preserve">11.040696144104</t>
@@ -5087,67 +5087,67 @@
     <t xml:space="preserve">11.071084022522</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8296747207642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9394054412842</t>
+    <t xml:space="preserve">10.8296737670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9394073486328</t>
   </si>
   <si>
     <t xml:space="preserve">10.9613523483276</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0153732299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9545984268188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.964729309082</t>
+    <t xml:space="preserve">11.0153751373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9546003341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9647283554077</t>
   </si>
   <si>
     <t xml:space="preserve">10.8178577423096</t>
   </si>
   <si>
-    <t xml:space="preserve">11.028881072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8769435882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8009748458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9208364486694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7587718963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8060388565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8786306381226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1267938613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3209352493286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3648281097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2854833602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0018701553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0170621871948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0744619369507</t>
+    <t xml:space="preserve">11.0288820266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8769426345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8009738922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9208374023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.758770942688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.806040763855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8786315917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1267948150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3209362030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3648271560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2854824066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0018692016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0170612335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0744609832764</t>
   </si>
   <si>
     <t xml:space="preserve">11.1706867218018</t>
@@ -5156,46 +5156,46 @@
     <t xml:space="preserve">11.4239149093628</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4965057373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3327512741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2213306427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3361282348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4289798736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5133867263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6551933288574</t>
+    <t xml:space="preserve">11.4965047836304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3327522277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2213325500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3361291885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4289779663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5133876800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6551923751831</t>
   </si>
   <si>
     <t xml:space="preserve">11.572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4711818695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.58935546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5285797119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7193441390991</t>
+    <t xml:space="preserve">11.4711828231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5893545150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5285816192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7193450927734</t>
   </si>
   <si>
     <t xml:space="preserve">11.6281833648682</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5353355407715</t>
+    <t xml:space="preserve">11.5353364944458</t>
   </si>
   <si>
     <t xml:space="preserve">11.5842914581299</t>
@@ -5210,19 +5210,19 @@
     <t xml:space="preserve">11.8746576309204</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9236145019531</t>
+    <t xml:space="preserve">11.9236154556274</t>
   </si>
   <si>
     <t xml:space="preserve">11.8577756881714</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8290777206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7581729888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7953147888184</t>
+    <t xml:space="preserve">11.8290767669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7581739425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7953128814697</t>
   </si>
   <si>
     <t xml:space="preserve">11.8459596633911</t>
@@ -5231,13 +5231,13 @@
     <t xml:space="preserve">11.8932275772095</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9134855270386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8797225952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9253044128418</t>
+    <t xml:space="preserve">11.9134864807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8797235488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9253034591675</t>
   </si>
   <si>
     <t xml:space="preserve">11.9472494125366</t>
@@ -5252,7 +5252,7 @@
     <t xml:space="preserve">12.1278848648071</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0569820404053</t>
+    <t xml:space="preserve">12.0569829940796</t>
   </si>
   <si>
     <t xml:space="preserve">12.2713804244995</t>
@@ -5264,7 +5264,7 @@
     <t xml:space="preserve">12.5212306976318</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4857797622681</t>
+    <t xml:space="preserve">12.4857778549194</t>
   </si>
   <si>
     <t xml:space="preserve">12.4418859481812</t>
@@ -5282,7 +5282,7 @@
     <t xml:space="preserve">12.7643280029297</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9736633300781</t>
+    <t xml:space="preserve">12.9736623764038</t>
   </si>
   <si>
     <t xml:space="preserve">12.9449653625488</t>
@@ -5291,13 +5291,13 @@
     <t xml:space="preserve">12.8403491973877</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1198949813843</t>
+    <t xml:space="preserve">13.1198968887329</t>
   </si>
   <si>
     <t xml:space="preserve">13.0650148391724</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8763628005981</t>
+    <t xml:space="preserve">12.8763637542725</t>
   </si>
   <si>
     <t xml:space="preserve">13.0667295455933</t>
@@ -5306,7 +5306,7 @@
     <t xml:space="preserve">13.04958152771</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0152807235718</t>
+    <t xml:space="preserve">13.0152797698975</t>
   </si>
   <si>
     <t xml:space="preserve">13.1816358566284</t>
@@ -5321,10 +5321,10 @@
     <t xml:space="preserve">12.7768907546997</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6294002532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4321727752686</t>
+    <t xml:space="preserve">12.6293983459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4321746826172</t>
   </si>
   <si>
     <t xml:space="preserve">12.3824367523193</t>
@@ -5333,7 +5333,7 @@
     <t xml:space="preserve">12.5539388656616</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8386325836182</t>
+    <t xml:space="preserve">12.8386316299438</t>
   </si>
   <si>
     <t xml:space="preserve">12.9912691116333</t>
@@ -5342,10 +5342,10 @@
     <t xml:space="preserve">12.9363889694214</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1164646148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.28968334198</t>
+    <t xml:space="preserve">13.1164655685425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2896823883057</t>
   </si>
   <si>
     <t xml:space="preserve">13.2742462158203</t>
@@ -5354,52 +5354,52 @@
     <t xml:space="preserve">13.3188371658325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4114503860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2502365112305</t>
+    <t xml:space="preserve">13.411449432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2502355575562</t>
   </si>
   <si>
     <t xml:space="preserve">13.2039308547974</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2365169525146</t>
+    <t xml:space="preserve">13.236517906189</t>
   </si>
   <si>
     <t xml:space="preserve">13.2107915878296</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2759637832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.299973487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1747770309448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2296571731567</t>
+    <t xml:space="preserve">13.2759618759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2999744415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1747760772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2296562194824</t>
   </si>
   <si>
     <t xml:space="preserve">13.4663305282593</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1764917373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2090787887573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.872932434082</t>
+    <t xml:space="preserve">13.17649269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.209077835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8729333877563</t>
   </si>
   <si>
     <t xml:space="preserve">12.713436126709</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8077621459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8609285354614</t>
+    <t xml:space="preserve">12.8077611923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8609275817871</t>
   </si>
   <si>
     <t xml:space="preserve">13.0615863800049</t>
@@ -5408,22 +5408,22 @@
     <t xml:space="preserve">13.0770206451416</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0255708694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7425928115845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0697469711304</t>
+    <t xml:space="preserve">13.0255689620972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7425909042358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0697460174561</t>
   </si>
   <si>
     <t xml:space="preserve">13.0053024291992</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8224220275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.007043838501</t>
+    <t xml:space="preserve">12.8224239349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0070428848267</t>
   </si>
   <si>
     <t xml:space="preserve">13.1219959259033</t>
@@ -5432,28 +5432,28 @@
     <t xml:space="preserve">13.0889043807983</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2352075576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1568298339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2090835571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2804918289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.027943611145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1411542892456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9861450195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8624820709229</t>
+    <t xml:space="preserve">13.2352085113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1568307876587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2090826034546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2804937362671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0279445648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1411561965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9861440658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8624830245972</t>
   </si>
   <si>
     <t xml:space="preserve">13.0714874267578</t>
@@ -5465,37 +5465,37 @@
     <t xml:space="preserve">12.8920917510986</t>
   </si>
   <si>
-    <t xml:space="preserve">12.845064163208</t>
+    <t xml:space="preserve">12.8450660705566</t>
   </si>
   <si>
     <t xml:space="preserve">12.9304084777832</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9007997512817</t>
+    <t xml:space="preserve">12.9008007049561</t>
   </si>
   <si>
     <t xml:space="preserve">13.0558109283447</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0854206085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2404327392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2369499206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3135833740234</t>
+    <t xml:space="preserve">13.0854215621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2404317855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2369480133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3135824203491</t>
   </si>
   <si>
     <t xml:space="preserve">13.4424705505371</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3745441436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3658351898193</t>
+    <t xml:space="preserve">13.3745431900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3658332824707</t>
   </si>
   <si>
     <t xml:space="preserve">13.5469722747803</t>
@@ -5507,13 +5507,13 @@
     <t xml:space="preserve">13.5156221389771</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5330381393433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1324462890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9965934753418</t>
+    <t xml:space="preserve">13.5330371856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1324472427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9965944290161</t>
   </si>
   <si>
     <t xml:space="preserve">12.9617595672607</t>
@@ -5522,7 +5522,7 @@
     <t xml:space="preserve">12.89905834198</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0993556976318</t>
+    <t xml:space="preserve">13.0993547439575</t>
   </si>
   <si>
     <t xml:space="preserve">13.0592956542969</t>
@@ -5531,73 +5531,73 @@
     <t xml:space="preserve">13.0035610198975</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7597246170044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7214050292969</t>
+    <t xml:space="preserve">12.7597227096558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7214031219482</t>
   </si>
   <si>
     <t xml:space="preserve">12.5838098526001</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4880151748657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5036907196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6186437606812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6848278045654</t>
+    <t xml:space="preserve">12.48801612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5036897659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6186447143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6848287582397</t>
   </si>
   <si>
     <t xml:space="preserve">12.8502912521362</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9931106567383</t>
+    <t xml:space="preserve">12.9931116104126</t>
   </si>
   <si>
     <t xml:space="preserve">12.8868675231934</t>
   </si>
   <si>
-    <t xml:space="preserve">12.702244758606</t>
+    <t xml:space="preserve">12.7022466659546</t>
   </si>
   <si>
     <t xml:space="preserve">12.5176258087158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.716178894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5141410827637</t>
+    <t xml:space="preserve">12.7161798477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5141429901123</t>
   </si>
   <si>
     <t xml:space="preserve">12.5106592178345</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4479570388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5733604431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6012277603149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6290950775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7179193496704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3260383605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3399715423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3068799972534</t>
+    <t xml:space="preserve">12.4479579925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5733594894409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6012268066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.629093170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7179203033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.32603931427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3399724960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3068780899048</t>
   </si>
   <si>
     <t xml:space="preserve">12.4549245834351</t>
@@ -5606,31 +5606,31 @@
     <t xml:space="preserve">12.39222240448</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4148635864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4113826751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5228500366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5019502639771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4078979492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4775657653809</t>
+    <t xml:space="preserve">12.4148645401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4113817214966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5228509902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5019493103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4078989028931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4775667190552</t>
   </si>
   <si>
     <t xml:space="preserve">12.5298166275024</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6343193054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7388210296631</t>
+    <t xml:space="preserve">12.6343212127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7388219833374</t>
   </si>
   <si>
     <t xml:space="preserve">12.7423048019409</t>
@@ -5639,55 +5639,55 @@
     <t xml:space="preserve">12.8032646179199</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6778612136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7945575714111</t>
+    <t xml:space="preserve">12.6778621673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7945566177368</t>
   </si>
   <si>
     <t xml:space="preserve">13.0436191558838</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6465129852295</t>
+    <t xml:space="preserve">12.6465110778809</t>
   </si>
   <si>
     <t xml:space="preserve">12.6325778961182</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5883026123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8893737792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6857070922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7158136367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7105026245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.887601852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8840608596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9017705917358</t>
+    <t xml:space="preserve">12.5883016586304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8893728256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6857080459595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7158145904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7105016708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8876008987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8840599060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9017686843872</t>
   </si>
   <si>
     <t xml:space="preserve">12.9708395004272</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3091020584106</t>
+    <t xml:space="preserve">13.3091011047363</t>
   </si>
   <si>
     <t xml:space="preserve">13.4383850097656</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5906915664673</t>
+    <t xml:space="preserve">13.590690612793</t>
   </si>
   <si>
     <t xml:space="preserve">13.7323732376099</t>
@@ -5702,19 +5702,19 @@
     <t xml:space="preserve">13.6154861450195</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5641260147095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9289531707764</t>
+    <t xml:space="preserve">13.5641250610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9289512634277</t>
   </si>
   <si>
     <t xml:space="preserve">13.7553949356079</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4596376419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5747518539429</t>
+    <t xml:space="preserve">13.4596366882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5747509002686</t>
   </si>
   <si>
     <t xml:space="preserve">13.4862022399902</t>
@@ -5729,37 +5729,37 @@
     <t xml:space="preserve">13.7429990768433</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4915142059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5074529647827</t>
+    <t xml:space="preserve">13.4915151596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.507453918457</t>
   </si>
   <si>
     <t xml:space="preserve">13.5127668380737</t>
   </si>
   <si>
-    <t xml:space="preserve">13.525164604187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4029655456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.12668800354</t>
+    <t xml:space="preserve">13.5251636505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.40296459198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1266870498657</t>
   </si>
   <si>
     <t xml:space="preserve">13.0239696502686</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1532526016235</t>
+    <t xml:space="preserve">13.1532535552979</t>
   </si>
   <si>
     <t xml:space="preserve">13.2542009353638</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2258644104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3108730316162</t>
+    <t xml:space="preserve">13.2258634567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3108711242676</t>
   </si>
   <si>
     <t xml:space="preserve">13.4419279098511</t>
@@ -5780,7 +5780,7 @@
     <t xml:space="preserve">13.1859970092773</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1212358474731</t>
+    <t xml:space="preserve">13.1212368011475</t>
   </si>
   <si>
     <t xml:space="preserve">12.9971103668213</t>
@@ -5792,13 +5792,13 @@
     <t xml:space="preserve">12.9377470016479</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1158399581909</t>
+    <t xml:space="preserve">13.1158390045166</t>
   </si>
   <si>
     <t xml:space="preserve">13.0942516326904</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9395456314087</t>
+    <t xml:space="preserve">12.939546585083</t>
   </si>
   <si>
     <t xml:space="preserve">12.9233560562134</t>
@@ -5810,19 +5810,19 @@
     <t xml:space="preserve">12.9683294296265</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6049489974976</t>
+    <t xml:space="preserve">12.6049499511719</t>
   </si>
   <si>
     <t xml:space="preserve">12.5437860488892</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6553173065186</t>
+    <t xml:space="preserve">12.6553182601929</t>
   </si>
   <si>
     <t xml:space="preserve">12.5851621627808</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6894979476929</t>
+    <t xml:space="preserve">12.6894989013672</t>
   </si>
   <si>
     <t xml:space="preserve">12.5815629959106</t>
@@ -5834,22 +5834,22 @@
     <t xml:space="preserve">12.3387107849121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1498260498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1732110977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3980760574341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5006113052368</t>
+    <t xml:space="preserve">12.149827003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1732120513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3980751037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5006122589111</t>
   </si>
   <si>
     <t xml:space="preserve">12.7110843658447</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5347909927368</t>
+    <t xml:space="preserve">12.5347919464111</t>
   </si>
   <si>
     <t xml:space="preserve">12.7038888931274</t>
@@ -5858,7 +5858,7 @@
     <t xml:space="preserve">12.8046283721924</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8082265853882</t>
+    <t xml:space="preserve">12.8082256317139</t>
   </si>
   <si>
     <t xml:space="preserve">12.8747863769531</t>
@@ -5870,10 +5870,10 @@
     <t xml:space="preserve">13.0708656311035</t>
   </si>
   <si>
-    <t xml:space="preserve">13.067268371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0079040527344</t>
+    <t xml:space="preserve">13.0672693252563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0079050064087</t>
   </si>
   <si>
     <t xml:space="preserve">13.1374254226685</t>
@@ -5882,7 +5882,7 @@
     <t xml:space="preserve">13.0007085800171</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8639917373657</t>
+    <t xml:space="preserve">12.8639936447144</t>
   </si>
   <si>
     <t xml:space="preserve">12.693097114563</t>
@@ -5894,37 +5894,37 @@
     <t xml:space="preserve">12.7722482681274</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8567953109741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8064270019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6031494140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7128829956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8531980514526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6643123626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6571178436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.615743637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6445245742798</t>
+    <t xml:space="preserve">12.8567962646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8064279556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6031503677368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7128839492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.853199005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6643133163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6571168899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6157426834106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6445264816284</t>
   </si>
   <si>
     <t xml:space="preserve">12.6103458404541</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1590127944946</t>
+    <t xml:space="preserve">13.1590137481689</t>
   </si>
   <si>
     <t xml:space="preserve">13.168007850647</t>
@@ -5942,13 +5942,13 @@
     <t xml:space="preserve">12.5329933166504</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5222005844116</t>
+    <t xml:space="preserve">12.5221996307373</t>
   </si>
   <si>
     <t xml:space="preserve">12.8334102630615</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0025091171265</t>
+    <t xml:space="preserve">13.0025081634521</t>
   </si>
   <si>
     <t xml:space="preserve">12.8855791091919</t>
@@ -5957,13 +5957,13 @@
     <t xml:space="preserve">13.0402851104736</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1482191085815</t>
+    <t xml:space="preserve">13.1482181549072</t>
   </si>
   <si>
     <t xml:space="preserve">13.0366868972778</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0564756393433</t>
+    <t xml:space="preserve">13.0564746856689</t>
   </si>
   <si>
     <t xml:space="preserve">12.9539384841919</t>
@@ -5972,13 +5972,13 @@
     <t xml:space="preserve">13.1302299499512</t>
   </si>
   <si>
-    <t xml:space="preserve">13.254355430603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2237730026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1967906951904</t>
+    <t xml:space="preserve">13.2543544769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2237739562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1967897415161</t>
   </si>
   <si>
     <t xml:space="preserve">13.3173170089722</t>
@@ -5990,7 +5990,7 @@
     <t xml:space="preserve">13.2219743728638</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8891773223877</t>
+    <t xml:space="preserve">12.8891763687134</t>
   </si>
   <si>
     <t xml:space="preserve">12.7398672103882</t>
@@ -6005,16 +6005,16 @@
     <t xml:space="preserve">12.4574394226074</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5995531082153</t>
+    <t xml:space="preserve">12.599552154541</t>
   </si>
   <si>
     <t xml:space="preserve">12.6948947906494</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7902364730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8172206878662</t>
+    <t xml:space="preserve">12.7902374267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8172216415405</t>
   </si>
   <si>
     <t xml:space="preserve">12.8460025787354</t>
@@ -6026,10 +6026,10 @@
     <t xml:space="preserve">12.9650144577026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8130464553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4230518341064</t>
+    <t xml:space="preserve">12.8130474090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4230527877808</t>
   </si>
   <si>
     <t xml:space="preserve">12.5146007537842</t>
@@ -6038,7 +6038,7 @@
     <t xml:space="preserve">12.5255861282349</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7160062789917</t>
+    <t xml:space="preserve">12.7160053253174</t>
   </si>
   <si>
     <t xml:space="preserve">12.9247350692749</t>
@@ -6047,13 +6047,13 @@
     <t xml:space="preserve">12.9137487411499</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1133232116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2781095504761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9943103790283</t>
+    <t xml:space="preserve">13.1133241653442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2781085968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9943113327026</t>
   </si>
   <si>
     <t xml:space="preserve">12.968677520752</t>
@@ -6062,7 +6062,7 @@
     <t xml:space="preserve">13.0565633773804</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1114921569824</t>
+    <t xml:space="preserve">13.1114912033081</t>
   </si>
   <si>
     <t xml:space="preserve">13.1407880783081</t>
@@ -6071,13 +6071,13 @@
     <t xml:space="preserve">12.7837505340576</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8496656417847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0510702133179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0712108612061</t>
+    <t xml:space="preserve">12.849666595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0510692596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0712099075317</t>
   </si>
   <si>
     <t xml:space="preserve">12.9814949035645</t>
@@ -6086,25 +6086,25 @@
     <t xml:space="preserve">13.023606300354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2085342407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8093843460083</t>
+    <t xml:space="preserve">13.2085332870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8093852996826</t>
   </si>
   <si>
     <t xml:space="preserve">12.8276929855347</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8478355407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8368482589722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9229040145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8203706741333</t>
+    <t xml:space="preserve">12.8478345870972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8368492126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9229030609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.820369720459</t>
   </si>
   <si>
     <t xml:space="preserve">12.8991003036499</t>
@@ -6116,7 +6116,7 @@
     <t xml:space="preserve">12.8258628845215</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6445989608765</t>
+    <t xml:space="preserve">12.6445980072021</t>
   </si>
   <si>
     <t xml:space="preserve">12.5585422515869</t>
@@ -6128,40 +6128,40 @@
     <t xml:space="preserve">12.9511938095093</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8002090454102</t>
+    <t xml:space="preserve">12.8002099990845</t>
   </si>
   <si>
     <t xml:space="preserve">12.7946166992188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8747701644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9698343276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8058013916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5411100387573</t>
+    <t xml:space="preserve">12.8747692108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9698352813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8058004379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5411109924316</t>
   </si>
   <si>
     <t xml:space="preserve">12.503830909729</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5112867355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4945106506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4348611831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5541591644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.56907081604</t>
+    <t xml:space="preserve">12.5112857818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4945116043091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4348621368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.554160118103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5690717697144</t>
   </si>
   <si>
     <t xml:space="preserve">12.5392465591431</t>
@@ -6176,10 +6176,10 @@
     <t xml:space="preserve">12.4926471710205</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4646863937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4143562316895</t>
+    <t xml:space="preserve">12.4646854400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4143571853638</t>
   </si>
   <si>
     <t xml:space="preserve">12.3919897079468</t>
@@ -6188,10 +6188,10 @@
     <t xml:space="preserve">12.2093152999878</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9148015975952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0154590606689</t>
+    <t xml:space="preserve">11.9148006439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0154581069946</t>
   </si>
   <si>
     <t xml:space="preserve">11.9129362106323</t>
@@ -6212,7 +6212,7 @@
     <t xml:space="preserve">12.5467023849487</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7125997543335</t>
+    <t xml:space="preserve">12.7126007080078</t>
   </si>
   <si>
     <t xml:space="preserve">12.7331037521362</t>
@@ -6230,13 +6230,13 @@
     <t xml:space="preserve">12.9288263320923</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0332107543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9959306716919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1338672637939</t>
+    <t xml:space="preserve">13.0332117080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9959316253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1338682174683</t>
   </si>
   <si>
     <t xml:space="preserve">12.9474668502808</t>
@@ -6248,7 +6248,7 @@
     <t xml:space="preserve">12.7461519241333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6697273254395</t>
+    <t xml:space="preserve">12.6697282791138</t>
   </si>
   <si>
     <t xml:space="preserve">12.496374130249</t>
@@ -6260,16 +6260,16 @@
     <t xml:space="preserve">12.5187425613403</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5355195999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7088718414307</t>
+    <t xml:space="preserve">12.5355176925659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.708872795105</t>
   </si>
   <si>
     <t xml:space="preserve">12.7685203552246</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7032804489136</t>
+    <t xml:space="preserve">12.7032794952393</t>
   </si>
   <si>
     <t xml:space="preserve">12.846809387207</t>
@@ -6278,7 +6278,7 @@
     <t xml:space="preserve">12.8729057312012</t>
   </si>
   <si>
-    <t xml:space="preserve">12.919506072998</t>
+    <t xml:space="preserve">12.9195079803467</t>
   </si>
   <si>
     <t xml:space="preserve">12.9418745040894</t>
@@ -6287,19 +6287,19 @@
     <t xml:space="preserve">13.1059093475342</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0723562240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0406675338745</t>
+    <t xml:space="preserve">13.0723543167114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0406665802002</t>
   </si>
   <si>
     <t xml:space="preserve">13.0835399627686</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1189565658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1357326507568</t>
+    <t xml:space="preserve">13.1189556121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1357316970825</t>
   </si>
   <si>
     <t xml:space="preserve">13.0984516143799</t>
@@ -6314,16 +6314,16 @@
     <t xml:space="preserve">13.0816764831543</t>
   </si>
   <si>
-    <t xml:space="preserve">13.176739692688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3034934997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1170921325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9120502471924</t>
+    <t xml:space="preserve">13.1767406463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3034944534302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1170930862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9120492935181</t>
   </si>
   <si>
     <t xml:space="preserve">12.9083223342896</t>
@@ -6332,13 +6332,13 @@
     <t xml:space="preserve">12.3621644973755</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2503242492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3174285888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6156730651855</t>
+    <t xml:space="preserve">12.2503232955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3174276351929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6156721115112</t>
   </si>
   <si>
     <t xml:space="preserve">12.6249904632568</t>
@@ -6350,13 +6350,13 @@
     <t xml:space="preserve">12.7275123596191</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7852973937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0704917907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1879243850708</t>
+    <t xml:space="preserve">12.7852964401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0704927444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1879253387451</t>
   </si>
   <si>
     <t xml:space="preserve">13.3612785339355</t>
@@ -6957,6 +6957,9 @@
   </si>
   <si>
     <t xml:space="preserve">16.7199993133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4440002441406</t>
   </si>
 </sst>
 </file>
@@ -73569,7 +73572,7 @@
     </row>
     <row r="2550">
       <c r="A2550" s="1" t="n">
-        <v>46036.6927893519</v>
+        <v>46036.3333333333</v>
       </c>
       <c r="B2550" t="n">
         <v>13804823</v>
@@ -73590,6 +73593,32 @@
         <v>2314</v>
       </c>
       <c r="H2550" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2551">
+      <c r="A2551" s="1" t="n">
+        <v>46037.6943402778</v>
+      </c>
+      <c r="B2551" t="n">
+        <v>15044180</v>
+      </c>
+      <c r="C2551" t="n">
+        <v>16.6219997406006</v>
+      </c>
+      <c r="D2551" t="n">
+        <v>16.2959995269775</v>
+      </c>
+      <c r="E2551" t="n">
+        <v>16.6040000915527</v>
+      </c>
+      <c r="F2551" t="n">
+        <v>16.4440002441406</v>
+      </c>
+      <c r="G2551" t="s">
+        <v>2315</v>
+      </c>
+      <c r="H2551" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ENI.MI.xlsx
+++ b/data/ENI.MI.xlsx
@@ -61692,24 +61692,47 @@
     </row>
     <row r="2667">
       <c r="A2667" s="1" t="n">
-        <v>46205.2916666667</v>
+        <v>46204.2916666667</v>
       </c>
       <c r="B2667" t="n">
-        <v>7422672</v>
+        <v>9337685</v>
       </c>
       <c r="C2667" t="n">
-        <v>20.4699993133545</v>
+        <v>20.5650005340576</v>
       </c>
       <c r="D2667" t="n">
-        <v>19.8700008392334</v>
+        <v>20.0799999237061</v>
       </c>
       <c r="E2667" t="n">
-        <v>19.9599990844727</v>
+        <v>20.5049991607666</v>
       </c>
       <c r="F2667" t="n">
-        <v>20.4099998474121</v>
+        <v>20.0799999237061</v>
       </c>
       <c r="G2667" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2668">
+      <c r="A2668" s="1" t="n">
+        <v>46206.2916666667</v>
+      </c>
+      <c r="B2668" t="n">
+        <v>4349839</v>
+      </c>
+      <c r="C2668" t="n">
+        <v>20.5450000762939</v>
+      </c>
+      <c r="D2668" t="n">
+        <v>20.3199996948242</v>
+      </c>
+      <c r="E2668" t="n">
+        <v>20.5300006866455</v>
+      </c>
+      <c r="F2668" t="n">
+        <v>20.4449996948242</v>
+      </c>
+      <c r="G2668" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ENI.MI.xlsx
+++ b/data/ENI.MI.xlsx
@@ -62198,22 +62198,22 @@
     </row>
     <row r="2689">
       <c r="A2689" s="1" t="n">
-        <v>46237.2916666667</v>
+        <v>46234.2916666667</v>
       </c>
       <c r="B2689" t="n">
-        <v>10116218</v>
+        <v>9533414</v>
       </c>
       <c r="C2689" t="n">
-        <v>23.7049999237061</v>
+        <v>24.0200004577637</v>
       </c>
       <c r="D2689" t="n">
-        <v>23.2999992370605</v>
+        <v>23.6499996185303</v>
       </c>
       <c r="E2689" t="n">
-        <v>23.5300006866455</v>
+        <v>23.6499996185303</v>
       </c>
       <c r="F2689" t="n">
-        <v>23.6949996948242</v>
+        <v>23.9799995422363</v>
       </c>
       <c r="G2689" t="s">
         <v>7</v>
@@ -62221,22 +62221,22 @@
     </row>
     <row r="2690">
       <c r="A2690" s="1" t="n">
-        <v>46238.2916666667</v>
+        <v>46237.2916666667</v>
       </c>
       <c r="B2690" t="n">
-        <v>11476822</v>
+        <v>10116218</v>
       </c>
       <c r="C2690" t="n">
-        <v>24.1599998474121</v>
+        <v>23.7049999237061</v>
       </c>
       <c r="D2690" t="n">
-        <v>23.0249996185303</v>
+        <v>23.2999992370605</v>
       </c>
       <c r="E2690" t="n">
-        <v>23.7000007629395</v>
+        <v>23.5300006866455</v>
       </c>
       <c r="F2690" t="n">
-        <v>23.25</v>
+        <v>23.6949996948242</v>
       </c>
       <c r="G2690" t="s">
         <v>7</v>
@@ -62244,24 +62244,68 @@
     </row>
     <row r="2691">
       <c r="A2691" s="1" t="n">
+        <v>46238.2916666667</v>
+      </c>
+      <c r="B2691" t="n">
+        <v>11476822</v>
+      </c>
+      <c r="C2691" t="n">
+        <v>24.1599998474121</v>
+      </c>
+      <c r="D2691" t="n">
+        <v>23.0249996185303</v>
+      </c>
+      <c r="E2691" t="n">
+        <v>23.7000007629395</v>
+      </c>
+      <c r="F2691" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="G2691" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2692">
+      <c r="A2692" s="1" t="n">
         <v>46239.2916666667</v>
       </c>
-      <c r="B2691" t="n">
+      <c r="B2692" t="n">
         <v>7867110</v>
       </c>
-      <c r="C2691" t="n">
+      <c r="C2692" t="n">
         <v>23.5349998474121</v>
       </c>
-      <c r="D2691" t="n">
+      <c r="D2692" t="n">
         <v>22.9850006103516</v>
       </c>
-      <c r="E2691" t="n">
+      <c r="E2692" t="n">
         <v>23.1399993896484</v>
       </c>
-      <c r="F2691" t="n">
+      <c r="F2692" t="n">
         <v>23.0849990844727</v>
       </c>
-      <c r="G2691" t="s">
+      <c r="G2692" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2693">
+      <c r="A2693" s="1" t="n">
+        <v>46240.2916666667</v>
+      </c>
+      <c r="B2693" t="n">
+        <v>6553027</v>
+      </c>
+      <c r="C2693" t="n">
+        <v>23.4050006866455</v>
+      </c>
+      <c r="D2693" t="n">
+        <v>23.0849990844727</v>
+      </c>
+      <c r="E2693" t="n">
+        <v>23.1599998474121</v>
+      </c>
+      <c r="F2693"/>
+      <c r="G2693" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ENI.MI.xlsx
+++ b/data/ENI.MI.xlsx
@@ -62339,7 +62339,7 @@
         <v>46245.2916666667</v>
       </c>
       <c r="B2695" t="n">
-        <v>7600367</v>
+        <v>7598423</v>
       </c>
       <c r="C2695" t="n">
         <v>24.1299991607666</v>
@@ -62354,6 +62354,29 @@
         <v>24.0499992370605</v>
       </c>
       <c r="G2695" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2696">
+      <c r="A2696" s="1" t="n">
+        <v>46246.2916666667</v>
+      </c>
+      <c r="B2696" t="n">
+        <v>7055579</v>
+      </c>
+      <c r="C2696" t="n">
+        <v>24.1749992370605</v>
+      </c>
+      <c r="D2696" t="n">
+        <v>23.7800006866455</v>
+      </c>
+      <c r="E2696" t="n">
+        <v>24.0499992370605</v>
+      </c>
+      <c r="F2696" t="n">
+        <v>23.8600006103516</v>
+      </c>
+      <c r="G2696" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ENI.MI.xlsx
+++ b/data/ENI.MI.xlsx
@@ -61991,22 +61991,22 @@
     </row>
     <row r="2680">
       <c r="A2680" s="1" t="n">
-        <v>46224.2916666667</v>
+        <v>46223.2916666667</v>
       </c>
       <c r="B2680" t="n">
-        <v>7848827</v>
+        <v>6685186</v>
       </c>
       <c r="C2680" t="n">
-        <v>21.9650001525879</v>
+        <v>22.0100002288818</v>
       </c>
       <c r="D2680" t="n">
-        <v>21.6450004577637</v>
+        <v>21.4249992370605</v>
       </c>
       <c r="E2680" t="n">
-        <v>21.7199993133545</v>
+        <v>21.9599990844727</v>
       </c>
       <c r="F2680" t="n">
-        <v>21.8700008392334</v>
+        <v>21.6399993896484</v>
       </c>
       <c r="G2680" t="s">
         <v>7</v>
@@ -62014,22 +62014,22 @@
     </row>
     <row r="2681">
       <c r="A2681" s="1" t="n">
-        <v>46225.2916666667</v>
+        <v>46224.2916666667</v>
       </c>
       <c r="B2681" t="n">
-        <v>10036359</v>
+        <v>7848827</v>
       </c>
       <c r="C2681" t="n">
-        <v>22.4249992370605</v>
+        <v>21.9650001525879</v>
       </c>
       <c r="D2681" t="n">
-        <v>22.0100002288818</v>
+        <v>21.6450004577637</v>
       </c>
       <c r="E2681" t="n">
-        <v>22.1000003814697</v>
+        <v>21.7199993133545</v>
       </c>
       <c r="F2681" t="n">
-        <v>22.3050003051758</v>
+        <v>21.8700008392334</v>
       </c>
       <c r="G2681" t="s">
         <v>7</v>
@@ -62037,22 +62037,22 @@
     </row>
     <row r="2682">
       <c r="A2682" s="1" t="n">
-        <v>46226.2916666667</v>
+        <v>46225.2916666667</v>
       </c>
       <c r="B2682" t="n">
-        <v>11430510</v>
+        <v>10036359</v>
       </c>
       <c r="C2682" t="n">
-        <v>23.0349998474121</v>
+        <v>22.4249992370605</v>
       </c>
       <c r="D2682" t="n">
-        <v>22.4249992370605</v>
+        <v>22.0100002288818</v>
       </c>
       <c r="E2682" t="n">
-        <v>22.5</v>
+        <v>22.1000003814697</v>
       </c>
       <c r="F2682" t="n">
-        <v>22.9650001525879</v>
+        <v>22.3050003051758</v>
       </c>
       <c r="G2682" t="s">
         <v>7</v>
@@ -62060,22 +62060,22 @@
     </row>
     <row r="2683">
       <c r="A2683" s="1" t="n">
-        <v>46227.2916666667</v>
+        <v>46226.2916666667</v>
       </c>
       <c r="B2683" t="n">
-        <v>8663020</v>
+        <v>11430510</v>
       </c>
       <c r="C2683" t="n">
-        <v>23.0200004577637</v>
+        <v>23.0349998474121</v>
       </c>
       <c r="D2683" t="n">
-        <v>22.6299991607666</v>
+        <v>22.4249992370605</v>
       </c>
       <c r="E2683" t="n">
-        <v>22.7450008392334</v>
+        <v>22.5</v>
       </c>
       <c r="F2683" t="n">
-        <v>22.9599990844727</v>
+        <v>22.9650001525879</v>
       </c>
       <c r="G2683" t="s">
         <v>7</v>
@@ -62083,22 +62083,22 @@
     </row>
     <row r="2684">
       <c r="A2684" s="1" t="n">
-        <v>46230.2916666667</v>
+        <v>46227.2916666667</v>
       </c>
       <c r="B2684" t="n">
-        <v>13820775</v>
+        <v>8663020</v>
       </c>
       <c r="C2684" t="n">
-        <v>22.4750003814697</v>
+        <v>23.0200004577637</v>
       </c>
       <c r="D2684" t="n">
-        <v>21.8500003814697</v>
+        <v>22.6299991607666</v>
       </c>
       <c r="E2684" t="n">
-        <v>22</v>
+        <v>22.7450008392334</v>
       </c>
       <c r="F2684" t="n">
-        <v>22.3999996185303</v>
+        <v>22.9599990844727</v>
       </c>
       <c r="G2684" t="s">
         <v>7</v>
@@ -62106,22 +62106,22 @@
     </row>
     <row r="2685">
       <c r="A2685" s="1" t="n">
-        <v>46231.2916666667</v>
+        <v>46230.2916666667</v>
       </c>
       <c r="B2685" t="n">
-        <v>8831375</v>
+        <v>13820775</v>
       </c>
       <c r="C2685" t="n">
-        <v>22.4699993133545</v>
+        <v>22.4750003814697</v>
       </c>
       <c r="D2685" t="n">
-        <v>22.0149993896484</v>
+        <v>21.8500003814697</v>
       </c>
       <c r="E2685" t="n">
-        <v>22.3150005340576</v>
+        <v>22</v>
       </c>
       <c r="F2685" t="n">
-        <v>22.0149993896484</v>
+        <v>22.3999996185303</v>
       </c>
       <c r="G2685" t="s">
         <v>7</v>
@@ -62129,22 +62129,22 @@
     </row>
     <row r="2686">
       <c r="A2686" s="1" t="n">
-        <v>46232.2916666667</v>
+        <v>46231.2916666667</v>
       </c>
       <c r="B2686" t="n">
-        <v>17457595</v>
+        <v>8831375</v>
       </c>
       <c r="C2686" t="n">
-        <v>23.6550006866455</v>
+        <v>22.4699993133545</v>
       </c>
       <c r="D2686" t="n">
-        <v>22.7999992370605</v>
+        <v>22.0149993896484</v>
       </c>
       <c r="E2686" t="n">
-        <v>22.9099998474121</v>
+        <v>22.3150005340576</v>
       </c>
       <c r="F2686" t="n">
-        <v>23.5750007629395</v>
+        <v>22.0149993896484</v>
       </c>
       <c r="G2686" t="s">
         <v>7</v>
@@ -62152,22 +62152,22 @@
     </row>
     <row r="2687">
       <c r="A2687" s="1" t="n">
-        <v>46233.2916666667</v>
+        <v>46232.2916666667</v>
       </c>
       <c r="B2687" t="n">
-        <v>11394093</v>
+        <v>17457595</v>
       </c>
       <c r="C2687" t="n">
-        <v>23.8999996185303</v>
+        <v>23.6550006866455</v>
       </c>
       <c r="D2687" t="n">
-        <v>23.3799991607666</v>
+        <v>22.7999992370605</v>
       </c>
       <c r="E2687" t="n">
-        <v>23.7000007629395</v>
+        <v>22.9099998474121</v>
       </c>
       <c r="F2687" t="n">
-        <v>23.8999996185303</v>
+        <v>23.5750007629395</v>
       </c>
       <c r="G2687" t="s">
         <v>7</v>
@@ -62175,22 +62175,22 @@
     </row>
     <row r="2688">
       <c r="A2688" s="1" t="n">
-        <v>46237.2916666667</v>
+        <v>46233.2916666667</v>
       </c>
       <c r="B2688" t="n">
-        <v>10116218</v>
+        <v>11394093</v>
       </c>
       <c r="C2688" t="n">
-        <v>23.7049999237061</v>
+        <v>23.8999996185303</v>
       </c>
       <c r="D2688" t="n">
-        <v>23.2999992370605</v>
+        <v>23.3799991607666</v>
       </c>
       <c r="E2688" t="n">
-        <v>23.5300006866455</v>
+        <v>23.7000007629395</v>
       </c>
       <c r="F2688" t="n">
-        <v>23.6949996948242</v>
+        <v>23.8999996185303</v>
       </c>
       <c r="G2688" t="s">
         <v>7</v>
@@ -62198,22 +62198,22 @@
     </row>
     <row r="2689">
       <c r="A2689" s="1" t="n">
-        <v>46238.2916666667</v>
+        <v>46237.2916666667</v>
       </c>
       <c r="B2689" t="n">
-        <v>11476822</v>
+        <v>10116218</v>
       </c>
       <c r="C2689" t="n">
-        <v>24.1599998474121</v>
+        <v>23.7049999237061</v>
       </c>
       <c r="D2689" t="n">
-        <v>23.0249996185303</v>
+        <v>23.2999992370605</v>
       </c>
       <c r="E2689" t="n">
-        <v>23.7000007629395</v>
+        <v>23.5300006866455</v>
       </c>
       <c r="F2689" t="n">
-        <v>23.25</v>
+        <v>23.6949996948242</v>
       </c>
       <c r="G2689" t="s">
         <v>7</v>
@@ -62221,22 +62221,22 @@
     </row>
     <row r="2690">
       <c r="A2690" s="1" t="n">
-        <v>46239.2916666667</v>
+        <v>46238.2916666667</v>
       </c>
       <c r="B2690" t="n">
-        <v>7867110</v>
+        <v>11476822</v>
       </c>
       <c r="C2690" t="n">
-        <v>23.5349998474121</v>
+        <v>24.1599998474121</v>
       </c>
       <c r="D2690" t="n">
-        <v>22.9850006103516</v>
+        <v>23.0249996185303</v>
       </c>
       <c r="E2690" t="n">
-        <v>23.1399993896484</v>
+        <v>23.7000007629395</v>
       </c>
       <c r="F2690" t="n">
-        <v>23.0849990844727</v>
+        <v>23.25</v>
       </c>
       <c r="G2690" t="s">
         <v>7</v>
@@ -62244,22 +62244,22 @@
     </row>
     <row r="2691">
       <c r="A2691" s="1" t="n">
-        <v>46240.2916666667</v>
+        <v>46239.2916666667</v>
       </c>
       <c r="B2691" t="n">
-        <v>6553027</v>
+        <v>7867110</v>
       </c>
       <c r="C2691" t="n">
-        <v>23.4050006866455</v>
+        <v>23.5349998474121</v>
       </c>
       <c r="D2691" t="n">
+        <v>22.9850006103516</v>
+      </c>
+      <c r="E2691" t="n">
+        <v>23.1399993896484</v>
+      </c>
+      <c r="F2691" t="n">
         <v>23.0849990844727</v>
-      </c>
-      <c r="E2691" t="n">
-        <v>23.1599998474121</v>
-      </c>
-      <c r="F2691" t="n">
-        <v>23.3999996185303</v>
       </c>
       <c r="G2691" t="s">
         <v>7</v>
@@ -62267,22 +62267,22 @@
     </row>
     <row r="2692">
       <c r="A2692" s="1" t="n">
-        <v>46241.2916666667</v>
+        <v>46240.2916666667</v>
       </c>
       <c r="B2692" t="n">
-        <v>5423436</v>
+        <v>6553027</v>
       </c>
       <c r="C2692" t="n">
-        <v>23.5699996948242</v>
+        <v>23.4050006866455</v>
       </c>
       <c r="D2692" t="n">
-        <v>23.1049995422363</v>
+        <v>23.0849990844727</v>
       </c>
       <c r="E2692" t="n">
-        <v>23.5</v>
+        <v>23.1599998474121</v>
       </c>
       <c r="F2692" t="n">
-        <v>23.2800006866455</v>
+        <v>23.3999996185303</v>
       </c>
       <c r="G2692" t="s">
         <v>7</v>
@@ -62290,22 +62290,22 @@
     </row>
     <row r="2693">
       <c r="A2693" s="1" t="n">
-        <v>46244.2916666667</v>
+        <v>46241.2916666667</v>
       </c>
       <c r="B2693" t="n">
-        <v>5598271</v>
+        <v>5423436</v>
       </c>
       <c r="C2693" t="n">
-        <v>23.6700000762939</v>
+        <v>23.5699996948242</v>
       </c>
       <c r="D2693" t="n">
-        <v>23.1900005340576</v>
+        <v>23.1049995422363</v>
       </c>
       <c r="E2693" t="n">
-        <v>23.25</v>
+        <v>23.5</v>
       </c>
       <c r="F2693" t="n">
-        <v>23.5750007629395</v>
+        <v>23.2800006866455</v>
       </c>
       <c r="G2693" t="s">
         <v>7</v>
@@ -62313,22 +62313,22 @@
     </row>
     <row r="2694">
       <c r="A2694" s="1" t="n">
-        <v>46245.2916666667</v>
+        <v>46244.2916666667</v>
       </c>
       <c r="B2694" t="n">
-        <v>7598423</v>
+        <v>5598271</v>
       </c>
       <c r="C2694" t="n">
-        <v>24.1299991607666</v>
+        <v>23.6700000762939</v>
       </c>
       <c r="D2694" t="n">
-        <v>23.8250007629395</v>
+        <v>23.1900005340576</v>
       </c>
       <c r="E2694" t="n">
-        <v>23.9400005340576</v>
+        <v>23.25</v>
       </c>
       <c r="F2694" t="n">
-        <v>24.0499992370605</v>
+        <v>23.5750007629395</v>
       </c>
       <c r="G2694" t="s">
         <v>7</v>
@@ -62336,22 +62336,22 @@
     </row>
     <row r="2695">
       <c r="A2695" s="1" t="n">
-        <v>46246.2916666667</v>
+        <v>46245.2916666667</v>
       </c>
       <c r="B2695" t="n">
-        <v>7055579</v>
+        <v>7598423</v>
       </c>
       <c r="C2695" t="n">
-        <v>24.1749992370605</v>
+        <v>24.1299991607666</v>
       </c>
       <c r="D2695" t="n">
-        <v>23.7800006866455</v>
+        <v>23.8250007629395</v>
       </c>
       <c r="E2695" t="n">
+        <v>23.9400005340576</v>
+      </c>
+      <c r="F2695" t="n">
         <v>24.0499992370605</v>
-      </c>
-      <c r="F2695" t="n">
-        <v>23.8600006103516</v>
       </c>
       <c r="G2695" t="s">
         <v>7</v>
@@ -62359,22 +62359,22 @@
     </row>
     <row r="2696">
       <c r="A2696" s="1" t="n">
-        <v>46247.2916666667</v>
+        <v>46246.2916666667</v>
       </c>
       <c r="B2696" t="n">
-        <v>6235898</v>
+        <v>7055579</v>
       </c>
       <c r="C2696" t="n">
-        <v>24.0200004577637</v>
+        <v>24.1749992370605</v>
       </c>
       <c r="D2696" t="n">
-        <v>23.4099998474121</v>
+        <v>23.7800006866455</v>
       </c>
       <c r="E2696" t="n">
-        <v>24</v>
+        <v>24.0499992370605</v>
       </c>
       <c r="F2696" t="n">
-        <v>23.7049999237061</v>
+        <v>23.8600006103516</v>
       </c>
       <c r="G2696" t="s">
         <v>7</v>
@@ -62382,22 +62382,22 @@
     </row>
     <row r="2697">
       <c r="A2697" s="1" t="n">
-        <v>46248.2916666667</v>
+        <v>46247.2916666667</v>
       </c>
       <c r="B2697" t="n">
-        <v>5362986</v>
+        <v>6235898</v>
       </c>
       <c r="C2697" t="n">
-        <v>23.8600006103516</v>
+        <v>24.0200004577637</v>
       </c>
       <c r="D2697" t="n">
-        <v>23.6450004577637</v>
+        <v>23.4099998474121</v>
       </c>
       <c r="E2697" t="n">
-        <v>23.7999992370605</v>
+        <v>24</v>
       </c>
       <c r="F2697" t="n">
-        <v>23.6949996948242</v>
+        <v>23.7049999237061</v>
       </c>
       <c r="G2697" t="s">
         <v>7</v>
@@ -62405,22 +62405,22 @@
     </row>
     <row r="2698">
       <c r="A2698" s="1" t="n">
-        <v>46251.2916666667</v>
+        <v>46248.2916666667</v>
       </c>
       <c r="B2698" t="n">
-        <v>4029994</v>
+        <v>5362986</v>
       </c>
       <c r="C2698" t="n">
-        <v>23.8899993896484</v>
+        <v>23.8600006103516</v>
       </c>
       <c r="D2698" t="n">
-        <v>23.6100006103516</v>
+        <v>23.6450004577637</v>
       </c>
       <c r="E2698" t="n">
-        <v>23.7199993133545</v>
+        <v>23.7999992370605</v>
       </c>
       <c r="F2698" t="n">
-        <v>23.7749996185303</v>
+        <v>23.6949996948242</v>
       </c>
       <c r="G2698" t="s">
         <v>7</v>
@@ -62428,22 +62428,22 @@
     </row>
     <row r="2699">
       <c r="A2699" s="1" t="n">
-        <v>46252.2916666667</v>
+        <v>46251.2916666667</v>
       </c>
       <c r="B2699" t="n">
-        <v>6788017</v>
+        <v>4029994</v>
       </c>
       <c r="C2699" t="n">
-        <v>24.2600002288818</v>
+        <v>23.8899993896484</v>
       </c>
       <c r="D2699" t="n">
-        <v>23.9300003051758</v>
+        <v>23.6100006103516</v>
       </c>
       <c r="E2699" t="n">
-        <v>24.0799999237061</v>
+        <v>23.7199993133545</v>
       </c>
       <c r="F2699" t="n">
-        <v>24</v>
+        <v>23.7749996185303</v>
       </c>
       <c r="G2699" t="s">
         <v>7</v>
@@ -62451,24 +62451,70 @@
     </row>
     <row r="2700">
       <c r="A2700" s="1" t="n">
-        <v>46253.2916666667</v>
+        <v>46252.2916666667</v>
       </c>
       <c r="B2700" t="n">
-        <v>7695414</v>
+        <v>6788017</v>
       </c>
       <c r="C2700" t="n">
-        <v>24.2450008392334</v>
+        <v>24.2600002288818</v>
       </c>
       <c r="D2700" t="n">
         <v>23.9300003051758</v>
       </c>
       <c r="E2700" t="n">
+        <v>24.0799999237061</v>
+      </c>
+      <c r="F2700" t="n">
+        <v>24</v>
+      </c>
+      <c r="G2700" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2701">
+      <c r="A2701" s="1" t="n">
+        <v>46253.2916666667</v>
+      </c>
+      <c r="B2701" t="n">
+        <v>7695414</v>
+      </c>
+      <c r="C2701" t="n">
         <v>24.2450008392334</v>
       </c>
-      <c r="F2700" t="n">
+      <c r="D2701" t="n">
         <v>23.9300003051758</v>
       </c>
-      <c r="G2700" t="s">
+      <c r="E2701" t="n">
+        <v>24.2450008392334</v>
+      </c>
+      <c r="F2701" t="n">
+        <v>23.9300003051758</v>
+      </c>
+      <c r="G2701" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2702">
+      <c r="A2702" s="1" t="n">
+        <v>46254.2916666667</v>
+      </c>
+      <c r="B2702" t="n">
+        <v>8943970</v>
+      </c>
+      <c r="C2702" t="n">
+        <v>24.5550003051758</v>
+      </c>
+      <c r="D2702" t="n">
+        <v>23.9599990844727</v>
+      </c>
+      <c r="E2702" t="n">
+        <v>24.1000003814697</v>
+      </c>
+      <c r="F2702" t="n">
+        <v>24.5499992370605</v>
+      </c>
+      <c r="G2702" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ENI.MI.xlsx
+++ b/data/ENI.MI.xlsx
@@ -62649,8 +62649,31 @@
       <c r="E2708" t="n">
         <v>22.9799995422363</v>
       </c>
-      <c r="F2708"/>
+      <c r="F2708" t="n">
+        <v>22.7099990844727</v>
+      </c>
       <c r="G2708" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2709">
+      <c r="A2709" s="1" t="n">
+        <v>46262.2916666667</v>
+      </c>
+      <c r="B2709" t="n">
+        <v>5607235</v>
+      </c>
+      <c r="C2709" t="n">
+        <v>23.0599994659424</v>
+      </c>
+      <c r="D2709" t="n">
+        <v>22.6800003051758</v>
+      </c>
+      <c r="E2709" t="n">
+        <v>22.9300003051758</v>
+      </c>
+      <c r="F2709"/>
+      <c r="G2709" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ENI.MI.xlsx
+++ b/data/ENI.MI.xlsx
@@ -62672,8 +62672,31 @@
       <c r="E2709" t="n">
         <v>22.9300003051758</v>
       </c>
-      <c r="F2709"/>
+      <c r="F2709" t="n">
+        <v>22.7900009155273</v>
+      </c>
       <c r="G2709" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2710">
+      <c r="A2710" s="1" t="n">
+        <v>46265.2916666667</v>
+      </c>
+      <c r="B2710" t="n">
+        <v>11677723</v>
+      </c>
+      <c r="C2710" t="n">
+        <v>23.4150009155273</v>
+      </c>
+      <c r="D2710" t="n">
+        <v>23.0650005340576</v>
+      </c>
+      <c r="E2710" t="n">
+        <v>23.1000003814697</v>
+      </c>
+      <c r="F2710"/>
+      <c r="G2710" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ENI.MI.xlsx
+++ b/data/ENI.MI.xlsx
@@ -62817,6 +62817,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2716">
+      <c r="A2716" s="1" t="n">
+        <v>46274.2916666667</v>
+      </c>
+      <c r="B2716" t="n">
+        <v>8728416</v>
+      </c>
+      <c r="C2716" t="n">
+        <v>23.9750003814697</v>
+      </c>
+      <c r="D2716" t="n">
+        <v>23.7299995422363</v>
+      </c>
+      <c r="E2716" t="n">
+        <v>23.7549991607666</v>
+      </c>
+      <c r="F2716" t="n">
+        <v>23.9500007629395</v>
+      </c>
+      <c r="G2716" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2717">
+      <c r="A2717" s="1" t="n">
+        <v>46275.2916666667</v>
+      </c>
+      <c r="B2717" t="n">
+        <v>7729266</v>
+      </c>
+      <c r="C2717" t="n">
+        <v>24.2999992370605</v>
+      </c>
+      <c r="D2717" t="n">
+        <v>23.8700008392334</v>
+      </c>
+      <c r="E2717" t="n">
+        <v>23.9500007629395</v>
+      </c>
+      <c r="F2717" t="n">
+        <v>24.0550003051758</v>
+      </c>
+      <c r="G2717" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ENI.MI.xlsx
+++ b/data/ENI.MI.xlsx
@@ -62863,6 +62863,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2718">
+      <c r="A2718" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B2718" t="n">
+        <v>8279155</v>
+      </c>
+      <c r="C2718" t="n">
+        <v>24.2049999237061</v>
+      </c>
+      <c r="D2718" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="E2718" t="n">
+        <v>24.2000007629395</v>
+      </c>
+      <c r="F2718" t="n">
+        <v>24</v>
+      </c>
+      <c r="G2718" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
